--- a/poll_averages.xlsx
+++ b/poll_averages.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L209"/>
+  <dimension ref="A1:L210"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -485,12 +485,12 @@
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
+          <t>ppc</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
           <t>oth</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>ppc</t>
         </is>
       </c>
     </row>
@@ -501,11 +501,11 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Léger</t>
+          <t>Abacus Data</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -515,24 +515,26 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="G2" t="n">
-        <v>0.34</v>
+        <v>0.36</v>
       </c>
       <c r="H2" t="n">
         <v>0.06</v>
       </c>
       <c r="I2" t="n">
-        <v>0.06</v>
+        <v>0.11</v>
       </c>
       <c r="J2" t="n">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="K2" t="n">
         <v>0.01</v>
       </c>
-      <c r="L2" t="inlineStr"/>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -541,11 +543,11 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>46173</v>
+        <v>46174</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Liaison Strategies</t>
+          <t>Léger</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -555,25 +557,23 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>0.41</v>
+        <v>0.5</v>
       </c>
       <c r="G3" t="n">
-        <v>0.32</v>
+        <v>0.34</v>
       </c>
       <c r="H3" t="n">
         <v>0.06</v>
       </c>
       <c r="I3" t="n">
-        <v>0.16</v>
+        <v>0.06</v>
       </c>
       <c r="J3" t="n">
         <v>0.02</v>
       </c>
-      <c r="K3" t="n">
-        <v>0.02</v>
-      </c>
+      <c r="K3" t="inlineStr"/>
       <c r="L3" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="4">
@@ -583,11 +583,11 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>46171</v>
+        <v>46173</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Nanos Research</t>
+          <t>Liaison Strategies</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -597,23 +597,25 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>0.403</v>
+        <v>0.41</v>
       </c>
       <c r="G4" t="n">
-        <v>0.328</v>
+        <v>0.32</v>
       </c>
       <c r="H4" t="n">
-        <v>0.066</v>
+        <v>0.06</v>
       </c>
       <c r="I4" t="n">
-        <v>0.132</v>
+        <v>0.16</v>
       </c>
       <c r="J4" t="n">
-        <v>0.051</v>
-      </c>
-      <c r="K4" t="inlineStr"/>
+        <v>0.02</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.02</v>
+      </c>
       <c r="L4" t="n">
-        <v>0.015</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="5">
@@ -623,11 +625,11 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>46166</v>
+        <v>46171</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Pallas Data</t>
+          <t>Nanos Research</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -637,22 +639,22 @@
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>0.45</v>
+        <v>0.403</v>
       </c>
       <c r="G5" t="n">
-        <v>0.32</v>
+        <v>0.328</v>
       </c>
       <c r="H5" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.066</v>
       </c>
       <c r="I5" t="n">
-        <v>0.11</v>
+        <v>0.132</v>
       </c>
       <c r="J5" t="n">
-        <v>0.03</v>
+        <v>0.051</v>
       </c>
       <c r="K5" t="n">
-        <v>0.02</v>
+        <v>0.015</v>
       </c>
       <c r="L5" t="inlineStr"/>
     </row>
@@ -663,11 +665,11 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>46165</v>
+        <v>46166</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Liaison Strategies</t>
+          <t>Pallas Data</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -677,25 +679,23 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>0.43</v>
+        <v>0.45</v>
       </c>
       <c r="G6" t="n">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="H6" t="n">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I6" t="n">
         <v>0.11</v>
       </c>
       <c r="J6" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="K6" t="n">
         <v>0.03</v>
       </c>
+      <c r="K6" t="inlineStr"/>
       <c r="L6" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="7">
@@ -705,11 +705,11 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>46164</v>
+        <v>46165</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Nanos Research</t>
+          <t>Liaison Strategies</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -719,23 +719,25 @@
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>0.411</v>
+        <v>0.43</v>
       </c>
       <c r="G7" t="n">
-        <v>0.327</v>
+        <v>0.31</v>
       </c>
       <c r="H7" t="n">
-        <v>0.064</v>
+        <v>0.06</v>
       </c>
       <c r="I7" t="n">
-        <v>0.126</v>
+        <v>0.11</v>
       </c>
       <c r="J7" t="n">
-        <v>0.048</v>
-      </c>
-      <c r="K7" t="inlineStr"/>
+        <v>0.02</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.03</v>
+      </c>
       <c r="L7" t="n">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="8">
@@ -745,11 +747,11 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>46162</v>
+        <v>46164</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Abacus Data</t>
+          <t>Nanos Research</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -759,24 +761,24 @@
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>0.47</v>
+        <v>0.411</v>
       </c>
       <c r="G8" t="n">
-        <v>0.35</v>
+        <v>0.327</v>
       </c>
       <c r="H8" t="n">
-        <v>0.06</v>
+        <v>0.064</v>
       </c>
       <c r="I8" t="n">
-        <v>0.08</v>
+        <v>0.126</v>
       </c>
       <c r="J8" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="n">
-        <v>0.01</v>
-      </c>
+        <v>0.048</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="L8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -785,11 +787,11 @@
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>46158</v>
+        <v>46162</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Liaison Strategies</t>
+          <t>Abacus Data</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -799,26 +801,24 @@
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>0.43</v>
+        <v>0.47</v>
       </c>
       <c r="G9" t="n">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="H9" t="n">
         <v>0.06</v>
       </c>
       <c r="I9" t="n">
-        <v>0.11</v>
+        <v>0.08</v>
       </c>
       <c r="J9" t="n">
         <v>0.02</v>
       </c>
       <c r="K9" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0.02</v>
-      </c>
+        <v>0.01</v>
+      </c>
+      <c r="L9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -827,11 +827,11 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>46157</v>
+        <v>46158</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Nanos Research</t>
+          <t>Liaison Strategies</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -841,23 +841,25 @@
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>0.423</v>
+        <v>0.43</v>
       </c>
       <c r="G10" t="n">
-        <v>0.327</v>
+        <v>0.34</v>
       </c>
       <c r="H10" t="n">
-        <v>0.058</v>
+        <v>0.06</v>
       </c>
       <c r="I10" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="J10" t="n">
-        <v>0.044</v>
-      </c>
-      <c r="K10" t="inlineStr"/>
+        <v>0.02</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.02</v>
+      </c>
       <c r="L10" t="n">
-        <v>0.019</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="11">
@@ -867,11 +869,11 @@
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>46151</v>
+        <v>46157</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Liaison Strategies</t>
+          <t>Nanos Research</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -881,26 +883,24 @@
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>0.44</v>
+        <v>0.423</v>
       </c>
       <c r="G11" t="n">
-        <v>0.33</v>
+        <v>0.327</v>
       </c>
       <c r="H11" t="n">
-        <v>0.06</v>
+        <v>0.058</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1</v>
+        <v>0.12</v>
       </c>
       <c r="J11" t="n">
-        <v>0.02</v>
+        <v>0.044</v>
       </c>
       <c r="K11" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0.02</v>
-      </c>
+        <v>0.019</v>
+      </c>
+      <c r="L11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -909,11 +909,11 @@
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>46150</v>
+        <v>46151</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Nanos Research</t>
+          <t>Liaison Strategies</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -923,21 +923,23 @@
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>0.455</v>
+        <v>0.44</v>
       </c>
       <c r="G12" t="n">
-        <v>0.334</v>
+        <v>0.33</v>
       </c>
       <c r="H12" t="n">
-        <v>0.053</v>
+        <v>0.06</v>
       </c>
       <c r="I12" t="n">
-        <v>0.08800000000000001</v>
+        <v>0.1</v>
       </c>
       <c r="J12" t="n">
-        <v>0.035</v>
-      </c>
-      <c r="K12" t="inlineStr"/>
+        <v>0.02</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0.02</v>
+      </c>
       <c r="L12" t="n">
         <v>0.02</v>
       </c>
@@ -953,7 +955,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Research Co.</t>
+          <t>Nanos Research</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -963,26 +965,24 @@
         <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>0.46</v>
+        <v>0.455</v>
       </c>
       <c r="G13" t="n">
-        <v>0.31</v>
+        <v>0.334</v>
       </c>
       <c r="H13" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.053</v>
       </c>
       <c r="I13" t="n">
-        <v>0.11</v>
+        <v>0.08800000000000001</v>
       </c>
       <c r="J13" t="n">
-        <v>0.03</v>
+        <v>0.035</v>
       </c>
       <c r="K13" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0.01</v>
-      </c>
+        <v>0.02</v>
+      </c>
+      <c r="L13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -991,11 +991,11 @@
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>46147</v>
+        <v>46150</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Abacus Data</t>
+          <t>Research Co.</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -1008,19 +1008,19 @@
         <v>0.46</v>
       </c>
       <c r="G14" t="n">
-        <v>0.36</v>
+        <v>0.31</v>
       </c>
       <c r="H14" t="n">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I14" t="n">
-        <v>0.08</v>
+        <v>0.11</v>
       </c>
       <c r="J14" t="n">
         <v>0.03</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="L14" t="n">
         <v>0.01</v>
@@ -1033,11 +1033,11 @@
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>46144</v>
+        <v>46147</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Liaison Strategies</t>
+          <t>Abacus Data</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -1047,25 +1047,25 @@
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="G15" t="n">
-        <v>0.33</v>
+        <v>0.36</v>
       </c>
       <c r="H15" t="n">
         <v>0.06</v>
       </c>
       <c r="I15" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="J15" t="n">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="K15" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="L15" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -1075,11 +1075,11 @@
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>46143</v>
+        <v>46144</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Nanos Research</t>
+          <t>Liaison Strategies</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -1089,23 +1089,25 @@
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>0.448</v>
+        <v>0.45</v>
       </c>
       <c r="G16" t="n">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="H16" t="n">
-        <v>0.05599999999999999</v>
+        <v>0.06</v>
       </c>
       <c r="I16" t="n">
-        <v>0.114</v>
+        <v>0.09</v>
       </c>
       <c r="J16" t="n">
-        <v>0.034</v>
-      </c>
-      <c r="K16" t="inlineStr"/>
+        <v>0.02</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0.02</v>
+      </c>
       <c r="L16" t="n">
-        <v>0.014</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="17">
@@ -1115,11 +1117,11 @@
         </is>
       </c>
       <c r="B17" s="2" t="n">
-        <v>46138</v>
+        <v>46143</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Léger</t>
+          <t>Nanos Research</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1129,22 +1131,22 @@
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>0.48</v>
+        <v>0.448</v>
       </c>
       <c r="G17" t="n">
-        <v>0.37</v>
+        <v>0.32</v>
       </c>
       <c r="H17" t="n">
-        <v>0.06</v>
+        <v>0.05599999999999999</v>
       </c>
       <c r="I17" t="n">
-        <v>0.06</v>
+        <v>0.114</v>
       </c>
       <c r="J17" t="n">
-        <v>0.02</v>
+        <v>0.034</v>
       </c>
       <c r="K17" t="n">
-        <v>0.01</v>
+        <v>0.014</v>
       </c>
       <c r="L17" t="inlineStr"/>
     </row>
@@ -1155,11 +1157,11 @@
         </is>
       </c>
       <c r="B18" s="2" t="n">
-        <v>46137</v>
+        <v>46138</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Liaison Strategies</t>
+          <t>Léger</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1169,25 +1171,23 @@
         <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>0.45</v>
+        <v>0.48</v>
       </c>
       <c r="G18" t="n">
-        <v>0.34</v>
+        <v>0.37</v>
       </c>
       <c r="H18" t="n">
         <v>0.06</v>
       </c>
       <c r="I18" t="n">
-        <v>0.09</v>
+        <v>0.06</v>
       </c>
       <c r="J18" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0.02</v>
-      </c>
+        <v>0.02</v>
+      </c>
+      <c r="K18" t="inlineStr"/>
       <c r="L18" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="19">
@@ -1197,11 +1197,11 @@
         </is>
       </c>
       <c r="B19" s="2" t="n">
-        <v>46136</v>
+        <v>46137</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Ekos</t>
+          <t>Liaison Strategies</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1211,22 +1211,22 @@
         <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>0.445</v>
+        <v>0.45</v>
       </c>
       <c r="G19" t="n">
-        <v>0.31</v>
+        <v>0.34</v>
       </c>
       <c r="H19" t="n">
-        <v>0.058</v>
+        <v>0.06</v>
       </c>
       <c r="I19" t="n">
-        <v>0.125</v>
+        <v>0.09</v>
       </c>
       <c r="J19" t="n">
         <v>0.03</v>
       </c>
       <c r="K19" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="L19" t="n">
         <v>0.02</v>
@@ -1243,7 +1243,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Nanos Research</t>
+          <t>Ekos</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1253,23 +1253,25 @@
         <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>0.446</v>
+        <v>0.445</v>
       </c>
       <c r="G20" t="n">
-        <v>0.32</v>
+        <v>0.31</v>
       </c>
       <c r="H20" t="n">
-        <v>0.05400000000000001</v>
+        <v>0.058</v>
       </c>
       <c r="I20" t="n">
-        <v>0.115</v>
+        <v>0.125</v>
       </c>
       <c r="J20" t="n">
-        <v>0.035</v>
-      </c>
-      <c r="K20" t="inlineStr"/>
+        <v>0.03</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0.02</v>
+      </c>
       <c r="L20" t="n">
-        <v>0.011</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="21">
@@ -1279,11 +1281,11 @@
         </is>
       </c>
       <c r="B21" s="2" t="n">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Abacus Data</t>
+          <t>Nanos Research</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1293,26 +1295,24 @@
         <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>0.45</v>
+        <v>0.446</v>
       </c>
       <c r="G21" t="n">
-        <v>0.36</v>
+        <v>0.32</v>
       </c>
       <c r="H21" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.05400000000000001</v>
       </c>
       <c r="I21" t="n">
-        <v>0.08</v>
+        <v>0.115</v>
       </c>
       <c r="J21" t="n">
-        <v>0.02</v>
+        <v>0.035</v>
       </c>
       <c r="K21" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0.01</v>
-      </c>
+        <v>0.011</v>
+      </c>
+      <c r="L21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1321,11 +1321,11 @@
         </is>
       </c>
       <c r="B22" s="2" t="n">
-        <v>46132</v>
+        <v>46134</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Angus Reid</t>
+          <t>Abacus Data</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1335,16 +1335,16 @@
         <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>0.42</v>
+        <v>0.45</v>
       </c>
       <c r="G22" t="n">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="H22" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="I22" t="n">
-        <v>0.12</v>
+        <v>0.08</v>
       </c>
       <c r="J22" t="n">
         <v>0.02</v>
@@ -1352,7 +1352,9 @@
       <c r="K22" t="n">
         <v>0.01</v>
       </c>
-      <c r="L22" t="inlineStr"/>
+      <c r="L22" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1361,11 +1363,11 @@
         </is>
       </c>
       <c r="B23" s="2" t="n">
-        <v>46130</v>
+        <v>46132</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Liaison Strategies</t>
+          <t>Angus Reid</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1375,25 +1377,23 @@
         <v>0</v>
       </c>
       <c r="F23" t="n">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="G23" t="n">
-        <v>0.33</v>
+        <v>0.35</v>
       </c>
       <c r="H23" t="n">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I23" t="n">
-        <v>0.1</v>
+        <v>0.12</v>
       </c>
       <c r="J23" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0.02</v>
-      </c>
+        <v>0.02</v>
+      </c>
+      <c r="K23" t="inlineStr"/>
       <c r="L23" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="24">
@@ -1403,11 +1403,11 @@
         </is>
       </c>
       <c r="B24" s="2" t="n">
-        <v>46129</v>
+        <v>46130</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Nanos Research</t>
+          <t>Liaison Strategies</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1417,23 +1417,25 @@
         <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>0.458</v>
+        <v>0.45</v>
       </c>
       <c r="G24" t="n">
-        <v>0.315</v>
+        <v>0.33</v>
       </c>
       <c r="H24" t="n">
-        <v>0.053</v>
+        <v>0.06</v>
       </c>
       <c r="I24" t="n">
-        <v>0.119</v>
+        <v>0.1</v>
       </c>
       <c r="J24" t="n">
-        <v>0.035</v>
-      </c>
-      <c r="K24" t="inlineStr"/>
+        <v>0.03</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0.02</v>
+      </c>
       <c r="L24" t="n">
-        <v>0.009000000000000001</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="25">
@@ -1443,11 +1445,11 @@
         </is>
       </c>
       <c r="B25" s="2" t="n">
-        <v>46125</v>
+        <v>46129</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>April 13, 2026</t>
+          <t>Nanos Research</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1456,12 +1458,24 @@
       <c r="E25" t="b">
         <v>0</v>
       </c>
-      <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
+      <c r="F25" t="n">
+        <v>0.458</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0.315</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.053</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.119</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0.009000000000000001</v>
+      </c>
       <c r="L25" t="inlineStr"/>
     </row>
     <row r="26">
@@ -1471,11 +1485,11 @@
         </is>
       </c>
       <c r="B26" s="2" t="n">
-        <v>46123</v>
+        <v>46125</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Liaison Strategies</t>
+          <t>April 13, 2026</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1484,27 +1498,13 @@
       <c r="E26" t="b">
         <v>0</v>
       </c>
-      <c r="F26" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="G26" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="H26" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="I26" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="J26" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="K26" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="L26" t="n">
-        <v>0.02</v>
-      </c>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1513,11 +1513,11 @@
         </is>
       </c>
       <c r="B27" s="2" t="n">
-        <v>46122</v>
+        <v>46123</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Nanos Research</t>
+          <t>Liaison Strategies</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1527,23 +1527,25 @@
         <v>0</v>
       </c>
       <c r="F27" t="n">
-        <v>0.453</v>
+        <v>0.43</v>
       </c>
       <c r="G27" t="n">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="H27" t="n">
-        <v>0.05400000000000001</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I27" t="n">
-        <v>0.122</v>
+        <v>0.1</v>
       </c>
       <c r="J27" t="n">
-        <v>0.035</v>
-      </c>
-      <c r="K27" t="inlineStr"/>
+        <v>0.03</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0.02</v>
+      </c>
       <c r="L27" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="28">
@@ -1553,11 +1555,11 @@
         </is>
       </c>
       <c r="B28" s="2" t="n">
-        <v>46120</v>
+        <v>46122</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Spark Insights</t>
+          <t>Nanos Research</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1567,20 +1569,22 @@
         <v>0</v>
       </c>
       <c r="F28" t="n">
-        <v>0.46</v>
+        <v>0.453</v>
       </c>
       <c r="G28" t="n">
         <v>0.32</v>
       </c>
       <c r="H28" t="n">
-        <v>0.06</v>
+        <v>0.05400000000000001</v>
       </c>
       <c r="I28" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="J28" t="inlineStr"/>
+        <v>0.122</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0.035</v>
+      </c>
       <c r="K28" t="n">
-        <v>0.08</v>
+        <v>0.01</v>
       </c>
       <c r="L28" t="inlineStr"/>
     </row>
@@ -1595,7 +1599,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Abacus Data</t>
+          <t>Spark Insights</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1605,25 +1609,21 @@
         <v>0</v>
       </c>
       <c r="F29" t="n">
-        <v>0.44</v>
+        <v>0.46</v>
       </c>
       <c r="G29" t="n">
-        <v>0.38</v>
+        <v>0.32</v>
       </c>
       <c r="H29" t="n">
         <v>0.06</v>
       </c>
       <c r="I29" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="n">
         <v>0.08</v>
-      </c>
-      <c r="J29" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="K29" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="L29" t="n">
-        <v>0.01</v>
       </c>
     </row>
     <row r="30">
@@ -1633,11 +1633,11 @@
         </is>
       </c>
       <c r="B30" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Ipsos</t>
+          <t>Abacus Data</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1647,25 +1647,25 @@
         <v>0</v>
       </c>
       <c r="F30" t="n">
-        <v>0.45</v>
+        <v>0.44</v>
       </c>
       <c r="G30" t="n">
-        <v>0.33</v>
+        <v>0.38</v>
       </c>
       <c r="H30" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="I30" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="J30" t="n">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="K30" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="L30" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="31">
@@ -1675,11 +1675,11 @@
         </is>
       </c>
       <c r="B31" s="2" t="n">
-        <v>46116</v>
+        <v>46119</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Liaison Strategies</t>
+          <t>Ipsos</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1689,25 +1689,25 @@
         <v>0</v>
       </c>
       <c r="F31" t="n">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="G31" t="n">
         <v>0.33</v>
       </c>
       <c r="H31" t="n">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I31" t="n">
         <v>0.09</v>
       </c>
       <c r="J31" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="K31" t="n">
         <v>0.02</v>
       </c>
       <c r="L31" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -1717,11 +1717,11 @@
         </is>
       </c>
       <c r="B32" s="2" t="n">
-        <v>46115</v>
+        <v>46116</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Nanos Research</t>
+          <t>Liaison Strategies</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1731,23 +1731,25 @@
         <v>0</v>
       </c>
       <c r="F32" t="n">
-        <v>0.457</v>
+        <v>0.44</v>
       </c>
       <c r="G32" t="n">
-        <v>0.305</v>
+        <v>0.33</v>
       </c>
       <c r="H32" t="n">
-        <v>0.05599999999999999</v>
+        <v>0.06</v>
       </c>
       <c r="I32" t="n">
-        <v>0.125</v>
+        <v>0.09</v>
       </c>
       <c r="J32" t="n">
-        <v>0.042</v>
-      </c>
-      <c r="K32" t="inlineStr"/>
+        <v>0.03</v>
+      </c>
+      <c r="K32" t="n">
+        <v>0.02</v>
+      </c>
       <c r="L32" t="n">
-        <v>0.011</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="33">
@@ -1757,11 +1759,11 @@
         </is>
       </c>
       <c r="B33" s="2" t="n">
-        <v>46111</v>
+        <v>46115</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Léger</t>
+          <t>Nanos Research</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1771,22 +1773,22 @@
         <v>0</v>
       </c>
       <c r="F33" t="n">
-        <v>0.48</v>
+        <v>0.457</v>
       </c>
       <c r="G33" t="n">
-        <v>0.34</v>
+        <v>0.305</v>
       </c>
       <c r="H33" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.05599999999999999</v>
       </c>
       <c r="I33" t="n">
-        <v>0.06</v>
+        <v>0.125</v>
       </c>
       <c r="J33" t="n">
-        <v>0.03</v>
+        <v>0.042</v>
       </c>
       <c r="K33" t="n">
-        <v>0.01</v>
+        <v>0.011</v>
       </c>
       <c r="L33" t="inlineStr"/>
     </row>
@@ -1797,11 +1799,11 @@
         </is>
       </c>
       <c r="B34" s="2" t="n">
-        <v>46110</v>
+        <v>46111</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>March 29, 2026</t>
+          <t>Léger</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1810,13 +1812,25 @@
       <c r="E34" t="b">
         <v>0</v>
       </c>
-      <c r="F34" t="inlineStr"/>
-      <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr"/>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
+      <c r="F34" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="G34" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="J34" t="n">
+        <v>0.03</v>
+      </c>
       <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
+      <c r="L34" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1825,11 +1839,11 @@
         </is>
       </c>
       <c r="B35" s="2" t="n">
-        <v>46109</v>
+        <v>46110</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Liaison Strategies</t>
+          <t>March 29, 2026</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1838,27 +1852,13 @@
       <c r="E35" t="b">
         <v>0</v>
       </c>
-      <c r="F35" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="G35" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="H35" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="I35" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="J35" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="K35" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="L35" t="n">
-        <v>0.02</v>
-      </c>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1867,11 +1867,11 @@
         </is>
       </c>
       <c r="B36" s="2" t="n">
-        <v>46108</v>
+        <v>46109</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Nanos Research</t>
+          <t>Liaison Strategies</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1881,23 +1881,25 @@
         <v>0</v>
       </c>
       <c r="F36" t="n">
-        <v>0.465</v>
+        <v>0.45</v>
       </c>
       <c r="G36" t="n">
-        <v>0.322</v>
+        <v>0.33</v>
       </c>
       <c r="H36" t="n">
-        <v>0.051</v>
+        <v>0.06</v>
       </c>
       <c r="I36" t="n">
-        <v>0.113</v>
+        <v>0.09</v>
       </c>
       <c r="J36" t="n">
-        <v>0.036</v>
-      </c>
-      <c r="K36" t="inlineStr"/>
+        <v>0.02</v>
+      </c>
+      <c r="K36" t="n">
+        <v>0.02</v>
+      </c>
       <c r="L36" t="n">
-        <v>0.011</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="37">
@@ -1907,11 +1909,11 @@
         </is>
       </c>
       <c r="B37" s="2" t="n">
-        <v>46107</v>
+        <v>46108</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Spark Insights</t>
+          <t>Nanos Research</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1921,20 +1923,22 @@
         <v>0</v>
       </c>
       <c r="F37" t="n">
-        <v>0.46</v>
+        <v>0.465</v>
       </c>
       <c r="G37" t="n">
-        <v>0.3</v>
+        <v>0.322</v>
       </c>
       <c r="H37" t="n">
-        <v>0.05</v>
+        <v>0.051</v>
       </c>
       <c r="I37" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="J37" t="inlineStr"/>
+        <v>0.113</v>
+      </c>
+      <c r="J37" t="n">
+        <v>0.036</v>
+      </c>
       <c r="K37" t="n">
-        <v>0.08</v>
+        <v>0.011</v>
       </c>
       <c r="L37" t="inlineStr"/>
     </row>
@@ -1945,11 +1949,11 @@
         </is>
       </c>
       <c r="B38" s="2" t="n">
-        <v>46105</v>
+        <v>46107</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Abacus Data</t>
+          <t>Spark Insights</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1959,25 +1963,21 @@
         <v>0</v>
       </c>
       <c r="F38" t="n">
-        <v>0.44</v>
+        <v>0.46</v>
       </c>
       <c r="G38" t="n">
-        <v>0.37</v>
+        <v>0.3</v>
       </c>
       <c r="H38" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="I38" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="J38" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="K38" t="n">
-        <v>0</v>
-      </c>
+        <v>0.11</v>
+      </c>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
       <c r="L38" t="n">
-        <v>0.01</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="39">
@@ -1987,11 +1987,11 @@
         </is>
       </c>
       <c r="B39" s="2" t="n">
-        <v>46102</v>
+        <v>46105</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Liaison Strategies</t>
+          <t>Abacus Data</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -2001,13 +2001,13 @@
         <v>0</v>
       </c>
       <c r="F39" t="n">
-        <v>0.46</v>
+        <v>0.44</v>
       </c>
       <c r="G39" t="n">
-        <v>0.32</v>
+        <v>0.37</v>
       </c>
       <c r="H39" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="I39" t="n">
         <v>0.09</v>
@@ -2016,10 +2016,10 @@
         <v>0.03</v>
       </c>
       <c r="K39" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="L39" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -2029,11 +2029,11 @@
         </is>
       </c>
       <c r="B40" s="2" t="n">
-        <v>46101</v>
+        <v>46102</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Nanos Research</t>
+          <t>Liaison Strategies</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -2043,23 +2043,25 @@
         <v>0</v>
       </c>
       <c r="F40" t="n">
-        <v>0.457</v>
+        <v>0.46</v>
       </c>
       <c r="G40" t="n">
-        <v>0.329</v>
+        <v>0.32</v>
       </c>
       <c r="H40" t="n">
-        <v>0.048</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I40" t="n">
-        <v>0.115</v>
+        <v>0.09</v>
       </c>
       <c r="J40" t="n">
-        <v>0.03700000000000001</v>
-      </c>
-      <c r="K40" t="inlineStr"/>
+        <v>0.03</v>
+      </c>
+      <c r="K40" t="n">
+        <v>0.02</v>
+      </c>
       <c r="L40" t="n">
-        <v>0.008</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="41">
@@ -2069,11 +2071,11 @@
         </is>
       </c>
       <c r="B41" s="2" t="n">
-        <v>46098</v>
+        <v>46101</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Angus Reid</t>
+          <t>Nanos Research</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -2083,22 +2085,22 @@
         <v>0</v>
       </c>
       <c r="F41" t="n">
-        <v>0.44</v>
+        <v>0.457</v>
       </c>
       <c r="G41" t="n">
-        <v>0.36</v>
+        <v>0.329</v>
       </c>
       <c r="H41" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.048</v>
       </c>
       <c r="I41" t="n">
-        <v>0.09</v>
+        <v>0.115</v>
       </c>
       <c r="J41" t="n">
-        <v>0.02</v>
+        <v>0.03700000000000001</v>
       </c>
       <c r="K41" t="n">
-        <v>0.01</v>
+        <v>0.008</v>
       </c>
       <c r="L41" t="inlineStr"/>
     </row>
@@ -2109,11 +2111,11 @@
         </is>
       </c>
       <c r="B42" s="2" t="n">
-        <v>46096</v>
+        <v>46098</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Ekos</t>
+          <t>Angus Reid</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -2123,25 +2125,23 @@
         <v>0</v>
       </c>
       <c r="F42" t="n">
-        <v>0.475</v>
+        <v>0.44</v>
       </c>
       <c r="G42" t="n">
-        <v>0.27</v>
+        <v>0.36</v>
       </c>
       <c r="H42" t="n">
-        <v>0.04099999999999999</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I42" t="n">
-        <v>0.151</v>
+        <v>0.09</v>
       </c>
       <c r="J42" t="n">
-        <v>0.045</v>
-      </c>
-      <c r="K42" t="n">
-        <v>0.004</v>
-      </c>
+        <v>0.02</v>
+      </c>
+      <c r="K42" t="inlineStr"/>
       <c r="L42" t="n">
-        <v>0.015</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="43">
@@ -2151,11 +2151,11 @@
         </is>
       </c>
       <c r="B43" s="2" t="n">
-        <v>46095</v>
+        <v>46096</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Liaison Strategies</t>
+          <t>Ekos</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -2165,25 +2165,25 @@
         <v>0</v>
       </c>
       <c r="F43" t="n">
-        <v>0.45</v>
+        <v>0.475</v>
       </c>
       <c r="G43" t="n">
-        <v>0.31</v>
+        <v>0.27</v>
       </c>
       <c r="H43" t="n">
-        <v>0.06</v>
+        <v>0.04099999999999999</v>
       </c>
       <c r="I43" t="n">
-        <v>0.08</v>
+        <v>0.151</v>
       </c>
       <c r="J43" t="n">
-        <v>0.03</v>
+        <v>0.045</v>
       </c>
       <c r="K43" t="n">
-        <v>0.04</v>
+        <v>0.015</v>
       </c>
       <c r="L43" t="n">
-        <v>0.04</v>
+        <v>0.004</v>
       </c>
     </row>
     <row r="44">
@@ -2193,11 +2193,11 @@
         </is>
       </c>
       <c r="B44" s="2" t="n">
-        <v>46094</v>
+        <v>46095</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Nanos Research</t>
+          <t>Liaison Strategies</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -2207,23 +2207,25 @@
         <v>0</v>
       </c>
       <c r="F44" t="n">
-        <v>0.478</v>
+        <v>0.45</v>
       </c>
       <c r="G44" t="n">
-        <v>0.311</v>
+        <v>0.31</v>
       </c>
       <c r="H44" t="n">
-        <v>0.045</v>
+        <v>0.06</v>
       </c>
       <c r="I44" t="n">
-        <v>0.112</v>
+        <v>0.08</v>
       </c>
       <c r="J44" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="K44" t="n">
         <v>0.04</v>
       </c>
-      <c r="K44" t="inlineStr"/>
       <c r="L44" t="n">
-        <v>0.011</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="45">
@@ -2233,11 +2235,11 @@
         </is>
       </c>
       <c r="B45" s="2" t="n">
-        <v>46092</v>
+        <v>46094</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Abacus Data</t>
+          <t>Nanos Research</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2247,26 +2249,24 @@
         <v>0</v>
       </c>
       <c r="F45" t="n">
-        <v>0.46</v>
+        <v>0.478</v>
       </c>
       <c r="G45" t="n">
-        <v>0.35</v>
+        <v>0.311</v>
       </c>
       <c r="H45" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.045</v>
       </c>
       <c r="I45" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.112</v>
       </c>
       <c r="J45" t="n">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="K45" t="n">
-        <v>0</v>
-      </c>
-      <c r="L45" t="n">
-        <v>0.01</v>
-      </c>
+        <v>0.011</v>
+      </c>
+      <c r="L45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2275,11 +2275,11 @@
         </is>
       </c>
       <c r="B46" s="2" t="n">
-        <v>46088</v>
+        <v>46092</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Liaison Strategies</t>
+          <t>Abacus Data</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2289,25 +2289,25 @@
         <v>0</v>
       </c>
       <c r="F46" t="n">
-        <v>0.44</v>
+        <v>0.46</v>
       </c>
       <c r="G46" t="n">
-        <v>0.3</v>
+        <v>0.35</v>
       </c>
       <c r="H46" t="n">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I46" t="n">
-        <v>0.09</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="J46" t="n">
         <v>0.03</v>
       </c>
       <c r="K46" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="L46" t="n">
-        <v>0.04</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -2317,11 +2317,11 @@
         </is>
       </c>
       <c r="B47" s="2" t="n">
-        <v>46087</v>
+        <v>46088</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Spark Insights</t>
+          <t>Liaison Strategies</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2331,22 +2331,26 @@
         <v>0</v>
       </c>
       <c r="F47" t="n">
-        <v>0.46</v>
+        <v>0.44</v>
       </c>
       <c r="G47" t="n">
-        <v>0.31</v>
+        <v>0.3</v>
       </c>
       <c r="H47" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="I47" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="J47" t="inlineStr"/>
+        <v>0.09</v>
+      </c>
+      <c r="J47" t="n">
+        <v>0.03</v>
+      </c>
       <c r="K47" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="L47" t="inlineStr"/>
+        <v>0.04</v>
+      </c>
+      <c r="L47" t="n">
+        <v>0.03</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2359,7 +2363,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Nanos Research</t>
+          <t>Spark Insights</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2372,20 +2376,18 @@
         <v>0.46</v>
       </c>
       <c r="G48" t="n">
-        <v>0.325</v>
+        <v>0.31</v>
       </c>
       <c r="H48" t="n">
-        <v>0.052</v>
+        <v>0.05</v>
       </c>
       <c r="I48" t="n">
         <v>0.1</v>
       </c>
-      <c r="J48" t="n">
-        <v>0.047</v>
-      </c>
+      <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="n">
-        <v>0.006999999999999999</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="49">
@@ -2395,11 +2397,11 @@
         </is>
       </c>
       <c r="B49" s="2" t="n">
-        <v>46083</v>
+        <v>46087</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Mainstreet Research</t>
+          <t>Nanos Research</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2412,23 +2414,21 @@
         <v>0.46</v>
       </c>
       <c r="G49" t="n">
-        <v>0.36</v>
+        <v>0.325</v>
       </c>
       <c r="H49" t="n">
-        <v>0.04</v>
+        <v>0.052</v>
       </c>
       <c r="I49" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.1</v>
       </c>
       <c r="J49" t="n">
-        <v>0.02</v>
+        <v>0.047</v>
       </c>
       <c r="K49" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="L49" t="n">
-        <v>0.03</v>
-      </c>
+        <v>0.006999999999999999</v>
+      </c>
+      <c r="L49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2441,7 +2441,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Léger</t>
+          <t>Mainstreet Research</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2451,24 +2451,26 @@
         <v>0</v>
       </c>
       <c r="F50" t="n">
-        <v>0.49</v>
+        <v>0.46</v>
       </c>
       <c r="G50" t="n">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="H50" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="I50" t="n">
-        <v>0.05</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="J50" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="K50" t="n">
         <v>0.03</v>
       </c>
-      <c r="K50" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="L50" t="inlineStr"/>
+      <c r="L50" t="n">
+        <v>0.02</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2477,11 +2479,11 @@
         </is>
       </c>
       <c r="B51" s="2" t="n">
-        <v>46081</v>
+        <v>46083</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Liaison Strategies</t>
+          <t>Léger</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2491,23 +2493,21 @@
         <v>0</v>
       </c>
       <c r="F51" t="n">
-        <v>0.43</v>
+        <v>0.49</v>
       </c>
       <c r="G51" t="n">
-        <v>0.33</v>
+        <v>0.35</v>
       </c>
       <c r="H51" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="I51" t="n">
-        <v>0.09</v>
+        <v>0.05</v>
       </c>
       <c r="J51" t="n">
         <v>0.03</v>
       </c>
-      <c r="K51" t="n">
-        <v>0.02</v>
-      </c>
+      <c r="K51" t="inlineStr"/>
       <c r="L51" t="n">
         <v>0.02</v>
       </c>
@@ -2519,11 +2519,11 @@
         </is>
       </c>
       <c r="B52" s="2" t="n">
-        <v>46080</v>
+        <v>46081</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Nanos Research</t>
+          <t>Liaison Strategies</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2533,23 +2533,25 @@
         <v>0</v>
       </c>
       <c r="F52" t="n">
-        <v>0.436</v>
+        <v>0.43</v>
       </c>
       <c r="G52" t="n">
-        <v>0.332</v>
+        <v>0.33</v>
       </c>
       <c r="H52" t="n">
-        <v>0.051</v>
+        <v>0.06</v>
       </c>
       <c r="I52" t="n">
-        <v>0.114</v>
+        <v>0.09</v>
       </c>
       <c r="J52" t="n">
-        <v>0.049</v>
-      </c>
-      <c r="K52" t="inlineStr"/>
+        <v>0.03</v>
+      </c>
+      <c r="K52" t="n">
+        <v>0.02</v>
+      </c>
       <c r="L52" t="n">
-        <v>0.006999999999999999</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="53">
@@ -2559,11 +2561,11 @@
         </is>
       </c>
       <c r="B53" s="2" t="n">
-        <v>46079</v>
+        <v>46080</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Ipsos</t>
+          <t>Nanos Research</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2573,26 +2575,24 @@
         <v>0</v>
       </c>
       <c r="F53" t="n">
-        <v>0.44</v>
+        <v>0.436</v>
       </c>
       <c r="G53" t="n">
-        <v>0.36</v>
+        <v>0.332</v>
       </c>
       <c r="H53" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.051</v>
       </c>
       <c r="I53" t="n">
-        <v>0.08</v>
+        <v>0.114</v>
       </c>
       <c r="J53" t="n">
-        <v>0.03</v>
+        <v>0.049</v>
       </c>
       <c r="K53" t="n">
-        <v>0</v>
-      </c>
-      <c r="L53" t="n">
-        <v>0.01</v>
-      </c>
+        <v>0.006999999999999999</v>
+      </c>
+      <c r="L53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2601,11 +2601,11 @@
         </is>
       </c>
       <c r="B54" s="2" t="n">
-        <v>46077</v>
+        <v>46079</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Pollara</t>
+          <t>Ipsos</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2615,22 +2615,26 @@
         <v>0</v>
       </c>
       <c r="F54" t="n">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="G54" t="n">
-        <v>0.34</v>
+        <v>0.36</v>
       </c>
       <c r="H54" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="I54" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="J54" t="inlineStr"/>
+        <v>0.08</v>
+      </c>
+      <c r="J54" t="n">
+        <v>0.03</v>
+      </c>
       <c r="K54" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="L54" t="inlineStr"/>
+        <v>0.01</v>
+      </c>
+      <c r="L54" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2639,11 +2643,11 @@
         </is>
       </c>
       <c r="B55" s="2" t="n">
-        <v>46076</v>
+        <v>46077</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Abacus Data</t>
+          <t>Pollara</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2653,25 +2657,21 @@
         <v>0</v>
       </c>
       <c r="F55" t="n">
-        <v>0.44</v>
+        <v>0.47</v>
       </c>
       <c r="G55" t="n">
-        <v>0.38</v>
+        <v>0.34</v>
       </c>
       <c r="H55" t="n">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I55" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="J55" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="n">
         <v>0.03</v>
-      </c>
-      <c r="K55" t="n">
-        <v>0</v>
-      </c>
-      <c r="L55" t="n">
-        <v>0.01</v>
       </c>
     </row>
     <row r="56">
@@ -2685,7 +2685,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Angus Reid</t>
+          <t>Abacus Data</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2695,24 +2695,26 @@
         <v>0</v>
       </c>
       <c r="F56" t="n">
-        <v>0.45</v>
+        <v>0.44</v>
       </c>
       <c r="G56" t="n">
-        <v>0.32</v>
+        <v>0.38</v>
       </c>
       <c r="H56" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="I56" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="I56" t="n">
-        <v>0.1</v>
-      </c>
       <c r="J56" t="n">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="K56" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="L56" t="inlineStr"/>
+        <v>0.01</v>
+      </c>
+      <c r="L56" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -2721,11 +2723,11 @@
         </is>
       </c>
       <c r="B57" s="2" t="n">
-        <v>46074</v>
+        <v>46076</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Liaison Strategies</t>
+          <t>Angus Reid</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2738,20 +2740,18 @@
         <v>0.45</v>
       </c>
       <c r="G57" t="n">
-        <v>0.33</v>
+        <v>0.32</v>
       </c>
       <c r="H57" t="n">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I57" t="n">
         <v>0.1</v>
       </c>
       <c r="J57" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="K57" t="n">
-        <v>0.02</v>
-      </c>
+        <v>0.04</v>
+      </c>
+      <c r="K57" t="inlineStr"/>
       <c r="L57" t="n">
         <v>0.02</v>
       </c>
@@ -2763,11 +2763,11 @@
         </is>
       </c>
       <c r="B58" s="2" t="n">
-        <v>46073</v>
+        <v>46074</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Nanos Research</t>
+          <t>Liaison Strategies</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2777,23 +2777,25 @@
         <v>0</v>
       </c>
       <c r="F58" t="n">
-        <v>0.413</v>
+        <v>0.45</v>
       </c>
       <c r="G58" t="n">
-        <v>0.337</v>
+        <v>0.33</v>
       </c>
       <c r="H58" t="n">
-        <v>0.076</v>
+        <v>0.06</v>
       </c>
       <c r="I58" t="n">
-        <v>0.106</v>
+        <v>0.1</v>
       </c>
       <c r="J58" t="n">
-        <v>0.049</v>
-      </c>
-      <c r="K58" t="inlineStr"/>
+        <v>0.02</v>
+      </c>
+      <c r="K58" t="n">
+        <v>0.02</v>
+      </c>
       <c r="L58" t="n">
-        <v>0.009000000000000001</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="59">
@@ -2803,11 +2805,11 @@
         </is>
       </c>
       <c r="B59" s="2" t="n">
-        <v>46070</v>
+        <v>46073</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Innovative Research</t>
+          <t>Nanos Research</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2817,22 +2819,22 @@
         <v>0</v>
       </c>
       <c r="F59" t="n">
-        <v>0.44</v>
+        <v>0.413</v>
       </c>
       <c r="G59" t="n">
-        <v>0.37</v>
+        <v>0.337</v>
       </c>
       <c r="H59" t="n">
-        <v>0.06</v>
+        <v>0.076</v>
       </c>
       <c r="I59" t="n">
-        <v>0.08</v>
+        <v>0.106</v>
       </c>
       <c r="J59" t="n">
-        <v>0.03</v>
+        <v>0.049</v>
       </c>
       <c r="K59" t="n">
-        <v>0.03</v>
+        <v>0.009000000000000001</v>
       </c>
       <c r="L59" t="inlineStr"/>
     </row>
@@ -2843,11 +2845,11 @@
         </is>
       </c>
       <c r="B60" s="2" t="n">
-        <v>46067</v>
+        <v>46070</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Liaison Strategies</t>
+          <t>Innovative Research</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2857,25 +2859,23 @@
         <v>0</v>
       </c>
       <c r="F60" t="n">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="G60" t="n">
-        <v>0.34</v>
+        <v>0.37</v>
       </c>
       <c r="H60" t="n">
         <v>0.06</v>
       </c>
       <c r="I60" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="J60" t="n">
         <v>0.03</v>
       </c>
-      <c r="K60" t="n">
-        <v>0.02</v>
-      </c>
+      <c r="K60" t="inlineStr"/>
       <c r="L60" t="n">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="61">
@@ -2885,11 +2885,11 @@
         </is>
       </c>
       <c r="B61" s="2" t="n">
-        <v>46066</v>
+        <v>46067</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Nanos Research</t>
+          <t>Liaison Strategies</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2899,23 +2899,25 @@
         <v>0</v>
       </c>
       <c r="F61" t="n">
-        <v>0.381</v>
+        <v>0.43</v>
       </c>
       <c r="G61" t="n">
-        <v>0.365</v>
+        <v>0.34</v>
       </c>
       <c r="H61" t="n">
-        <v>0.083</v>
+        <v>0.06</v>
       </c>
       <c r="I61" t="n">
-        <v>0.111</v>
+        <v>0.09</v>
       </c>
       <c r="J61" t="n">
-        <v>0.044</v>
-      </c>
-      <c r="K61" t="inlineStr"/>
+        <v>0.03</v>
+      </c>
+      <c r="K61" t="n">
+        <v>0.02</v>
+      </c>
       <c r="L61" t="n">
-        <v>0.006999999999999999</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="62">
@@ -2925,11 +2927,11 @@
         </is>
       </c>
       <c r="B62" s="2" t="n">
-        <v>46063</v>
+        <v>46066</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Abacus Data</t>
+          <t>Nanos Research</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2939,26 +2941,24 @@
         <v>0</v>
       </c>
       <c r="F62" t="n">
-        <v>0.44</v>
+        <v>0.381</v>
       </c>
       <c r="G62" t="n">
-        <v>0.37</v>
+        <v>0.365</v>
       </c>
       <c r="H62" t="n">
-        <v>0.06</v>
+        <v>0.083</v>
       </c>
       <c r="I62" t="n">
-        <v>0.08</v>
+        <v>0.111</v>
       </c>
       <c r="J62" t="n">
-        <v>0.03</v>
+        <v>0.044</v>
       </c>
       <c r="K62" t="n">
-        <v>0</v>
-      </c>
-      <c r="L62" t="n">
-        <v>0.01</v>
-      </c>
+        <v>0.006999999999999999</v>
+      </c>
+      <c r="L62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -2967,11 +2967,11 @@
         </is>
       </c>
       <c r="B63" s="2" t="n">
-        <v>46060</v>
+        <v>46063</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Liaison Strategies</t>
+          <t>Abacus Data</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2981,25 +2981,25 @@
         <v>0</v>
       </c>
       <c r="F63" t="n">
-        <v>0.42</v>
+        <v>0.44</v>
       </c>
       <c r="G63" t="n">
-        <v>0.35</v>
+        <v>0.37</v>
       </c>
       <c r="H63" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="I63" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="J63" t="n">
         <v>0.03</v>
       </c>
       <c r="K63" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="L63" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64">
@@ -3009,11 +3009,11 @@
         </is>
       </c>
       <c r="B64" s="2" t="n">
-        <v>46059</v>
+        <v>46060</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Nanos Research</t>
+          <t>Liaison Strategies</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -3023,23 +3023,25 @@
         <v>0</v>
       </c>
       <c r="F64" t="n">
-        <v>0.391</v>
+        <v>0.42</v>
       </c>
       <c r="G64" t="n">
-        <v>0.352</v>
+        <v>0.35</v>
       </c>
       <c r="H64" t="n">
-        <v>0.08800000000000001</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I64" t="n">
-        <v>0.126</v>
+        <v>0.09</v>
       </c>
       <c r="J64" t="n">
-        <v>0.029</v>
-      </c>
-      <c r="K64" t="inlineStr"/>
+        <v>0.03</v>
+      </c>
+      <c r="K64" t="n">
+        <v>0.02</v>
+      </c>
       <c r="L64" t="n">
-        <v>0.009000000000000001</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="65">
@@ -3049,11 +3051,11 @@
         </is>
       </c>
       <c r="B65" s="2" t="n">
-        <v>46058</v>
+        <v>46059</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Research Co.</t>
+          <t>Nanos Research</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -3063,26 +3065,24 @@
         <v>0</v>
       </c>
       <c r="F65" t="n">
-        <v>0.45</v>
+        <v>0.391</v>
       </c>
       <c r="G65" t="n">
-        <v>0.32</v>
+        <v>0.352</v>
       </c>
       <c r="H65" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.08800000000000001</v>
       </c>
       <c r="I65" t="n">
-        <v>0.1</v>
+        <v>0.126</v>
       </c>
       <c r="J65" t="n">
-        <v>0.03</v>
+        <v>0.029</v>
       </c>
       <c r="K65" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="L65" t="n">
-        <v>0.02</v>
-      </c>
+        <v>0.009000000000000001</v>
+      </c>
+      <c r="L65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -3091,11 +3091,11 @@
         </is>
       </c>
       <c r="B66" s="2" t="n">
-        <v>46055</v>
+        <v>46058</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Innovative Research</t>
+          <t>Research Co.</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -3105,10 +3105,10 @@
         <v>0</v>
       </c>
       <c r="F66" t="n">
-        <v>0.4</v>
+        <v>0.45</v>
       </c>
       <c r="G66" t="n">
-        <v>0.38</v>
+        <v>0.32</v>
       </c>
       <c r="H66" t="n">
         <v>0.07000000000000001</v>
@@ -3122,7 +3122,9 @@
       <c r="K66" t="n">
         <v>0.02</v>
       </c>
-      <c r="L66" t="inlineStr"/>
+      <c r="L66" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -3135,7 +3137,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Mainstreet Research</t>
+          <t>Innovative Research</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -3145,25 +3147,23 @@
         <v>0</v>
       </c>
       <c r="F67" t="n">
-        <v>0.51</v>
+        <v>0.4</v>
       </c>
       <c r="G67" t="n">
-        <v>0.355</v>
+        <v>0.38</v>
       </c>
       <c r="H67" t="n">
-        <v>0.055</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I67" t="n">
-        <v>0.04</v>
+        <v>0.1</v>
       </c>
       <c r="J67" t="n">
-        <v>0.022</v>
-      </c>
-      <c r="K67" t="n">
-        <v>0.011</v>
-      </c>
+        <v>0.03</v>
+      </c>
+      <c r="K67" t="inlineStr"/>
       <c r="L67" t="n">
-        <v>0.006</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="68">
@@ -3173,11 +3173,11 @@
         </is>
       </c>
       <c r="B68" s="2" t="n">
-        <v>46053</v>
+        <v>46055</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Liaison Strategies</t>
+          <t>Mainstreet Research</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -3187,25 +3187,25 @@
         <v>0</v>
       </c>
       <c r="F68" t="n">
-        <v>0.43</v>
+        <v>0.51</v>
       </c>
       <c r="G68" t="n">
-        <v>0.35</v>
+        <v>0.355</v>
       </c>
       <c r="H68" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.055</v>
       </c>
       <c r="I68" t="n">
-        <v>0.08</v>
+        <v>0.04</v>
       </c>
       <c r="J68" t="n">
-        <v>0.03</v>
+        <v>0.022</v>
       </c>
       <c r="K68" t="n">
-        <v>0.02</v>
+        <v>0.006</v>
       </c>
       <c r="L68" t="n">
-        <v>0.02</v>
+        <v>0.011</v>
       </c>
     </row>
     <row r="69">
@@ -3215,11 +3215,11 @@
         </is>
       </c>
       <c r="B69" s="2" t="n">
-        <v>46052</v>
+        <v>46053</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Ekos</t>
+          <t>Liaison Strategies</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -3229,25 +3229,25 @@
         <v>0</v>
       </c>
       <c r="F69" t="n">
-        <v>0.444</v>
+        <v>0.43</v>
       </c>
       <c r="G69" t="n">
-        <v>0.295</v>
+        <v>0.35</v>
       </c>
       <c r="H69" t="n">
-        <v>0.053</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I69" t="n">
-        <v>0.138</v>
+        <v>0.08</v>
       </c>
       <c r="J69" t="n">
-        <v>0.039</v>
+        <v>0.03</v>
       </c>
       <c r="K69" t="n">
-        <v>0.015</v>
+        <v>0.02</v>
       </c>
       <c r="L69" t="n">
-        <v>0.016</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="70">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Nanos Research</t>
+          <t>Ekos</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -3271,23 +3271,25 @@
         <v>0</v>
       </c>
       <c r="F70" t="n">
-        <v>0.389</v>
+        <v>0.444</v>
       </c>
       <c r="G70" t="n">
-        <v>0.352</v>
+        <v>0.295</v>
       </c>
       <c r="H70" t="n">
-        <v>0.092</v>
+        <v>0.053</v>
       </c>
       <c r="I70" t="n">
-        <v>0.125</v>
+        <v>0.138</v>
       </c>
       <c r="J70" t="n">
-        <v>0.025</v>
-      </c>
-      <c r="K70" t="inlineStr"/>
+        <v>0.039</v>
+      </c>
+      <c r="K70" t="n">
+        <v>0.016</v>
+      </c>
       <c r="L70" t="n">
-        <v>0.013</v>
+        <v>0.015</v>
       </c>
     </row>
     <row r="71">
@@ -3297,11 +3299,11 @@
         </is>
       </c>
       <c r="B71" s="2" t="n">
-        <v>46049</v>
+        <v>46052</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Abacus Data</t>
+          <t>Nanos Research</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -3311,26 +3313,24 @@
         <v>0</v>
       </c>
       <c r="F71" t="n">
-        <v>0.43</v>
+        <v>0.389</v>
       </c>
       <c r="G71" t="n">
-        <v>0.39</v>
+        <v>0.352</v>
       </c>
       <c r="H71" t="n">
-        <v>0.06</v>
+        <v>0.092</v>
       </c>
       <c r="I71" t="n">
-        <v>0.08</v>
+        <v>0.125</v>
       </c>
       <c r="J71" t="n">
-        <v>0.02</v>
+        <v>0.025</v>
       </c>
       <c r="K71" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="L71" t="n">
-        <v>0.02</v>
-      </c>
+        <v>0.013</v>
+      </c>
+      <c r="L71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -3339,11 +3339,11 @@
         </is>
       </c>
       <c r="B72" s="2" t="n">
-        <v>46048</v>
+        <v>46049</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Léger</t>
+          <t>Abacus Data</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -3353,24 +3353,26 @@
         <v>0</v>
       </c>
       <c r="F72" t="n">
-        <v>0.47</v>
+        <v>0.43</v>
       </c>
       <c r="G72" t="n">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="H72" t="n">
         <v>0.06</v>
       </c>
       <c r="I72" t="n">
-        <v>0.05</v>
+        <v>0.08</v>
       </c>
       <c r="J72" t="n">
         <v>0.02</v>
       </c>
       <c r="K72" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="L72" t="inlineStr"/>
+        <v>0.02</v>
+      </c>
+      <c r="L72" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -3383,7 +3385,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Angus Reid</t>
+          <t>Léger</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -3393,24 +3395,24 @@
         <v>0</v>
       </c>
       <c r="F73" t="n">
-        <v>0.41</v>
+        <v>0.47</v>
       </c>
       <c r="G73" t="n">
         <v>0.38</v>
       </c>
       <c r="H73" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="I73" t="n">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="J73" t="n">
         <v>0.02</v>
       </c>
-      <c r="K73" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="L73" t="inlineStr"/>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -3419,11 +3421,11 @@
         </is>
       </c>
       <c r="B74" s="2" t="n">
-        <v>46046</v>
+        <v>46048</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Liaison Strategies</t>
+          <t>Angus Reid</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3433,23 +3435,21 @@
         <v>0</v>
       </c>
       <c r="F74" t="n">
-        <v>0.42</v>
+        <v>0.41</v>
       </c>
       <c r="G74" t="n">
-        <v>0.34</v>
+        <v>0.38</v>
       </c>
       <c r="H74" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I74" t="n">
         <v>0.1</v>
       </c>
       <c r="J74" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="K74" t="n">
-        <v>0.02</v>
-      </c>
+        <v>0.02</v>
+      </c>
+      <c r="K74" t="inlineStr"/>
       <c r="L74" t="n">
         <v>0.02</v>
       </c>
@@ -3461,11 +3461,11 @@
         </is>
       </c>
       <c r="B75" s="2" t="n">
-        <v>46045</v>
+        <v>46046</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Nanos Research</t>
+          <t>Liaison Strategies</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3475,23 +3475,25 @@
         <v>0</v>
       </c>
       <c r="F75" t="n">
-        <v>0.392</v>
+        <v>0.42</v>
       </c>
       <c r="G75" t="n">
-        <v>0.352</v>
+        <v>0.34</v>
       </c>
       <c r="H75" t="n">
         <v>0.08</v>
       </c>
       <c r="I75" t="n">
-        <v>0.116</v>
+        <v>0.1</v>
       </c>
       <c r="J75" t="n">
-        <v>0.036</v>
-      </c>
-      <c r="K75" t="inlineStr"/>
+        <v>0.03</v>
+      </c>
+      <c r="K75" t="n">
+        <v>0.02</v>
+      </c>
       <c r="L75" t="n">
-        <v>0.021</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="76">
@@ -3501,11 +3503,11 @@
         </is>
       </c>
       <c r="B76" s="2" t="n">
-        <v>46039</v>
+        <v>46045</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Liaison Strategies</t>
+          <t>Nanos Research</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3515,26 +3517,24 @@
         <v>0</v>
       </c>
       <c r="F76" t="n">
-        <v>0.4</v>
+        <v>0.392</v>
       </c>
       <c r="G76" t="n">
-        <v>0.35</v>
+        <v>0.352</v>
       </c>
       <c r="H76" t="n">
         <v>0.08</v>
       </c>
       <c r="I76" t="n">
-        <v>0.11</v>
+        <v>0.116</v>
       </c>
       <c r="J76" t="n">
-        <v>0.03</v>
+        <v>0.036</v>
       </c>
       <c r="K76" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="L76" t="n">
-        <v>0.01</v>
-      </c>
+        <v>0.021</v>
+      </c>
+      <c r="L76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -3543,11 +3543,11 @@
         </is>
       </c>
       <c r="B77" s="2" t="n">
-        <v>46038</v>
+        <v>46039</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Abacus Data</t>
+          <t>Liaison Strategies</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3557,16 +3557,16 @@
         <v>0</v>
       </c>
       <c r="F77" t="n">
-        <v>0.41</v>
+        <v>0.4</v>
       </c>
       <c r="G77" t="n">
-        <v>0.39</v>
+        <v>0.35</v>
       </c>
       <c r="H77" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="I77" t="n">
-        <v>0.08</v>
+        <v>0.11</v>
       </c>
       <c r="J77" t="n">
         <v>0.03</v>
@@ -3589,7 +3589,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Nanos Research</t>
+          <t>Abacus Data</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3599,23 +3599,25 @@
         <v>0</v>
       </c>
       <c r="F78" t="n">
-        <v>0.388</v>
+        <v>0.41</v>
       </c>
       <c r="G78" t="n">
-        <v>0.348</v>
+        <v>0.39</v>
       </c>
       <c r="H78" t="n">
-        <v>0.077</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I78" t="n">
-        <v>0.115</v>
+        <v>0.08</v>
       </c>
       <c r="J78" t="n">
-        <v>0.046</v>
-      </c>
-      <c r="K78" t="inlineStr"/>
+        <v>0.03</v>
+      </c>
+      <c r="K78" t="n">
+        <v>0.02</v>
+      </c>
       <c r="L78" t="n">
-        <v>0.024</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="79">
@@ -3625,11 +3627,11 @@
         </is>
       </c>
       <c r="B79" s="2" t="n">
-        <v>46036</v>
+        <v>46038</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Abacus Data</t>
+          <t>Nanos Research</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3639,26 +3641,24 @@
         <v>0</v>
       </c>
       <c r="F79" t="n">
-        <v>0.4</v>
+        <v>0.388</v>
       </c>
       <c r="G79" t="n">
-        <v>0.4</v>
+        <v>0.348</v>
       </c>
       <c r="H79" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.077</v>
       </c>
       <c r="I79" t="n">
-        <v>0.08</v>
+        <v>0.115</v>
       </c>
       <c r="J79" t="n">
-        <v>0.03</v>
+        <v>0.046</v>
       </c>
       <c r="K79" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="L79" t="n">
-        <v>0.01</v>
-      </c>
+        <v>0.024</v>
+      </c>
+      <c r="L79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -3667,11 +3667,11 @@
         </is>
       </c>
       <c r="B80" s="2" t="n">
-        <v>46034</v>
+        <v>46036</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Pallas Data</t>
+          <t>Abacus Data</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3684,21 +3684,23 @@
         <v>0.4</v>
       </c>
       <c r="G80" t="n">
-        <v>0.37</v>
+        <v>0.4</v>
       </c>
       <c r="H80" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="I80" t="n">
-        <v>0.11</v>
+        <v>0.08</v>
       </c>
       <c r="J80" t="n">
         <v>0.03</v>
       </c>
       <c r="K80" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="L80" t="inlineStr"/>
+        <v>0.01</v>
+      </c>
+      <c r="L80" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -3707,11 +3709,11 @@
         </is>
       </c>
       <c r="B81" s="2" t="n">
-        <v>46032</v>
+        <v>46034</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Liaison Strategies</t>
+          <t>Pallas Data</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3721,25 +3723,23 @@
         <v>0</v>
       </c>
       <c r="F81" t="n">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="G81" t="n">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="H81" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I81" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="J81" t="n">
         <v>0.03</v>
       </c>
-      <c r="K81" t="n">
-        <v>0.02</v>
-      </c>
+      <c r="K81" t="inlineStr"/>
       <c r="L81" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="82">
@@ -3749,11 +3749,11 @@
         </is>
       </c>
       <c r="B82" s="2" t="n">
-        <v>46031</v>
+        <v>46032</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Nanos Research</t>
+          <t>Liaison Strategies</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3763,23 +3763,25 @@
         <v>0</v>
       </c>
       <c r="F82" t="n">
-        <v>0.388</v>
+        <v>0.39</v>
       </c>
       <c r="G82" t="n">
-        <v>0.355</v>
+        <v>0.36</v>
       </c>
       <c r="H82" t="n">
-        <v>0.076</v>
+        <v>0.08</v>
       </c>
       <c r="I82" t="n">
-        <v>0.109</v>
+        <v>0.12</v>
       </c>
       <c r="J82" t="n">
-        <v>0.039</v>
-      </c>
-      <c r="K82" t="inlineStr"/>
+        <v>0.03</v>
+      </c>
+      <c r="K82" t="n">
+        <v>0.01</v>
+      </c>
       <c r="L82" t="n">
-        <v>0.021</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="83">
@@ -3789,11 +3791,11 @@
         </is>
       </c>
       <c r="B83" s="2" t="n">
-        <v>46025</v>
+        <v>46031</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Liaison Strategies</t>
+          <t>Nanos Research</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3803,26 +3805,24 @@
         <v>0</v>
       </c>
       <c r="F83" t="n">
-        <v>0.38</v>
+        <v>0.388</v>
       </c>
       <c r="G83" t="n">
-        <v>0.37</v>
+        <v>0.355</v>
       </c>
       <c r="H83" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.076</v>
       </c>
       <c r="I83" t="n">
-        <v>0.12</v>
+        <v>0.109</v>
       </c>
       <c r="J83" t="n">
-        <v>0.03</v>
+        <v>0.039</v>
       </c>
       <c r="K83" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="L83" t="n">
-        <v>0.01</v>
-      </c>
+        <v>0.021</v>
+      </c>
+      <c r="L83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -3831,11 +3831,11 @@
         </is>
       </c>
       <c r="B84" s="2" t="n">
-        <v>46024</v>
+        <v>46025</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Nanos Research</t>
+          <t>Liaison Strategies</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3845,23 +3845,25 @@
         <v>0</v>
       </c>
       <c r="F84" t="n">
-        <v>0.377</v>
+        <v>0.38</v>
       </c>
       <c r="G84" t="n">
-        <v>0.355</v>
+        <v>0.37</v>
       </c>
       <c r="H84" t="n">
-        <v>0.076</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I84" t="n">
-        <v>0.117</v>
+        <v>0.12</v>
       </c>
       <c r="J84" t="n">
-        <v>0.039</v>
-      </c>
-      <c r="K84" t="inlineStr"/>
+        <v>0.03</v>
+      </c>
+      <c r="K84" t="n">
+        <v>0.01</v>
+      </c>
       <c r="L84" t="n">
-        <v>0.019</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="85">
@@ -3871,11 +3873,11 @@
         </is>
       </c>
       <c r="B85" s="2" t="n">
-        <v>46019</v>
+        <v>46024</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Liaison Strategies</t>
+          <t>Nanos Research</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3885,26 +3887,24 @@
         <v>0</v>
       </c>
       <c r="F85" t="n">
-        <v>0.39</v>
+        <v>0.377</v>
       </c>
       <c r="G85" t="n">
-        <v>0.37</v>
+        <v>0.355</v>
       </c>
       <c r="H85" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.076</v>
       </c>
       <c r="I85" t="n">
-        <v>0.11</v>
+        <v>0.117</v>
       </c>
       <c r="J85" t="n">
-        <v>0.03</v>
+        <v>0.039</v>
       </c>
       <c r="K85" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="L85" t="n">
-        <v>0.02</v>
-      </c>
+        <v>0.019</v>
+      </c>
+      <c r="L85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -3913,11 +3913,11 @@
         </is>
       </c>
       <c r="B86" s="2" t="n">
-        <v>46017</v>
+        <v>46019</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Nanos Research</t>
+          <t>Liaison Strategies</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3927,23 +3927,25 @@
         <v>0</v>
       </c>
       <c r="F86" t="n">
-        <v>0.384</v>
+        <v>0.39</v>
       </c>
       <c r="G86" t="n">
-        <v>0.347</v>
+        <v>0.37</v>
       </c>
       <c r="H86" t="n">
-        <v>0.07400000000000001</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I86" t="n">
-        <v>0.113</v>
+        <v>0.11</v>
       </c>
       <c r="J86" t="n">
-        <v>0.039</v>
-      </c>
-      <c r="K86" t="inlineStr"/>
+        <v>0.03</v>
+      </c>
+      <c r="K86" t="n">
+        <v>0.02</v>
+      </c>
       <c r="L86" t="n">
-        <v>0.017</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="87">
@@ -3953,11 +3955,11 @@
         </is>
       </c>
       <c r="B87" s="2" t="n">
-        <v>46012</v>
+        <v>46017</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Liaison Strategies</t>
+          <t>Nanos Research</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3967,26 +3969,24 @@
         <v>0</v>
       </c>
       <c r="F87" t="n">
-        <v>0.38</v>
+        <v>0.384</v>
       </c>
       <c r="G87" t="n">
-        <v>0.38</v>
+        <v>0.347</v>
       </c>
       <c r="H87" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.07400000000000001</v>
       </c>
       <c r="I87" t="n">
-        <v>0.12</v>
+        <v>0.113</v>
       </c>
       <c r="J87" t="n">
-        <v>0.03</v>
+        <v>0.039</v>
       </c>
       <c r="K87" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="L87" t="n">
-        <v>0.02</v>
-      </c>
+        <v>0.017</v>
+      </c>
+      <c r="L87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -3995,11 +3995,11 @@
         </is>
       </c>
       <c r="B88" s="2" t="n">
-        <v>46010</v>
+        <v>46012</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Nanos Research</t>
+          <t>Liaison Strategies</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -4009,23 +4009,25 @@
         <v>0</v>
       </c>
       <c r="F88" t="n">
-        <v>0.363</v>
+        <v>0.38</v>
       </c>
       <c r="G88" t="n">
-        <v>0.356</v>
+        <v>0.38</v>
       </c>
       <c r="H88" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I88" t="n">
-        <v>0.114</v>
+        <v>0.12</v>
       </c>
       <c r="J88" t="n">
-        <v>0.035</v>
-      </c>
-      <c r="K88" t="inlineStr"/>
+        <v>0.03</v>
+      </c>
+      <c r="K88" t="n">
+        <v>0.02</v>
+      </c>
       <c r="L88" t="n">
-        <v>0.018</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="89">
@@ -4035,11 +4037,11 @@
         </is>
       </c>
       <c r="B89" s="2" t="n">
-        <v>46006</v>
+        <v>46010</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Pallas Data</t>
+          <t>Nanos Research</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -4049,22 +4051,22 @@
         <v>0</v>
       </c>
       <c r="F89" t="n">
-        <v>0.409</v>
+        <v>0.363</v>
       </c>
       <c r="G89" t="n">
-        <v>0.377</v>
+        <v>0.356</v>
       </c>
       <c r="H89" t="n">
-        <v>0.08199999999999999</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="I89" t="n">
-        <v>0.079</v>
+        <v>0.114</v>
       </c>
       <c r="J89" t="n">
-        <v>0.036</v>
+        <v>0.035</v>
       </c>
       <c r="K89" t="n">
-        <v>0.017</v>
+        <v>0.018</v>
       </c>
       <c r="L89" t="inlineStr"/>
     </row>
@@ -4079,7 +4081,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Ipsos</t>
+          <t>Pallas Data</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -4089,23 +4091,23 @@
         <v>0</v>
       </c>
       <c r="F90" t="n">
-        <v>0.4</v>
+        <v>0.409</v>
       </c>
       <c r="G90" t="n">
-        <v>0.37</v>
+        <v>0.377</v>
       </c>
       <c r="H90" t="n">
-        <v>0.09</v>
+        <v>0.08199999999999999</v>
       </c>
       <c r="I90" t="n">
-        <v>0.09</v>
+        <v>0.079</v>
       </c>
       <c r="J90" t="n">
-        <v>0.02</v>
+        <v>0.036</v>
       </c>
       <c r="K90" t="inlineStr"/>
       <c r="L90" t="n">
-        <v>0.02</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="91">
@@ -4115,11 +4117,11 @@
         </is>
       </c>
       <c r="B91" s="2" t="n">
-        <v>46005</v>
+        <v>46006</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Innovative Research</t>
+          <t>Ipsos</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -4129,19 +4131,19 @@
         <v>0</v>
       </c>
       <c r="F91" t="n">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="G91" t="n">
-        <v>0.39</v>
+        <v>0.37</v>
       </c>
       <c r="H91" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="I91" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="J91" t="n">
-        <v>0.04</v>
+        <v>0.02</v>
       </c>
       <c r="K91" t="n">
         <v>0.02</v>
@@ -4155,11 +4157,11 @@
         </is>
       </c>
       <c r="B92" s="2" t="n">
-        <v>46003</v>
+        <v>46005</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Mainstreet Research</t>
+          <t>Innovative Research</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -4169,25 +4171,23 @@
         <v>0</v>
       </c>
       <c r="F92" t="n">
-        <v>0.41</v>
+        <v>0.39</v>
       </c>
       <c r="G92" t="n">
-        <v>0.42</v>
+        <v>0.39</v>
       </c>
       <c r="H92" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="I92" t="n">
-        <v>0.06</v>
+        <v>0.1</v>
       </c>
       <c r="J92" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="K92" t="n">
-        <v>0.01</v>
-      </c>
+        <v>0.04</v>
+      </c>
+      <c r="K92" t="inlineStr"/>
       <c r="L92" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="93">
@@ -4201,7 +4201,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Nanos Research</t>
+          <t>Mainstreet Research</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -4211,23 +4211,25 @@
         <v>0</v>
       </c>
       <c r="F93" t="n">
-        <v>0.385</v>
+        <v>0.41</v>
       </c>
       <c r="G93" t="n">
-        <v>0.36</v>
+        <v>0.42</v>
       </c>
       <c r="H93" t="n">
-        <v>0.067</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I93" t="n">
-        <v>0.108</v>
+        <v>0.06</v>
       </c>
       <c r="J93" t="n">
-        <v>0.03700000000000001</v>
-      </c>
-      <c r="K93" t="inlineStr"/>
+        <v>0.01</v>
+      </c>
+      <c r="K93" t="n">
+        <v>0.01</v>
+      </c>
       <c r="L93" t="n">
-        <v>0.019</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="94">
@@ -4237,11 +4239,11 @@
         </is>
       </c>
       <c r="B94" s="2" t="n">
-        <v>46000</v>
+        <v>46003</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Abacus Data</t>
+          <t>Nanos Research</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -4251,26 +4253,24 @@
         <v>0</v>
       </c>
       <c r="F94" t="n">
-        <v>0.41</v>
+        <v>0.385</v>
       </c>
       <c r="G94" t="n">
-        <v>0.41</v>
+        <v>0.36</v>
       </c>
       <c r="H94" t="n">
-        <v>0.06</v>
+        <v>0.067</v>
       </c>
       <c r="I94" t="n">
-        <v>0.09</v>
+        <v>0.108</v>
       </c>
       <c r="J94" t="n">
-        <v>0.02</v>
+        <v>0.03700000000000001</v>
       </c>
       <c r="K94" t="n">
-        <v>0</v>
-      </c>
-      <c r="L94" t="n">
-        <v>0.01</v>
-      </c>
+        <v>0.019</v>
+      </c>
+      <c r="L94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -4279,11 +4279,11 @@
         </is>
       </c>
       <c r="B95" s="2" t="n">
-        <v>45996</v>
+        <v>46000</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Nanos Research</t>
+          <t>Abacus Data</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -4293,23 +4293,25 @@
         <v>0</v>
       </c>
       <c r="F95" t="n">
-        <v>0.391</v>
+        <v>0.41</v>
       </c>
       <c r="G95" t="n">
-        <v>0.3779999999999999</v>
+        <v>0.41</v>
       </c>
       <c r="H95" t="n">
-        <v>0.063</v>
+        <v>0.06</v>
       </c>
       <c r="I95" t="n">
-        <v>0.095</v>
+        <v>0.09</v>
       </c>
       <c r="J95" t="n">
-        <v>0.033</v>
-      </c>
-      <c r="K95" t="inlineStr"/>
+        <v>0.02</v>
+      </c>
+      <c r="K95" t="n">
+        <v>0.01</v>
+      </c>
       <c r="L95" t="n">
-        <v>0.018</v>
+        <v>0</v>
       </c>
     </row>
     <row r="96">
@@ -4319,11 +4321,11 @@
         </is>
       </c>
       <c r="B96" s="2" t="n">
-        <v>45992</v>
+        <v>45996</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Innovative Research</t>
+          <t>Nanos Research</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -4333,22 +4335,22 @@
         <v>0</v>
       </c>
       <c r="F96" t="n">
-        <v>0.39</v>
+        <v>0.391</v>
       </c>
       <c r="G96" t="n">
-        <v>0.38</v>
+        <v>0.3779999999999999</v>
       </c>
       <c r="H96" t="n">
-        <v>0.08</v>
+        <v>0.063</v>
       </c>
       <c r="I96" t="n">
-        <v>0.09</v>
+        <v>0.095</v>
       </c>
       <c r="J96" t="n">
-        <v>0.04</v>
+        <v>0.033</v>
       </c>
       <c r="K96" t="n">
-        <v>0.02</v>
+        <v>0.018</v>
       </c>
       <c r="L96" t="inlineStr"/>
     </row>
@@ -4363,7 +4365,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Abacus Data</t>
+          <t>Innovative Research</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -4373,25 +4375,23 @@
         <v>0</v>
       </c>
       <c r="F97" t="n">
-        <v>0.41</v>
+        <v>0.39</v>
       </c>
       <c r="G97" t="n">
-        <v>0.41</v>
+        <v>0.38</v>
       </c>
       <c r="H97" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="I97" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="J97" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="K97" t="n">
-        <v>0.01</v>
-      </c>
+        <v>0.04</v>
+      </c>
+      <c r="K97" t="inlineStr"/>
       <c r="L97" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="98">
@@ -4405,7 +4405,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Angus Reid</t>
+          <t>Abacus Data</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -4415,22 +4415,26 @@
         <v>0</v>
       </c>
       <c r="F98" t="n">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="G98" t="n">
-        <v>0.37</v>
+        <v>0.41</v>
       </c>
       <c r="H98" t="n">
-        <v>0.09</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I98" t="n">
-        <v>0.1</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="J98" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="K98" t="inlineStr"/>
-      <c r="L98" t="inlineStr"/>
+        <v>0.02</v>
+      </c>
+      <c r="K98" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L98" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -4439,11 +4443,11 @@
         </is>
       </c>
       <c r="B99" s="2" t="n">
-        <v>45991</v>
+        <v>45992</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Léger</t>
+          <t>Angus Reid</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -4453,23 +4457,21 @@
         <v>0</v>
       </c>
       <c r="F99" t="n">
-        <v>0.43</v>
+        <v>0.4</v>
       </c>
       <c r="G99" t="n">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="H99" t="n">
         <v>0.09</v>
       </c>
       <c r="I99" t="n">
-        <v>0.08</v>
+        <v>0.1</v>
       </c>
       <c r="J99" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="K99" t="n">
-        <v>0.01</v>
-      </c>
+        <v>0.03</v>
+      </c>
+      <c r="K99" t="inlineStr"/>
       <c r="L99" t="inlineStr"/>
     </row>
     <row r="100">
@@ -4483,7 +4485,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Liaison Strategies</t>
+          <t>Léger</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -4493,25 +4495,23 @@
         <v>0</v>
       </c>
       <c r="F100" t="n">
-        <v>0.41</v>
+        <v>0.43</v>
       </c>
       <c r="G100" t="n">
         <v>0.36</v>
       </c>
       <c r="H100" t="n">
-        <v>0.05</v>
+        <v>0.09</v>
       </c>
       <c r="I100" t="n">
-        <v>0.12</v>
+        <v>0.08</v>
       </c>
       <c r="J100" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="K100" t="n">
-        <v>0.01</v>
-      </c>
+        <v>0.04</v>
+      </c>
+      <c r="K100" t="inlineStr"/>
       <c r="L100" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="101">
@@ -4521,11 +4521,11 @@
         </is>
       </c>
       <c r="B101" s="2" t="n">
-        <v>45989</v>
+        <v>45991</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Nanos Research</t>
+          <t>Liaison Strategies</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -4535,25 +4535,25 @@
         <v>0</v>
       </c>
       <c r="F101" t="n">
-        <v>0.419</v>
+        <v>0.41</v>
       </c>
       <c r="G101" t="n">
-        <v>0.382</v>
+        <v>0.36</v>
       </c>
       <c r="H101" t="n">
-        <v>0.073</v>
+        <v>0.05</v>
       </c>
       <c r="I101" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.12</v>
       </c>
       <c r="J101" t="n">
-        <v>0.027</v>
+        <v>0.02</v>
       </c>
       <c r="K101" t="n">
-        <v>0.003</v>
+        <v>0.02</v>
       </c>
       <c r="L101" t="n">
-        <v>0.012</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="102">
@@ -4563,11 +4563,11 @@
         </is>
       </c>
       <c r="B102" s="2" t="n">
-        <v>45988</v>
+        <v>45989</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Abacus Data</t>
+          <t>Nanos Research</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -4577,25 +4577,25 @@
         <v>0</v>
       </c>
       <c r="F102" t="n">
-        <v>0.41</v>
+        <v>0.419</v>
       </c>
       <c r="G102" t="n">
-        <v>0.4</v>
+        <v>0.382</v>
       </c>
       <c r="H102" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.073</v>
       </c>
       <c r="I102" t="n">
-        <v>0.08</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="J102" t="n">
-        <v>0.02</v>
+        <v>0.027</v>
       </c>
       <c r="K102" t="n">
-        <v>0.01</v>
+        <v>0.012</v>
       </c>
       <c r="L102" t="n">
-        <v>0.01</v>
+        <v>0.003</v>
       </c>
     </row>
     <row r="103">
@@ -4605,11 +4605,11 @@
         </is>
       </c>
       <c r="B103" s="2" t="n">
-        <v>45982</v>
+        <v>45988</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Nanos Research</t>
+          <t>Abacus Data</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4619,25 +4619,25 @@
         <v>0</v>
       </c>
       <c r="F103" t="n">
-        <v>0.419</v>
+        <v>0.41</v>
       </c>
       <c r="G103" t="n">
-        <v>0.3720000000000001</v>
+        <v>0.4</v>
       </c>
       <c r="H103" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="I103" t="n">
-        <v>0.091</v>
+        <v>0.08</v>
       </c>
       <c r="J103" t="n">
-        <v>0.027</v>
+        <v>0.02</v>
       </c>
       <c r="K103" t="n">
-        <v>0.005</v>
+        <v>0.01</v>
       </c>
       <c r="L103" t="n">
-        <v>0.016</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="104">
@@ -4647,11 +4647,11 @@
         </is>
       </c>
       <c r="B104" s="2" t="n">
-        <v>45979</v>
+        <v>45982</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Kolosowski Strategies</t>
+          <t>Nanos Research</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4661,25 +4661,25 @@
         <v>0</v>
       </c>
       <c r="F104" t="n">
-        <v>0.44</v>
+        <v>0.419</v>
       </c>
       <c r="G104" t="n">
-        <v>0.44</v>
+        <v>0.3720000000000001</v>
       </c>
       <c r="H104" t="n">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I104" t="n">
-        <v>0.03</v>
+        <v>0.091</v>
       </c>
       <c r="J104" t="n">
-        <v>0.01</v>
+        <v>0.027</v>
       </c>
       <c r="K104" t="n">
-        <v>0</v>
+        <v>0.016</v>
       </c>
       <c r="L104" t="n">
-        <v>0.01</v>
+        <v>0.005</v>
       </c>
     </row>
     <row r="105">
@@ -4689,11 +4689,11 @@
         </is>
       </c>
       <c r="B105" s="2" t="n">
-        <v>45975</v>
+        <v>45979</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Nanos Research</t>
+          <t>Kolosowski Strategies</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4703,25 +4703,25 @@
         <v>0</v>
       </c>
       <c r="F105" t="n">
-        <v>0.402</v>
+        <v>0.44</v>
       </c>
       <c r="G105" t="n">
-        <v>0.382</v>
+        <v>0.44</v>
       </c>
       <c r="H105" t="n">
-        <v>0.07400000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="I105" t="n">
-        <v>0.101</v>
+        <v>0.03</v>
       </c>
       <c r="J105" t="n">
-        <v>0.022</v>
+        <v>0.01</v>
       </c>
       <c r="K105" t="n">
-        <v>0.008</v>
+        <v>0.01</v>
       </c>
       <c r="L105" t="n">
-        <v>0.013</v>
+        <v>0</v>
       </c>
     </row>
     <row r="106">
@@ -4731,11 +4731,11 @@
         </is>
       </c>
       <c r="B106" s="2" t="n">
-        <v>45972</v>
+        <v>45975</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Ekos</t>
+          <t>Nanos Research</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4745,25 +4745,25 @@
         <v>0</v>
       </c>
       <c r="F106" t="n">
-        <v>0.441</v>
+        <v>0.402</v>
       </c>
       <c r="G106" t="n">
-        <v>0.332</v>
+        <v>0.382</v>
       </c>
       <c r="H106" t="n">
-        <v>0.05400000000000001</v>
+        <v>0.07400000000000001</v>
       </c>
       <c r="I106" t="n">
-        <v>0.107</v>
+        <v>0.101</v>
       </c>
       <c r="J106" t="n">
-        <v>0.033</v>
+        <v>0.022</v>
       </c>
       <c r="K106" t="n">
-        <v>0.014</v>
+        <v>0.013</v>
       </c>
       <c r="L106" t="n">
-        <v>0.018</v>
+        <v>0.008</v>
       </c>
     </row>
     <row r="107">
@@ -4773,11 +4773,11 @@
         </is>
       </c>
       <c r="B107" s="2" t="n">
-        <v>45969</v>
+        <v>45972</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Mainstreet Research</t>
+          <t>Ekos</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4787,25 +4787,25 @@
         <v>0</v>
       </c>
       <c r="F107" t="n">
-        <v>0.44</v>
+        <v>0.441</v>
       </c>
       <c r="G107" t="n">
-        <v>0.4</v>
+        <v>0.332</v>
       </c>
       <c r="H107" t="n">
-        <v>0.06</v>
+        <v>0.05400000000000001</v>
       </c>
       <c r="I107" t="n">
-        <v>0.05</v>
+        <v>0.107</v>
       </c>
       <c r="J107" t="n">
-        <v>0.02</v>
+        <v>0.033</v>
       </c>
       <c r="K107" t="n">
-        <v>0.02</v>
+        <v>0.018</v>
       </c>
       <c r="L107" t="n">
-        <v>0.02</v>
+        <v>0.014</v>
       </c>
     </row>
     <row r="108">
@@ -4819,7 +4819,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Liaison Strategies</t>
+          <t>Mainstreet Research</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4832,22 +4832,22 @@
         <v>0.44</v>
       </c>
       <c r="G108" t="n">
-        <v>0.36</v>
+        <v>0.4</v>
       </c>
       <c r="H108" t="n">
         <v>0.06</v>
       </c>
       <c r="I108" t="n">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="J108" t="n">
         <v>0.02</v>
       </c>
       <c r="K108" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="L108" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="109">
@@ -4857,11 +4857,11 @@
         </is>
       </c>
       <c r="B109" s="2" t="n">
-        <v>45968</v>
+        <v>45969</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Angus Reid</t>
+          <t>Liaison Strategies</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4871,22 +4871,26 @@
         <v>0</v>
       </c>
       <c r="F109" t="n">
-        <v>0.4</v>
+        <v>0.44</v>
       </c>
       <c r="G109" t="n">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="H109" t="n">
-        <v>0.08</v>
+        <v>0.06</v>
       </c>
       <c r="I109" t="n">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
       <c r="J109" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="K109" t="inlineStr"/>
-      <c r="L109" t="inlineStr"/>
+        <v>0.02</v>
+      </c>
+      <c r="K109" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L109" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -4899,7 +4903,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Nanos Research</t>
+          <t>Angus Reid</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4912,23 +4916,19 @@
         <v>0.4</v>
       </c>
       <c r="G110" t="n">
-        <v>0.368</v>
+        <v>0.38</v>
       </c>
       <c r="H110" t="n">
-        <v>0.075</v>
+        <v>0.08</v>
       </c>
       <c r="I110" t="n">
-        <v>0.114</v>
+        <v>0.09</v>
       </c>
       <c r="J110" t="n">
-        <v>0.023</v>
-      </c>
-      <c r="K110" t="n">
-        <v>0.008</v>
-      </c>
-      <c r="L110" t="n">
-        <v>0.012</v>
-      </c>
+        <v>0.03</v>
+      </c>
+      <c r="K110" t="inlineStr"/>
+      <c r="L110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -4937,11 +4937,11 @@
         </is>
       </c>
       <c r="B111" s="2" t="n">
-        <v>45967</v>
+        <v>45968</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Abacus Data</t>
+          <t>Nanos Research</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4954,22 +4954,22 @@
         <v>0.4</v>
       </c>
       <c r="G111" t="n">
-        <v>0.41</v>
+        <v>0.368</v>
       </c>
       <c r="H111" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.075</v>
       </c>
       <c r="I111" t="n">
-        <v>0.08</v>
+        <v>0.114</v>
       </c>
       <c r="J111" t="n">
-        <v>0.02</v>
+        <v>0.023</v>
       </c>
       <c r="K111" t="n">
-        <v>0</v>
+        <v>0.012</v>
       </c>
       <c r="L111" t="n">
-        <v>0.01</v>
+        <v>0.008</v>
       </c>
     </row>
     <row r="112">
@@ -4979,11 +4979,11 @@
         </is>
       </c>
       <c r="B112" s="2" t="n">
-        <v>45965</v>
+        <v>45967</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Ekos</t>
+          <t>Abacus Data</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4993,25 +4993,25 @@
         <v>0</v>
       </c>
       <c r="F112" t="n">
-        <v>0.434</v>
+        <v>0.4</v>
       </c>
       <c r="G112" t="n">
-        <v>0.355</v>
+        <v>0.41</v>
       </c>
       <c r="H112" t="n">
-        <v>0.058</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I112" t="n">
         <v>0.08</v>
       </c>
       <c r="J112" t="n">
-        <v>0.035</v>
+        <v>0.02</v>
       </c>
       <c r="K112" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="L112" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
     </row>
     <row r="113">
@@ -5025,7 +5025,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Liaison Strategies</t>
+          <t>Ekos</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -5035,25 +5035,25 @@
         <v>0</v>
       </c>
       <c r="F113" t="n">
-        <v>0.42</v>
+        <v>0.434</v>
       </c>
       <c r="G113" t="n">
-        <v>0.38</v>
+        <v>0.355</v>
       </c>
       <c r="H113" t="n">
-        <v>0.05</v>
+        <v>0.058</v>
       </c>
       <c r="I113" t="n">
-        <v>0.11</v>
+        <v>0.08</v>
       </c>
       <c r="J113" t="n">
-        <v>0.02</v>
+        <v>0.035</v>
       </c>
       <c r="K113" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="L113" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="114">
@@ -5063,11 +5063,11 @@
         </is>
       </c>
       <c r="B114" s="2" t="n">
-        <v>45964</v>
+        <v>45965</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Léger</t>
+          <t>Liaison Strategies</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -5077,24 +5077,26 @@
         <v>0</v>
       </c>
       <c r="F114" t="n">
-        <v>0.43</v>
+        <v>0.42</v>
       </c>
       <c r="G114" t="n">
         <v>0.38</v>
       </c>
       <c r="H114" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.05</v>
       </c>
       <c r="I114" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.11</v>
       </c>
       <c r="J114" t="n">
-        <v>0.04</v>
+        <v>0.02</v>
       </c>
       <c r="K114" t="n">
         <v>0.01</v>
       </c>
-      <c r="L114" t="inlineStr"/>
+      <c r="L114" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -5103,11 +5105,11 @@
         </is>
       </c>
       <c r="B115" s="2" t="n">
-        <v>45961</v>
+        <v>45964</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Nanos Research</t>
+          <t>Léger</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -5117,25 +5119,23 @@
         <v>0</v>
       </c>
       <c r="F115" t="n">
-        <v>0.393</v>
+        <v>0.43</v>
       </c>
       <c r="G115" t="n">
-        <v>0.371</v>
+        <v>0.38</v>
       </c>
       <c r="H115" t="n">
-        <v>0.066</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I115" t="n">
-        <v>0.125</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="J115" t="n">
-        <v>0.017</v>
-      </c>
-      <c r="K115" t="n">
-        <v>0</v>
-      </c>
+        <v>0.04</v>
+      </c>
+      <c r="K115" t="inlineStr"/>
       <c r="L115" t="n">
-        <v>0.015</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="116">
@@ -5145,11 +5145,11 @@
         </is>
       </c>
       <c r="B116" s="2" t="n">
-        <v>45959</v>
+        <v>45961</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Abacus Data</t>
+          <t>Nanos Research</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -5159,25 +5159,25 @@
         <v>0</v>
       </c>
       <c r="F116" t="n">
-        <v>0.4</v>
+        <v>0.393</v>
       </c>
       <c r="G116" t="n">
-        <v>0.42</v>
+        <v>0.371</v>
       </c>
       <c r="H116" t="n">
-        <v>0.06</v>
+        <v>0.066</v>
       </c>
       <c r="I116" t="n">
-        <v>0.08</v>
+        <v>0.125</v>
       </c>
       <c r="J116" t="n">
-        <v>0.03</v>
+        <v>0.017</v>
       </c>
       <c r="K116" t="n">
-        <v>0.01</v>
+        <v>0.015</v>
       </c>
       <c r="L116" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
     </row>
     <row r="117">
@@ -5187,11 +5187,11 @@
         </is>
       </c>
       <c r="B117" s="2" t="n">
-        <v>45954</v>
+        <v>45959</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Nanos Research</t>
+          <t>Abacus Data</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -5201,25 +5201,25 @@
         <v>0</v>
       </c>
       <c r="F117" t="n">
-        <v>0.394</v>
+        <v>0.4</v>
       </c>
       <c r="G117" t="n">
-        <v>0.37</v>
+        <v>0.42</v>
       </c>
       <c r="H117" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="I117" t="n">
-        <v>0.127</v>
+        <v>0.08</v>
       </c>
       <c r="J117" t="n">
-        <v>0.016</v>
+        <v>0.03</v>
       </c>
       <c r="K117" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="L117" t="n">
-        <v>0.012</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="118">
@@ -5233,7 +5233,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Ekos</t>
+          <t>Nanos Research</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -5243,25 +5243,25 @@
         <v>0</v>
       </c>
       <c r="F118" t="n">
-        <v>0.435</v>
+        <v>0.394</v>
       </c>
       <c r="G118" t="n">
-        <v>0.324</v>
+        <v>0.37</v>
       </c>
       <c r="H118" t="n">
-        <v>0.057</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I118" t="n">
-        <v>0.124</v>
+        <v>0.127</v>
       </c>
       <c r="J118" t="n">
-        <v>0.03</v>
+        <v>0.016</v>
       </c>
       <c r="K118" t="n">
-        <v>0.01</v>
+        <v>0.012</v>
       </c>
       <c r="L118" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
     </row>
     <row r="119">
@@ -5271,11 +5271,11 @@
         </is>
       </c>
       <c r="B119" s="2" t="n">
-        <v>45947</v>
+        <v>45954</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Nanos Research</t>
+          <t>Ekos</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -5285,25 +5285,25 @@
         <v>0</v>
       </c>
       <c r="F119" t="n">
-        <v>0.393</v>
+        <v>0.435</v>
       </c>
       <c r="G119" t="n">
-        <v>0.366</v>
+        <v>0.324</v>
       </c>
       <c r="H119" t="n">
-        <v>0.068</v>
+        <v>0.057</v>
       </c>
       <c r="I119" t="n">
-        <v>0.121</v>
+        <v>0.124</v>
       </c>
       <c r="J119" t="n">
-        <v>0.028</v>
+        <v>0.03</v>
       </c>
       <c r="K119" t="n">
-        <v>0.011</v>
+        <v>0.02</v>
       </c>
       <c r="L119" t="n">
-        <v>0.013</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="120">
@@ -5313,11 +5313,11 @@
         </is>
       </c>
       <c r="B120" s="2" t="n">
-        <v>45945</v>
+        <v>45947</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Abacus Data</t>
+          <t>Nanos Research</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -5327,25 +5327,25 @@
         <v>0</v>
       </c>
       <c r="F120" t="n">
-        <v>0.4</v>
+        <v>0.393</v>
       </c>
       <c r="G120" t="n">
-        <v>0.41</v>
+        <v>0.366</v>
       </c>
       <c r="H120" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.068</v>
       </c>
       <c r="I120" t="n">
-        <v>0.08</v>
+        <v>0.121</v>
       </c>
       <c r="J120" t="n">
-        <v>0.03</v>
+        <v>0.028</v>
       </c>
       <c r="K120" t="n">
-        <v>0.01</v>
+        <v>0.013</v>
       </c>
       <c r="L120" t="n">
-        <v>0.01</v>
+        <v>0.011</v>
       </c>
     </row>
     <row r="121">
@@ -5359,7 +5359,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Pallas Data</t>
+          <t>Abacus Data</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -5369,25 +5369,25 @@
         <v>0</v>
       </c>
       <c r="F121" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G121" t="n">
         <v>0.41</v>
       </c>
-      <c r="G121" t="n">
-        <v>0.37</v>
-      </c>
       <c r="H121" t="n">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I121" t="n">
-        <v>0.11</v>
+        <v>0.08</v>
       </c>
       <c r="J121" t="n">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="K121" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="L121" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="122">
@@ -5397,11 +5397,11 @@
         </is>
       </c>
       <c r="B122" s="2" t="n">
-        <v>45940</v>
+        <v>45945</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Nanos Research</t>
+          <t>Pallas Data</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -5411,25 +5411,25 @@
         <v>0</v>
       </c>
       <c r="F122" t="n">
-        <v>0.385</v>
+        <v>0.41</v>
       </c>
       <c r="G122" t="n">
-        <v>0.368</v>
+        <v>0.37</v>
       </c>
       <c r="H122" t="n">
-        <v>0.065</v>
+        <v>0.06</v>
       </c>
       <c r="I122" t="n">
-        <v>0.122</v>
+        <v>0.11</v>
       </c>
       <c r="J122" t="n">
-        <v>0.039</v>
+        <v>0.02</v>
       </c>
       <c r="K122" t="n">
-        <v>0.006999999999999999</v>
+        <v>0.02</v>
       </c>
       <c r="L122" t="n">
-        <v>0.014</v>
+        <v>0</v>
       </c>
     </row>
     <row r="123">
@@ -5439,11 +5439,11 @@
         </is>
       </c>
       <c r="B123" s="2" t="n">
-        <v>45935</v>
+        <v>45940</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Léger</t>
+          <t>Nanos Research</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -5453,24 +5453,26 @@
         <v>0</v>
       </c>
       <c r="F123" t="n">
-        <v>0.44</v>
+        <v>0.385</v>
       </c>
       <c r="G123" t="n">
-        <v>0.38</v>
+        <v>0.368</v>
       </c>
       <c r="H123" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.065</v>
       </c>
       <c r="I123" t="n">
-        <v>0.06</v>
+        <v>0.122</v>
       </c>
       <c r="J123" t="n">
-        <v>0.03</v>
+        <v>0.039</v>
       </c>
       <c r="K123" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="L123" t="inlineStr"/>
+        <v>0.014</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.006999999999999999</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -5479,11 +5481,11 @@
         </is>
       </c>
       <c r="B124" s="2" t="n">
-        <v>45933</v>
+        <v>45935</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Nanos Research</t>
+          <t>Léger</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -5493,25 +5495,23 @@
         <v>0</v>
       </c>
       <c r="F124" t="n">
-        <v>0.391</v>
+        <v>0.44</v>
       </c>
       <c r="G124" t="n">
-        <v>0.379</v>
+        <v>0.38</v>
       </c>
       <c r="H124" t="n">
-        <v>0.062</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I124" t="n">
-        <v>0.115</v>
+        <v>0.06</v>
       </c>
       <c r="J124" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="K124" t="n">
-        <v>0.004</v>
-      </c>
+        <v>0.03</v>
+      </c>
+      <c r="K124" t="inlineStr"/>
       <c r="L124" t="n">
-        <v>0.009000000000000001</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="125">
@@ -5521,11 +5521,11 @@
         </is>
       </c>
       <c r="B125" s="2" t="n">
-        <v>45931</v>
+        <v>45933</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Abacus Data</t>
+          <t>Nanos Research</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -5535,25 +5535,25 @@
         <v>0</v>
       </c>
       <c r="F125" t="n">
-        <v>0.4</v>
+        <v>0.391</v>
       </c>
       <c r="G125" t="n">
-        <v>0.41</v>
+        <v>0.379</v>
       </c>
       <c r="H125" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.062</v>
       </c>
       <c r="I125" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.115</v>
       </c>
       <c r="J125" t="n">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="K125" t="n">
-        <v>0.01</v>
+        <v>0.009000000000000001</v>
       </c>
       <c r="L125" t="n">
-        <v>0.02</v>
+        <v>0.004</v>
       </c>
     </row>
     <row r="126">
@@ -5563,11 +5563,11 @@
         </is>
       </c>
       <c r="B126" s="2" t="n">
-        <v>45926</v>
+        <v>45931</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Nanos Research</t>
+          <t>Abacus Data</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -5577,25 +5577,25 @@
         <v>0</v>
       </c>
       <c r="F126" t="n">
-        <v>0.407</v>
+        <v>0.4</v>
       </c>
       <c r="G126" t="n">
-        <v>0.366</v>
+        <v>0.41</v>
       </c>
       <c r="H126" t="n">
-        <v>0.048</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I126" t="n">
-        <v>0.119</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="J126" t="n">
-        <v>0.043</v>
+        <v>0.03</v>
       </c>
       <c r="K126" t="n">
-        <v>0.005</v>
+        <v>0.02</v>
       </c>
       <c r="L126" t="n">
-        <v>0.012</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="127">
@@ -5605,11 +5605,11 @@
         </is>
       </c>
       <c r="B127" s="2" t="n">
-        <v>45922</v>
+        <v>45926</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Angus Reid</t>
+          <t>Nanos Research</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -5619,25 +5619,25 @@
         <v>0</v>
       </c>
       <c r="F127" t="n">
-        <v>0.38</v>
+        <v>0.407</v>
       </c>
       <c r="G127" t="n">
-        <v>0.41</v>
+        <v>0.366</v>
       </c>
       <c r="H127" t="n">
-        <v>0.08</v>
+        <v>0.048</v>
       </c>
       <c r="I127" t="n">
-        <v>0.1</v>
+        <v>0.119</v>
       </c>
       <c r="J127" t="n">
-        <v>0.02</v>
+        <v>0.043</v>
       </c>
       <c r="K127" t="n">
-        <v>0.01</v>
+        <v>0.012</v>
       </c>
       <c r="L127" t="n">
-        <v>0.01</v>
+        <v>0.005</v>
       </c>
     </row>
     <row r="128">
@@ -5647,11 +5647,11 @@
         </is>
       </c>
       <c r="B128" s="2" t="n">
-        <v>45921</v>
+        <v>45922</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Liaison Strategies</t>
+          <t>Angus Reid</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -5661,13 +5661,13 @@
         <v>0</v>
       </c>
       <c r="F128" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="G128" t="n">
-        <v>0.37</v>
+        <v>0.41</v>
       </c>
       <c r="H128" t="n">
-        <v>0.05</v>
+        <v>0.08</v>
       </c>
       <c r="I128" t="n">
         <v>0.1</v>
@@ -5679,7 +5679,7 @@
         <v>0.01</v>
       </c>
       <c r="L128" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="129">
@@ -5689,11 +5689,11 @@
         </is>
       </c>
       <c r="B129" s="2" t="n">
-        <v>45919</v>
+        <v>45921</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Nanos Research</t>
+          <t>Liaison Strategies</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -5703,25 +5703,25 @@
         <v>0</v>
       </c>
       <c r="F129" t="n">
-        <v>0.406</v>
+        <v>0.43</v>
       </c>
       <c r="G129" t="n">
-        <v>0.357</v>
+        <v>0.37</v>
       </c>
       <c r="H129" t="n">
-        <v>0.055</v>
+        <v>0.05</v>
       </c>
       <c r="I129" t="n">
-        <v>0.116</v>
+        <v>0.1</v>
       </c>
       <c r="J129" t="n">
-        <v>0.032</v>
+        <v>0.02</v>
       </c>
       <c r="K129" t="n">
-        <v>0.012</v>
+        <v>0.02</v>
       </c>
       <c r="L129" t="n">
-        <v>0.022</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="130">
@@ -5731,11 +5731,11 @@
         </is>
       </c>
       <c r="B130" s="2" t="n">
-        <v>45917</v>
+        <v>45919</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Abacus Data</t>
+          <t>Nanos Research</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -5745,25 +5745,25 @@
         <v>0</v>
       </c>
       <c r="F130" t="n">
-        <v>0.4</v>
+        <v>0.406</v>
       </c>
       <c r="G130" t="n">
-        <v>0.4</v>
+        <v>0.357</v>
       </c>
       <c r="H130" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.055</v>
       </c>
       <c r="I130" t="n">
-        <v>0.08</v>
+        <v>0.116</v>
       </c>
       <c r="J130" t="n">
-        <v>0.03</v>
+        <v>0.032</v>
       </c>
       <c r="K130" t="n">
-        <v>0.01</v>
+        <v>0.022</v>
       </c>
       <c r="L130" t="n">
-        <v>0.01</v>
+        <v>0.012</v>
       </c>
     </row>
     <row r="131">
@@ -5773,11 +5773,11 @@
         </is>
       </c>
       <c r="B131" s="2" t="n">
-        <v>45912</v>
+        <v>45917</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Research Co.</t>
+          <t>Abacus Data</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5787,19 +5787,19 @@
         <v>0</v>
       </c>
       <c r="F131" t="n">
-        <v>0.43</v>
+        <v>0.4</v>
       </c>
       <c r="G131" t="n">
-        <v>0.38</v>
+        <v>0.4</v>
       </c>
       <c r="H131" t="n">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I131" t="n">
         <v>0.08</v>
       </c>
       <c r="J131" t="n">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="K131" t="n">
         <v>0.01</v>
@@ -5819,7 +5819,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Nanos Research</t>
+          <t>Research Co.</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5829,25 +5829,25 @@
         <v>0</v>
       </c>
       <c r="F132" t="n">
-        <v>0.418</v>
+        <v>0.43</v>
       </c>
       <c r="G132" t="n">
-        <v>0.345</v>
+        <v>0.38</v>
       </c>
       <c r="H132" t="n">
-        <v>0.055</v>
+        <v>0.06</v>
       </c>
       <c r="I132" t="n">
-        <v>0.128</v>
+        <v>0.08</v>
       </c>
       <c r="J132" t="n">
-        <v>0.025</v>
+        <v>0.02</v>
       </c>
       <c r="K132" t="n">
         <v>0.01</v>
       </c>
       <c r="L132" t="n">
-        <v>0.019</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="133">
@@ -5861,7 +5861,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Ekos</t>
+          <t>Nanos Research</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5871,25 +5871,25 @@
         <v>0</v>
       </c>
       <c r="F133" t="n">
-        <v>0.42</v>
+        <v>0.418</v>
       </c>
       <c r="G133" t="n">
-        <v>0.34</v>
+        <v>0.345</v>
       </c>
       <c r="H133" t="n">
-        <v>0.052</v>
+        <v>0.055</v>
       </c>
       <c r="I133" t="n">
-        <v>0.126</v>
+        <v>0.128</v>
       </c>
       <c r="J133" t="n">
-        <v>0.03</v>
+        <v>0.025</v>
       </c>
       <c r="K133" t="n">
-        <v>0.01</v>
+        <v>0.019</v>
       </c>
       <c r="L133" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="134">
@@ -5899,11 +5899,11 @@
         </is>
       </c>
       <c r="B134" s="2" t="n">
-        <v>45908</v>
+        <v>45912</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Ipsos</t>
+          <t>Ekos</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5913,25 +5913,25 @@
         <v>0</v>
       </c>
       <c r="F134" t="n">
-        <v>0.43</v>
+        <v>0.42</v>
       </c>
       <c r="G134" t="n">
-        <v>0.39</v>
+        <v>0.34</v>
       </c>
       <c r="H134" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.052</v>
       </c>
       <c r="I134" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.126</v>
       </c>
       <c r="J134" t="n">
-        <v>0.01</v>
+        <v>0.03</v>
       </c>
       <c r="K134" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="L134" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="135">
@@ -5941,11 +5941,11 @@
         </is>
       </c>
       <c r="B135" s="2" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Léger</t>
+          <t>Ipsos</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5955,24 +5955,26 @@
         <v>0</v>
       </c>
       <c r="F135" t="n">
-        <v>0.47</v>
+        <v>0.43</v>
       </c>
       <c r="G135" t="n">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="H135" t="n">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I135" t="n">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="J135" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="K135" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="L135" t="inlineStr"/>
+        <v>0.02</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -5981,11 +5983,11 @@
         </is>
       </c>
       <c r="B136" s="2" t="n">
-        <v>45905</v>
+        <v>45907</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Nanos Research</t>
+          <t>Léger</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5995,25 +5997,23 @@
         <v>0</v>
       </c>
       <c r="F136" t="n">
-        <v>0.427</v>
+        <v>0.47</v>
       </c>
       <c r="G136" t="n">
-        <v>0.329</v>
+        <v>0.38</v>
       </c>
       <c r="H136" t="n">
-        <v>0.052</v>
+        <v>0.06</v>
       </c>
       <c r="I136" t="n">
-        <v>0.128</v>
+        <v>0.06</v>
       </c>
       <c r="J136" t="n">
-        <v>0.035</v>
-      </c>
-      <c r="K136" t="n">
-        <v>0.013</v>
-      </c>
+        <v>0.02</v>
+      </c>
+      <c r="K136" t="inlineStr"/>
       <c r="L136" t="n">
-        <v>0.016</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="137">
@@ -6023,11 +6023,11 @@
         </is>
       </c>
       <c r="B137" s="2" t="n">
-        <v>45904</v>
+        <v>45905</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Angus Reid</t>
+          <t>Nanos Research</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -6037,25 +6037,25 @@
         <v>0</v>
       </c>
       <c r="F137" t="n">
-        <v>0.38</v>
+        <v>0.427</v>
       </c>
       <c r="G137" t="n">
-        <v>0.4</v>
+        <v>0.329</v>
       </c>
       <c r="H137" t="n">
-        <v>0.08</v>
+        <v>0.052</v>
       </c>
       <c r="I137" t="n">
-        <v>0.1</v>
+        <v>0.128</v>
       </c>
       <c r="J137" t="n">
-        <v>0.02</v>
+        <v>0.035</v>
       </c>
       <c r="K137" t="n">
-        <v>0.02</v>
+        <v>0.016</v>
       </c>
       <c r="L137" t="n">
-        <v>0.01</v>
+        <v>0.013</v>
       </c>
     </row>
     <row r="138">
@@ -6065,11 +6065,11 @@
         </is>
       </c>
       <c r="B138" s="2" t="n">
-        <v>45902</v>
+        <v>45904</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Abacus Data</t>
+          <t>Angus Reid</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -6079,16 +6079,16 @@
         <v>0</v>
       </c>
       <c r="F138" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="G138" t="n">
         <v>0.4</v>
       </c>
       <c r="H138" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="I138" t="n">
-        <v>0.06</v>
+        <v>0.1</v>
       </c>
       <c r="J138" t="n">
         <v>0.02</v>
@@ -6097,7 +6097,7 @@
         <v>0.01</v>
       </c>
       <c r="L138" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="139">
@@ -6107,11 +6107,11 @@
         </is>
       </c>
       <c r="B139" s="2" t="n">
-        <v>45901</v>
+        <v>45902</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Mainstreet Research</t>
+          <t>Abacus Data</t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -6121,25 +6121,25 @@
         <v>0</v>
       </c>
       <c r="F139" t="n">
-        <v>0.423</v>
+        <v>0.43</v>
       </c>
       <c r="G139" t="n">
-        <v>0.404</v>
+        <v>0.4</v>
       </c>
       <c r="H139" t="n">
-        <v>0.05</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I139" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="J139" t="n">
-        <v>0.012</v>
+        <v>0.02</v>
       </c>
       <c r="K139" t="n">
-        <v>0.013</v>
+        <v>0.01</v>
       </c>
       <c r="L139" t="n">
-        <v>0.016</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="140">
@@ -6149,11 +6149,11 @@
         </is>
       </c>
       <c r="B140" s="2" t="n">
-        <v>45898</v>
+        <v>45901</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Nanos Research</t>
+          <t>Mainstreet Research</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -6163,25 +6163,25 @@
         <v>0</v>
       </c>
       <c r="F140" t="n">
-        <v>0.433</v>
+        <v>0.423</v>
       </c>
       <c r="G140" t="n">
-        <v>0.324</v>
+        <v>0.404</v>
       </c>
       <c r="H140" t="n">
-        <v>0.062</v>
+        <v>0.05</v>
       </c>
       <c r="I140" t="n">
-        <v>0.127</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="J140" t="n">
-        <v>0.029</v>
+        <v>0.012</v>
       </c>
       <c r="K140" t="n">
-        <v>0.009000000000000001</v>
+        <v>0.016</v>
       </c>
       <c r="L140" t="n">
-        <v>0.016</v>
+        <v>0.013</v>
       </c>
     </row>
     <row r="141">
@@ -6191,11 +6191,11 @@
         </is>
       </c>
       <c r="B141" s="2" t="n">
-        <v>45896</v>
+        <v>45898</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Liaison Strategies</t>
+          <t>Nanos Research</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -6205,25 +6205,25 @@
         <v>0</v>
       </c>
       <c r="F141" t="n">
-        <v>0.44</v>
+        <v>0.433</v>
       </c>
       <c r="G141" t="n">
-        <v>0.35</v>
+        <v>0.324</v>
       </c>
       <c r="H141" t="n">
-        <v>0.05</v>
+        <v>0.062</v>
       </c>
       <c r="I141" t="n">
-        <v>0.1</v>
+        <v>0.127</v>
       </c>
       <c r="J141" t="n">
-        <v>0.02</v>
+        <v>0.029</v>
       </c>
       <c r="K141" t="n">
-        <v>0.01</v>
+        <v>0.016</v>
       </c>
       <c r="L141" t="n">
-        <v>0.02</v>
+        <v>0.009000000000000001</v>
       </c>
     </row>
     <row r="142">
@@ -6233,11 +6233,11 @@
         </is>
       </c>
       <c r="B142" s="2" t="n">
-        <v>45891</v>
+        <v>45896</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Nanos Research</t>
+          <t>Liaison Strategies</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -6247,25 +6247,25 @@
         <v>0</v>
       </c>
       <c r="F142" t="n">
-        <v>0.4370000000000001</v>
+        <v>0.44</v>
       </c>
       <c r="G142" t="n">
-        <v>0.342</v>
+        <v>0.35</v>
       </c>
       <c r="H142" t="n">
-        <v>0.055</v>
+        <v>0.05</v>
       </c>
       <c r="I142" t="n">
-        <v>0.107</v>
+        <v>0.1</v>
       </c>
       <c r="J142" t="n">
-        <v>0.033</v>
+        <v>0.02</v>
       </c>
       <c r="K142" t="n">
-        <v>0.008</v>
+        <v>0.02</v>
       </c>
       <c r="L142" t="n">
-        <v>0.016</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="143">
@@ -6275,11 +6275,11 @@
         </is>
       </c>
       <c r="B143" s="2" t="n">
-        <v>45888</v>
+        <v>45891</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>August 19, 2025</t>
+          <t>Nanos Research</t>
         </is>
       </c>
       <c r="D143" t="n">
@@ -6288,13 +6288,27 @@
       <c r="E143" t="b">
         <v>0</v>
       </c>
-      <c r="F143" t="inlineStr"/>
-      <c r="G143" t="inlineStr"/>
-      <c r="H143" t="inlineStr"/>
-      <c r="I143" t="inlineStr"/>
-      <c r="J143" t="inlineStr"/>
-      <c r="K143" t="inlineStr"/>
-      <c r="L143" t="inlineStr"/>
+      <c r="F143" t="n">
+        <v>0.4370000000000001</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.342</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.055</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.107</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.033</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.016</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.008</v>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -6307,7 +6321,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Abacus Data</t>
+          <t>August 19, 2025</t>
         </is>
       </c>
       <c r="D144" t="n">
@@ -6316,25 +6330,13 @@
       <c r="E144" t="b">
         <v>0</v>
       </c>
-      <c r="F144" t="n">
-        <v>0.39</v>
-      </c>
-      <c r="G144" t="n">
-        <v>0.41</v>
-      </c>
-      <c r="H144" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="I144" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="J144" t="n">
-        <v>0.02</v>
-      </c>
+      <c r="F144" t="inlineStr"/>
+      <c r="G144" t="inlineStr"/>
+      <c r="H144" t="inlineStr"/>
+      <c r="I144" t="inlineStr"/>
+      <c r="J144" t="inlineStr"/>
       <c r="K144" t="inlineStr"/>
-      <c r="L144" t="n">
-        <v>0.02</v>
-      </c>
+      <c r="L144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -6343,11 +6345,11 @@
         </is>
       </c>
       <c r="B145" s="2" t="n">
-        <v>45887</v>
+        <v>45888</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>August 18, 2025</t>
+          <t>Abacus Data</t>
         </is>
       </c>
       <c r="D145" t="n">
@@ -6356,12 +6358,24 @@
       <c r="E145" t="b">
         <v>0</v>
       </c>
-      <c r="F145" t="inlineStr"/>
-      <c r="G145" t="inlineStr"/>
-      <c r="H145" t="inlineStr"/>
-      <c r="I145" t="inlineStr"/>
-      <c r="J145" t="inlineStr"/>
-      <c r="K145" t="inlineStr"/>
+      <c r="F145" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="G145" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="H145" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="I145" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="J145" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="K145" t="n">
+        <v>0.02</v>
+      </c>
       <c r="L145" t="inlineStr"/>
     </row>
     <row r="146">
@@ -6371,11 +6385,11 @@
         </is>
       </c>
       <c r="B146" s="2" t="n">
-        <v>45884</v>
+        <v>45887</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Nanos Research</t>
+          <t>August 18, 2025</t>
         </is>
       </c>
       <c r="D146" t="n">
@@ -6384,27 +6398,13 @@
       <c r="E146" t="b">
         <v>0</v>
       </c>
-      <c r="F146" t="n">
-        <v>0.444</v>
-      </c>
-      <c r="G146" t="n">
-        <v>0.324</v>
-      </c>
-      <c r="H146" t="n">
-        <v>0.049</v>
-      </c>
-      <c r="I146" t="n">
-        <v>0.116</v>
-      </c>
-      <c r="J146" t="n">
-        <v>0.032</v>
-      </c>
-      <c r="K146" t="n">
-        <v>0.006999999999999999</v>
-      </c>
-      <c r="L146" t="n">
-        <v>0.028</v>
-      </c>
+      <c r="F146" t="inlineStr"/>
+      <c r="G146" t="inlineStr"/>
+      <c r="H146" t="inlineStr"/>
+      <c r="I146" t="inlineStr"/>
+      <c r="J146" t="inlineStr"/>
+      <c r="K146" t="inlineStr"/>
+      <c r="L146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -6413,7 +6413,7 @@
         </is>
       </c>
       <c r="B147" s="2" t="n">
-        <v>45877</v>
+        <v>45884</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
@@ -6427,25 +6427,25 @@
         <v>0</v>
       </c>
       <c r="F147" t="n">
-        <v>0.448</v>
+        <v>0.444</v>
       </c>
       <c r="G147" t="n">
-        <v>0.319</v>
+        <v>0.324</v>
       </c>
       <c r="H147" t="n">
-        <v>0.061</v>
+        <v>0.049</v>
       </c>
       <c r="I147" t="n">
-        <v>0.115</v>
+        <v>0.116</v>
       </c>
       <c r="J147" t="n">
-        <v>0.026</v>
+        <v>0.032</v>
       </c>
       <c r="K147" t="n">
-        <v>0.006</v>
+        <v>0.028</v>
       </c>
       <c r="L147" t="n">
-        <v>0.025</v>
+        <v>0.006999999999999999</v>
       </c>
     </row>
     <row r="148">
@@ -6459,7 +6459,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Liaison Strategies</t>
+          <t>Nanos Research</t>
         </is>
       </c>
       <c r="D148" t="n">
@@ -6469,25 +6469,25 @@
         <v>0</v>
       </c>
       <c r="F148" t="n">
-        <v>0.44</v>
+        <v>0.448</v>
       </c>
       <c r="G148" t="n">
-        <v>0.35</v>
+        <v>0.319</v>
       </c>
       <c r="H148" t="n">
-        <v>0.06</v>
+        <v>0.061</v>
       </c>
       <c r="I148" t="n">
-        <v>0.11</v>
+        <v>0.115</v>
       </c>
       <c r="J148" t="n">
-        <v>0.03</v>
+        <v>0.026</v>
       </c>
       <c r="K148" t="n">
-        <v>0.01</v>
+        <v>0.025</v>
       </c>
       <c r="L148" t="n">
-        <v>0.01</v>
+        <v>0.006</v>
       </c>
     </row>
     <row r="149">
@@ -6497,11 +6497,11 @@
         </is>
       </c>
       <c r="B149" s="2" t="n">
-        <v>45876</v>
+        <v>45877</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Abacus Data</t>
+          <t>Liaison Strategies</t>
         </is>
       </c>
       <c r="D149" t="n">
@@ -6511,23 +6511,25 @@
         <v>0</v>
       </c>
       <c r="F149" t="n">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="G149" t="n">
-        <v>0.4</v>
+        <v>0.35</v>
       </c>
       <c r="H149" t="n">
         <v>0.06</v>
       </c>
       <c r="I149" t="n">
-        <v>0.08</v>
+        <v>0.11</v>
       </c>
       <c r="J149" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="K149" t="inlineStr"/>
+        <v>0.03</v>
+      </c>
+      <c r="K149" t="n">
+        <v>0.01</v>
+      </c>
       <c r="L149" t="n">
-        <v>0.015</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="150">
@@ -6537,11 +6539,11 @@
         </is>
       </c>
       <c r="B150" s="2" t="n">
-        <v>45873</v>
+        <v>45876</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Léger</t>
+          <t>Abacus Data</t>
         </is>
       </c>
       <c r="D150" t="n">
@@ -6551,22 +6553,22 @@
         <v>0</v>
       </c>
       <c r="F150" t="n">
-        <v>0.46</v>
+        <v>0.43</v>
       </c>
       <c r="G150" t="n">
-        <v>0.36</v>
+        <v>0.4</v>
       </c>
       <c r="H150" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="I150" t="n">
-        <v>0.06</v>
+        <v>0.08</v>
       </c>
       <c r="J150" t="n">
-        <v>0.03</v>
+        <v>0.015</v>
       </c>
       <c r="K150" t="n">
-        <v>0.01</v>
+        <v>0.015</v>
       </c>
       <c r="L150" t="inlineStr"/>
     </row>
@@ -6577,11 +6579,11 @@
         </is>
       </c>
       <c r="B151" s="2" t="n">
-        <v>45870</v>
+        <v>45873</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Pallas Data</t>
+          <t>Léger</t>
         </is>
       </c>
       <c r="D151" t="n">
@@ -6591,24 +6593,24 @@
         <v>0</v>
       </c>
       <c r="F151" t="n">
-        <v>0.4320000000000001</v>
+        <v>0.46</v>
       </c>
       <c r="G151" t="n">
-        <v>0.376</v>
+        <v>0.36</v>
       </c>
       <c r="H151" t="n">
-        <v>0.063</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I151" t="n">
-        <v>0.075</v>
+        <v>0.06</v>
       </c>
       <c r="J151" t="n">
-        <v>0.022</v>
-      </c>
-      <c r="K151" t="n">
-        <v>0.032</v>
-      </c>
-      <c r="L151" t="inlineStr"/>
+        <v>0.03</v>
+      </c>
+      <c r="K151" t="inlineStr"/>
+      <c r="L151" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -6621,7 +6623,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Nanos Research</t>
+          <t>Pallas Data</t>
         </is>
       </c>
       <c r="D152" t="n">
@@ -6631,25 +6633,23 @@
         <v>0</v>
       </c>
       <c r="F152" t="n">
-        <v>0.4370000000000001</v>
+        <v>0.4320000000000001</v>
       </c>
       <c r="G152" t="n">
-        <v>0.325</v>
+        <v>0.376</v>
       </c>
       <c r="H152" t="n">
-        <v>0.053</v>
+        <v>0.063</v>
       </c>
       <c r="I152" t="n">
-        <v>0.12</v>
+        <v>0.075</v>
       </c>
       <c r="J152" t="n">
-        <v>0.025</v>
-      </c>
-      <c r="K152" t="n">
-        <v>0.01</v>
-      </c>
+        <v>0.022</v>
+      </c>
+      <c r="K152" t="inlineStr"/>
       <c r="L152" t="n">
-        <v>0.03</v>
+        <v>0.032</v>
       </c>
     </row>
     <row r="153">
@@ -6659,11 +6659,11 @@
         </is>
       </c>
       <c r="B153" s="2" t="n">
-        <v>45866</v>
+        <v>45870</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Innovative Research</t>
+          <t>Nanos Research</t>
         </is>
       </c>
       <c r="D153" t="n">
@@ -6673,24 +6673,26 @@
         <v>0</v>
       </c>
       <c r="F153" t="n">
-        <v>0.41</v>
+        <v>0.4370000000000001</v>
       </c>
       <c r="G153" t="n">
-        <v>0.39</v>
+        <v>0.325</v>
       </c>
       <c r="H153" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.053</v>
       </c>
       <c r="I153" t="n">
-        <v>0.09</v>
+        <v>0.12</v>
       </c>
       <c r="J153" t="n">
-        <v>0.04</v>
+        <v>0.025</v>
       </c>
       <c r="K153" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="L153" t="inlineStr"/>
+        <v>0.03</v>
+      </c>
+      <c r="L153" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -6699,11 +6701,11 @@
         </is>
       </c>
       <c r="B154" s="2" t="n">
-        <v>45863</v>
+        <v>45866</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Liaison Strategies</t>
+          <t>Innovative Research</t>
         </is>
       </c>
       <c r="D154" t="n">
@@ -6713,25 +6715,23 @@
         <v>0</v>
       </c>
       <c r="F154" t="n">
-        <v>0.43</v>
+        <v>0.41</v>
       </c>
       <c r="G154" t="n">
-        <v>0.36</v>
+        <v>0.39</v>
       </c>
       <c r="H154" t="n">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I154" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="J154" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="K154" t="n">
-        <v>0.01</v>
-      </c>
+        <v>0.04</v>
+      </c>
+      <c r="K154" t="inlineStr"/>
       <c r="L154" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="155">
@@ -6745,7 +6745,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Nanos Research</t>
+          <t>Liaison Strategies</t>
         </is>
       </c>
       <c r="D155" t="n">
@@ -6755,25 +6755,25 @@
         <v>0</v>
       </c>
       <c r="F155" t="n">
-        <v>0.436</v>
+        <v>0.43</v>
       </c>
       <c r="G155" t="n">
-        <v>0.335</v>
+        <v>0.36</v>
       </c>
       <c r="H155" t="n">
-        <v>0.059</v>
+        <v>0.06</v>
       </c>
       <c r="I155" t="n">
-        <v>0.121</v>
+        <v>0.1</v>
       </c>
       <c r="J155" t="n">
-        <v>0.023</v>
+        <v>0.03</v>
       </c>
       <c r="K155" t="n">
-        <v>0.008</v>
+        <v>0.01</v>
       </c>
       <c r="L155" t="n">
-        <v>0.018</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="156">
@@ -6783,7 +6783,7 @@
         </is>
       </c>
       <c r="B156" s="2" t="n">
-        <v>45856</v>
+        <v>45863</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
@@ -6797,25 +6797,25 @@
         <v>0</v>
       </c>
       <c r="F156" t="n">
-        <v>0.4429999999999999</v>
+        <v>0.436</v>
       </c>
       <c r="G156" t="n">
-        <v>0.34</v>
+        <v>0.335</v>
       </c>
       <c r="H156" t="n">
-        <v>0.066</v>
+        <v>0.059</v>
       </c>
       <c r="I156" t="n">
-        <v>0.103</v>
+        <v>0.121</v>
       </c>
       <c r="J156" t="n">
         <v>0.023</v>
       </c>
       <c r="K156" t="n">
-        <v>0.005</v>
+        <v>0.018</v>
       </c>
       <c r="L156" t="n">
-        <v>0.02</v>
+        <v>0.008</v>
       </c>
     </row>
     <row r="157">
@@ -6825,11 +6825,11 @@
         </is>
       </c>
       <c r="B157" s="2" t="n">
-        <v>45853</v>
+        <v>45856</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Abacus Data</t>
+          <t>Nanos Research</t>
         </is>
       </c>
       <c r="D157" t="n">
@@ -6839,25 +6839,25 @@
         <v>0</v>
       </c>
       <c r="F157" t="n">
-        <v>0.43</v>
+        <v>0.4429999999999999</v>
       </c>
       <c r="G157" t="n">
-        <v>0.4</v>
+        <v>0.34</v>
       </c>
       <c r="H157" t="n">
-        <v>0.06</v>
+        <v>0.066</v>
       </c>
       <c r="I157" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.103</v>
       </c>
       <c r="J157" t="n">
-        <v>0.03</v>
+        <v>0.023</v>
       </c>
       <c r="K157" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="L157" t="n">
-        <v>0.01</v>
+        <v>0.005</v>
       </c>
     </row>
     <row r="158">
@@ -6867,11 +6867,11 @@
         </is>
       </c>
       <c r="B158" s="2" t="n">
-        <v>45852</v>
+        <v>45853</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Ekos</t>
+          <t>Abacus Data</t>
         </is>
       </c>
       <c r="D158" t="n">
@@ -6881,25 +6881,25 @@
         <v>0</v>
       </c>
       <c r="F158" t="n">
-        <v>0.4320000000000001</v>
+        <v>0.43</v>
       </c>
       <c r="G158" t="n">
-        <v>0.305</v>
+        <v>0.4</v>
       </c>
       <c r="H158" t="n">
-        <v>0.055</v>
+        <v>0.06</v>
       </c>
       <c r="I158" t="n">
-        <v>0.13</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="J158" t="n">
-        <v>0.035</v>
+        <v>0.03</v>
       </c>
       <c r="K158" t="n">
         <v>0.01</v>
       </c>
       <c r="L158" t="n">
-        <v>0.036</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="159">
@@ -6909,11 +6909,11 @@
         </is>
       </c>
       <c r="B159" s="2" t="n">
-        <v>45849</v>
+        <v>45852</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Nanos Research</t>
+          <t>Ekos</t>
         </is>
       </c>
       <c r="D159" t="n">
@@ -6923,25 +6923,25 @@
         <v>0</v>
       </c>
       <c r="F159" t="n">
-        <v>0.445</v>
+        <v>0.4320000000000001</v>
       </c>
       <c r="G159" t="n">
-        <v>0.338</v>
+        <v>0.305</v>
       </c>
       <c r="H159" t="n">
-        <v>0.059</v>
+        <v>0.055</v>
       </c>
       <c r="I159" t="n">
-        <v>0.111</v>
+        <v>0.13</v>
       </c>
       <c r="J159" t="n">
-        <v>0.021</v>
+        <v>0.035</v>
       </c>
       <c r="K159" t="n">
-        <v>0.006999999999999999</v>
+        <v>0.036</v>
       </c>
       <c r="L159" t="n">
-        <v>0.019</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="160">
@@ -6951,11 +6951,11 @@
         </is>
       </c>
       <c r="B160" s="2" t="n">
-        <v>45844</v>
+        <v>45849</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Léger</t>
+          <t>Nanos Research</t>
         </is>
       </c>
       <c r="D160" t="n">
@@ -6965,24 +6965,26 @@
         <v>0</v>
       </c>
       <c r="F160" t="n">
-        <v>0.48</v>
+        <v>0.445</v>
       </c>
       <c r="G160" t="n">
-        <v>0.35</v>
+        <v>0.338</v>
       </c>
       <c r="H160" t="n">
-        <v>0.06</v>
+        <v>0.059</v>
       </c>
       <c r="I160" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.111</v>
       </c>
       <c r="J160" t="n">
-        <v>0.03</v>
+        <v>0.021</v>
       </c>
       <c r="K160" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="L160" t="inlineStr"/>
+        <v>0.019</v>
+      </c>
+      <c r="L160" t="n">
+        <v>0.006999999999999999</v>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -6991,11 +6993,11 @@
         </is>
       </c>
       <c r="B161" s="2" t="n">
-        <v>45842</v>
+        <v>45844</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Liaison Strategies</t>
+          <t>Léger</t>
         </is>
       </c>
       <c r="D161" t="n">
@@ -7005,7 +7007,7 @@
         <v>0</v>
       </c>
       <c r="F161" t="n">
-        <v>0.46</v>
+        <v>0.48</v>
       </c>
       <c r="G161" t="n">
         <v>0.35</v>
@@ -7014,14 +7016,12 @@
         <v>0.06</v>
       </c>
       <c r="I161" t="n">
-        <v>0.09</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="J161" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="K161" t="n">
-        <v>0.01</v>
-      </c>
+        <v>0.03</v>
+      </c>
+      <c r="K161" t="inlineStr"/>
       <c r="L161" t="n">
         <v>0.01</v>
       </c>
@@ -7037,7 +7037,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Nanos Research</t>
+          <t>Liaison Strategies</t>
         </is>
       </c>
       <c r="D162" t="n">
@@ -7047,25 +7047,25 @@
         <v>0</v>
       </c>
       <c r="F162" t="n">
-        <v>0.451</v>
+        <v>0.46</v>
       </c>
       <c r="G162" t="n">
-        <v>0.326</v>
+        <v>0.35</v>
       </c>
       <c r="H162" t="n">
-        <v>0.062</v>
+        <v>0.06</v>
       </c>
       <c r="I162" t="n">
-        <v>0.115</v>
+        <v>0.09</v>
       </c>
       <c r="J162" t="n">
-        <v>0.018</v>
+        <v>0.02</v>
       </c>
       <c r="K162" t="n">
         <v>0.01</v>
       </c>
       <c r="L162" t="n">
-        <v>0.018</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="163">
@@ -7075,11 +7075,11 @@
         </is>
       </c>
       <c r="B163" s="2" t="n">
-        <v>45840</v>
+        <v>45842</v>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Research Co.</t>
+          <t>Nanos Research</t>
         </is>
       </c>
       <c r="D163" t="n">
@@ -7089,22 +7089,22 @@
         <v>0</v>
       </c>
       <c r="F163" t="n">
-        <v>0.47</v>
+        <v>0.451</v>
       </c>
       <c r="G163" t="n">
-        <v>0.37</v>
+        <v>0.326</v>
       </c>
       <c r="H163" t="n">
-        <v>0.06</v>
+        <v>0.062</v>
       </c>
       <c r="I163" t="n">
-        <v>0.06</v>
+        <v>0.115</v>
       </c>
       <c r="J163" t="n">
-        <v>0.02</v>
+        <v>0.018</v>
       </c>
       <c r="K163" t="n">
-        <v>0.01</v>
+        <v>0.018</v>
       </c>
       <c r="L163" t="n">
         <v>0.01</v>
@@ -7121,7 +7121,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Abacus Data</t>
+          <t>Research Co.</t>
         </is>
       </c>
       <c r="D164" t="n">
@@ -7131,25 +7131,25 @@
         <v>0</v>
       </c>
       <c r="F164" t="n">
-        <v>0.41</v>
+        <v>0.47</v>
       </c>
       <c r="G164" t="n">
-        <v>0.4</v>
+        <v>0.37</v>
       </c>
       <c r="H164" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="I164" t="n">
-        <v>0.09</v>
+        <v>0.06</v>
       </c>
       <c r="J164" t="n">
         <v>0.02</v>
       </c>
       <c r="K164" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="L164" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="165">
@@ -7159,11 +7159,11 @@
         </is>
       </c>
       <c r="B165" s="2" t="n">
-        <v>45838</v>
+        <v>45840</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Innovative Research</t>
+          <t>Abacus Data</t>
         </is>
       </c>
       <c r="D165" t="n">
@@ -7173,24 +7173,26 @@
         <v>0</v>
       </c>
       <c r="F165" t="n">
-        <v>0.43</v>
+        <v>0.41</v>
       </c>
       <c r="G165" t="n">
-        <v>0.38</v>
+        <v>0.4</v>
       </c>
       <c r="H165" t="n">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I165" t="n">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="J165" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="K165" t="n">
         <v>0.02</v>
       </c>
-      <c r="L165" t="inlineStr"/>
+      <c r="L165" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -7199,11 +7201,11 @@
         </is>
       </c>
       <c r="B166" s="2" t="n">
-        <v>45835</v>
+        <v>45838</v>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Nanos Research</t>
+          <t>Innovative Research</t>
         </is>
       </c>
       <c r="D166" t="n">
@@ -7213,25 +7215,23 @@
         <v>0</v>
       </c>
       <c r="F166" t="n">
-        <v>0.445</v>
+        <v>0.43</v>
       </c>
       <c r="G166" t="n">
-        <v>0.314</v>
+        <v>0.38</v>
       </c>
       <c r="H166" t="n">
-        <v>0.059</v>
+        <v>0.06</v>
       </c>
       <c r="I166" t="n">
-        <v>0.128</v>
+        <v>0.08</v>
       </c>
       <c r="J166" t="n">
-        <v>0.025</v>
-      </c>
-      <c r="K166" t="n">
-        <v>0.012</v>
-      </c>
+        <v>0.03</v>
+      </c>
+      <c r="K166" t="inlineStr"/>
       <c r="L166" t="n">
-        <v>0.017</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="167">
@@ -7241,11 +7241,11 @@
         </is>
       </c>
       <c r="B167" s="2" t="n">
-        <v>45834</v>
+        <v>45835</v>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Mainstreet Research</t>
+          <t>Nanos Research</t>
         </is>
       </c>
       <c r="D167" t="n">
@@ -7255,25 +7255,25 @@
         <v>0</v>
       </c>
       <c r="F167" t="n">
-        <v>0.47</v>
+        <v>0.445</v>
       </c>
       <c r="G167" t="n">
-        <v>0.38</v>
+        <v>0.314</v>
       </c>
       <c r="H167" t="n">
-        <v>0.03</v>
+        <v>0.059</v>
       </c>
       <c r="I167" t="n">
-        <v>0.06</v>
+        <v>0.128</v>
       </c>
       <c r="J167" t="n">
-        <v>0.03</v>
+        <v>0.025</v>
       </c>
       <c r="K167" t="n">
-        <v>0.02</v>
+        <v>0.017</v>
       </c>
       <c r="L167" t="n">
-        <v>0.01</v>
+        <v>0.012</v>
       </c>
     </row>
     <row r="168">
@@ -7283,11 +7283,11 @@
         </is>
       </c>
       <c r="B168" s="2" t="n">
-        <v>45828</v>
+        <v>45834</v>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Liaison Strategies</t>
+          <t>Mainstreet Research</t>
         </is>
       </c>
       <c r="D168" t="n">
@@ -7297,16 +7297,16 @@
         <v>0</v>
       </c>
       <c r="F168" t="n">
-        <v>0.42</v>
+        <v>0.47</v>
       </c>
       <c r="G168" t="n">
         <v>0.38</v>
       </c>
       <c r="H168" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="I168" t="n">
         <v>0.06</v>
-      </c>
-      <c r="I168" t="n">
-        <v>0.11</v>
       </c>
       <c r="J168" t="n">
         <v>0.03</v>
@@ -7315,7 +7315,7 @@
         <v>0.01</v>
       </c>
       <c r="L168" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="169">
@@ -7329,7 +7329,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Nanos Research</t>
+          <t>Liaison Strategies</t>
         </is>
       </c>
       <c r="D169" t="n">
@@ -7339,25 +7339,25 @@
         <v>0</v>
       </c>
       <c r="F169" t="n">
-        <v>0.452</v>
+        <v>0.42</v>
       </c>
       <c r="G169" t="n">
-        <v>0.308</v>
+        <v>0.38</v>
       </c>
       <c r="H169" t="n">
-        <v>0.061</v>
+        <v>0.06</v>
       </c>
       <c r="I169" t="n">
-        <v>0.122</v>
+        <v>0.11</v>
       </c>
       <c r="J169" t="n">
-        <v>0.029</v>
+        <v>0.03</v>
       </c>
       <c r="K169" t="n">
-        <v>0.013</v>
+        <v>0.01</v>
       </c>
       <c r="L169" t="n">
-        <v>0.015</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="170">
@@ -7367,11 +7367,11 @@
         </is>
       </c>
       <c r="B170" s="2" t="n">
-        <v>45827</v>
+        <v>45828</v>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Abacus Data</t>
+          <t>Nanos Research</t>
         </is>
       </c>
       <c r="D170" t="n">
@@ -7381,25 +7381,25 @@
         <v>0</v>
       </c>
       <c r="F170" t="n">
-        <v>0.42</v>
+        <v>0.452</v>
       </c>
       <c r="G170" t="n">
-        <v>0.39</v>
+        <v>0.308</v>
       </c>
       <c r="H170" t="n">
-        <v>0.06</v>
+        <v>0.061</v>
       </c>
       <c r="I170" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.122</v>
       </c>
       <c r="J170" t="n">
-        <v>0.03</v>
+        <v>0.029</v>
       </c>
       <c r="K170" t="n">
-        <v>0.01</v>
+        <v>0.015</v>
       </c>
       <c r="L170" t="n">
-        <v>0.01</v>
+        <v>0.013</v>
       </c>
     </row>
     <row r="171">
@@ -7409,11 +7409,11 @@
         </is>
       </c>
       <c r="B171" s="2" t="n">
-        <v>45821</v>
+        <v>45827</v>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Nanos Research</t>
+          <t>Abacus Data</t>
         </is>
       </c>
       <c r="D171" t="n">
@@ -7423,25 +7423,25 @@
         <v>0</v>
       </c>
       <c r="F171" t="n">
-        <v>0.442</v>
+        <v>0.42</v>
       </c>
       <c r="G171" t="n">
-        <v>0.322</v>
+        <v>0.39</v>
       </c>
       <c r="H171" t="n">
-        <v>0.063</v>
+        <v>0.06</v>
       </c>
       <c r="I171" t="n">
-        <v>0.114</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="J171" t="n">
-        <v>0.032</v>
+        <v>0.03</v>
       </c>
       <c r="K171" t="n">
         <v>0.01</v>
       </c>
       <c r="L171" t="n">
-        <v>0.017</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="172">
@@ -7451,11 +7451,11 @@
         </is>
       </c>
       <c r="B172" s="2" t="n">
-        <v>45814</v>
+        <v>45821</v>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Liaison Strategies</t>
+          <t>Nanos Research</t>
         </is>
       </c>
       <c r="D172" t="n">
@@ -7465,22 +7465,22 @@
         <v>0</v>
       </c>
       <c r="F172" t="n">
-        <v>0.42</v>
+        <v>0.442</v>
       </c>
       <c r="G172" t="n">
-        <v>0.39</v>
+        <v>0.322</v>
       </c>
       <c r="H172" t="n">
-        <v>0.06</v>
+        <v>0.063</v>
       </c>
       <c r="I172" t="n">
-        <v>0.09</v>
+        <v>0.114</v>
       </c>
       <c r="J172" t="n">
-        <v>0.02</v>
+        <v>0.032</v>
       </c>
       <c r="K172" t="n">
-        <v>0.01</v>
+        <v>0.017</v>
       </c>
       <c r="L172" t="n">
         <v>0.01</v>
@@ -7497,7 +7497,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Nanos Research</t>
+          <t>Liaison Strategies</t>
         </is>
       </c>
       <c r="D173" t="n">
@@ -7507,25 +7507,25 @@
         <v>0</v>
       </c>
       <c r="F173" t="n">
-        <v>0.426</v>
+        <v>0.42</v>
       </c>
       <c r="G173" t="n">
-        <v>0.328</v>
+        <v>0.39</v>
       </c>
       <c r="H173" t="n">
-        <v>0.065</v>
+        <v>0.06</v>
       </c>
       <c r="I173" t="n">
-        <v>0.12</v>
+        <v>0.09</v>
       </c>
       <c r="J173" t="n">
-        <v>0.039</v>
+        <v>0.02</v>
       </c>
       <c r="K173" t="n">
-        <v>0.009000000000000001</v>
+        <v>0.01</v>
       </c>
       <c r="L173" t="n">
-        <v>0.013</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="174">
@@ -7535,11 +7535,11 @@
         </is>
       </c>
       <c r="B174" s="2" t="n">
-        <v>45813</v>
+        <v>45814</v>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Abacus Data</t>
+          <t>Nanos Research</t>
         </is>
       </c>
       <c r="D174" t="n">
@@ -7549,25 +7549,25 @@
         <v>0</v>
       </c>
       <c r="F174" t="n">
-        <v>0.42</v>
+        <v>0.426</v>
       </c>
       <c r="G174" t="n">
-        <v>0.39</v>
+        <v>0.328</v>
       </c>
       <c r="H174" t="n">
-        <v>0.06</v>
+        <v>0.065</v>
       </c>
       <c r="I174" t="n">
-        <v>0.08</v>
+        <v>0.12</v>
       </c>
       <c r="J174" t="n">
-        <v>0.03</v>
+        <v>0.039</v>
       </c>
       <c r="K174" t="n">
-        <v>0</v>
+        <v>0.013</v>
       </c>
       <c r="L174" t="n">
-        <v>0.01</v>
+        <v>0.009000000000000001</v>
       </c>
     </row>
     <row r="175">
@@ -7577,11 +7577,11 @@
         </is>
       </c>
       <c r="B175" s="2" t="n">
-        <v>45812</v>
+        <v>45813</v>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Ekos</t>
+          <t>Abacus Data</t>
         </is>
       </c>
       <c r="D175" t="n">
@@ -7591,16 +7591,16 @@
         <v>0</v>
       </c>
       <c r="F175" t="n">
-        <v>0.439</v>
+        <v>0.42</v>
       </c>
       <c r="G175" t="n">
-        <v>0.32</v>
+        <v>0.39</v>
       </c>
       <c r="H175" t="n">
-        <v>0.052</v>
+        <v>0.06</v>
       </c>
       <c r="I175" t="n">
-        <v>0.127</v>
+        <v>0.08</v>
       </c>
       <c r="J175" t="n">
         <v>0.03</v>
@@ -7609,7 +7609,7 @@
         <v>0.01</v>
       </c>
       <c r="L175" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
     </row>
     <row r="176">
@@ -7619,11 +7619,11 @@
         </is>
       </c>
       <c r="B176" s="2" t="n">
-        <v>45807</v>
+        <v>45812</v>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Spark Insights</t>
+          <t>Ekos</t>
         </is>
       </c>
       <c r="D176" t="n">
@@ -7633,22 +7633,26 @@
         <v>0</v>
       </c>
       <c r="F176" t="n">
-        <v>0.41</v>
+        <v>0.439</v>
       </c>
       <c r="G176" t="n">
-        <v>0.4</v>
+        <v>0.32</v>
       </c>
       <c r="H176" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.052</v>
       </c>
       <c r="I176" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="J176" t="inlineStr"/>
+        <v>0.127</v>
+      </c>
+      <c r="J176" t="n">
+        <v>0.03</v>
+      </c>
       <c r="K176" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="L176" t="inlineStr"/>
+        <v>0.03</v>
+      </c>
+      <c r="L176" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -7661,7 +7665,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Nanos Research</t>
+          <t>Spark Insights</t>
         </is>
       </c>
       <c r="D177" t="n">
@@ -7671,25 +7675,21 @@
         <v>0</v>
       </c>
       <c r="F177" t="n">
-        <v>0.417</v>
+        <v>0.41</v>
       </c>
       <c r="G177" t="n">
-        <v>0.364</v>
+        <v>0.4</v>
       </c>
       <c r="H177" t="n">
-        <v>0.065</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I177" t="n">
-        <v>0.105</v>
-      </c>
-      <c r="J177" t="n">
-        <v>0.034</v>
-      </c>
-      <c r="K177" t="n">
-        <v>0.003</v>
-      </c>
+        <v>0.08</v>
+      </c>
+      <c r="J177" t="inlineStr"/>
+      <c r="K177" t="inlineStr"/>
       <c r="L177" t="n">
-        <v>0.011</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="178">
@@ -7699,11 +7699,11 @@
         </is>
       </c>
       <c r="B178" s="2" t="n">
-        <v>45800</v>
+        <v>45807</v>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Liaison Strategies</t>
+          <t>Nanos Research</t>
         </is>
       </c>
       <c r="D178" t="n">
@@ -7713,25 +7713,25 @@
         <v>0</v>
       </c>
       <c r="F178" t="n">
-        <v>0.44</v>
+        <v>0.417</v>
       </c>
       <c r="G178" t="n">
-        <v>0.39</v>
+        <v>0.364</v>
       </c>
       <c r="H178" t="n">
-        <v>0.06</v>
+        <v>0.065</v>
       </c>
       <c r="I178" t="n">
-        <v>0.08</v>
+        <v>0.105</v>
       </c>
       <c r="J178" t="n">
-        <v>0.01</v>
+        <v>0.034</v>
       </c>
       <c r="K178" t="n">
-        <v>0.01</v>
+        <v>0.011</v>
       </c>
       <c r="L178" t="n">
-        <v>0.01</v>
+        <v>0.003</v>
       </c>
     </row>
     <row r="179">
@@ -7745,7 +7745,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Nanos Research</t>
+          <t>Liaison Strategies</t>
         </is>
       </c>
       <c r="D179" t="n">
@@ -7755,25 +7755,25 @@
         <v>0</v>
       </c>
       <c r="F179" t="n">
-        <v>0.404</v>
+        <v>0.44</v>
       </c>
       <c r="G179" t="n">
-        <v>0.386</v>
+        <v>0.39</v>
       </c>
       <c r="H179" t="n">
-        <v>0.059</v>
+        <v>0.06</v>
       </c>
       <c r="I179" t="n">
-        <v>0.098</v>
+        <v>0.08</v>
       </c>
       <c r="J179" t="n">
-        <v>0.03700000000000001</v>
+        <v>0.01</v>
       </c>
       <c r="K179" t="n">
-        <v>0.003</v>
+        <v>0.01</v>
       </c>
       <c r="L179" t="n">
-        <v>0.013</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="180">
@@ -7783,11 +7783,11 @@
         </is>
       </c>
       <c r="B180" s="2" t="n">
-        <v>45799</v>
+        <v>45800</v>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Innovative Research</t>
+          <t>Nanos Research</t>
         </is>
       </c>
       <c r="D180" t="n">
@@ -7797,24 +7797,26 @@
         <v>0</v>
       </c>
       <c r="F180" t="n">
-        <v>0.42</v>
+        <v>0.404</v>
       </c>
       <c r="G180" t="n">
-        <v>0.39</v>
+        <v>0.386</v>
       </c>
       <c r="H180" t="n">
-        <v>0.06</v>
+        <v>0.059</v>
       </c>
       <c r="I180" t="n">
-        <v>0.08</v>
+        <v>0.098</v>
       </c>
       <c r="J180" t="n">
-        <v>0.03</v>
+        <v>0.03700000000000001</v>
       </c>
       <c r="K180" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="L180" t="inlineStr"/>
+        <v>0.013</v>
+      </c>
+      <c r="L180" t="n">
+        <v>0.003</v>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -7823,11 +7825,11 @@
         </is>
       </c>
       <c r="B181" s="2" t="n">
-        <v>45798</v>
+        <v>45799</v>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Abacus Data</t>
+          <t>Innovative Research</t>
         </is>
       </c>
       <c r="D181" t="n">
@@ -7837,13 +7839,13 @@
         <v>0</v>
       </c>
       <c r="F181" t="n">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="G181" t="n">
-        <v>0.4</v>
+        <v>0.39</v>
       </c>
       <c r="H181" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="I181" t="n">
         <v>0.08</v>
@@ -7851,11 +7853,9 @@
       <c r="J181" t="n">
         <v>0.03</v>
       </c>
-      <c r="K181" t="n">
-        <v>0</v>
-      </c>
+      <c r="K181" t="inlineStr"/>
       <c r="L181" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="182">
@@ -7865,11 +7865,11 @@
         </is>
       </c>
       <c r="B182" s="2" t="n">
-        <v>45793</v>
+        <v>45798</v>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Nanos Research</t>
+          <t>Abacus Data</t>
         </is>
       </c>
       <c r="D182" t="n">
@@ -7879,25 +7879,25 @@
         <v>0</v>
       </c>
       <c r="F182" t="n">
-        <v>0.414</v>
+        <v>0.41</v>
       </c>
       <c r="G182" t="n">
-        <v>0.396</v>
+        <v>0.4</v>
       </c>
       <c r="H182" t="n">
-        <v>0.047</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I182" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="J182" t="n">
-        <v>0.039</v>
+        <v>0.03</v>
       </c>
       <c r="K182" t="n">
-        <v>0.006</v>
+        <v>0.01</v>
       </c>
       <c r="L182" t="n">
-        <v>0.013</v>
+        <v>0</v>
       </c>
     </row>
     <row r="183">
@@ -7907,11 +7907,11 @@
         </is>
       </c>
       <c r="B183" s="2" t="n">
-        <v>45786</v>
+        <v>45793</v>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Liaison Strategies</t>
+          <t>Nanos Research</t>
         </is>
       </c>
       <c r="D183" t="n">
@@ -7921,25 +7921,25 @@
         <v>0</v>
       </c>
       <c r="F183" t="n">
-        <v>0.45</v>
+        <v>0.414</v>
       </c>
       <c r="G183" t="n">
-        <v>0.4</v>
+        <v>0.396</v>
       </c>
       <c r="H183" t="n">
-        <v>0.06</v>
+        <v>0.047</v>
       </c>
       <c r="I183" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="J183" t="n">
-        <v>0.01</v>
+        <v>0.039</v>
       </c>
       <c r="K183" t="n">
-        <v>0</v>
+        <v>0.013</v>
       </c>
       <c r="L183" t="n">
-        <v>0.01</v>
+        <v>0.006</v>
       </c>
     </row>
     <row r="184">
@@ -7953,7 +7953,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Nanos Research</t>
+          <t>Liaison Strategies</t>
         </is>
       </c>
       <c r="D184" t="n">
@@ -7963,25 +7963,25 @@
         <v>0</v>
       </c>
       <c r="F184" t="n">
-        <v>0.415</v>
+        <v>0.45</v>
       </c>
       <c r="G184" t="n">
-        <v>0.405</v>
+        <v>0.4</v>
       </c>
       <c r="H184" t="n">
-        <v>0.051</v>
+        <v>0.06</v>
       </c>
       <c r="I184" t="n">
-        <v>0.078</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="J184" t="n">
-        <v>0.033</v>
+        <v>0.01</v>
       </c>
       <c r="K184" t="n">
-        <v>0.005</v>
+        <v>0.01</v>
       </c>
       <c r="L184" t="n">
-        <v>0.013</v>
+        <v>0</v>
       </c>
     </row>
     <row r="185">
@@ -7991,11 +7991,11 @@
         </is>
       </c>
       <c r="B185" s="2" t="n">
-        <v>45782</v>
+        <v>45786</v>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>May 5, 2025</t>
+          <t>Nanos Research</t>
         </is>
       </c>
       <c r="D185" t="n">
@@ -8004,13 +8004,27 @@
       <c r="E185" t="b">
         <v>0</v>
       </c>
-      <c r="F185" t="inlineStr"/>
-      <c r="G185" t="inlineStr"/>
-      <c r="H185" t="inlineStr"/>
-      <c r="I185" t="inlineStr"/>
-      <c r="J185" t="inlineStr"/>
-      <c r="K185" t="inlineStr"/>
-      <c r="L185" t="inlineStr"/>
+      <c r="F185" t="n">
+        <v>0.415</v>
+      </c>
+      <c r="G185" t="n">
+        <v>0.405</v>
+      </c>
+      <c r="H185" t="n">
+        <v>0.051</v>
+      </c>
+      <c r="I185" t="n">
+        <v>0.078</v>
+      </c>
+      <c r="J185" t="n">
+        <v>0.033</v>
+      </c>
+      <c r="K185" t="n">
+        <v>0.013</v>
+      </c>
+      <c r="L185" t="n">
+        <v>0.005</v>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -8019,11 +8033,11 @@
         </is>
       </c>
       <c r="B186" s="2" t="n">
-        <v>45779</v>
+        <v>45782</v>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Nanos Research</t>
+          <t>May 5, 2025</t>
         </is>
       </c>
       <c r="D186" t="n">
@@ -8032,27 +8046,13 @@
       <c r="E186" t="b">
         <v>0</v>
       </c>
-      <c r="F186" t="n">
-        <v>0.418</v>
-      </c>
-      <c r="G186" t="n">
-        <v>0.392</v>
-      </c>
-      <c r="H186" t="n">
-        <v>0.058</v>
-      </c>
-      <c r="I186" t="n">
-        <v>0.079</v>
-      </c>
-      <c r="J186" t="n">
-        <v>0.032</v>
-      </c>
-      <c r="K186" t="n">
-        <v>0.008</v>
-      </c>
-      <c r="L186" t="n">
-        <v>0.013</v>
-      </c>
+      <c r="F186" t="inlineStr"/>
+      <c r="G186" t="inlineStr"/>
+      <c r="H186" t="inlineStr"/>
+      <c r="I186" t="inlineStr"/>
+      <c r="J186" t="inlineStr"/>
+      <c r="K186" t="inlineStr"/>
+      <c r="L186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -8061,11 +8061,11 @@
         </is>
       </c>
       <c r="B187" s="2" t="n">
-        <v>45777</v>
+        <v>45779</v>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>April 30, 2025</t>
+          <t>Nanos Research</t>
         </is>
       </c>
       <c r="D187" t="n">
@@ -8074,13 +8074,27 @@
       <c r="E187" t="b">
         <v>0</v>
       </c>
-      <c r="F187" t="inlineStr"/>
-      <c r="G187" t="inlineStr"/>
-      <c r="H187" t="inlineStr"/>
-      <c r="I187" t="inlineStr"/>
-      <c r="J187" t="inlineStr"/>
-      <c r="K187" t="inlineStr"/>
-      <c r="L187" t="inlineStr"/>
+      <c r="F187" t="n">
+        <v>0.418</v>
+      </c>
+      <c r="G187" t="n">
+        <v>0.392</v>
+      </c>
+      <c r="H187" t="n">
+        <v>0.058</v>
+      </c>
+      <c r="I187" t="n">
+        <v>0.079</v>
+      </c>
+      <c r="J187" t="n">
+        <v>0.032</v>
+      </c>
+      <c r="K187" t="n">
+        <v>0.013</v>
+      </c>
+      <c r="L187" t="n">
+        <v>0.008</v>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -8089,11 +8103,11 @@
         </is>
       </c>
       <c r="B188" s="2" t="n">
-        <v>45776</v>
+        <v>45777</v>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>April 29, 2025</t>
+          <t>April 30, 2025</t>
         </is>
       </c>
       <c r="D188" t="n">
@@ -8117,11 +8131,11 @@
         </is>
       </c>
       <c r="B189" s="2" t="n">
-        <v>45775</v>
+        <v>45776</v>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>2025 election</t>
+          <t>April 29, 2025</t>
         </is>
       </c>
       <c r="D189" t="n">
@@ -8130,40 +8144,26 @@
       <c r="E189" t="b">
         <v>0</v>
       </c>
-      <c r="F189" t="n">
-        <v>0.4379999999999999</v>
-      </c>
-      <c r="G189" t="n">
-        <v>0.413</v>
-      </c>
-      <c r="H189" t="n">
-        <v>0.063</v>
-      </c>
-      <c r="I189" t="n">
-        <v>0.063</v>
-      </c>
-      <c r="J189" t="n">
-        <v>0.012</v>
-      </c>
-      <c r="K189" t="n">
-        <v>0.004</v>
-      </c>
-      <c r="L189" t="n">
-        <v>0.006999999999999999</v>
-      </c>
+      <c r="F189" t="inlineStr"/>
+      <c r="G189" t="inlineStr"/>
+      <c r="H189" t="inlineStr"/>
+      <c r="I189" t="inlineStr"/>
+      <c r="J189" t="inlineStr"/>
+      <c r="K189" t="inlineStr"/>
+      <c r="L189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>Quebec</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="B190" s="2" t="n">
-        <v>46139</v>
+        <v>45775</v>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Liaison Strategies</t>
+          <t>2025 election</t>
         </is>
       </c>
       <c r="D190" t="n">
@@ -8173,25 +8173,25 @@
         <v>0</v>
       </c>
       <c r="F190" t="n">
-        <v>0.42</v>
+        <v>0.4379999999999999</v>
       </c>
       <c r="G190" t="n">
-        <v>0.21</v>
+        <v>0.413</v>
       </c>
       <c r="H190" t="n">
-        <v>0.22</v>
+        <v>0.063</v>
       </c>
       <c r="I190" t="n">
-        <v>0.09</v>
+        <v>0.063</v>
       </c>
       <c r="J190" t="n">
-        <v>0.03</v>
+        <v>0.012</v>
       </c>
       <c r="K190" t="n">
-        <v>0.01</v>
+        <v>0.006999999999999999</v>
       </c>
       <c r="L190" t="n">
-        <v>0.02</v>
+        <v>0.004</v>
       </c>
     </row>
     <row r="191">
@@ -8201,11 +8201,11 @@
         </is>
       </c>
       <c r="B191" s="2" t="n">
-        <v>46132</v>
+        <v>46139</v>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Léger</t>
+          <t>Liaison Strategies</t>
         </is>
       </c>
       <c r="D191" t="n">
@@ -8215,24 +8215,26 @@
         <v>0</v>
       </c>
       <c r="F191" t="n">
-        <v>0.47</v>
+        <v>0.42</v>
       </c>
       <c r="G191" t="n">
-        <v>0.17</v>
+        <v>0.21</v>
       </c>
       <c r="H191" t="n">
-        <v>0.29</v>
+        <v>0.22</v>
       </c>
       <c r="I191" t="n">
-        <v>0.05</v>
+        <v>0.09</v>
       </c>
       <c r="J191" t="n">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="K191" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="L191" t="inlineStr"/>
+        <v>0.02</v>
+      </c>
+      <c r="L191" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -8241,7 +8243,7 @@
         </is>
       </c>
       <c r="B192" s="2" t="n">
-        <v>45971</v>
+        <v>46132</v>
       </c>
       <c r="C192" t="inlineStr">
         <is>
@@ -8255,13 +8257,13 @@
         <v>0</v>
       </c>
       <c r="F192" t="n">
-        <v>0.39</v>
+        <v>0.47</v>
       </c>
       <c r="G192" t="n">
-        <v>0.25</v>
+        <v>0.17</v>
       </c>
       <c r="H192" t="n">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="I192" t="n">
         <v>0.05</v>
@@ -8281,7 +8283,7 @@
         </is>
       </c>
       <c r="B193" s="2" t="n">
-        <v>45915</v>
+        <v>45971</v>
       </c>
       <c r="C193" t="inlineStr">
         <is>
@@ -8295,19 +8297,19 @@
         <v>0</v>
       </c>
       <c r="F193" t="n">
-        <v>0.42</v>
+        <v>0.39</v>
       </c>
       <c r="G193" t="n">
-        <v>0.21</v>
+        <v>0.25</v>
       </c>
       <c r="H193" t="n">
-        <v>0.3</v>
+        <v>0.28</v>
       </c>
       <c r="I193" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="J193" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="K193" t="n">
         <v>0.01</v>
@@ -8321,7 +8323,7 @@
         </is>
       </c>
       <c r="B194" s="2" t="n">
-        <v>45887</v>
+        <v>45915</v>
       </c>
       <c r="C194" t="inlineStr">
         <is>
@@ -8335,24 +8337,24 @@
         <v>0</v>
       </c>
       <c r="F194" t="n">
-        <v>0.43</v>
+        <v>0.42</v>
       </c>
       <c r="G194" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="H194" t="n">
-        <v>0.28</v>
+        <v>0.3</v>
       </c>
       <c r="I194" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="J194" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="K194" t="n">
-        <v>0</v>
-      </c>
-      <c r="L194" t="inlineStr"/>
+        <v>0.03</v>
+      </c>
+      <c r="K194" t="inlineStr"/>
+      <c r="L194" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -8361,7 +8363,7 @@
         </is>
       </c>
       <c r="B195" s="2" t="n">
-        <v>45830</v>
+        <v>45887</v>
       </c>
       <c r="C195" t="inlineStr">
         <is>
@@ -8375,24 +8377,24 @@
         <v>0</v>
       </c>
       <c r="F195" t="n">
-        <v>0.44</v>
+        <v>0.43</v>
       </c>
       <c r="G195" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="H195" t="n">
-        <v>0.25</v>
+        <v>0.28</v>
       </c>
       <c r="I195" t="n">
         <v>0.05</v>
       </c>
       <c r="J195" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="K195" t="n">
-        <v>0</v>
-      </c>
-      <c r="L195" t="inlineStr"/>
+        <v>0.02</v>
+      </c>
+      <c r="K195" t="inlineStr"/>
+      <c r="L195" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -8401,11 +8403,11 @@
         </is>
       </c>
       <c r="B196" s="2" t="n">
-        <v>45775</v>
+        <v>45830</v>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>2025 election</t>
+          <t>Léger</t>
         </is>
       </c>
       <c r="D196" t="n">
@@ -8415,39 +8417,37 @@
         <v>0</v>
       </c>
       <c r="F196" t="n">
-        <v>0.426</v>
+        <v>0.44</v>
       </c>
       <c r="G196" t="n">
-        <v>0.233</v>
+        <v>0.23</v>
       </c>
       <c r="H196" t="n">
-        <v>0.277</v>
+        <v>0.25</v>
       </c>
       <c r="I196" t="n">
-        <v>0.045</v>
+        <v>0.05</v>
       </c>
       <c r="J196" t="n">
-        <v>0.009000000000000001</v>
-      </c>
-      <c r="K196" t="n">
-        <v>0.002</v>
-      </c>
+        <v>0.03</v>
+      </c>
+      <c r="K196" t="inlineStr"/>
       <c r="L196" t="n">
-        <v>0.008</v>
+        <v>0</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>Ontario</t>
+          <t>Quebec</t>
         </is>
       </c>
       <c r="B197" s="2" t="n">
-        <v>45802</v>
+        <v>45775</v>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Léger</t>
+          <t>2025 election</t>
         </is>
       </c>
       <c r="D197" t="n">
@@ -8457,22 +8457,26 @@
         <v>0</v>
       </c>
       <c r="F197" t="n">
-        <v>0.54</v>
+        <v>0.426</v>
       </c>
       <c r="G197" t="n">
-        <v>0.37</v>
-      </c>
-      <c r="H197" t="inlineStr"/>
+        <v>0.233</v>
+      </c>
+      <c r="H197" t="n">
+        <v>0.277</v>
+      </c>
       <c r="I197" t="n">
-        <v>0.05</v>
+        <v>0.045</v>
       </c>
       <c r="J197" t="n">
-        <v>0.03</v>
+        <v>0.009000000000000001</v>
       </c>
       <c r="K197" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="L197" t="inlineStr"/>
+        <v>0.008</v>
+      </c>
+      <c r="L197" t="n">
+        <v>0.002</v>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -8481,11 +8485,11 @@
         </is>
       </c>
       <c r="B198" s="2" t="n">
-        <v>45775</v>
+        <v>45802</v>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>2025 election</t>
+          <t>Léger</t>
         </is>
       </c>
       <c r="D198" t="n">
@@ -8495,37 +8499,35 @@
         <v>0</v>
       </c>
       <c r="F198" t="n">
-        <v>0.49</v>
+        <v>0.54</v>
       </c>
       <c r="G198" t="n">
-        <v>0.4379999999999999</v>
+        <v>0.37</v>
       </c>
       <c r="H198" t="inlineStr"/>
       <c r="I198" t="n">
-        <v>0.049</v>
+        <v>0.05</v>
       </c>
       <c r="J198" t="n">
-        <v>0.012</v>
-      </c>
-      <c r="K198" t="n">
-        <v>0.002</v>
-      </c>
+        <v>0.03</v>
+      </c>
+      <c r="K198" t="inlineStr"/>
       <c r="L198" t="n">
-        <v>0.006999999999999999</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>Manitoba</t>
+          <t>Ontario</t>
         </is>
       </c>
       <c r="B199" s="2" t="n">
-        <v>46094</v>
+        <v>45775</v>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Probe Research</t>
+          <t>2025 election</t>
         </is>
       </c>
       <c r="D199" t="n">
@@ -8535,20 +8537,24 @@
         <v>0</v>
       </c>
       <c r="F199" t="n">
-        <v>0.46</v>
+        <v>0.49</v>
       </c>
       <c r="G199" t="n">
-        <v>0.39</v>
+        <v>0.4379999999999999</v>
       </c>
       <c r="H199" t="inlineStr"/>
       <c r="I199" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="J199" t="inlineStr"/>
+        <v>0.049</v>
+      </c>
+      <c r="J199" t="n">
+        <v>0.012</v>
+      </c>
       <c r="K199" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="L199" t="inlineStr"/>
+        <v>0.006999999999999999</v>
+      </c>
+      <c r="L199" t="n">
+        <v>0.002</v>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -8557,7 +8563,7 @@
         </is>
       </c>
       <c r="B200" s="2" t="n">
-        <v>46001</v>
+        <v>46094</v>
       </c>
       <c r="C200" t="inlineStr">
         <is>
@@ -8571,20 +8577,20 @@
         <v>0</v>
       </c>
       <c r="F200" t="n">
-        <v>0.43</v>
+        <v>0.46</v>
       </c>
       <c r="G200" t="n">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="H200" t="inlineStr"/>
       <c r="I200" t="n">
-        <v>0.14</v>
+        <v>0.08</v>
       </c>
       <c r="J200" t="inlineStr"/>
-      <c r="K200" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="L200" t="inlineStr"/>
+      <c r="K200" t="inlineStr"/>
+      <c r="L200" t="n">
+        <v>0.05</v>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -8593,11 +8599,11 @@
         </is>
       </c>
       <c r="B201" s="2" t="n">
-        <v>45775</v>
+        <v>46001</v>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>2025 election</t>
+          <t>Probe Research</t>
         </is>
       </c>
       <c r="D201" t="n">
@@ -8607,37 +8613,33 @@
         <v>0</v>
       </c>
       <c r="F201" t="n">
-        <v>0.408</v>
+        <v>0.43</v>
       </c>
       <c r="G201" t="n">
-        <v>0.463</v>
+        <v>0.38</v>
       </c>
       <c r="H201" t="inlineStr"/>
       <c r="I201" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="J201" t="n">
-        <v>0.006999999999999999</v>
-      </c>
-      <c r="K201" t="n">
-        <v>0.002</v>
-      </c>
+        <v>0.14</v>
+      </c>
+      <c r="J201" t="inlineStr"/>
+      <c r="K201" t="inlineStr"/>
       <c r="L201" t="n">
-        <v>0.01</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>Alberta</t>
+          <t>Manitoba</t>
         </is>
       </c>
       <c r="B202" s="2" t="n">
-        <v>46134</v>
+        <v>45775</v>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Mainstreet Research</t>
+          <t>2025 election</t>
         </is>
       </c>
       <c r="D202" t="n">
@@ -8647,23 +8649,23 @@
         <v>0</v>
       </c>
       <c r="F202" t="n">
-        <v>0.403</v>
+        <v>0.408</v>
       </c>
       <c r="G202" t="n">
-        <v>0.458</v>
+        <v>0.463</v>
       </c>
       <c r="H202" t="inlineStr"/>
       <c r="I202" t="n">
-        <v>0.08900000000000001</v>
+        <v>0.11</v>
       </c>
       <c r="J202" t="n">
-        <v>0.011</v>
+        <v>0.006999999999999999</v>
       </c>
       <c r="K202" t="n">
-        <v>0.014</v>
+        <v>0.01</v>
       </c>
       <c r="L202" t="n">
-        <v>0.025</v>
+        <v>0.002</v>
       </c>
     </row>
     <row r="203">
@@ -8673,11 +8675,11 @@
         </is>
       </c>
       <c r="B203" s="2" t="n">
-        <v>46078</v>
+        <v>46134</v>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Abacus Data</t>
+          <t>Mainstreet Research</t>
         </is>
       </c>
       <c r="D203" t="n">
@@ -8687,23 +8689,23 @@
         <v>0</v>
       </c>
       <c r="F203" t="n">
-        <v>0.36</v>
+        <v>0.403</v>
       </c>
       <c r="G203" t="n">
-        <v>0.51</v>
+        <v>0.458</v>
       </c>
       <c r="H203" t="inlineStr"/>
       <c r="I203" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.08900000000000001</v>
       </c>
       <c r="J203" t="n">
-        <v>0.01</v>
+        <v>0.011</v>
       </c>
       <c r="K203" t="n">
-        <v>0.02</v>
+        <v>0.025</v>
       </c>
       <c r="L203" t="n">
-        <v>0.02</v>
+        <v>0.014</v>
       </c>
     </row>
     <row r="204">
@@ -8713,11 +8715,11 @@
         </is>
       </c>
       <c r="B204" s="2" t="n">
-        <v>46065</v>
+        <v>46078</v>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Mainstreet Research</t>
+          <t>Abacus Data</t>
         </is>
       </c>
       <c r="D204" t="n">
@@ -8727,23 +8729,23 @@
         <v>0</v>
       </c>
       <c r="F204" t="n">
-        <v>0.45</v>
+        <v>0.36</v>
       </c>
       <c r="G204" t="n">
-        <v>0.48</v>
+        <v>0.51</v>
       </c>
       <c r="H204" t="inlineStr"/>
       <c r="I204" t="n">
-        <v>0.05</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="J204" t="n">
         <v>0.01</v>
       </c>
       <c r="K204" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="L204" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="205">
@@ -8753,11 +8755,11 @@
         </is>
       </c>
       <c r="B205" s="2" t="n">
-        <v>45802</v>
+        <v>46065</v>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Léger</t>
+          <t>Mainstreet Research</t>
         </is>
       </c>
       <c r="D205" t="n">
@@ -8767,22 +8769,24 @@
         <v>0</v>
       </c>
       <c r="F205" t="n">
-        <v>0.35</v>
+        <v>0.45</v>
       </c>
       <c r="G205" t="n">
-        <v>0.54</v>
+        <v>0.48</v>
       </c>
       <c r="H205" t="inlineStr"/>
       <c r="I205" t="n">
         <v>0.05</v>
       </c>
       <c r="J205" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="K205" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="L205" t="inlineStr"/>
+        <v>0.01</v>
+      </c>
+      <c r="L205" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -8791,11 +8795,11 @@
         </is>
       </c>
       <c r="B206" s="2" t="n">
-        <v>45775</v>
+        <v>45802</v>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>2025 election</t>
+          <t>Léger</t>
         </is>
       </c>
       <c r="D206" t="n">
@@ -8805,37 +8809,35 @@
         <v>0</v>
       </c>
       <c r="F206" t="n">
-        <v>0.279</v>
+        <v>0.35</v>
       </c>
       <c r="G206" t="n">
-        <v>0.635</v>
+        <v>0.54</v>
       </c>
       <c r="H206" t="inlineStr"/>
       <c r="I206" t="n">
-        <v>0.063</v>
+        <v>0.05</v>
       </c>
       <c r="J206" t="n">
-        <v>0.004</v>
-      </c>
-      <c r="K206" t="n">
-        <v>0.008</v>
-      </c>
+        <v>0.03</v>
+      </c>
+      <c r="K206" t="inlineStr"/>
       <c r="L206" t="n">
-        <v>0.009000000000000001</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>British Columbia</t>
+          <t>Alberta</t>
         </is>
       </c>
       <c r="B207" s="2" t="n">
-        <v>46125</v>
+        <v>45775</v>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Mainstreet Research</t>
+          <t>2025 election</t>
         </is>
       </c>
       <c r="D207" t="n">
@@ -8845,23 +8847,23 @@
         <v>0</v>
       </c>
       <c r="F207" t="n">
-        <v>0.512</v>
+        <v>0.279</v>
       </c>
       <c r="G207" t="n">
-        <v>0.322</v>
+        <v>0.635</v>
       </c>
       <c r="H207" t="inlineStr"/>
       <c r="I207" t="n">
-        <v>0.08800000000000001</v>
+        <v>0.063</v>
       </c>
       <c r="J207" t="n">
-        <v>0.03700000000000001</v>
+        <v>0.004</v>
       </c>
       <c r="K207" t="n">
-        <v>0.032</v>
+        <v>0.009000000000000001</v>
       </c>
       <c r="L207" t="n">
-        <v>0</v>
+        <v>0.008</v>
       </c>
     </row>
     <row r="208">
@@ -8871,7 +8873,7 @@
         </is>
       </c>
       <c r="B208" s="2" t="n">
-        <v>46094</v>
+        <v>46125</v>
       </c>
       <c r="C208" t="inlineStr">
         <is>
@@ -8885,23 +8887,23 @@
         <v>0</v>
       </c>
       <c r="F208" t="n">
-        <v>0.467</v>
+        <v>0.512</v>
       </c>
       <c r="G208" t="n">
-        <v>0.341</v>
+        <v>0.322</v>
       </c>
       <c r="H208" t="inlineStr"/>
       <c r="I208" t="n">
-        <v>0.096</v>
+        <v>0.08800000000000001</v>
       </c>
       <c r="J208" t="n">
-        <v>0.039</v>
+        <v>0.03700000000000001</v>
       </c>
       <c r="K208" t="n">
-        <v>0.043</v>
+        <v>0</v>
       </c>
       <c r="L208" t="n">
-        <v>0.014</v>
+        <v>0.032</v>
       </c>
     </row>
     <row r="209">
@@ -8911,11 +8913,11 @@
         </is>
       </c>
       <c r="B209" s="2" t="n">
-        <v>45775</v>
+        <v>46094</v>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>2025 election</t>
+          <t>Mainstreet Research</t>
         </is>
       </c>
       <c r="D209" t="n">
@@ -8925,23 +8927,63 @@
         <v>0</v>
       </c>
       <c r="F209" t="n">
-        <v>0.418</v>
+        <v>0.467</v>
       </c>
       <c r="G209" t="n">
-        <v>0.41</v>
+        <v>0.341</v>
       </c>
       <c r="H209" t="inlineStr"/>
       <c r="I209" t="n">
+        <v>0.096</v>
+      </c>
+      <c r="J209" t="n">
+        <v>0.039</v>
+      </c>
+      <c r="K209" t="n">
+        <v>0.014</v>
+      </c>
+      <c r="L209" t="n">
+        <v>0.043</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="B210" s="2" t="n">
+        <v>45775</v>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>2025 election</t>
+        </is>
+      </c>
+      <c r="D210" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E210" t="b">
+        <v>0</v>
+      </c>
+      <c r="F210" t="n">
+        <v>0.418</v>
+      </c>
+      <c r="G210" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="H210" t="inlineStr"/>
+      <c r="I210" t="n">
         <v>0.13</v>
       </c>
-      <c r="J209" t="n">
+      <c r="J210" t="n">
         <v>0.03</v>
       </c>
-      <c r="K209" t="n">
+      <c r="K210" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="L210" t="n">
         <v>0.006</v>
-      </c>
-      <c r="L209" t="n">
-        <v>0.005</v>
       </c>
     </row>
   </sheetData>

--- a/poll_averages.xlsx
+++ b/poll_averages.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L210"/>
+  <dimension ref="A1:L212"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -501,11 +501,11 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>46175</v>
+        <v>46178</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Abacus Data</t>
+          <t>Nanos Research</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -515,26 +515,24 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>0.44</v>
+        <v>0.423</v>
       </c>
       <c r="G2" t="n">
-        <v>0.36</v>
+        <v>0.294</v>
       </c>
       <c r="H2" t="n">
+        <v>0.067</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.131</v>
+      </c>
+      <c r="J2" t="n">
         <v>0.06</v>
       </c>
-      <c r="I2" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="J2" t="n">
-        <v>0.03</v>
-      </c>
       <c r="K2" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="L2" t="n">
-        <v>0</v>
-      </c>
+        <v>0.02</v>
+      </c>
+      <c r="L2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -543,11 +541,11 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>46174</v>
+        <v>46179</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Léger</t>
+          <t>Liaison Strategies</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -557,23 +555,25 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="G3" t="n">
-        <v>0.34</v>
+        <v>0.32</v>
       </c>
       <c r="H3" t="n">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I3" t="n">
-        <v>0.06</v>
+        <v>0.15</v>
       </c>
       <c r="J3" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="K3" t="inlineStr"/>
+        <v>0.03</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.02</v>
+      </c>
       <c r="L3" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="4">
@@ -583,11 +583,11 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>46173</v>
+        <v>46175</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Liaison Strategies</t>
+          <t>Abacus Data</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -597,25 +597,25 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>0.41</v>
+        <v>0.44</v>
       </c>
       <c r="G4" t="n">
-        <v>0.32</v>
+        <v>0.36</v>
       </c>
       <c r="H4" t="n">
         <v>0.06</v>
       </c>
       <c r="I4" t="n">
-        <v>0.16</v>
+        <v>0.11</v>
       </c>
       <c r="J4" t="n">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="K4" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="L4" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -625,11 +625,11 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>46171</v>
+        <v>46174</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Nanos Research</t>
+          <t>Léger</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -639,24 +639,24 @@
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>0.403</v>
+        <v>0.5</v>
       </c>
       <c r="G5" t="n">
-        <v>0.328</v>
+        <v>0.34</v>
       </c>
       <c r="H5" t="n">
-        <v>0.066</v>
+        <v>0.06</v>
       </c>
       <c r="I5" t="n">
-        <v>0.132</v>
+        <v>0.06</v>
       </c>
       <c r="J5" t="n">
-        <v>0.051</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="L5" t="inlineStr"/>
+        <v>0.02</v>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -665,11 +665,11 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>46166</v>
+        <v>46173</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Pallas Data</t>
+          <t>Liaison Strategies</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -679,21 +679,23 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>0.45</v>
+        <v>0.41</v>
       </c>
       <c r="G6" t="n">
         <v>0.32</v>
       </c>
       <c r="H6" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="I6" t="n">
-        <v>0.11</v>
+        <v>0.16</v>
       </c>
       <c r="J6" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="K6" t="inlineStr"/>
+        <v>0.02</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.02</v>
+      </c>
       <c r="L6" t="n">
         <v>0.02</v>
       </c>
@@ -705,11 +707,11 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>46165</v>
+        <v>46171</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Liaison Strategies</t>
+          <t>Nanos Research</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -719,26 +721,24 @@
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>0.43</v>
+        <v>0.403</v>
       </c>
       <c r="G7" t="n">
-        <v>0.31</v>
+        <v>0.328</v>
       </c>
       <c r="H7" t="n">
-        <v>0.06</v>
+        <v>0.066</v>
       </c>
       <c r="I7" t="n">
-        <v>0.11</v>
+        <v>0.132</v>
       </c>
       <c r="J7" t="n">
-        <v>0.02</v>
+        <v>0.051</v>
       </c>
       <c r="K7" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0.03</v>
-      </c>
+        <v>0.015</v>
+      </c>
+      <c r="L7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -747,11 +747,11 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>46164</v>
+        <v>46166</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Nanos Research</t>
+          <t>Pallas Data</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -761,24 +761,24 @@
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>0.411</v>
+        <v>0.45</v>
       </c>
       <c r="G8" t="n">
-        <v>0.327</v>
+        <v>0.32</v>
       </c>
       <c r="H8" t="n">
-        <v>0.064</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I8" t="n">
-        <v>0.126</v>
+        <v>0.11</v>
       </c>
       <c r="J8" t="n">
-        <v>0.048</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="L8" t="inlineStr"/>
+        <v>0.03</v>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="n">
+        <v>0.02</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -787,11 +787,11 @@
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>46162</v>
+        <v>46165</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Abacus Data</t>
+          <t>Liaison Strategies</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -801,24 +801,26 @@
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>0.47</v>
+        <v>0.43</v>
       </c>
       <c r="G9" t="n">
-        <v>0.35</v>
+        <v>0.31</v>
       </c>
       <c r="H9" t="n">
         <v>0.06</v>
       </c>
       <c r="I9" t="n">
-        <v>0.08</v>
+        <v>0.11</v>
       </c>
       <c r="J9" t="n">
         <v>0.02</v>
       </c>
       <c r="K9" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="L9" t="inlineStr"/>
+        <v>0.03</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.03</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -827,11 +829,11 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>46158</v>
+        <v>46164</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Liaison Strategies</t>
+          <t>Nanos Research</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -841,26 +843,24 @@
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>0.43</v>
+        <v>0.411</v>
       </c>
       <c r="G10" t="n">
-        <v>0.34</v>
+        <v>0.327</v>
       </c>
       <c r="H10" t="n">
-        <v>0.06</v>
+        <v>0.064</v>
       </c>
       <c r="I10" t="n">
-        <v>0.11</v>
+        <v>0.126</v>
       </c>
       <c r="J10" t="n">
-        <v>0.02</v>
+        <v>0.048</v>
       </c>
       <c r="K10" t="n">
         <v>0.02</v>
       </c>
-      <c r="L10" t="n">
-        <v>0.02</v>
-      </c>
+      <c r="L10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -869,11 +869,11 @@
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>46157</v>
+        <v>46162</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Nanos Research</t>
+          <t>Abacus Data</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -883,22 +883,22 @@
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>0.423</v>
+        <v>0.47</v>
       </c>
       <c r="G11" t="n">
-        <v>0.327</v>
+        <v>0.35</v>
       </c>
       <c r="H11" t="n">
-        <v>0.058</v>
+        <v>0.06</v>
       </c>
       <c r="I11" t="n">
-        <v>0.12</v>
+        <v>0.08</v>
       </c>
       <c r="J11" t="n">
-        <v>0.044</v>
+        <v>0.02</v>
       </c>
       <c r="K11" t="n">
-        <v>0.019</v>
+        <v>0.01</v>
       </c>
       <c r="L11" t="inlineStr"/>
     </row>
@@ -909,7 +909,7 @@
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>46151</v>
+        <v>46158</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -923,16 +923,16 @@
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>0.44</v>
+        <v>0.43</v>
       </c>
       <c r="G12" t="n">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="H12" t="n">
         <v>0.06</v>
       </c>
       <c r="I12" t="n">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="J12" t="n">
         <v>0.02</v>
@@ -951,7 +951,7 @@
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>46150</v>
+        <v>46157</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -965,22 +965,22 @@
         <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>0.455</v>
+        <v>0.423</v>
       </c>
       <c r="G13" t="n">
-        <v>0.334</v>
+        <v>0.327</v>
       </c>
       <c r="H13" t="n">
-        <v>0.053</v>
+        <v>0.058</v>
       </c>
       <c r="I13" t="n">
-        <v>0.08800000000000001</v>
+        <v>0.12</v>
       </c>
       <c r="J13" t="n">
-        <v>0.035</v>
+        <v>0.044</v>
       </c>
       <c r="K13" t="n">
-        <v>0.02</v>
+        <v>0.019</v>
       </c>
       <c r="L13" t="inlineStr"/>
     </row>
@@ -991,11 +991,11 @@
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>46150</v>
+        <v>46151</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Research Co.</t>
+          <t>Liaison Strategies</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -1005,25 +1005,25 @@
         <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>0.46</v>
+        <v>0.44</v>
       </c>
       <c r="G14" t="n">
-        <v>0.31</v>
+        <v>0.33</v>
       </c>
       <c r="H14" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="I14" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="J14" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="K14" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="L14" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="15">
@@ -1033,11 +1033,11 @@
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>46147</v>
+        <v>46150</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Abacus Data</t>
+          <t>Nanos Research</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -1047,26 +1047,24 @@
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>0.46</v>
+        <v>0.455</v>
       </c>
       <c r="G15" t="n">
-        <v>0.36</v>
+        <v>0.334</v>
       </c>
       <c r="H15" t="n">
-        <v>0.06</v>
+        <v>0.053</v>
       </c>
       <c r="I15" t="n">
-        <v>0.08</v>
+        <v>0.08800000000000001</v>
       </c>
       <c r="J15" t="n">
-        <v>0.03</v>
+        <v>0.035</v>
       </c>
       <c r="K15" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
+        <v>0.02</v>
+      </c>
+      <c r="L15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1075,11 +1073,11 @@
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>46144</v>
+        <v>46150</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Liaison Strategies</t>
+          <t>Research Co.</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -1089,25 +1087,25 @@
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="G16" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="H16" t="n">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I16" t="n">
-        <v>0.09</v>
+        <v>0.11</v>
       </c>
       <c r="J16" t="n">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="K16" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="L16" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="17">
@@ -1117,11 +1115,11 @@
         </is>
       </c>
       <c r="B17" s="2" t="n">
-        <v>46143</v>
+        <v>46147</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Nanos Research</t>
+          <t>Abacus Data</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1131,24 +1129,26 @@
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>0.448</v>
+        <v>0.46</v>
       </c>
       <c r="G17" t="n">
-        <v>0.32</v>
+        <v>0.36</v>
       </c>
       <c r="H17" t="n">
-        <v>0.05599999999999999</v>
+        <v>0.06</v>
       </c>
       <c r="I17" t="n">
-        <v>0.114</v>
+        <v>0.08</v>
       </c>
       <c r="J17" t="n">
-        <v>0.034</v>
+        <v>0.03</v>
       </c>
       <c r="K17" t="n">
-        <v>0.014</v>
-      </c>
-      <c r="L17" t="inlineStr"/>
+        <v>0.01</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1157,11 +1157,11 @@
         </is>
       </c>
       <c r="B18" s="2" t="n">
-        <v>46138</v>
+        <v>46144</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Léger</t>
+          <t>Liaison Strategies</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1171,23 +1171,25 @@
         <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>0.48</v>
+        <v>0.45</v>
       </c>
       <c r="G18" t="n">
-        <v>0.37</v>
+        <v>0.33</v>
       </c>
       <c r="H18" t="n">
         <v>0.06</v>
       </c>
       <c r="I18" t="n">
-        <v>0.06</v>
+        <v>0.09</v>
       </c>
       <c r="J18" t="n">
         <v>0.02</v>
       </c>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="n">
+        <v>0.02</v>
+      </c>
       <c r="L18" t="n">
-        <v>0.01</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="19">
@@ -1197,11 +1199,11 @@
         </is>
       </c>
       <c r="B19" s="2" t="n">
-        <v>46137</v>
+        <v>46143</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Liaison Strategies</t>
+          <t>Nanos Research</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1211,26 +1213,24 @@
         <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>0.45</v>
+        <v>0.448</v>
       </c>
       <c r="G19" t="n">
-        <v>0.34</v>
+        <v>0.32</v>
       </c>
       <c r="H19" t="n">
-        <v>0.06</v>
+        <v>0.05599999999999999</v>
       </c>
       <c r="I19" t="n">
-        <v>0.09</v>
+        <v>0.114</v>
       </c>
       <c r="J19" t="n">
-        <v>0.03</v>
+        <v>0.034</v>
       </c>
       <c r="K19" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0.02</v>
-      </c>
+        <v>0.014</v>
+      </c>
+      <c r="L19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1239,11 +1239,11 @@
         </is>
       </c>
       <c r="B20" s="2" t="n">
-        <v>46136</v>
+        <v>46138</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Ekos</t>
+          <t>Léger</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1253,23 +1253,21 @@
         <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>0.445</v>
+        <v>0.48</v>
       </c>
       <c r="G20" t="n">
-        <v>0.31</v>
+        <v>0.37</v>
       </c>
       <c r="H20" t="n">
-        <v>0.058</v>
+        <v>0.06</v>
       </c>
       <c r="I20" t="n">
-        <v>0.125</v>
+        <v>0.06</v>
       </c>
       <c r="J20" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0.02</v>
-      </c>
+        <v>0.02</v>
+      </c>
+      <c r="K20" t="inlineStr"/>
       <c r="L20" t="n">
         <v>0.01</v>
       </c>
@@ -1281,11 +1279,11 @@
         </is>
       </c>
       <c r="B21" s="2" t="n">
-        <v>46136</v>
+        <v>46137</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Nanos Research</t>
+          <t>Liaison Strategies</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1295,24 +1293,26 @@
         <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>0.446</v>
+        <v>0.45</v>
       </c>
       <c r="G21" t="n">
-        <v>0.32</v>
+        <v>0.34</v>
       </c>
       <c r="H21" t="n">
-        <v>0.05400000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="I21" t="n">
-        <v>0.115</v>
+        <v>0.09</v>
       </c>
       <c r="J21" t="n">
-        <v>0.035</v>
+        <v>0.03</v>
       </c>
       <c r="K21" t="n">
-        <v>0.011</v>
-      </c>
-      <c r="L21" t="inlineStr"/>
+        <v>0.02</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0.02</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1321,11 +1321,11 @@
         </is>
       </c>
       <c r="B22" s="2" t="n">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Abacus Data</t>
+          <t>Ekos</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1335,22 +1335,22 @@
         <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>0.45</v>
+        <v>0.445</v>
       </c>
       <c r="G22" t="n">
-        <v>0.36</v>
+        <v>0.31</v>
       </c>
       <c r="H22" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.058</v>
       </c>
       <c r="I22" t="n">
-        <v>0.08</v>
+        <v>0.125</v>
       </c>
       <c r="J22" t="n">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="K22" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="L22" t="n">
         <v>0.01</v>
@@ -1363,11 +1363,11 @@
         </is>
       </c>
       <c r="B23" s="2" t="n">
-        <v>46132</v>
+        <v>46136</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Angus Reid</t>
+          <t>Nanos Research</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1377,24 +1377,24 @@
         <v>0</v>
       </c>
       <c r="F23" t="n">
-        <v>0.42</v>
+        <v>0.446</v>
       </c>
       <c r="G23" t="n">
-        <v>0.35</v>
+        <v>0.32</v>
       </c>
       <c r="H23" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.05400000000000001</v>
       </c>
       <c r="I23" t="n">
-        <v>0.12</v>
+        <v>0.115</v>
       </c>
       <c r="J23" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="n">
-        <v>0.01</v>
-      </c>
+        <v>0.035</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0.011</v>
+      </c>
+      <c r="L23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1403,11 +1403,11 @@
         </is>
       </c>
       <c r="B24" s="2" t="n">
-        <v>46130</v>
+        <v>46134</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Liaison Strategies</t>
+          <t>Abacus Data</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1420,22 +1420,22 @@
         <v>0.45</v>
       </c>
       <c r="G24" t="n">
-        <v>0.33</v>
+        <v>0.36</v>
       </c>
       <c r="H24" t="n">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I24" t="n">
-        <v>0.1</v>
+        <v>0.08</v>
       </c>
       <c r="J24" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="K24" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="L24" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="25">
@@ -1445,11 +1445,11 @@
         </is>
       </c>
       <c r="B25" s="2" t="n">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Nanos Research</t>
+          <t>Angus Reid</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1459,24 +1459,24 @@
         <v>0</v>
       </c>
       <c r="F25" t="n">
-        <v>0.458</v>
+        <v>0.42</v>
       </c>
       <c r="G25" t="n">
-        <v>0.315</v>
+        <v>0.35</v>
       </c>
       <c r="H25" t="n">
-        <v>0.053</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I25" t="n">
-        <v>0.119</v>
+        <v>0.12</v>
       </c>
       <c r="J25" t="n">
-        <v>0.035</v>
-      </c>
-      <c r="K25" t="n">
-        <v>0.009000000000000001</v>
-      </c>
-      <c r="L25" t="inlineStr"/>
+        <v>0.02</v>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1485,11 +1485,11 @@
         </is>
       </c>
       <c r="B26" s="2" t="n">
-        <v>46125</v>
+        <v>46130</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>April 13, 2026</t>
+          <t>Liaison Strategies</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1498,13 +1498,27 @@
       <c r="E26" t="b">
         <v>0</v>
       </c>
-      <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
+      <c r="F26" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0.02</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1513,11 +1527,11 @@
         </is>
       </c>
       <c r="B27" s="2" t="n">
-        <v>46123</v>
+        <v>46129</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Liaison Strategies</t>
+          <t>Nanos Research</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1527,26 +1541,24 @@
         <v>0</v>
       </c>
       <c r="F27" t="n">
-        <v>0.43</v>
+        <v>0.458</v>
       </c>
       <c r="G27" t="n">
-        <v>0.33</v>
+        <v>0.315</v>
       </c>
       <c r="H27" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.053</v>
       </c>
       <c r="I27" t="n">
-        <v>0.1</v>
+        <v>0.119</v>
       </c>
       <c r="J27" t="n">
-        <v>0.03</v>
+        <v>0.035</v>
       </c>
       <c r="K27" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="L27" t="n">
-        <v>0.02</v>
-      </c>
+        <v>0.009000000000000001</v>
+      </c>
+      <c r="L27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1555,11 +1567,11 @@
         </is>
       </c>
       <c r="B28" s="2" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Nanos Research</t>
+          <t>April 13, 2026</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1568,24 +1580,12 @@
       <c r="E28" t="b">
         <v>0</v>
       </c>
-      <c r="F28" t="n">
-        <v>0.453</v>
-      </c>
-      <c r="G28" t="n">
-        <v>0.32</v>
-      </c>
-      <c r="H28" t="n">
-        <v>0.05400000000000001</v>
-      </c>
-      <c r="I28" t="n">
-        <v>0.122</v>
-      </c>
-      <c r="J28" t="n">
-        <v>0.035</v>
-      </c>
-      <c r="K28" t="n">
-        <v>0.01</v>
-      </c>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
     </row>
     <row r="29">
@@ -1595,11 +1595,11 @@
         </is>
       </c>
       <c r="B29" s="2" t="n">
-        <v>46120</v>
+        <v>46123</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Spark Insights</t>
+          <t>Liaison Strategies</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1609,21 +1609,25 @@
         <v>0</v>
       </c>
       <c r="F29" t="n">
-        <v>0.46</v>
+        <v>0.43</v>
       </c>
       <c r="G29" t="n">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="H29" t="n">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I29" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
+        <v>0.1</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0.02</v>
+      </c>
       <c r="L29" t="n">
-        <v>0.08</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="30">
@@ -1633,11 +1637,11 @@
         </is>
       </c>
       <c r="B30" s="2" t="n">
-        <v>46120</v>
+        <v>46122</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Abacus Data</t>
+          <t>Nanos Research</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1647,26 +1651,24 @@
         <v>0</v>
       </c>
       <c r="F30" t="n">
-        <v>0.44</v>
+        <v>0.453</v>
       </c>
       <c r="G30" t="n">
-        <v>0.38</v>
+        <v>0.32</v>
       </c>
       <c r="H30" t="n">
-        <v>0.06</v>
+        <v>0.05400000000000001</v>
       </c>
       <c r="I30" t="n">
-        <v>0.08</v>
+        <v>0.122</v>
       </c>
       <c r="J30" t="n">
-        <v>0.03</v>
+        <v>0.035</v>
       </c>
       <c r="K30" t="n">
         <v>0.01</v>
       </c>
-      <c r="L30" t="n">
-        <v>0.01</v>
-      </c>
+      <c r="L30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1675,11 +1677,11 @@
         </is>
       </c>
       <c r="B31" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Ipsos</t>
+          <t>Spark Insights</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1689,25 +1691,21 @@
         <v>0</v>
       </c>
       <c r="F31" t="n">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="G31" t="n">
-        <v>0.33</v>
+        <v>0.32</v>
       </c>
       <c r="H31" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="I31" t="n">
         <v>0.09</v>
       </c>
-      <c r="J31" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="K31" t="n">
-        <v>0.02</v>
-      </c>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="32">
@@ -1717,11 +1715,11 @@
         </is>
       </c>
       <c r="B32" s="2" t="n">
-        <v>46116</v>
+        <v>46120</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Liaison Strategies</t>
+          <t>Abacus Data</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1734,22 +1732,22 @@
         <v>0.44</v>
       </c>
       <c r="G32" t="n">
-        <v>0.33</v>
+        <v>0.38</v>
       </c>
       <c r="H32" t="n">
         <v>0.06</v>
       </c>
       <c r="I32" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="J32" t="n">
         <v>0.03</v>
       </c>
       <c r="K32" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="L32" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="33">
@@ -1759,11 +1757,11 @@
         </is>
       </c>
       <c r="B33" s="2" t="n">
-        <v>46115</v>
+        <v>46119</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Nanos Research</t>
+          <t>Ipsos</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1773,24 +1771,26 @@
         <v>0</v>
       </c>
       <c r="F33" t="n">
-        <v>0.457</v>
+        <v>0.45</v>
       </c>
       <c r="G33" t="n">
-        <v>0.305</v>
+        <v>0.33</v>
       </c>
       <c r="H33" t="n">
-        <v>0.05599999999999999</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I33" t="n">
-        <v>0.125</v>
+        <v>0.09</v>
       </c>
       <c r="J33" t="n">
-        <v>0.042</v>
+        <v>0.02</v>
       </c>
       <c r="K33" t="n">
-        <v>0.011</v>
-      </c>
-      <c r="L33" t="inlineStr"/>
+        <v>0.02</v>
+      </c>
+      <c r="L33" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1799,11 +1799,11 @@
         </is>
       </c>
       <c r="B34" s="2" t="n">
-        <v>46111</v>
+        <v>46116</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Léger</t>
+          <t>Liaison Strategies</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1813,23 +1813,25 @@
         <v>0</v>
       </c>
       <c r="F34" t="n">
-        <v>0.48</v>
+        <v>0.44</v>
       </c>
       <c r="G34" t="n">
-        <v>0.34</v>
+        <v>0.33</v>
       </c>
       <c r="H34" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="I34" t="n">
-        <v>0.06</v>
+        <v>0.09</v>
       </c>
       <c r="J34" t="n">
         <v>0.03</v>
       </c>
-      <c r="K34" t="inlineStr"/>
+      <c r="K34" t="n">
+        <v>0.02</v>
+      </c>
       <c r="L34" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="35">
@@ -1839,11 +1841,11 @@
         </is>
       </c>
       <c r="B35" s="2" t="n">
-        <v>46110</v>
+        <v>46115</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>March 29, 2026</t>
+          <t>Nanos Research</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1852,12 +1854,24 @@
       <c r="E35" t="b">
         <v>0</v>
       </c>
-      <c r="F35" t="inlineStr"/>
-      <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr"/>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
+      <c r="F35" t="n">
+        <v>0.457</v>
+      </c>
+      <c r="G35" t="n">
+        <v>0.305</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0.05599999999999999</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="J35" t="n">
+        <v>0.042</v>
+      </c>
+      <c r="K35" t="n">
+        <v>0.011</v>
+      </c>
       <c r="L35" t="inlineStr"/>
     </row>
     <row r="36">
@@ -1867,11 +1881,11 @@
         </is>
       </c>
       <c r="B36" s="2" t="n">
-        <v>46109</v>
+        <v>46111</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Liaison Strategies</t>
+          <t>Léger</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1881,25 +1895,23 @@
         <v>0</v>
       </c>
       <c r="F36" t="n">
-        <v>0.45</v>
+        <v>0.48</v>
       </c>
       <c r="G36" t="n">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="H36" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="I36" t="n">
         <v>0.06</v>
       </c>
-      <c r="I36" t="n">
-        <v>0.09</v>
-      </c>
       <c r="J36" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="K36" t="n">
-        <v>0.02</v>
-      </c>
+        <v>0.03</v>
+      </c>
+      <c r="K36" t="inlineStr"/>
       <c r="L36" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="37">
@@ -1909,11 +1921,11 @@
         </is>
       </c>
       <c r="B37" s="2" t="n">
-        <v>46108</v>
+        <v>46110</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Nanos Research</t>
+          <t>March 29, 2026</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1922,24 +1934,12 @@
       <c r="E37" t="b">
         <v>0</v>
       </c>
-      <c r="F37" t="n">
-        <v>0.465</v>
-      </c>
-      <c r="G37" t="n">
-        <v>0.322</v>
-      </c>
-      <c r="H37" t="n">
-        <v>0.051</v>
-      </c>
-      <c r="I37" t="n">
-        <v>0.113</v>
-      </c>
-      <c r="J37" t="n">
-        <v>0.036</v>
-      </c>
-      <c r="K37" t="n">
-        <v>0.011</v>
-      </c>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
     </row>
     <row r="38">
@@ -1949,11 +1949,11 @@
         </is>
       </c>
       <c r="B38" s="2" t="n">
-        <v>46107</v>
+        <v>46109</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Spark Insights</t>
+          <t>Liaison Strategies</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1963,21 +1963,25 @@
         <v>0</v>
       </c>
       <c r="F38" t="n">
-        <v>0.46</v>
+        <v>0.45</v>
       </c>
       <c r="G38" t="n">
-        <v>0.3</v>
+        <v>0.33</v>
       </c>
       <c r="H38" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="I38" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
+        <v>0.09</v>
+      </c>
+      <c r="J38" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="K38" t="n">
+        <v>0.02</v>
+      </c>
       <c r="L38" t="n">
-        <v>0.08</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="39">
@@ -1987,11 +1991,11 @@
         </is>
       </c>
       <c r="B39" s="2" t="n">
-        <v>46105</v>
+        <v>46108</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Abacus Data</t>
+          <t>Nanos Research</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -2001,26 +2005,24 @@
         <v>0</v>
       </c>
       <c r="F39" t="n">
-        <v>0.44</v>
+        <v>0.465</v>
       </c>
       <c r="G39" t="n">
-        <v>0.37</v>
+        <v>0.322</v>
       </c>
       <c r="H39" t="n">
-        <v>0.06</v>
+        <v>0.051</v>
       </c>
       <c r="I39" t="n">
-        <v>0.09</v>
+        <v>0.113</v>
       </c>
       <c r="J39" t="n">
-        <v>0.03</v>
+        <v>0.036</v>
       </c>
       <c r="K39" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="L39" t="n">
-        <v>0</v>
-      </c>
+        <v>0.011</v>
+      </c>
+      <c r="L39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2029,11 +2031,11 @@
         </is>
       </c>
       <c r="B40" s="2" t="n">
-        <v>46102</v>
+        <v>46107</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Liaison Strategies</t>
+          <t>Spark Insights</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -2046,22 +2048,18 @@
         <v>0.46</v>
       </c>
       <c r="G40" t="n">
-        <v>0.32</v>
+        <v>0.3</v>
       </c>
       <c r="H40" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.05</v>
       </c>
       <c r="I40" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="J40" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="K40" t="n">
-        <v>0.02</v>
-      </c>
+        <v>0.11</v>
+      </c>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
       <c r="L40" t="n">
-        <v>0.02</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="41">
@@ -2071,11 +2069,11 @@
         </is>
       </c>
       <c r="B41" s="2" t="n">
-        <v>46101</v>
+        <v>46105</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Nanos Research</t>
+          <t>Abacus Data</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -2085,24 +2083,26 @@
         <v>0</v>
       </c>
       <c r="F41" t="n">
-        <v>0.457</v>
+        <v>0.44</v>
       </c>
       <c r="G41" t="n">
-        <v>0.329</v>
+        <v>0.37</v>
       </c>
       <c r="H41" t="n">
-        <v>0.048</v>
+        <v>0.06</v>
       </c>
       <c r="I41" t="n">
-        <v>0.115</v>
+        <v>0.09</v>
       </c>
       <c r="J41" t="n">
-        <v>0.03700000000000001</v>
+        <v>0.03</v>
       </c>
       <c r="K41" t="n">
-        <v>0.008</v>
-      </c>
-      <c r="L41" t="inlineStr"/>
+        <v>0.01</v>
+      </c>
+      <c r="L41" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2111,11 +2111,11 @@
         </is>
       </c>
       <c r="B42" s="2" t="n">
-        <v>46098</v>
+        <v>46102</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Angus Reid</t>
+          <t>Liaison Strategies</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -2125,10 +2125,10 @@
         <v>0</v>
       </c>
       <c r="F42" t="n">
-        <v>0.44</v>
+        <v>0.46</v>
       </c>
       <c r="G42" t="n">
-        <v>0.36</v>
+        <v>0.32</v>
       </c>
       <c r="H42" t="n">
         <v>0.07000000000000001</v>
@@ -2137,11 +2137,13 @@
         <v>0.09</v>
       </c>
       <c r="J42" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="K42" t="inlineStr"/>
+        <v>0.03</v>
+      </c>
+      <c r="K42" t="n">
+        <v>0.02</v>
+      </c>
       <c r="L42" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="43">
@@ -2151,11 +2153,11 @@
         </is>
       </c>
       <c r="B43" s="2" t="n">
-        <v>46096</v>
+        <v>46101</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Ekos</t>
+          <t>Nanos Research</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -2165,26 +2167,24 @@
         <v>0</v>
       </c>
       <c r="F43" t="n">
-        <v>0.475</v>
+        <v>0.457</v>
       </c>
       <c r="G43" t="n">
-        <v>0.27</v>
+        <v>0.329</v>
       </c>
       <c r="H43" t="n">
-        <v>0.04099999999999999</v>
+        <v>0.048</v>
       </c>
       <c r="I43" t="n">
-        <v>0.151</v>
+        <v>0.115</v>
       </c>
       <c r="J43" t="n">
-        <v>0.045</v>
+        <v>0.03700000000000001</v>
       </c>
       <c r="K43" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="L43" t="n">
-        <v>0.004</v>
-      </c>
+        <v>0.008</v>
+      </c>
+      <c r="L43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2193,11 +2193,11 @@
         </is>
       </c>
       <c r="B44" s="2" t="n">
-        <v>46095</v>
+        <v>46098</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Liaison Strategies</t>
+          <t>Angus Reid</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -2207,25 +2207,23 @@
         <v>0</v>
       </c>
       <c r="F44" t="n">
-        <v>0.45</v>
+        <v>0.44</v>
       </c>
       <c r="G44" t="n">
-        <v>0.31</v>
+        <v>0.36</v>
       </c>
       <c r="H44" t="n">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I44" t="n">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="J44" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="K44" t="n">
-        <v>0.04</v>
-      </c>
+        <v>0.02</v>
+      </c>
+      <c r="K44" t="inlineStr"/>
       <c r="L44" t="n">
-        <v>0.04</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="45">
@@ -2235,11 +2233,11 @@
         </is>
       </c>
       <c r="B45" s="2" t="n">
-        <v>46094</v>
+        <v>46096</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Nanos Research</t>
+          <t>Ekos</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2249,24 +2247,26 @@
         <v>0</v>
       </c>
       <c r="F45" t="n">
-        <v>0.478</v>
+        <v>0.475</v>
       </c>
       <c r="G45" t="n">
-        <v>0.311</v>
+        <v>0.27</v>
       </c>
       <c r="H45" t="n">
+        <v>0.04099999999999999</v>
+      </c>
+      <c r="I45" t="n">
+        <v>0.151</v>
+      </c>
+      <c r="J45" t="n">
         <v>0.045</v>
       </c>
-      <c r="I45" t="n">
-        <v>0.112</v>
-      </c>
-      <c r="J45" t="n">
-        <v>0.04</v>
-      </c>
       <c r="K45" t="n">
-        <v>0.011</v>
-      </c>
-      <c r="L45" t="inlineStr"/>
+        <v>0.015</v>
+      </c>
+      <c r="L45" t="n">
+        <v>0.004</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2275,11 +2275,11 @@
         </is>
       </c>
       <c r="B46" s="2" t="n">
-        <v>46092</v>
+        <v>46095</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Abacus Data</t>
+          <t>Liaison Strategies</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2289,25 +2289,25 @@
         <v>0</v>
       </c>
       <c r="F46" t="n">
-        <v>0.46</v>
+        <v>0.45</v>
       </c>
       <c r="G46" t="n">
-        <v>0.35</v>
+        <v>0.31</v>
       </c>
       <c r="H46" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="I46" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="J46" t="n">
         <v>0.03</v>
       </c>
       <c r="K46" t="n">
-        <v>0.01</v>
+        <v>0.04</v>
       </c>
       <c r="L46" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="47">
@@ -2317,11 +2317,11 @@
         </is>
       </c>
       <c r="B47" s="2" t="n">
-        <v>46088</v>
+        <v>46094</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Liaison Strategies</t>
+          <t>Nanos Research</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2331,26 +2331,24 @@
         <v>0</v>
       </c>
       <c r="F47" t="n">
-        <v>0.44</v>
+        <v>0.478</v>
       </c>
       <c r="G47" t="n">
-        <v>0.3</v>
+        <v>0.311</v>
       </c>
       <c r="H47" t="n">
-        <v>0.06</v>
+        <v>0.045</v>
       </c>
       <c r="I47" t="n">
-        <v>0.09</v>
+        <v>0.112</v>
       </c>
       <c r="J47" t="n">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="K47" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="L47" t="n">
-        <v>0.03</v>
-      </c>
+        <v>0.011</v>
+      </c>
+      <c r="L47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2359,11 +2357,11 @@
         </is>
       </c>
       <c r="B48" s="2" t="n">
-        <v>46087</v>
+        <v>46092</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Spark Insights</t>
+          <t>Abacus Data</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2376,18 +2374,22 @@
         <v>0.46</v>
       </c>
       <c r="G48" t="n">
-        <v>0.31</v>
+        <v>0.35</v>
       </c>
       <c r="H48" t="n">
-        <v>0.05</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I48" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="J48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="J48" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="K48" t="n">
+        <v>0.01</v>
+      </c>
       <c r="L48" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -2397,11 +2399,11 @@
         </is>
       </c>
       <c r="B49" s="2" t="n">
-        <v>46087</v>
+        <v>46088</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Nanos Research</t>
+          <t>Liaison Strategies</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2411,24 +2413,26 @@
         <v>0</v>
       </c>
       <c r="F49" t="n">
-        <v>0.46</v>
+        <v>0.44</v>
       </c>
       <c r="G49" t="n">
-        <v>0.325</v>
+        <v>0.3</v>
       </c>
       <c r="H49" t="n">
-        <v>0.052</v>
+        <v>0.06</v>
       </c>
       <c r="I49" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="J49" t="n">
-        <v>0.047</v>
+        <v>0.03</v>
       </c>
       <c r="K49" t="n">
-        <v>0.006999999999999999</v>
-      </c>
-      <c r="L49" t="inlineStr"/>
+        <v>0.04</v>
+      </c>
+      <c r="L49" t="n">
+        <v>0.03</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2437,11 +2441,11 @@
         </is>
       </c>
       <c r="B50" s="2" t="n">
-        <v>46083</v>
+        <v>46087</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Mainstreet Research</t>
+          <t>Spark Insights</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2454,22 +2458,18 @@
         <v>0.46</v>
       </c>
       <c r="G50" t="n">
-        <v>0.36</v>
+        <v>0.31</v>
       </c>
       <c r="H50" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="I50" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="J50" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="K50" t="n">
-        <v>0.03</v>
-      </c>
+        <v>0.1</v>
+      </c>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
       <c r="L50" t="n">
-        <v>0.02</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="51">
@@ -2479,11 +2479,11 @@
         </is>
       </c>
       <c r="B51" s="2" t="n">
-        <v>46083</v>
+        <v>46087</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Léger</t>
+          <t>Nanos Research</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2493,24 +2493,24 @@
         <v>0</v>
       </c>
       <c r="F51" t="n">
-        <v>0.49</v>
+        <v>0.46</v>
       </c>
       <c r="G51" t="n">
-        <v>0.35</v>
+        <v>0.325</v>
       </c>
       <c r="H51" t="n">
-        <v>0.05</v>
+        <v>0.052</v>
       </c>
       <c r="I51" t="n">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="J51" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="n">
-        <v>0.02</v>
-      </c>
+        <v>0.047</v>
+      </c>
+      <c r="K51" t="n">
+        <v>0.006999999999999999</v>
+      </c>
+      <c r="L51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2519,11 +2519,11 @@
         </is>
       </c>
       <c r="B52" s="2" t="n">
-        <v>46081</v>
+        <v>46083</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Liaison Strategies</t>
+          <t>Mainstreet Research</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2533,22 +2533,22 @@
         <v>0</v>
       </c>
       <c r="F52" t="n">
-        <v>0.43</v>
+        <v>0.46</v>
       </c>
       <c r="G52" t="n">
-        <v>0.33</v>
+        <v>0.36</v>
       </c>
       <c r="H52" t="n">
-        <v>0.06</v>
+        <v>0.04</v>
       </c>
       <c r="I52" t="n">
-        <v>0.09</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="J52" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="K52" t="n">
         <v>0.03</v>
-      </c>
-      <c r="K52" t="n">
-        <v>0.02</v>
       </c>
       <c r="L52" t="n">
         <v>0.02</v>
@@ -2561,11 +2561,11 @@
         </is>
       </c>
       <c r="B53" s="2" t="n">
-        <v>46080</v>
+        <v>46083</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Nanos Research</t>
+          <t>Léger</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2575,24 +2575,24 @@
         <v>0</v>
       </c>
       <c r="F53" t="n">
-        <v>0.436</v>
+        <v>0.49</v>
       </c>
       <c r="G53" t="n">
-        <v>0.332</v>
+        <v>0.35</v>
       </c>
       <c r="H53" t="n">
-        <v>0.051</v>
+        <v>0.05</v>
       </c>
       <c r="I53" t="n">
-        <v>0.114</v>
+        <v>0.05</v>
       </c>
       <c r="J53" t="n">
-        <v>0.049</v>
-      </c>
-      <c r="K53" t="n">
-        <v>0.006999999999999999</v>
-      </c>
-      <c r="L53" t="inlineStr"/>
+        <v>0.03</v>
+      </c>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="n">
+        <v>0.02</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2601,11 +2601,11 @@
         </is>
       </c>
       <c r="B54" s="2" t="n">
-        <v>46079</v>
+        <v>46081</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Ipsos</t>
+          <t>Liaison Strategies</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2615,25 +2615,25 @@
         <v>0</v>
       </c>
       <c r="F54" t="n">
-        <v>0.44</v>
+        <v>0.43</v>
       </c>
       <c r="G54" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="H54" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="I54" t="n">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="J54" t="n">
         <v>0.03</v>
       </c>
       <c r="K54" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="L54" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="55">
@@ -2643,11 +2643,11 @@
         </is>
       </c>
       <c r="B55" s="2" t="n">
-        <v>46077</v>
+        <v>46080</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Pollara</t>
+          <t>Nanos Research</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2657,22 +2657,24 @@
         <v>0</v>
       </c>
       <c r="F55" t="n">
-        <v>0.47</v>
+        <v>0.436</v>
       </c>
       <c r="G55" t="n">
-        <v>0.34</v>
+        <v>0.332</v>
       </c>
       <c r="H55" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.051</v>
       </c>
       <c r="I55" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="J55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
-      <c r="L55" t="n">
-        <v>0.03</v>
-      </c>
+        <v>0.114</v>
+      </c>
+      <c r="J55" t="n">
+        <v>0.049</v>
+      </c>
+      <c r="K55" t="n">
+        <v>0.006999999999999999</v>
+      </c>
+      <c r="L55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2681,11 +2683,11 @@
         </is>
       </c>
       <c r="B56" s="2" t="n">
-        <v>46076</v>
+        <v>46079</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Abacus Data</t>
+          <t>Ipsos</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2698,13 +2700,13 @@
         <v>0.44</v>
       </c>
       <c r="G56" t="n">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="H56" t="n">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I56" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="J56" t="n">
         <v>0.03</v>
@@ -2723,11 +2725,11 @@
         </is>
       </c>
       <c r="B57" s="2" t="n">
-        <v>46076</v>
+        <v>46077</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Angus Reid</t>
+          <t>Pollara</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2737,23 +2739,21 @@
         <v>0</v>
       </c>
       <c r="F57" t="n">
-        <v>0.45</v>
+        <v>0.47</v>
       </c>
       <c r="G57" t="n">
-        <v>0.32</v>
+        <v>0.34</v>
       </c>
       <c r="H57" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="I57" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="J57" t="n">
-        <v>0.04</v>
-      </c>
+        <v>0.09</v>
+      </c>
+      <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr"/>
       <c r="L57" t="n">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="58">
@@ -2763,11 +2763,11 @@
         </is>
       </c>
       <c r="B58" s="2" t="n">
-        <v>46074</v>
+        <v>46076</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Liaison Strategies</t>
+          <t>Abacus Data</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2777,25 +2777,25 @@
         <v>0</v>
       </c>
       <c r="F58" t="n">
-        <v>0.45</v>
+        <v>0.44</v>
       </c>
       <c r="G58" t="n">
-        <v>0.33</v>
+        <v>0.38</v>
       </c>
       <c r="H58" t="n">
         <v>0.06</v>
       </c>
       <c r="I58" t="n">
-        <v>0.1</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="J58" t="n">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="K58" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="L58" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59">
@@ -2805,11 +2805,11 @@
         </is>
       </c>
       <c r="B59" s="2" t="n">
-        <v>46073</v>
+        <v>46076</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Nanos Research</t>
+          <t>Angus Reid</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2819,24 +2819,24 @@
         <v>0</v>
       </c>
       <c r="F59" t="n">
-        <v>0.413</v>
+        <v>0.45</v>
       </c>
       <c r="G59" t="n">
-        <v>0.337</v>
+        <v>0.32</v>
       </c>
       <c r="H59" t="n">
-        <v>0.076</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I59" t="n">
-        <v>0.106</v>
+        <v>0.1</v>
       </c>
       <c r="J59" t="n">
-        <v>0.049</v>
-      </c>
-      <c r="K59" t="n">
-        <v>0.009000000000000001</v>
-      </c>
-      <c r="L59" t="inlineStr"/>
+        <v>0.04</v>
+      </c>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="n">
+        <v>0.02</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -2845,11 +2845,11 @@
         </is>
       </c>
       <c r="B60" s="2" t="n">
-        <v>46070</v>
+        <v>46074</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Innovative Research</t>
+          <t>Liaison Strategies</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2859,23 +2859,25 @@
         <v>0</v>
       </c>
       <c r="F60" t="n">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="G60" t="n">
-        <v>0.37</v>
+        <v>0.33</v>
       </c>
       <c r="H60" t="n">
         <v>0.06</v>
       </c>
       <c r="I60" t="n">
-        <v>0.08</v>
+        <v>0.1</v>
       </c>
       <c r="J60" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="K60" t="inlineStr"/>
+        <v>0.02</v>
+      </c>
+      <c r="K60" t="n">
+        <v>0.02</v>
+      </c>
       <c r="L60" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="61">
@@ -2885,11 +2887,11 @@
         </is>
       </c>
       <c r="B61" s="2" t="n">
-        <v>46067</v>
+        <v>46073</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Liaison Strategies</t>
+          <t>Nanos Research</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2899,26 +2901,24 @@
         <v>0</v>
       </c>
       <c r="F61" t="n">
-        <v>0.43</v>
+        <v>0.413</v>
       </c>
       <c r="G61" t="n">
-        <v>0.34</v>
+        <v>0.337</v>
       </c>
       <c r="H61" t="n">
-        <v>0.06</v>
+        <v>0.076</v>
       </c>
       <c r="I61" t="n">
-        <v>0.09</v>
+        <v>0.106</v>
       </c>
       <c r="J61" t="n">
-        <v>0.03</v>
+        <v>0.049</v>
       </c>
       <c r="K61" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="L61" t="n">
-        <v>0.02</v>
-      </c>
+        <v>0.009000000000000001</v>
+      </c>
+      <c r="L61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -2927,11 +2927,11 @@
         </is>
       </c>
       <c r="B62" s="2" t="n">
-        <v>46066</v>
+        <v>46070</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Nanos Research</t>
+          <t>Innovative Research</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2941,24 +2941,24 @@
         <v>0</v>
       </c>
       <c r="F62" t="n">
-        <v>0.381</v>
+        <v>0.44</v>
       </c>
       <c r="G62" t="n">
-        <v>0.365</v>
+        <v>0.37</v>
       </c>
       <c r="H62" t="n">
-        <v>0.083</v>
+        <v>0.06</v>
       </c>
       <c r="I62" t="n">
-        <v>0.111</v>
+        <v>0.08</v>
       </c>
       <c r="J62" t="n">
-        <v>0.044</v>
-      </c>
-      <c r="K62" t="n">
-        <v>0.006999999999999999</v>
-      </c>
-      <c r="L62" t="inlineStr"/>
+        <v>0.03</v>
+      </c>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="n">
+        <v>0.03</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -2967,11 +2967,11 @@
         </is>
       </c>
       <c r="B63" s="2" t="n">
-        <v>46063</v>
+        <v>46067</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Abacus Data</t>
+          <t>Liaison Strategies</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2981,25 +2981,25 @@
         <v>0</v>
       </c>
       <c r="F63" t="n">
-        <v>0.44</v>
+        <v>0.43</v>
       </c>
       <c r="G63" t="n">
-        <v>0.37</v>
+        <v>0.34</v>
       </c>
       <c r="H63" t="n">
         <v>0.06</v>
       </c>
       <c r="I63" t="n">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="J63" t="n">
         <v>0.03</v>
       </c>
       <c r="K63" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="L63" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="64">
@@ -3009,11 +3009,11 @@
         </is>
       </c>
       <c r="B64" s="2" t="n">
-        <v>46060</v>
+        <v>46066</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Liaison Strategies</t>
+          <t>Nanos Research</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -3023,26 +3023,24 @@
         <v>0</v>
       </c>
       <c r="F64" t="n">
-        <v>0.42</v>
+        <v>0.381</v>
       </c>
       <c r="G64" t="n">
-        <v>0.35</v>
+        <v>0.365</v>
       </c>
       <c r="H64" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.083</v>
       </c>
       <c r="I64" t="n">
-        <v>0.09</v>
+        <v>0.111</v>
       </c>
       <c r="J64" t="n">
-        <v>0.03</v>
+        <v>0.044</v>
       </c>
       <c r="K64" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="L64" t="n">
-        <v>0.02</v>
-      </c>
+        <v>0.006999999999999999</v>
+      </c>
+      <c r="L64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -3051,11 +3049,11 @@
         </is>
       </c>
       <c r="B65" s="2" t="n">
-        <v>46059</v>
+        <v>46063</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Nanos Research</t>
+          <t>Abacus Data</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -3065,24 +3063,26 @@
         <v>0</v>
       </c>
       <c r="F65" t="n">
-        <v>0.391</v>
+        <v>0.44</v>
       </c>
       <c r="G65" t="n">
-        <v>0.352</v>
+        <v>0.37</v>
       </c>
       <c r="H65" t="n">
-        <v>0.08800000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="I65" t="n">
-        <v>0.126</v>
+        <v>0.08</v>
       </c>
       <c r="J65" t="n">
-        <v>0.029</v>
+        <v>0.03</v>
       </c>
       <c r="K65" t="n">
-        <v>0.009000000000000001</v>
-      </c>
-      <c r="L65" t="inlineStr"/>
+        <v>0.01</v>
+      </c>
+      <c r="L65" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -3091,11 +3091,11 @@
         </is>
       </c>
       <c r="B66" s="2" t="n">
-        <v>46058</v>
+        <v>46060</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Research Co.</t>
+          <t>Liaison Strategies</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -3105,16 +3105,16 @@
         <v>0</v>
       </c>
       <c r="F66" t="n">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="G66" t="n">
-        <v>0.32</v>
+        <v>0.35</v>
       </c>
       <c r="H66" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="I66" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="J66" t="n">
         <v>0.03</v>
@@ -3123,7 +3123,7 @@
         <v>0.02</v>
       </c>
       <c r="L66" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="67">
@@ -3133,11 +3133,11 @@
         </is>
       </c>
       <c r="B67" s="2" t="n">
-        <v>46055</v>
+        <v>46059</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Innovative Research</t>
+          <t>Nanos Research</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -3147,24 +3147,24 @@
         <v>0</v>
       </c>
       <c r="F67" t="n">
-        <v>0.4</v>
+        <v>0.391</v>
       </c>
       <c r="G67" t="n">
-        <v>0.38</v>
+        <v>0.352</v>
       </c>
       <c r="H67" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.08800000000000001</v>
       </c>
       <c r="I67" t="n">
-        <v>0.1</v>
+        <v>0.126</v>
       </c>
       <c r="J67" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="K67" t="inlineStr"/>
-      <c r="L67" t="n">
-        <v>0.02</v>
-      </c>
+        <v>0.029</v>
+      </c>
+      <c r="K67" t="n">
+        <v>0.009000000000000001</v>
+      </c>
+      <c r="L67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -3173,11 +3173,11 @@
         </is>
       </c>
       <c r="B68" s="2" t="n">
-        <v>46055</v>
+        <v>46058</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Mainstreet Research</t>
+          <t>Research Co.</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -3187,25 +3187,25 @@
         <v>0</v>
       </c>
       <c r="F68" t="n">
-        <v>0.51</v>
+        <v>0.45</v>
       </c>
       <c r="G68" t="n">
-        <v>0.355</v>
+        <v>0.32</v>
       </c>
       <c r="H68" t="n">
-        <v>0.055</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I68" t="n">
-        <v>0.04</v>
+        <v>0.1</v>
       </c>
       <c r="J68" t="n">
-        <v>0.022</v>
+        <v>0.03</v>
       </c>
       <c r="K68" t="n">
-        <v>0.006</v>
+        <v>0.02</v>
       </c>
       <c r="L68" t="n">
-        <v>0.011</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="69">
@@ -3215,11 +3215,11 @@
         </is>
       </c>
       <c r="B69" s="2" t="n">
-        <v>46053</v>
+        <v>46055</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Liaison Strategies</t>
+          <t>Innovative Research</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -3229,23 +3229,21 @@
         <v>0</v>
       </c>
       <c r="F69" t="n">
-        <v>0.43</v>
+        <v>0.4</v>
       </c>
       <c r="G69" t="n">
-        <v>0.35</v>
+        <v>0.38</v>
       </c>
       <c r="H69" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="I69" t="n">
-        <v>0.08</v>
+        <v>0.1</v>
       </c>
       <c r="J69" t="n">
         <v>0.03</v>
       </c>
-      <c r="K69" t="n">
-        <v>0.02</v>
-      </c>
+      <c r="K69" t="inlineStr"/>
       <c r="L69" t="n">
         <v>0.02</v>
       </c>
@@ -3257,11 +3255,11 @@
         </is>
       </c>
       <c r="B70" s="2" t="n">
-        <v>46052</v>
+        <v>46055</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Ekos</t>
+          <t>Mainstreet Research</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -3271,25 +3269,25 @@
         <v>0</v>
       </c>
       <c r="F70" t="n">
-        <v>0.444</v>
+        <v>0.51</v>
       </c>
       <c r="G70" t="n">
-        <v>0.295</v>
+        <v>0.355</v>
       </c>
       <c r="H70" t="n">
-        <v>0.053</v>
+        <v>0.055</v>
       </c>
       <c r="I70" t="n">
-        <v>0.138</v>
+        <v>0.04</v>
       </c>
       <c r="J70" t="n">
-        <v>0.039</v>
+        <v>0.022</v>
       </c>
       <c r="K70" t="n">
-        <v>0.016</v>
+        <v>0.006</v>
       </c>
       <c r="L70" t="n">
-        <v>0.015</v>
+        <v>0.011</v>
       </c>
     </row>
     <row r="71">
@@ -3299,11 +3297,11 @@
         </is>
       </c>
       <c r="B71" s="2" t="n">
-        <v>46052</v>
+        <v>46053</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Nanos Research</t>
+          <t>Liaison Strategies</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -3313,24 +3311,26 @@
         <v>0</v>
       </c>
       <c r="F71" t="n">
-        <v>0.389</v>
+        <v>0.43</v>
       </c>
       <c r="G71" t="n">
-        <v>0.352</v>
+        <v>0.35</v>
       </c>
       <c r="H71" t="n">
-        <v>0.092</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I71" t="n">
-        <v>0.125</v>
+        <v>0.08</v>
       </c>
       <c r="J71" t="n">
-        <v>0.025</v>
+        <v>0.03</v>
       </c>
       <c r="K71" t="n">
-        <v>0.013</v>
-      </c>
-      <c r="L71" t="inlineStr"/>
+        <v>0.02</v>
+      </c>
+      <c r="L71" t="n">
+        <v>0.02</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -3339,11 +3339,11 @@
         </is>
       </c>
       <c r="B72" s="2" t="n">
-        <v>46049</v>
+        <v>46052</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Abacus Data</t>
+          <t>Ekos</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -3353,25 +3353,25 @@
         <v>0</v>
       </c>
       <c r="F72" t="n">
-        <v>0.43</v>
+        <v>0.444</v>
       </c>
       <c r="G72" t="n">
-        <v>0.39</v>
+        <v>0.295</v>
       </c>
       <c r="H72" t="n">
-        <v>0.06</v>
+        <v>0.053</v>
       </c>
       <c r="I72" t="n">
-        <v>0.08</v>
+        <v>0.138</v>
       </c>
       <c r="J72" t="n">
-        <v>0.02</v>
+        <v>0.039</v>
       </c>
       <c r="K72" t="n">
-        <v>0.02</v>
+        <v>0.016</v>
       </c>
       <c r="L72" t="n">
-        <v>0.01</v>
+        <v>0.015</v>
       </c>
     </row>
     <row r="73">
@@ -3381,11 +3381,11 @@
         </is>
       </c>
       <c r="B73" s="2" t="n">
-        <v>46048</v>
+        <v>46052</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Léger</t>
+          <t>Nanos Research</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -3395,24 +3395,24 @@
         <v>0</v>
       </c>
       <c r="F73" t="n">
-        <v>0.47</v>
+        <v>0.389</v>
       </c>
       <c r="G73" t="n">
-        <v>0.38</v>
+        <v>0.352</v>
       </c>
       <c r="H73" t="n">
-        <v>0.06</v>
+        <v>0.092</v>
       </c>
       <c r="I73" t="n">
-        <v>0.05</v>
+        <v>0.125</v>
       </c>
       <c r="J73" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="K73" t="inlineStr"/>
-      <c r="L73" t="n">
-        <v>0.01</v>
-      </c>
+        <v>0.025</v>
+      </c>
+      <c r="K73" t="n">
+        <v>0.013</v>
+      </c>
+      <c r="L73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -3421,11 +3421,11 @@
         </is>
       </c>
       <c r="B74" s="2" t="n">
-        <v>46048</v>
+        <v>46049</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Angus Reid</t>
+          <t>Abacus Data</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3435,23 +3435,25 @@
         <v>0</v>
       </c>
       <c r="F74" t="n">
-        <v>0.41</v>
+        <v>0.43</v>
       </c>
       <c r="G74" t="n">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="H74" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="I74" t="n">
-        <v>0.1</v>
+        <v>0.08</v>
       </c>
       <c r="J74" t="n">
         <v>0.02</v>
       </c>
-      <c r="K74" t="inlineStr"/>
+      <c r="K74" t="n">
+        <v>0.02</v>
+      </c>
       <c r="L74" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="75">
@@ -3461,11 +3463,11 @@
         </is>
       </c>
       <c r="B75" s="2" t="n">
-        <v>46046</v>
+        <v>46048</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Liaison Strategies</t>
+          <t>Léger</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3475,25 +3477,23 @@
         <v>0</v>
       </c>
       <c r="F75" t="n">
-        <v>0.42</v>
+        <v>0.47</v>
       </c>
       <c r="G75" t="n">
-        <v>0.34</v>
+        <v>0.38</v>
       </c>
       <c r="H75" t="n">
-        <v>0.08</v>
+        <v>0.06</v>
       </c>
       <c r="I75" t="n">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="J75" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="K75" t="n">
-        <v>0.02</v>
-      </c>
+        <v>0.02</v>
+      </c>
+      <c r="K75" t="inlineStr"/>
       <c r="L75" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="76">
@@ -3503,11 +3503,11 @@
         </is>
       </c>
       <c r="B76" s="2" t="n">
-        <v>46045</v>
+        <v>46048</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Nanos Research</t>
+          <t>Angus Reid</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3517,24 +3517,24 @@
         <v>0</v>
       </c>
       <c r="F76" t="n">
-        <v>0.392</v>
+        <v>0.41</v>
       </c>
       <c r="G76" t="n">
-        <v>0.352</v>
+        <v>0.38</v>
       </c>
       <c r="H76" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I76" t="n">
-        <v>0.116</v>
+        <v>0.1</v>
       </c>
       <c r="J76" t="n">
-        <v>0.036</v>
-      </c>
-      <c r="K76" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="L76" t="inlineStr"/>
+        <v>0.02</v>
+      </c>
+      <c r="K76" t="inlineStr"/>
+      <c r="L76" t="n">
+        <v>0.02</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -3543,7 +3543,7 @@
         </is>
       </c>
       <c r="B77" s="2" t="n">
-        <v>46039</v>
+        <v>46046</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -3557,22 +3557,22 @@
         <v>0</v>
       </c>
       <c r="F77" t="n">
-        <v>0.4</v>
+        <v>0.42</v>
       </c>
       <c r="G77" t="n">
-        <v>0.35</v>
+        <v>0.34</v>
       </c>
       <c r="H77" t="n">
         <v>0.08</v>
       </c>
       <c r="I77" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="J77" t="n">
         <v>0.03</v>
       </c>
       <c r="K77" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="L77" t="n">
         <v>0.02</v>
@@ -3585,11 +3585,11 @@
         </is>
       </c>
       <c r="B78" s="2" t="n">
-        <v>46038</v>
+        <v>46045</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Abacus Data</t>
+          <t>Nanos Research</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3599,26 +3599,24 @@
         <v>0</v>
       </c>
       <c r="F78" t="n">
-        <v>0.41</v>
+        <v>0.392</v>
       </c>
       <c r="G78" t="n">
-        <v>0.39</v>
+        <v>0.352</v>
       </c>
       <c r="H78" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="I78" t="n">
-        <v>0.08</v>
+        <v>0.116</v>
       </c>
       <c r="J78" t="n">
-        <v>0.03</v>
+        <v>0.036</v>
       </c>
       <c r="K78" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="L78" t="n">
-        <v>0.01</v>
-      </c>
+        <v>0.021</v>
+      </c>
+      <c r="L78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -3627,11 +3625,11 @@
         </is>
       </c>
       <c r="B79" s="2" t="n">
-        <v>46038</v>
+        <v>46039</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Nanos Research</t>
+          <t>Liaison Strategies</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3641,24 +3639,26 @@
         <v>0</v>
       </c>
       <c r="F79" t="n">
-        <v>0.388</v>
+        <v>0.4</v>
       </c>
       <c r="G79" t="n">
-        <v>0.348</v>
+        <v>0.35</v>
       </c>
       <c r="H79" t="n">
-        <v>0.077</v>
+        <v>0.08</v>
       </c>
       <c r="I79" t="n">
-        <v>0.115</v>
+        <v>0.11</v>
       </c>
       <c r="J79" t="n">
-        <v>0.046</v>
+        <v>0.03</v>
       </c>
       <c r="K79" t="n">
-        <v>0.024</v>
-      </c>
-      <c r="L79" t="inlineStr"/>
+        <v>0.01</v>
+      </c>
+      <c r="L79" t="n">
+        <v>0.02</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -3667,7 +3667,7 @@
         </is>
       </c>
       <c r="B80" s="2" t="n">
-        <v>46036</v>
+        <v>46038</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -3681,10 +3681,10 @@
         <v>0</v>
       </c>
       <c r="F80" t="n">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="G80" t="n">
-        <v>0.4</v>
+        <v>0.39</v>
       </c>
       <c r="H80" t="n">
         <v>0.07000000000000001</v>
@@ -3696,7 +3696,7 @@
         <v>0.03</v>
       </c>
       <c r="K80" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="L80" t="n">
         <v>0.01</v>
@@ -3709,11 +3709,11 @@
         </is>
       </c>
       <c r="B81" s="2" t="n">
-        <v>46034</v>
+        <v>46038</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Pallas Data</t>
+          <t>Nanos Research</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3723,24 +3723,24 @@
         <v>0</v>
       </c>
       <c r="F81" t="n">
-        <v>0.4</v>
+        <v>0.388</v>
       </c>
       <c r="G81" t="n">
-        <v>0.37</v>
+        <v>0.348</v>
       </c>
       <c r="H81" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.077</v>
       </c>
       <c r="I81" t="n">
-        <v>0.11</v>
+        <v>0.115</v>
       </c>
       <c r="J81" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="K81" t="inlineStr"/>
-      <c r="L81" t="n">
-        <v>0.02</v>
-      </c>
+        <v>0.046</v>
+      </c>
+      <c r="K81" t="n">
+        <v>0.024</v>
+      </c>
+      <c r="L81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -3749,11 +3749,11 @@
         </is>
       </c>
       <c r="B82" s="2" t="n">
-        <v>46032</v>
+        <v>46036</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Liaison Strategies</t>
+          <t>Abacus Data</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3763,16 +3763,16 @@
         <v>0</v>
       </c>
       <c r="F82" t="n">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="G82" t="n">
-        <v>0.36</v>
+        <v>0.4</v>
       </c>
       <c r="H82" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="I82" t="n">
         <v>0.08</v>
-      </c>
-      <c r="I82" t="n">
-        <v>0.12</v>
       </c>
       <c r="J82" t="n">
         <v>0.03</v>
@@ -3781,7 +3781,7 @@
         <v>0.01</v>
       </c>
       <c r="L82" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="83">
@@ -3791,11 +3791,11 @@
         </is>
       </c>
       <c r="B83" s="2" t="n">
-        <v>46031</v>
+        <v>46034</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Nanos Research</t>
+          <t>Pallas Data</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3805,24 +3805,24 @@
         <v>0</v>
       </c>
       <c r="F83" t="n">
-        <v>0.388</v>
+        <v>0.4</v>
       </c>
       <c r="G83" t="n">
-        <v>0.355</v>
+        <v>0.37</v>
       </c>
       <c r="H83" t="n">
-        <v>0.076</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I83" t="n">
-        <v>0.109</v>
+        <v>0.11</v>
       </c>
       <c r="J83" t="n">
-        <v>0.039</v>
-      </c>
-      <c r="K83" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="L83" t="inlineStr"/>
+        <v>0.03</v>
+      </c>
+      <c r="K83" t="inlineStr"/>
+      <c r="L83" t="n">
+        <v>0.02</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -3831,7 +3831,7 @@
         </is>
       </c>
       <c r="B84" s="2" t="n">
-        <v>46025</v>
+        <v>46032</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -3845,13 +3845,13 @@
         <v>0</v>
       </c>
       <c r="F84" t="n">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="G84" t="n">
-        <v>0.37</v>
+        <v>0.36</v>
       </c>
       <c r="H84" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="I84" t="n">
         <v>0.12</v>
@@ -3873,7 +3873,7 @@
         </is>
       </c>
       <c r="B85" s="2" t="n">
-        <v>46024</v>
+        <v>46031</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -3887,7 +3887,7 @@
         <v>0</v>
       </c>
       <c r="F85" t="n">
-        <v>0.377</v>
+        <v>0.388</v>
       </c>
       <c r="G85" t="n">
         <v>0.355</v>
@@ -3896,13 +3896,13 @@
         <v>0.076</v>
       </c>
       <c r="I85" t="n">
-        <v>0.117</v>
+        <v>0.109</v>
       </c>
       <c r="J85" t="n">
         <v>0.039</v>
       </c>
       <c r="K85" t="n">
-        <v>0.019</v>
+        <v>0.021</v>
       </c>
       <c r="L85" t="inlineStr"/>
     </row>
@@ -3913,7 +3913,7 @@
         </is>
       </c>
       <c r="B86" s="2" t="n">
-        <v>46019</v>
+        <v>46025</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -3927,7 +3927,7 @@
         <v>0</v>
       </c>
       <c r="F86" t="n">
-        <v>0.39</v>
+        <v>0.38</v>
       </c>
       <c r="G86" t="n">
         <v>0.37</v>
@@ -3936,16 +3936,16 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="I86" t="n">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="J86" t="n">
         <v>0.03</v>
       </c>
       <c r="K86" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="L86" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="87">
@@ -3955,7 +3955,7 @@
         </is>
       </c>
       <c r="B87" s="2" t="n">
-        <v>46017</v>
+        <v>46024</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -3969,22 +3969,22 @@
         <v>0</v>
       </c>
       <c r="F87" t="n">
-        <v>0.384</v>
+        <v>0.377</v>
       </c>
       <c r="G87" t="n">
-        <v>0.347</v>
+        <v>0.355</v>
       </c>
       <c r="H87" t="n">
-        <v>0.07400000000000001</v>
+        <v>0.076</v>
       </c>
       <c r="I87" t="n">
-        <v>0.113</v>
+        <v>0.117</v>
       </c>
       <c r="J87" t="n">
         <v>0.039</v>
       </c>
       <c r="K87" t="n">
-        <v>0.017</v>
+        <v>0.019</v>
       </c>
       <c r="L87" t="inlineStr"/>
     </row>
@@ -3995,7 +3995,7 @@
         </is>
       </c>
       <c r="B88" s="2" t="n">
-        <v>46012</v>
+        <v>46019</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -4009,16 +4009,16 @@
         <v>0</v>
       </c>
       <c r="F88" t="n">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="G88" t="n">
-        <v>0.38</v>
+        <v>0.37</v>
       </c>
       <c r="H88" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="I88" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="J88" t="n">
         <v>0.03</v>
@@ -4037,7 +4037,7 @@
         </is>
       </c>
       <c r="B89" s="2" t="n">
-        <v>46010</v>
+        <v>46017</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -4051,22 +4051,22 @@
         <v>0</v>
       </c>
       <c r="F89" t="n">
-        <v>0.363</v>
+        <v>0.384</v>
       </c>
       <c r="G89" t="n">
-        <v>0.356</v>
+        <v>0.347</v>
       </c>
       <c r="H89" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.07400000000000001</v>
       </c>
       <c r="I89" t="n">
-        <v>0.114</v>
+        <v>0.113</v>
       </c>
       <c r="J89" t="n">
-        <v>0.035</v>
+        <v>0.039</v>
       </c>
       <c r="K89" t="n">
-        <v>0.018</v>
+        <v>0.017</v>
       </c>
       <c r="L89" t="inlineStr"/>
     </row>
@@ -4077,11 +4077,11 @@
         </is>
       </c>
       <c r="B90" s="2" t="n">
-        <v>46006</v>
+        <v>46012</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Pallas Data</t>
+          <t>Liaison Strategies</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -4091,23 +4091,25 @@
         <v>0</v>
       </c>
       <c r="F90" t="n">
-        <v>0.409</v>
+        <v>0.38</v>
       </c>
       <c r="G90" t="n">
-        <v>0.377</v>
+        <v>0.38</v>
       </c>
       <c r="H90" t="n">
-        <v>0.08199999999999999</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I90" t="n">
-        <v>0.079</v>
+        <v>0.12</v>
       </c>
       <c r="J90" t="n">
-        <v>0.036</v>
-      </c>
-      <c r="K90" t="inlineStr"/>
+        <v>0.03</v>
+      </c>
+      <c r="K90" t="n">
+        <v>0.02</v>
+      </c>
       <c r="L90" t="n">
-        <v>0.017</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="91">
@@ -4117,11 +4119,11 @@
         </is>
       </c>
       <c r="B91" s="2" t="n">
-        <v>46006</v>
+        <v>46010</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Ipsos</t>
+          <t>Nanos Research</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -4131,22 +4133,22 @@
         <v>0</v>
       </c>
       <c r="F91" t="n">
-        <v>0.4</v>
+        <v>0.363</v>
       </c>
       <c r="G91" t="n">
-        <v>0.37</v>
+        <v>0.356</v>
       </c>
       <c r="H91" t="n">
-        <v>0.09</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="I91" t="n">
-        <v>0.09</v>
+        <v>0.114</v>
       </c>
       <c r="J91" t="n">
-        <v>0.02</v>
+        <v>0.035</v>
       </c>
       <c r="K91" t="n">
-        <v>0.02</v>
+        <v>0.018</v>
       </c>
       <c r="L91" t="inlineStr"/>
     </row>
@@ -4157,11 +4159,11 @@
         </is>
       </c>
       <c r="B92" s="2" t="n">
-        <v>46005</v>
+        <v>46006</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Innovative Research</t>
+          <t>Pallas Data</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -4171,23 +4173,23 @@
         <v>0</v>
       </c>
       <c r="F92" t="n">
-        <v>0.39</v>
+        <v>0.409</v>
       </c>
       <c r="G92" t="n">
-        <v>0.39</v>
+        <v>0.377</v>
       </c>
       <c r="H92" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.08199999999999999</v>
       </c>
       <c r="I92" t="n">
-        <v>0.1</v>
+        <v>0.079</v>
       </c>
       <c r="J92" t="n">
-        <v>0.04</v>
+        <v>0.036</v>
       </c>
       <c r="K92" t="inlineStr"/>
       <c r="L92" t="n">
-        <v>0.02</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="93">
@@ -4197,11 +4199,11 @@
         </is>
       </c>
       <c r="B93" s="2" t="n">
-        <v>46003</v>
+        <v>46006</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Mainstreet Research</t>
+          <t>Ipsos</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -4211,26 +4213,24 @@
         <v>0</v>
       </c>
       <c r="F93" t="n">
-        <v>0.41</v>
+        <v>0.4</v>
       </c>
       <c r="G93" t="n">
-        <v>0.42</v>
+        <v>0.37</v>
       </c>
       <c r="H93" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="I93" t="n">
-        <v>0.06</v>
+        <v>0.09</v>
       </c>
       <c r="J93" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="K93" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="L93" t="n">
-        <v>0.01</v>
-      </c>
+        <v>0.02</v>
+      </c>
+      <c r="L93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -4239,11 +4239,11 @@
         </is>
       </c>
       <c r="B94" s="2" t="n">
-        <v>46003</v>
+        <v>46005</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Nanos Research</t>
+          <t>Innovative Research</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -4253,24 +4253,24 @@
         <v>0</v>
       </c>
       <c r="F94" t="n">
-        <v>0.385</v>
+        <v>0.39</v>
       </c>
       <c r="G94" t="n">
-        <v>0.36</v>
+        <v>0.39</v>
       </c>
       <c r="H94" t="n">
-        <v>0.067</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I94" t="n">
-        <v>0.108</v>
+        <v>0.1</v>
       </c>
       <c r="J94" t="n">
-        <v>0.03700000000000001</v>
-      </c>
-      <c r="K94" t="n">
-        <v>0.019</v>
-      </c>
-      <c r="L94" t="inlineStr"/>
+        <v>0.04</v>
+      </c>
+      <c r="K94" t="inlineStr"/>
+      <c r="L94" t="n">
+        <v>0.02</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -4279,11 +4279,11 @@
         </is>
       </c>
       <c r="B95" s="2" t="n">
-        <v>46000</v>
+        <v>46003</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Abacus Data</t>
+          <t>Mainstreet Research</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -4296,22 +4296,22 @@
         <v>0.41</v>
       </c>
       <c r="G95" t="n">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="H95" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="I95" t="n">
         <v>0.06</v>
       </c>
-      <c r="I95" t="n">
-        <v>0.09</v>
-      </c>
       <c r="J95" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="K95" t="n">
         <v>0.01</v>
       </c>
       <c r="L95" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="96">
@@ -4321,7 +4321,7 @@
         </is>
       </c>
       <c r="B96" s="2" t="n">
-        <v>45996</v>
+        <v>46003</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -4335,22 +4335,22 @@
         <v>0</v>
       </c>
       <c r="F96" t="n">
-        <v>0.391</v>
+        <v>0.385</v>
       </c>
       <c r="G96" t="n">
-        <v>0.3779999999999999</v>
+        <v>0.36</v>
       </c>
       <c r="H96" t="n">
-        <v>0.063</v>
+        <v>0.067</v>
       </c>
       <c r="I96" t="n">
-        <v>0.095</v>
+        <v>0.108</v>
       </c>
       <c r="J96" t="n">
-        <v>0.033</v>
+        <v>0.03700000000000001</v>
       </c>
       <c r="K96" t="n">
-        <v>0.018</v>
+        <v>0.019</v>
       </c>
       <c r="L96" t="inlineStr"/>
     </row>
@@ -4361,11 +4361,11 @@
         </is>
       </c>
       <c r="B97" s="2" t="n">
-        <v>45992</v>
+        <v>46000</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Innovative Research</t>
+          <t>Abacus Data</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -4375,23 +4375,25 @@
         <v>0</v>
       </c>
       <c r="F97" t="n">
-        <v>0.39</v>
+        <v>0.41</v>
       </c>
       <c r="G97" t="n">
-        <v>0.38</v>
+        <v>0.41</v>
       </c>
       <c r="H97" t="n">
-        <v>0.08</v>
+        <v>0.06</v>
       </c>
       <c r="I97" t="n">
         <v>0.09</v>
       </c>
       <c r="J97" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="K97" t="inlineStr"/>
+        <v>0.02</v>
+      </c>
+      <c r="K97" t="n">
+        <v>0.01</v>
+      </c>
       <c r="L97" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
     </row>
     <row r="98">
@@ -4401,11 +4403,11 @@
         </is>
       </c>
       <c r="B98" s="2" t="n">
-        <v>45992</v>
+        <v>45996</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Abacus Data</t>
+          <t>Nanos Research</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -4415,26 +4417,24 @@
         <v>0</v>
       </c>
       <c r="F98" t="n">
-        <v>0.41</v>
+        <v>0.391</v>
       </c>
       <c r="G98" t="n">
-        <v>0.41</v>
+        <v>0.3779999999999999</v>
       </c>
       <c r="H98" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.063</v>
       </c>
       <c r="I98" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.095</v>
       </c>
       <c r="J98" t="n">
-        <v>0.02</v>
+        <v>0.033</v>
       </c>
       <c r="K98" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="L98" t="n">
-        <v>0.01</v>
-      </c>
+        <v>0.018</v>
+      </c>
+      <c r="L98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -4447,7 +4447,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Angus Reid</t>
+          <t>Innovative Research</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -4457,22 +4457,24 @@
         <v>0</v>
       </c>
       <c r="F99" t="n">
-        <v>0.4</v>
+        <v>0.39</v>
       </c>
       <c r="G99" t="n">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="H99" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="I99" t="n">
         <v>0.09</v>
       </c>
-      <c r="I99" t="n">
-        <v>0.1</v>
-      </c>
       <c r="J99" t="n">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="K99" t="inlineStr"/>
-      <c r="L99" t="inlineStr"/>
+      <c r="L99" t="n">
+        <v>0.02</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -4481,11 +4483,11 @@
         </is>
       </c>
       <c r="B100" s="2" t="n">
-        <v>45991</v>
+        <v>45992</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Léger</t>
+          <t>Abacus Data</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -4495,21 +4497,23 @@
         <v>0</v>
       </c>
       <c r="F100" t="n">
-        <v>0.43</v>
+        <v>0.41</v>
       </c>
       <c r="G100" t="n">
-        <v>0.36</v>
+        <v>0.41</v>
       </c>
       <c r="H100" t="n">
-        <v>0.09</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I100" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="J100" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="K100" t="inlineStr"/>
+        <v>0.02</v>
+      </c>
+      <c r="K100" t="n">
+        <v>0.01</v>
+      </c>
       <c r="L100" t="n">
         <v>0.01</v>
       </c>
@@ -4521,11 +4525,11 @@
         </is>
       </c>
       <c r="B101" s="2" t="n">
-        <v>45991</v>
+        <v>45992</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Liaison Strategies</t>
+          <t>Angus Reid</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -4535,26 +4539,22 @@
         <v>0</v>
       </c>
       <c r="F101" t="n">
-        <v>0.41</v>
+        <v>0.4</v>
       </c>
       <c r="G101" t="n">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="H101" t="n">
-        <v>0.05</v>
+        <v>0.09</v>
       </c>
       <c r="I101" t="n">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="J101" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="K101" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="L101" t="n">
-        <v>0.01</v>
-      </c>
+        <v>0.03</v>
+      </c>
+      <c r="K101" t="inlineStr"/>
+      <c r="L101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -4563,11 +4563,11 @@
         </is>
       </c>
       <c r="B102" s="2" t="n">
-        <v>45989</v>
+        <v>45991</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Nanos Research</t>
+          <t>Léger</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -4577,25 +4577,23 @@
         <v>0</v>
       </c>
       <c r="F102" t="n">
-        <v>0.419</v>
+        <v>0.43</v>
       </c>
       <c r="G102" t="n">
-        <v>0.382</v>
+        <v>0.36</v>
       </c>
       <c r="H102" t="n">
-        <v>0.073</v>
+        <v>0.09</v>
       </c>
       <c r="I102" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="J102" t="n">
-        <v>0.027</v>
-      </c>
-      <c r="K102" t="n">
-        <v>0.012</v>
-      </c>
+        <v>0.04</v>
+      </c>
+      <c r="K102" t="inlineStr"/>
       <c r="L102" t="n">
-        <v>0.003</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="103">
@@ -4605,11 +4603,11 @@
         </is>
       </c>
       <c r="B103" s="2" t="n">
-        <v>45988</v>
+        <v>45991</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Abacus Data</t>
+          <t>Liaison Strategies</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4622,19 +4620,19 @@
         <v>0.41</v>
       </c>
       <c r="G103" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="H103" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.05</v>
       </c>
       <c r="I103" t="n">
-        <v>0.08</v>
+        <v>0.12</v>
       </c>
       <c r="J103" t="n">
         <v>0.02</v>
       </c>
       <c r="K103" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="L103" t="n">
         <v>0.01</v>
@@ -4647,7 +4645,7 @@
         </is>
       </c>
       <c r="B104" s="2" t="n">
-        <v>45982</v>
+        <v>45989</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -4664,22 +4662,22 @@
         <v>0.419</v>
       </c>
       <c r="G104" t="n">
-        <v>0.3720000000000001</v>
+        <v>0.382</v>
       </c>
       <c r="H104" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.073</v>
       </c>
       <c r="I104" t="n">
-        <v>0.091</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="J104" t="n">
         <v>0.027</v>
       </c>
       <c r="K104" t="n">
-        <v>0.016</v>
+        <v>0.012</v>
       </c>
       <c r="L104" t="n">
-        <v>0.005</v>
+        <v>0.003</v>
       </c>
     </row>
     <row r="105">
@@ -4689,11 +4687,11 @@
         </is>
       </c>
       <c r="B105" s="2" t="n">
-        <v>45979</v>
+        <v>45988</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Kolosowski Strategies</t>
+          <t>Abacus Data</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4703,25 +4701,25 @@
         <v>0</v>
       </c>
       <c r="F105" t="n">
-        <v>0.44</v>
+        <v>0.41</v>
       </c>
       <c r="G105" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="H105" t="n">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I105" t="n">
-        <v>0.03</v>
+        <v>0.08</v>
       </c>
       <c r="J105" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="K105" t="n">
         <v>0.01</v>
       </c>
       <c r="L105" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="106">
@@ -4731,7 +4729,7 @@
         </is>
       </c>
       <c r="B106" s="2" t="n">
-        <v>45975</v>
+        <v>45982</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -4745,25 +4743,25 @@
         <v>0</v>
       </c>
       <c r="F106" t="n">
-        <v>0.402</v>
+        <v>0.419</v>
       </c>
       <c r="G106" t="n">
-        <v>0.382</v>
+        <v>0.3720000000000001</v>
       </c>
       <c r="H106" t="n">
-        <v>0.07400000000000001</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I106" t="n">
-        <v>0.101</v>
+        <v>0.091</v>
       </c>
       <c r="J106" t="n">
-        <v>0.022</v>
+        <v>0.027</v>
       </c>
       <c r="K106" t="n">
-        <v>0.013</v>
+        <v>0.016</v>
       </c>
       <c r="L106" t="n">
-        <v>0.008</v>
+        <v>0.005</v>
       </c>
     </row>
     <row r="107">
@@ -4773,11 +4771,11 @@
         </is>
       </c>
       <c r="B107" s="2" t="n">
-        <v>45972</v>
+        <v>45979</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Ekos</t>
+          <t>Kolosowski Strategies</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4787,25 +4785,25 @@
         <v>0</v>
       </c>
       <c r="F107" t="n">
-        <v>0.441</v>
+        <v>0.44</v>
       </c>
       <c r="G107" t="n">
-        <v>0.332</v>
+        <v>0.44</v>
       </c>
       <c r="H107" t="n">
-        <v>0.05400000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="I107" t="n">
-        <v>0.107</v>
+        <v>0.03</v>
       </c>
       <c r="J107" t="n">
-        <v>0.033</v>
+        <v>0.01</v>
       </c>
       <c r="K107" t="n">
-        <v>0.018</v>
+        <v>0.01</v>
       </c>
       <c r="L107" t="n">
-        <v>0.014</v>
+        <v>0</v>
       </c>
     </row>
     <row r="108">
@@ -4815,11 +4813,11 @@
         </is>
       </c>
       <c r="B108" s="2" t="n">
-        <v>45969</v>
+        <v>45975</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Mainstreet Research</t>
+          <t>Nanos Research</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4829,25 +4827,25 @@
         <v>0</v>
       </c>
       <c r="F108" t="n">
-        <v>0.44</v>
+        <v>0.402</v>
       </c>
       <c r="G108" t="n">
-        <v>0.4</v>
+        <v>0.382</v>
       </c>
       <c r="H108" t="n">
-        <v>0.06</v>
+        <v>0.07400000000000001</v>
       </c>
       <c r="I108" t="n">
-        <v>0.05</v>
+        <v>0.101</v>
       </c>
       <c r="J108" t="n">
-        <v>0.02</v>
+        <v>0.022</v>
       </c>
       <c r="K108" t="n">
-        <v>0.02</v>
+        <v>0.013</v>
       </c>
       <c r="L108" t="n">
-        <v>0.02</v>
+        <v>0.008</v>
       </c>
     </row>
     <row r="109">
@@ -4857,11 +4855,11 @@
         </is>
       </c>
       <c r="B109" s="2" t="n">
-        <v>45969</v>
+        <v>45972</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Liaison Strategies</t>
+          <t>Ekos</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4871,25 +4869,25 @@
         <v>0</v>
       </c>
       <c r="F109" t="n">
-        <v>0.44</v>
+        <v>0.441</v>
       </c>
       <c r="G109" t="n">
-        <v>0.36</v>
+        <v>0.332</v>
       </c>
       <c r="H109" t="n">
-        <v>0.06</v>
+        <v>0.05400000000000001</v>
       </c>
       <c r="I109" t="n">
-        <v>0.1</v>
+        <v>0.107</v>
       </c>
       <c r="J109" t="n">
-        <v>0.02</v>
+        <v>0.033</v>
       </c>
       <c r="K109" t="n">
-        <v>0.01</v>
+        <v>0.018</v>
       </c>
       <c r="L109" t="n">
-        <v>0.01</v>
+        <v>0.014</v>
       </c>
     </row>
     <row r="110">
@@ -4899,11 +4897,11 @@
         </is>
       </c>
       <c r="B110" s="2" t="n">
-        <v>45968</v>
+        <v>45969</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Angus Reid</t>
+          <t>Mainstreet Research</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4913,22 +4911,26 @@
         <v>0</v>
       </c>
       <c r="F110" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="G110" t="n">
         <v>0.4</v>
       </c>
-      <c r="G110" t="n">
-        <v>0.38</v>
-      </c>
       <c r="H110" t="n">
-        <v>0.08</v>
+        <v>0.06</v>
       </c>
       <c r="I110" t="n">
-        <v>0.09</v>
+        <v>0.05</v>
       </c>
       <c r="J110" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="K110" t="inlineStr"/>
-      <c r="L110" t="inlineStr"/>
+        <v>0.02</v>
+      </c>
+      <c r="K110" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="L110" t="n">
+        <v>0.02</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -4937,11 +4939,11 @@
         </is>
       </c>
       <c r="B111" s="2" t="n">
-        <v>45968</v>
+        <v>45969</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Nanos Research</t>
+          <t>Liaison Strategies</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4951,25 +4953,25 @@
         <v>0</v>
       </c>
       <c r="F111" t="n">
-        <v>0.4</v>
+        <v>0.44</v>
       </c>
       <c r="G111" t="n">
-        <v>0.368</v>
+        <v>0.36</v>
       </c>
       <c r="H111" t="n">
-        <v>0.075</v>
+        <v>0.06</v>
       </c>
       <c r="I111" t="n">
-        <v>0.114</v>
+        <v>0.1</v>
       </c>
       <c r="J111" t="n">
-        <v>0.023</v>
+        <v>0.02</v>
       </c>
       <c r="K111" t="n">
-        <v>0.012</v>
+        <v>0.01</v>
       </c>
       <c r="L111" t="n">
-        <v>0.008</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="112">
@@ -4979,11 +4981,11 @@
         </is>
       </c>
       <c r="B112" s="2" t="n">
-        <v>45967</v>
+        <v>45968</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Abacus Data</t>
+          <t>Angus Reid</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4996,23 +4998,19 @@
         <v>0.4</v>
       </c>
       <c r="G112" t="n">
-        <v>0.41</v>
+        <v>0.38</v>
       </c>
       <c r="H112" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="I112" t="n">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="J112" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="K112" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="L112" t="n">
-        <v>0</v>
-      </c>
+        <v>0.03</v>
+      </c>
+      <c r="K112" t="inlineStr"/>
+      <c r="L112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -5021,11 +5019,11 @@
         </is>
       </c>
       <c r="B113" s="2" t="n">
-        <v>45965</v>
+        <v>45968</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Ekos</t>
+          <t>Nanos Research</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -5035,25 +5033,25 @@
         <v>0</v>
       </c>
       <c r="F113" t="n">
-        <v>0.434</v>
+        <v>0.4</v>
       </c>
       <c r="G113" t="n">
-        <v>0.355</v>
+        <v>0.368</v>
       </c>
       <c r="H113" t="n">
-        <v>0.058</v>
+        <v>0.075</v>
       </c>
       <c r="I113" t="n">
-        <v>0.08</v>
+        <v>0.114</v>
       </c>
       <c r="J113" t="n">
-        <v>0.035</v>
+        <v>0.023</v>
       </c>
       <c r="K113" t="n">
-        <v>0.02</v>
+        <v>0.012</v>
       </c>
       <c r="L113" t="n">
-        <v>0.02</v>
+        <v>0.008</v>
       </c>
     </row>
     <row r="114">
@@ -5063,11 +5061,11 @@
         </is>
       </c>
       <c r="B114" s="2" t="n">
-        <v>45965</v>
+        <v>45967</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Liaison Strategies</t>
+          <t>Abacus Data</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -5077,16 +5075,16 @@
         <v>0</v>
       </c>
       <c r="F114" t="n">
-        <v>0.42</v>
+        <v>0.4</v>
       </c>
       <c r="G114" t="n">
-        <v>0.38</v>
+        <v>0.41</v>
       </c>
       <c r="H114" t="n">
-        <v>0.05</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I114" t="n">
-        <v>0.11</v>
+        <v>0.08</v>
       </c>
       <c r="J114" t="n">
         <v>0.02</v>
@@ -5095,7 +5093,7 @@
         <v>0.01</v>
       </c>
       <c r="L114" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
     </row>
     <row r="115">
@@ -5105,11 +5103,11 @@
         </is>
       </c>
       <c r="B115" s="2" t="n">
-        <v>45964</v>
+        <v>45965</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Léger</t>
+          <t>Ekos</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -5119,23 +5117,25 @@
         <v>0</v>
       </c>
       <c r="F115" t="n">
-        <v>0.43</v>
+        <v>0.434</v>
       </c>
       <c r="G115" t="n">
-        <v>0.38</v>
+        <v>0.355</v>
       </c>
       <c r="H115" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.058</v>
       </c>
       <c r="I115" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="J115" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="K115" t="inlineStr"/>
+        <v>0.035</v>
+      </c>
+      <c r="K115" t="n">
+        <v>0.02</v>
+      </c>
       <c r="L115" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="116">
@@ -5145,11 +5145,11 @@
         </is>
       </c>
       <c r="B116" s="2" t="n">
-        <v>45961</v>
+        <v>45965</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Nanos Research</t>
+          <t>Liaison Strategies</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -5159,25 +5159,25 @@
         <v>0</v>
       </c>
       <c r="F116" t="n">
-        <v>0.393</v>
+        <v>0.42</v>
       </c>
       <c r="G116" t="n">
-        <v>0.371</v>
+        <v>0.38</v>
       </c>
       <c r="H116" t="n">
-        <v>0.066</v>
+        <v>0.05</v>
       </c>
       <c r="I116" t="n">
-        <v>0.125</v>
+        <v>0.11</v>
       </c>
       <c r="J116" t="n">
-        <v>0.017</v>
+        <v>0.02</v>
       </c>
       <c r="K116" t="n">
-        <v>0.015</v>
+        <v>0.01</v>
       </c>
       <c r="L116" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="117">
@@ -5187,11 +5187,11 @@
         </is>
       </c>
       <c r="B117" s="2" t="n">
-        <v>45959</v>
+        <v>45964</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Abacus Data</t>
+          <t>Léger</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -5201,23 +5201,21 @@
         <v>0</v>
       </c>
       <c r="F117" t="n">
-        <v>0.4</v>
+        <v>0.43</v>
       </c>
       <c r="G117" t="n">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="H117" t="n">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I117" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="J117" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="K117" t="n">
-        <v>0.01</v>
-      </c>
+        <v>0.04</v>
+      </c>
+      <c r="K117" t="inlineStr"/>
       <c r="L117" t="n">
         <v>0.01</v>
       </c>
@@ -5229,7 +5227,7 @@
         </is>
       </c>
       <c r="B118" s="2" t="n">
-        <v>45954</v>
+        <v>45961</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -5243,22 +5241,22 @@
         <v>0</v>
       </c>
       <c r="F118" t="n">
-        <v>0.394</v>
+        <v>0.393</v>
       </c>
       <c r="G118" t="n">
-        <v>0.37</v>
+        <v>0.371</v>
       </c>
       <c r="H118" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.066</v>
       </c>
       <c r="I118" t="n">
-        <v>0.127</v>
+        <v>0.125</v>
       </c>
       <c r="J118" t="n">
-        <v>0.016</v>
+        <v>0.017</v>
       </c>
       <c r="K118" t="n">
-        <v>0.012</v>
+        <v>0.015</v>
       </c>
       <c r="L118" t="n">
         <v>0</v>
@@ -5271,11 +5269,11 @@
         </is>
       </c>
       <c r="B119" s="2" t="n">
-        <v>45954</v>
+        <v>45959</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Ekos</t>
+          <t>Abacus Data</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -5285,22 +5283,22 @@
         <v>0</v>
       </c>
       <c r="F119" t="n">
-        <v>0.435</v>
+        <v>0.4</v>
       </c>
       <c r="G119" t="n">
-        <v>0.324</v>
+        <v>0.42</v>
       </c>
       <c r="H119" t="n">
-        <v>0.057</v>
+        <v>0.06</v>
       </c>
       <c r="I119" t="n">
-        <v>0.124</v>
+        <v>0.08</v>
       </c>
       <c r="J119" t="n">
         <v>0.03</v>
       </c>
       <c r="K119" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="L119" t="n">
         <v>0.01</v>
@@ -5313,7 +5311,7 @@
         </is>
       </c>
       <c r="B120" s="2" t="n">
-        <v>45947</v>
+        <v>45954</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -5327,25 +5325,25 @@
         <v>0</v>
       </c>
       <c r="F120" t="n">
-        <v>0.393</v>
+        <v>0.394</v>
       </c>
       <c r="G120" t="n">
-        <v>0.366</v>
+        <v>0.37</v>
       </c>
       <c r="H120" t="n">
-        <v>0.068</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I120" t="n">
-        <v>0.121</v>
+        <v>0.127</v>
       </c>
       <c r="J120" t="n">
-        <v>0.028</v>
+        <v>0.016</v>
       </c>
       <c r="K120" t="n">
-        <v>0.013</v>
+        <v>0.012</v>
       </c>
       <c r="L120" t="n">
-        <v>0.011</v>
+        <v>0</v>
       </c>
     </row>
     <row r="121">
@@ -5355,11 +5353,11 @@
         </is>
       </c>
       <c r="B121" s="2" t="n">
-        <v>45945</v>
+        <v>45954</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Abacus Data</t>
+          <t>Ekos</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -5369,22 +5367,22 @@
         <v>0</v>
       </c>
       <c r="F121" t="n">
-        <v>0.4</v>
+        <v>0.435</v>
       </c>
       <c r="G121" t="n">
-        <v>0.41</v>
+        <v>0.324</v>
       </c>
       <c r="H121" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.057</v>
       </c>
       <c r="I121" t="n">
-        <v>0.08</v>
+        <v>0.124</v>
       </c>
       <c r="J121" t="n">
         <v>0.03</v>
       </c>
       <c r="K121" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="L121" t="n">
         <v>0.01</v>
@@ -5397,11 +5395,11 @@
         </is>
       </c>
       <c r="B122" s="2" t="n">
-        <v>45945</v>
+        <v>45947</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Pallas Data</t>
+          <t>Nanos Research</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -5411,25 +5409,25 @@
         <v>0</v>
       </c>
       <c r="F122" t="n">
-        <v>0.41</v>
+        <v>0.393</v>
       </c>
       <c r="G122" t="n">
-        <v>0.37</v>
+        <v>0.366</v>
       </c>
       <c r="H122" t="n">
-        <v>0.06</v>
+        <v>0.068</v>
       </c>
       <c r="I122" t="n">
-        <v>0.11</v>
+        <v>0.121</v>
       </c>
       <c r="J122" t="n">
-        <v>0.02</v>
+        <v>0.028</v>
       </c>
       <c r="K122" t="n">
-        <v>0.02</v>
+        <v>0.013</v>
       </c>
       <c r="L122" t="n">
-        <v>0</v>
+        <v>0.011</v>
       </c>
     </row>
     <row r="123">
@@ -5439,11 +5437,11 @@
         </is>
       </c>
       <c r="B123" s="2" t="n">
-        <v>45940</v>
+        <v>45945</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Nanos Research</t>
+          <t>Abacus Data</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -5453,25 +5451,25 @@
         <v>0</v>
       </c>
       <c r="F123" t="n">
-        <v>0.385</v>
+        <v>0.4</v>
       </c>
       <c r="G123" t="n">
-        <v>0.368</v>
+        <v>0.41</v>
       </c>
       <c r="H123" t="n">
-        <v>0.065</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I123" t="n">
-        <v>0.122</v>
+        <v>0.08</v>
       </c>
       <c r="J123" t="n">
-        <v>0.039</v>
+        <v>0.03</v>
       </c>
       <c r="K123" t="n">
-        <v>0.014</v>
+        <v>0.01</v>
       </c>
       <c r="L123" t="n">
-        <v>0.006999999999999999</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="124">
@@ -5481,11 +5479,11 @@
         </is>
       </c>
       <c r="B124" s="2" t="n">
-        <v>45935</v>
+        <v>45945</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Léger</t>
+          <t>Pallas Data</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -5495,23 +5493,25 @@
         <v>0</v>
       </c>
       <c r="F124" t="n">
-        <v>0.44</v>
+        <v>0.41</v>
       </c>
       <c r="G124" t="n">
-        <v>0.38</v>
+        <v>0.37</v>
       </c>
       <c r="H124" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="I124" t="n">
-        <v>0.06</v>
+        <v>0.11</v>
       </c>
       <c r="J124" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="K124" t="inlineStr"/>
+        <v>0.02</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.02</v>
+      </c>
       <c r="L124" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
     </row>
     <row r="125">
@@ -5521,7 +5521,7 @@
         </is>
       </c>
       <c r="B125" s="2" t="n">
-        <v>45933</v>
+        <v>45940</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -5535,25 +5535,25 @@
         <v>0</v>
       </c>
       <c r="F125" t="n">
-        <v>0.391</v>
+        <v>0.385</v>
       </c>
       <c r="G125" t="n">
-        <v>0.379</v>
+        <v>0.368</v>
       </c>
       <c r="H125" t="n">
-        <v>0.062</v>
+        <v>0.065</v>
       </c>
       <c r="I125" t="n">
-        <v>0.115</v>
+        <v>0.122</v>
       </c>
       <c r="J125" t="n">
-        <v>0.04</v>
+        <v>0.039</v>
       </c>
       <c r="K125" t="n">
-        <v>0.009000000000000001</v>
+        <v>0.014</v>
       </c>
       <c r="L125" t="n">
-        <v>0.004</v>
+        <v>0.006999999999999999</v>
       </c>
     </row>
     <row r="126">
@@ -5563,11 +5563,11 @@
         </is>
       </c>
       <c r="B126" s="2" t="n">
-        <v>45931</v>
+        <v>45935</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Abacus Data</t>
+          <t>Léger</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -5577,25 +5577,23 @@
         <v>0</v>
       </c>
       <c r="F126" t="n">
-        <v>0.4</v>
+        <v>0.44</v>
       </c>
       <c r="G126" t="n">
-        <v>0.41</v>
+        <v>0.38</v>
       </c>
       <c r="H126" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="I126" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="J126" t="n">
         <v>0.03</v>
       </c>
-      <c r="K126" t="n">
-        <v>0.02</v>
-      </c>
+      <c r="K126" t="inlineStr"/>
       <c r="L126" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="127">
@@ -5605,7 +5603,7 @@
         </is>
       </c>
       <c r="B127" s="2" t="n">
-        <v>45926</v>
+        <v>45933</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -5619,25 +5617,25 @@
         <v>0</v>
       </c>
       <c r="F127" t="n">
-        <v>0.407</v>
+        <v>0.391</v>
       </c>
       <c r="G127" t="n">
-        <v>0.366</v>
+        <v>0.379</v>
       </c>
       <c r="H127" t="n">
-        <v>0.048</v>
+        <v>0.062</v>
       </c>
       <c r="I127" t="n">
-        <v>0.119</v>
+        <v>0.115</v>
       </c>
       <c r="J127" t="n">
-        <v>0.043</v>
+        <v>0.04</v>
       </c>
       <c r="K127" t="n">
-        <v>0.012</v>
+        <v>0.009000000000000001</v>
       </c>
       <c r="L127" t="n">
-        <v>0.005</v>
+        <v>0.004</v>
       </c>
     </row>
     <row r="128">
@@ -5647,11 +5645,11 @@
         </is>
       </c>
       <c r="B128" s="2" t="n">
-        <v>45922</v>
+        <v>45931</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Angus Reid</t>
+          <t>Abacus Data</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -5661,22 +5659,22 @@
         <v>0</v>
       </c>
       <c r="F128" t="n">
-        <v>0.38</v>
+        <v>0.4</v>
       </c>
       <c r="G128" t="n">
         <v>0.41</v>
       </c>
       <c r="H128" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I128" t="n">
-        <v>0.1</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="J128" t="n">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="K128" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="L128" t="n">
         <v>0.01</v>
@@ -5689,11 +5687,11 @@
         </is>
       </c>
       <c r="B129" s="2" t="n">
-        <v>45921</v>
+        <v>45926</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Liaison Strategies</t>
+          <t>Nanos Research</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -5703,25 +5701,25 @@
         <v>0</v>
       </c>
       <c r="F129" t="n">
-        <v>0.43</v>
+        <v>0.407</v>
       </c>
       <c r="G129" t="n">
-        <v>0.37</v>
+        <v>0.366</v>
       </c>
       <c r="H129" t="n">
-        <v>0.05</v>
+        <v>0.048</v>
       </c>
       <c r="I129" t="n">
-        <v>0.1</v>
+        <v>0.119</v>
       </c>
       <c r="J129" t="n">
-        <v>0.02</v>
+        <v>0.043</v>
       </c>
       <c r="K129" t="n">
-        <v>0.02</v>
+        <v>0.012</v>
       </c>
       <c r="L129" t="n">
-        <v>0.01</v>
+        <v>0.005</v>
       </c>
     </row>
     <row r="130">
@@ -5731,11 +5729,11 @@
         </is>
       </c>
       <c r="B130" s="2" t="n">
-        <v>45919</v>
+        <v>45922</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Nanos Research</t>
+          <t>Angus Reid</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -5745,25 +5743,25 @@
         <v>0</v>
       </c>
       <c r="F130" t="n">
-        <v>0.406</v>
+        <v>0.38</v>
       </c>
       <c r="G130" t="n">
-        <v>0.357</v>
+        <v>0.41</v>
       </c>
       <c r="H130" t="n">
-        <v>0.055</v>
+        <v>0.08</v>
       </c>
       <c r="I130" t="n">
-        <v>0.116</v>
+        <v>0.1</v>
       </c>
       <c r="J130" t="n">
-        <v>0.032</v>
+        <v>0.02</v>
       </c>
       <c r="K130" t="n">
-        <v>0.022</v>
+        <v>0.01</v>
       </c>
       <c r="L130" t="n">
-        <v>0.012</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="131">
@@ -5773,11 +5771,11 @@
         </is>
       </c>
       <c r="B131" s="2" t="n">
-        <v>45917</v>
+        <v>45921</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Abacus Data</t>
+          <t>Liaison Strategies</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5787,22 +5785,22 @@
         <v>0</v>
       </c>
       <c r="F131" t="n">
-        <v>0.4</v>
+        <v>0.43</v>
       </c>
       <c r="G131" t="n">
-        <v>0.4</v>
+        <v>0.37</v>
       </c>
       <c r="H131" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.05</v>
       </c>
       <c r="I131" t="n">
-        <v>0.08</v>
+        <v>0.1</v>
       </c>
       <c r="J131" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="K131" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="L131" t="n">
         <v>0.01</v>
@@ -5815,11 +5813,11 @@
         </is>
       </c>
       <c r="B132" s="2" t="n">
-        <v>45912</v>
+        <v>45919</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Research Co.</t>
+          <t>Nanos Research</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5829,25 +5827,25 @@
         <v>0</v>
       </c>
       <c r="F132" t="n">
-        <v>0.43</v>
+        <v>0.406</v>
       </c>
       <c r="G132" t="n">
-        <v>0.38</v>
+        <v>0.357</v>
       </c>
       <c r="H132" t="n">
-        <v>0.06</v>
+        <v>0.055</v>
       </c>
       <c r="I132" t="n">
-        <v>0.08</v>
+        <v>0.116</v>
       </c>
       <c r="J132" t="n">
-        <v>0.02</v>
+        <v>0.032</v>
       </c>
       <c r="K132" t="n">
-        <v>0.01</v>
+        <v>0.022</v>
       </c>
       <c r="L132" t="n">
-        <v>0.01</v>
+        <v>0.012</v>
       </c>
     </row>
     <row r="133">
@@ -5857,11 +5855,11 @@
         </is>
       </c>
       <c r="B133" s="2" t="n">
-        <v>45912</v>
+        <v>45917</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Nanos Research</t>
+          <t>Abacus Data</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5871,22 +5869,22 @@
         <v>0</v>
       </c>
       <c r="F133" t="n">
-        <v>0.418</v>
+        <v>0.4</v>
       </c>
       <c r="G133" t="n">
-        <v>0.345</v>
+        <v>0.4</v>
       </c>
       <c r="H133" t="n">
-        <v>0.055</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I133" t="n">
-        <v>0.128</v>
+        <v>0.08</v>
       </c>
       <c r="J133" t="n">
-        <v>0.025</v>
+        <v>0.03</v>
       </c>
       <c r="K133" t="n">
-        <v>0.019</v>
+        <v>0.01</v>
       </c>
       <c r="L133" t="n">
         <v>0.01</v>
@@ -5903,7 +5901,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Ekos</t>
+          <t>Research Co.</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5913,22 +5911,22 @@
         <v>0</v>
       </c>
       <c r="F134" t="n">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="G134" t="n">
-        <v>0.34</v>
+        <v>0.38</v>
       </c>
       <c r="H134" t="n">
-        <v>0.052</v>
+        <v>0.06</v>
       </c>
       <c r="I134" t="n">
-        <v>0.126</v>
+        <v>0.08</v>
       </c>
       <c r="J134" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="K134" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="L134" t="n">
         <v>0.01</v>
@@ -5941,11 +5939,11 @@
         </is>
       </c>
       <c r="B135" s="2" t="n">
-        <v>45908</v>
+        <v>45912</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Ipsos</t>
+          <t>Nanos Research</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5955,25 +5953,25 @@
         <v>0</v>
       </c>
       <c r="F135" t="n">
-        <v>0.43</v>
+        <v>0.418</v>
       </c>
       <c r="G135" t="n">
-        <v>0.39</v>
+        <v>0.345</v>
       </c>
       <c r="H135" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.055</v>
       </c>
       <c r="I135" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.128</v>
       </c>
       <c r="J135" t="n">
-        <v>0.01</v>
+        <v>0.025</v>
       </c>
       <c r="K135" t="n">
-        <v>0.02</v>
+        <v>0.019</v>
       </c>
       <c r="L135" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="136">
@@ -5983,11 +5981,11 @@
         </is>
       </c>
       <c r="B136" s="2" t="n">
-        <v>45907</v>
+        <v>45912</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Léger</t>
+          <t>Ekos</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5997,21 +5995,23 @@
         <v>0</v>
       </c>
       <c r="F136" t="n">
-        <v>0.47</v>
+        <v>0.42</v>
       </c>
       <c r="G136" t="n">
-        <v>0.38</v>
+        <v>0.34</v>
       </c>
       <c r="H136" t="n">
-        <v>0.06</v>
+        <v>0.052</v>
       </c>
       <c r="I136" t="n">
-        <v>0.06</v>
+        <v>0.126</v>
       </c>
       <c r="J136" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="K136" t="inlineStr"/>
+        <v>0.03</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.02</v>
+      </c>
       <c r="L136" t="n">
         <v>0.01</v>
       </c>
@@ -6023,11 +6023,11 @@
         </is>
       </c>
       <c r="B137" s="2" t="n">
-        <v>45905</v>
+        <v>45908</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Nanos Research</t>
+          <t>Ipsos</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -6037,25 +6037,25 @@
         <v>0</v>
       </c>
       <c r="F137" t="n">
-        <v>0.427</v>
+        <v>0.43</v>
       </c>
       <c r="G137" t="n">
-        <v>0.329</v>
+        <v>0.39</v>
       </c>
       <c r="H137" t="n">
-        <v>0.052</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I137" t="n">
-        <v>0.128</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="J137" t="n">
-        <v>0.035</v>
+        <v>0.01</v>
       </c>
       <c r="K137" t="n">
-        <v>0.016</v>
+        <v>0.02</v>
       </c>
       <c r="L137" t="n">
-        <v>0.013</v>
+        <v>0</v>
       </c>
     </row>
     <row r="138">
@@ -6065,11 +6065,11 @@
         </is>
       </c>
       <c r="B138" s="2" t="n">
-        <v>45904</v>
+        <v>45907</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Angus Reid</t>
+          <t>Léger</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -6079,25 +6079,23 @@
         <v>0</v>
       </c>
       <c r="F138" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="G138" t="n">
         <v>0.38</v>
       </c>
-      <c r="G138" t="n">
-        <v>0.4</v>
-      </c>
       <c r="H138" t="n">
-        <v>0.08</v>
+        <v>0.06</v>
       </c>
       <c r="I138" t="n">
-        <v>0.1</v>
+        <v>0.06</v>
       </c>
       <c r="J138" t="n">
         <v>0.02</v>
       </c>
-      <c r="K138" t="n">
-        <v>0.01</v>
-      </c>
+      <c r="K138" t="inlineStr"/>
       <c r="L138" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="139">
@@ -6107,11 +6105,11 @@
         </is>
       </c>
       <c r="B139" s="2" t="n">
-        <v>45902</v>
+        <v>45905</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Abacus Data</t>
+          <t>Nanos Research</t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -6121,25 +6119,25 @@
         <v>0</v>
       </c>
       <c r="F139" t="n">
-        <v>0.43</v>
+        <v>0.427</v>
       </c>
       <c r="G139" t="n">
-        <v>0.4</v>
+        <v>0.329</v>
       </c>
       <c r="H139" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.052</v>
       </c>
       <c r="I139" t="n">
-        <v>0.06</v>
+        <v>0.128</v>
       </c>
       <c r="J139" t="n">
-        <v>0.02</v>
+        <v>0.035</v>
       </c>
       <c r="K139" t="n">
-        <v>0.01</v>
+        <v>0.016</v>
       </c>
       <c r="L139" t="n">
-        <v>0.01</v>
+        <v>0.013</v>
       </c>
     </row>
     <row r="140">
@@ -6149,11 +6147,11 @@
         </is>
       </c>
       <c r="B140" s="2" t="n">
-        <v>45901</v>
+        <v>45904</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Mainstreet Research</t>
+          <t>Angus Reid</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -6163,25 +6161,25 @@
         <v>0</v>
       </c>
       <c r="F140" t="n">
-        <v>0.423</v>
+        <v>0.38</v>
       </c>
       <c r="G140" t="n">
-        <v>0.404</v>
+        <v>0.4</v>
       </c>
       <c r="H140" t="n">
-        <v>0.05</v>
+        <v>0.08</v>
       </c>
       <c r="I140" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.1</v>
       </c>
       <c r="J140" t="n">
-        <v>0.012</v>
+        <v>0.02</v>
       </c>
       <c r="K140" t="n">
-        <v>0.016</v>
+        <v>0.01</v>
       </c>
       <c r="L140" t="n">
-        <v>0.013</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="141">
@@ -6191,11 +6189,11 @@
         </is>
       </c>
       <c r="B141" s="2" t="n">
-        <v>45898</v>
+        <v>45902</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Nanos Research</t>
+          <t>Abacus Data</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -6205,25 +6203,25 @@
         <v>0</v>
       </c>
       <c r="F141" t="n">
-        <v>0.433</v>
+        <v>0.43</v>
       </c>
       <c r="G141" t="n">
-        <v>0.324</v>
+        <v>0.4</v>
       </c>
       <c r="H141" t="n">
-        <v>0.062</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I141" t="n">
-        <v>0.127</v>
+        <v>0.06</v>
       </c>
       <c r="J141" t="n">
-        <v>0.029</v>
+        <v>0.02</v>
       </c>
       <c r="K141" t="n">
-        <v>0.016</v>
+        <v>0.01</v>
       </c>
       <c r="L141" t="n">
-        <v>0.009000000000000001</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="142">
@@ -6233,11 +6231,11 @@
         </is>
       </c>
       <c r="B142" s="2" t="n">
-        <v>45896</v>
+        <v>45901</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Liaison Strategies</t>
+          <t>Mainstreet Research</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -6247,25 +6245,25 @@
         <v>0</v>
       </c>
       <c r="F142" t="n">
-        <v>0.44</v>
+        <v>0.423</v>
       </c>
       <c r="G142" t="n">
-        <v>0.35</v>
+        <v>0.404</v>
       </c>
       <c r="H142" t="n">
         <v>0.05</v>
       </c>
       <c r="I142" t="n">
-        <v>0.1</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="J142" t="n">
-        <v>0.02</v>
+        <v>0.012</v>
       </c>
       <c r="K142" t="n">
-        <v>0.02</v>
+        <v>0.016</v>
       </c>
       <c r="L142" t="n">
-        <v>0.01</v>
+        <v>0.013</v>
       </c>
     </row>
     <row r="143">
@@ -6275,7 +6273,7 @@
         </is>
       </c>
       <c r="B143" s="2" t="n">
-        <v>45891</v>
+        <v>45898</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
@@ -6289,25 +6287,25 @@
         <v>0</v>
       </c>
       <c r="F143" t="n">
-        <v>0.4370000000000001</v>
+        <v>0.433</v>
       </c>
       <c r="G143" t="n">
-        <v>0.342</v>
+        <v>0.324</v>
       </c>
       <c r="H143" t="n">
-        <v>0.055</v>
+        <v>0.062</v>
       </c>
       <c r="I143" t="n">
-        <v>0.107</v>
+        <v>0.127</v>
       </c>
       <c r="J143" t="n">
-        <v>0.033</v>
+        <v>0.029</v>
       </c>
       <c r="K143" t="n">
         <v>0.016</v>
       </c>
       <c r="L143" t="n">
-        <v>0.008</v>
+        <v>0.009000000000000001</v>
       </c>
     </row>
     <row r="144">
@@ -6317,11 +6315,11 @@
         </is>
       </c>
       <c r="B144" s="2" t="n">
-        <v>45888</v>
+        <v>45896</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>August 19, 2025</t>
+          <t>Liaison Strategies</t>
         </is>
       </c>
       <c r="D144" t="n">
@@ -6330,13 +6328,27 @@
       <c r="E144" t="b">
         <v>0</v>
       </c>
-      <c r="F144" t="inlineStr"/>
-      <c r="G144" t="inlineStr"/>
-      <c r="H144" t="inlineStr"/>
-      <c r="I144" t="inlineStr"/>
-      <c r="J144" t="inlineStr"/>
-      <c r="K144" t="inlineStr"/>
-      <c r="L144" t="inlineStr"/>
+      <c r="F144" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="G144" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="H144" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="I144" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="J144" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="K144" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="L144" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -6345,11 +6357,11 @@
         </is>
       </c>
       <c r="B145" s="2" t="n">
-        <v>45888</v>
+        <v>45891</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Abacus Data</t>
+          <t>Nanos Research</t>
         </is>
       </c>
       <c r="D145" t="n">
@@ -6359,24 +6371,26 @@
         <v>0</v>
       </c>
       <c r="F145" t="n">
-        <v>0.39</v>
+        <v>0.4370000000000001</v>
       </c>
       <c r="G145" t="n">
-        <v>0.41</v>
+        <v>0.342</v>
       </c>
       <c r="H145" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.055</v>
       </c>
       <c r="I145" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.107</v>
       </c>
       <c r="J145" t="n">
-        <v>0.02</v>
+        <v>0.033</v>
       </c>
       <c r="K145" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="L145" t="inlineStr"/>
+        <v>0.016</v>
+      </c>
+      <c r="L145" t="n">
+        <v>0.008</v>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -6385,11 +6399,11 @@
         </is>
       </c>
       <c r="B146" s="2" t="n">
-        <v>45887</v>
+        <v>45888</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>August 18, 2025</t>
+          <t>August 19, 2025</t>
         </is>
       </c>
       <c r="D146" t="n">
@@ -6413,11 +6427,11 @@
         </is>
       </c>
       <c r="B147" s="2" t="n">
-        <v>45884</v>
+        <v>45888</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Nanos Research</t>
+          <t>Abacus Data</t>
         </is>
       </c>
       <c r="D147" t="n">
@@ -6427,26 +6441,24 @@
         <v>0</v>
       </c>
       <c r="F147" t="n">
-        <v>0.444</v>
+        <v>0.39</v>
       </c>
       <c r="G147" t="n">
-        <v>0.324</v>
+        <v>0.41</v>
       </c>
       <c r="H147" t="n">
-        <v>0.049</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I147" t="n">
-        <v>0.116</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="J147" t="n">
-        <v>0.032</v>
+        <v>0.02</v>
       </c>
       <c r="K147" t="n">
-        <v>0.028</v>
-      </c>
-      <c r="L147" t="n">
-        <v>0.006999999999999999</v>
-      </c>
+        <v>0.02</v>
+      </c>
+      <c r="L147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -6455,11 +6467,11 @@
         </is>
       </c>
       <c r="B148" s="2" t="n">
-        <v>45877</v>
+        <v>45887</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Nanos Research</t>
+          <t>August 18, 2025</t>
         </is>
       </c>
       <c r="D148" t="n">
@@ -6468,27 +6480,13 @@
       <c r="E148" t="b">
         <v>0</v>
       </c>
-      <c r="F148" t="n">
-        <v>0.448</v>
-      </c>
-      <c r="G148" t="n">
-        <v>0.319</v>
-      </c>
-      <c r="H148" t="n">
-        <v>0.061</v>
-      </c>
-      <c r="I148" t="n">
-        <v>0.115</v>
-      </c>
-      <c r="J148" t="n">
-        <v>0.026</v>
-      </c>
-      <c r="K148" t="n">
-        <v>0.025</v>
-      </c>
-      <c r="L148" t="n">
-        <v>0.006</v>
-      </c>
+      <c r="F148" t="inlineStr"/>
+      <c r="G148" t="inlineStr"/>
+      <c r="H148" t="inlineStr"/>
+      <c r="I148" t="inlineStr"/>
+      <c r="J148" t="inlineStr"/>
+      <c r="K148" t="inlineStr"/>
+      <c r="L148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -6497,11 +6495,11 @@
         </is>
       </c>
       <c r="B149" s="2" t="n">
-        <v>45877</v>
+        <v>45884</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Liaison Strategies</t>
+          <t>Nanos Research</t>
         </is>
       </c>
       <c r="D149" t="n">
@@ -6511,25 +6509,25 @@
         <v>0</v>
       </c>
       <c r="F149" t="n">
-        <v>0.44</v>
+        <v>0.444</v>
       </c>
       <c r="G149" t="n">
-        <v>0.35</v>
+        <v>0.324</v>
       </c>
       <c r="H149" t="n">
-        <v>0.06</v>
+        <v>0.049</v>
       </c>
       <c r="I149" t="n">
-        <v>0.11</v>
+        <v>0.116</v>
       </c>
       <c r="J149" t="n">
-        <v>0.03</v>
+        <v>0.032</v>
       </c>
       <c r="K149" t="n">
-        <v>0.01</v>
+        <v>0.028</v>
       </c>
       <c r="L149" t="n">
-        <v>0.01</v>
+        <v>0.006999999999999999</v>
       </c>
     </row>
     <row r="150">
@@ -6539,11 +6537,11 @@
         </is>
       </c>
       <c r="B150" s="2" t="n">
-        <v>45876</v>
+        <v>45877</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Abacus Data</t>
+          <t>Nanos Research</t>
         </is>
       </c>
       <c r="D150" t="n">
@@ -6553,24 +6551,26 @@
         <v>0</v>
       </c>
       <c r="F150" t="n">
-        <v>0.43</v>
+        <v>0.448</v>
       </c>
       <c r="G150" t="n">
-        <v>0.4</v>
+        <v>0.319</v>
       </c>
       <c r="H150" t="n">
-        <v>0.06</v>
+        <v>0.061</v>
       </c>
       <c r="I150" t="n">
-        <v>0.08</v>
+        <v>0.115</v>
       </c>
       <c r="J150" t="n">
-        <v>0.015</v>
+        <v>0.026</v>
       </c>
       <c r="K150" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="L150" t="inlineStr"/>
+        <v>0.025</v>
+      </c>
+      <c r="L150" t="n">
+        <v>0.006</v>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -6579,11 +6579,11 @@
         </is>
       </c>
       <c r="B151" s="2" t="n">
-        <v>45873</v>
+        <v>45877</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Léger</t>
+          <t>Liaison Strategies</t>
         </is>
       </c>
       <c r="D151" t="n">
@@ -6593,21 +6593,23 @@
         <v>0</v>
       </c>
       <c r="F151" t="n">
-        <v>0.46</v>
+        <v>0.44</v>
       </c>
       <c r="G151" t="n">
-        <v>0.36</v>
+        <v>0.35</v>
       </c>
       <c r="H151" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="I151" t="n">
-        <v>0.06</v>
+        <v>0.11</v>
       </c>
       <c r="J151" t="n">
         <v>0.03</v>
       </c>
-      <c r="K151" t="inlineStr"/>
+      <c r="K151" t="n">
+        <v>0.01</v>
+      </c>
       <c r="L151" t="n">
         <v>0.01</v>
       </c>
@@ -6619,11 +6621,11 @@
         </is>
       </c>
       <c r="B152" s="2" t="n">
-        <v>45870</v>
+        <v>45876</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Pallas Data</t>
+          <t>Abacus Data</t>
         </is>
       </c>
       <c r="D152" t="n">
@@ -6633,24 +6635,24 @@
         <v>0</v>
       </c>
       <c r="F152" t="n">
-        <v>0.4320000000000001</v>
+        <v>0.43</v>
       </c>
       <c r="G152" t="n">
-        <v>0.376</v>
+        <v>0.4</v>
       </c>
       <c r="H152" t="n">
-        <v>0.063</v>
+        <v>0.06</v>
       </c>
       <c r="I152" t="n">
-        <v>0.075</v>
+        <v>0.08</v>
       </c>
       <c r="J152" t="n">
-        <v>0.022</v>
-      </c>
-      <c r="K152" t="inlineStr"/>
-      <c r="L152" t="n">
-        <v>0.032</v>
-      </c>
+        <v>0.015</v>
+      </c>
+      <c r="K152" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="L152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -6659,11 +6661,11 @@
         </is>
       </c>
       <c r="B153" s="2" t="n">
-        <v>45870</v>
+        <v>45873</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Nanos Research</t>
+          <t>Léger</t>
         </is>
       </c>
       <c r="D153" t="n">
@@ -6673,23 +6675,21 @@
         <v>0</v>
       </c>
       <c r="F153" t="n">
-        <v>0.4370000000000001</v>
+        <v>0.46</v>
       </c>
       <c r="G153" t="n">
-        <v>0.325</v>
+        <v>0.36</v>
       </c>
       <c r="H153" t="n">
-        <v>0.053</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I153" t="n">
-        <v>0.12</v>
+        <v>0.06</v>
       </c>
       <c r="J153" t="n">
-        <v>0.025</v>
-      </c>
-      <c r="K153" t="n">
         <v>0.03</v>
       </c>
+      <c r="K153" t="inlineStr"/>
       <c r="L153" t="n">
         <v>0.01</v>
       </c>
@@ -6701,11 +6701,11 @@
         </is>
       </c>
       <c r="B154" s="2" t="n">
-        <v>45866</v>
+        <v>45870</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Innovative Research</t>
+          <t>Pallas Data</t>
         </is>
       </c>
       <c r="D154" t="n">
@@ -6715,23 +6715,23 @@
         <v>0</v>
       </c>
       <c r="F154" t="n">
-        <v>0.41</v>
+        <v>0.4320000000000001</v>
       </c>
       <c r="G154" t="n">
-        <v>0.39</v>
+        <v>0.376</v>
       </c>
       <c r="H154" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.063</v>
       </c>
       <c r="I154" t="n">
-        <v>0.09</v>
+        <v>0.075</v>
       </c>
       <c r="J154" t="n">
-        <v>0.04</v>
+        <v>0.022</v>
       </c>
       <c r="K154" t="inlineStr"/>
       <c r="L154" t="n">
-        <v>0.02</v>
+        <v>0.032</v>
       </c>
     </row>
     <row r="155">
@@ -6741,11 +6741,11 @@
         </is>
       </c>
       <c r="B155" s="2" t="n">
-        <v>45863</v>
+        <v>45870</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Liaison Strategies</t>
+          <t>Nanos Research</t>
         </is>
       </c>
       <c r="D155" t="n">
@@ -6755,22 +6755,22 @@
         <v>0</v>
       </c>
       <c r="F155" t="n">
-        <v>0.43</v>
+        <v>0.4370000000000001</v>
       </c>
       <c r="G155" t="n">
-        <v>0.36</v>
+        <v>0.325</v>
       </c>
       <c r="H155" t="n">
-        <v>0.06</v>
+        <v>0.053</v>
       </c>
       <c r="I155" t="n">
-        <v>0.1</v>
+        <v>0.12</v>
       </c>
       <c r="J155" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="K155" t="n">
         <v>0.03</v>
-      </c>
-      <c r="K155" t="n">
-        <v>0.01</v>
       </c>
       <c r="L155" t="n">
         <v>0.01</v>
@@ -6783,11 +6783,11 @@
         </is>
       </c>
       <c r="B156" s="2" t="n">
-        <v>45863</v>
+        <v>45866</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Nanos Research</t>
+          <t>Innovative Research</t>
         </is>
       </c>
       <c r="D156" t="n">
@@ -6797,25 +6797,23 @@
         <v>0</v>
       </c>
       <c r="F156" t="n">
-        <v>0.436</v>
+        <v>0.41</v>
       </c>
       <c r="G156" t="n">
-        <v>0.335</v>
+        <v>0.39</v>
       </c>
       <c r="H156" t="n">
-        <v>0.059</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I156" t="n">
-        <v>0.121</v>
+        <v>0.09</v>
       </c>
       <c r="J156" t="n">
-        <v>0.023</v>
-      </c>
-      <c r="K156" t="n">
-        <v>0.018</v>
-      </c>
+        <v>0.04</v>
+      </c>
+      <c r="K156" t="inlineStr"/>
       <c r="L156" t="n">
-        <v>0.008</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="157">
@@ -6825,11 +6823,11 @@
         </is>
       </c>
       <c r="B157" s="2" t="n">
-        <v>45856</v>
+        <v>45863</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Nanos Research</t>
+          <t>Liaison Strategies</t>
         </is>
       </c>
       <c r="D157" t="n">
@@ -6839,25 +6837,25 @@
         <v>0</v>
       </c>
       <c r="F157" t="n">
-        <v>0.4429999999999999</v>
+        <v>0.43</v>
       </c>
       <c r="G157" t="n">
-        <v>0.34</v>
+        <v>0.36</v>
       </c>
       <c r="H157" t="n">
-        <v>0.066</v>
+        <v>0.06</v>
       </c>
       <c r="I157" t="n">
-        <v>0.103</v>
+        <v>0.1</v>
       </c>
       <c r="J157" t="n">
-        <v>0.023</v>
+        <v>0.03</v>
       </c>
       <c r="K157" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="L157" t="n">
-        <v>0.005</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="158">
@@ -6867,11 +6865,11 @@
         </is>
       </c>
       <c r="B158" s="2" t="n">
-        <v>45853</v>
+        <v>45863</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Abacus Data</t>
+          <t>Nanos Research</t>
         </is>
       </c>
       <c r="D158" t="n">
@@ -6881,25 +6879,25 @@
         <v>0</v>
       </c>
       <c r="F158" t="n">
-        <v>0.43</v>
+        <v>0.436</v>
       </c>
       <c r="G158" t="n">
-        <v>0.4</v>
+        <v>0.335</v>
       </c>
       <c r="H158" t="n">
-        <v>0.06</v>
+        <v>0.059</v>
       </c>
       <c r="I158" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.121</v>
       </c>
       <c r="J158" t="n">
-        <v>0.03</v>
+        <v>0.023</v>
       </c>
       <c r="K158" t="n">
-        <v>0.01</v>
+        <v>0.018</v>
       </c>
       <c r="L158" t="n">
-        <v>0.01</v>
+        <v>0.008</v>
       </c>
     </row>
     <row r="159">
@@ -6909,11 +6907,11 @@
         </is>
       </c>
       <c r="B159" s="2" t="n">
-        <v>45852</v>
+        <v>45856</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Ekos</t>
+          <t>Nanos Research</t>
         </is>
       </c>
       <c r="D159" t="n">
@@ -6923,25 +6921,25 @@
         <v>0</v>
       </c>
       <c r="F159" t="n">
-        <v>0.4320000000000001</v>
+        <v>0.4429999999999999</v>
       </c>
       <c r="G159" t="n">
-        <v>0.305</v>
+        <v>0.34</v>
       </c>
       <c r="H159" t="n">
-        <v>0.055</v>
+        <v>0.066</v>
       </c>
       <c r="I159" t="n">
-        <v>0.13</v>
+        <v>0.103</v>
       </c>
       <c r="J159" t="n">
-        <v>0.035</v>
+        <v>0.023</v>
       </c>
       <c r="K159" t="n">
-        <v>0.036</v>
+        <v>0.02</v>
       </c>
       <c r="L159" t="n">
-        <v>0.01</v>
+        <v>0.005</v>
       </c>
     </row>
     <row r="160">
@@ -6951,11 +6949,11 @@
         </is>
       </c>
       <c r="B160" s="2" t="n">
-        <v>45849</v>
+        <v>45853</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Nanos Research</t>
+          <t>Abacus Data</t>
         </is>
       </c>
       <c r="D160" t="n">
@@ -6965,25 +6963,25 @@
         <v>0</v>
       </c>
       <c r="F160" t="n">
-        <v>0.445</v>
+        <v>0.43</v>
       </c>
       <c r="G160" t="n">
-        <v>0.338</v>
+        <v>0.4</v>
       </c>
       <c r="H160" t="n">
-        <v>0.059</v>
+        <v>0.06</v>
       </c>
       <c r="I160" t="n">
-        <v>0.111</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="J160" t="n">
-        <v>0.021</v>
+        <v>0.03</v>
       </c>
       <c r="K160" t="n">
-        <v>0.019</v>
+        <v>0.01</v>
       </c>
       <c r="L160" t="n">
-        <v>0.006999999999999999</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="161">
@@ -6993,11 +6991,11 @@
         </is>
       </c>
       <c r="B161" s="2" t="n">
-        <v>45844</v>
+        <v>45852</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Léger</t>
+          <t>Ekos</t>
         </is>
       </c>
       <c r="D161" t="n">
@@ -7007,21 +7005,23 @@
         <v>0</v>
       </c>
       <c r="F161" t="n">
-        <v>0.48</v>
+        <v>0.4320000000000001</v>
       </c>
       <c r="G161" t="n">
-        <v>0.35</v>
+        <v>0.305</v>
       </c>
       <c r="H161" t="n">
-        <v>0.06</v>
+        <v>0.055</v>
       </c>
       <c r="I161" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.13</v>
       </c>
       <c r="J161" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="K161" t="inlineStr"/>
+        <v>0.035</v>
+      </c>
+      <c r="K161" t="n">
+        <v>0.036</v>
+      </c>
       <c r="L161" t="n">
         <v>0.01</v>
       </c>
@@ -7033,11 +7033,11 @@
         </is>
       </c>
       <c r="B162" s="2" t="n">
-        <v>45842</v>
+        <v>45849</v>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Liaison Strategies</t>
+          <t>Nanos Research</t>
         </is>
       </c>
       <c r="D162" t="n">
@@ -7047,25 +7047,25 @@
         <v>0</v>
       </c>
       <c r="F162" t="n">
-        <v>0.46</v>
+        <v>0.445</v>
       </c>
       <c r="G162" t="n">
-        <v>0.35</v>
+        <v>0.338</v>
       </c>
       <c r="H162" t="n">
-        <v>0.06</v>
+        <v>0.059</v>
       </c>
       <c r="I162" t="n">
-        <v>0.09</v>
+        <v>0.111</v>
       </c>
       <c r="J162" t="n">
-        <v>0.02</v>
+        <v>0.021</v>
       </c>
       <c r="K162" t="n">
-        <v>0.01</v>
+        <v>0.019</v>
       </c>
       <c r="L162" t="n">
-        <v>0.01</v>
+        <v>0.006999999999999999</v>
       </c>
     </row>
     <row r="163">
@@ -7075,11 +7075,11 @@
         </is>
       </c>
       <c r="B163" s="2" t="n">
-        <v>45842</v>
+        <v>45844</v>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Nanos Research</t>
+          <t>Léger</t>
         </is>
       </c>
       <c r="D163" t="n">
@@ -7089,23 +7089,21 @@
         <v>0</v>
       </c>
       <c r="F163" t="n">
-        <v>0.451</v>
+        <v>0.48</v>
       </c>
       <c r="G163" t="n">
-        <v>0.326</v>
+        <v>0.35</v>
       </c>
       <c r="H163" t="n">
-        <v>0.062</v>
+        <v>0.06</v>
       </c>
       <c r="I163" t="n">
-        <v>0.115</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="J163" t="n">
-        <v>0.018</v>
-      </c>
-      <c r="K163" t="n">
-        <v>0.018</v>
-      </c>
+        <v>0.03</v>
+      </c>
+      <c r="K163" t="inlineStr"/>
       <c r="L163" t="n">
         <v>0.01</v>
       </c>
@@ -7117,11 +7115,11 @@
         </is>
       </c>
       <c r="B164" s="2" t="n">
-        <v>45840</v>
+        <v>45842</v>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Research Co.</t>
+          <t>Liaison Strategies</t>
         </is>
       </c>
       <c r="D164" t="n">
@@ -7131,16 +7129,16 @@
         <v>0</v>
       </c>
       <c r="F164" t="n">
-        <v>0.47</v>
+        <v>0.46</v>
       </c>
       <c r="G164" t="n">
-        <v>0.37</v>
+        <v>0.35</v>
       </c>
       <c r="H164" t="n">
         <v>0.06</v>
       </c>
       <c r="I164" t="n">
-        <v>0.06</v>
+        <v>0.09</v>
       </c>
       <c r="J164" t="n">
         <v>0.02</v>
@@ -7159,11 +7157,11 @@
         </is>
       </c>
       <c r="B165" s="2" t="n">
-        <v>45840</v>
+        <v>45842</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Abacus Data</t>
+          <t>Nanos Research</t>
         </is>
       </c>
       <c r="D165" t="n">
@@ -7173,25 +7171,25 @@
         <v>0</v>
       </c>
       <c r="F165" t="n">
-        <v>0.41</v>
+        <v>0.451</v>
       </c>
       <c r="G165" t="n">
-        <v>0.4</v>
+        <v>0.326</v>
       </c>
       <c r="H165" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.062</v>
       </c>
       <c r="I165" t="n">
-        <v>0.09</v>
+        <v>0.115</v>
       </c>
       <c r="J165" t="n">
-        <v>0.02</v>
+        <v>0.018</v>
       </c>
       <c r="K165" t="n">
-        <v>0.02</v>
+        <v>0.018</v>
       </c>
       <c r="L165" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="166">
@@ -7201,11 +7199,11 @@
         </is>
       </c>
       <c r="B166" s="2" t="n">
-        <v>45838</v>
+        <v>45840</v>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Innovative Research</t>
+          <t>Research Co.</t>
         </is>
       </c>
       <c r="D166" t="n">
@@ -7215,23 +7213,25 @@
         <v>0</v>
       </c>
       <c r="F166" t="n">
-        <v>0.43</v>
+        <v>0.47</v>
       </c>
       <c r="G166" t="n">
-        <v>0.38</v>
+        <v>0.37</v>
       </c>
       <c r="H166" t="n">
         <v>0.06</v>
       </c>
       <c r="I166" t="n">
-        <v>0.08</v>
+        <v>0.06</v>
       </c>
       <c r="J166" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="K166" t="inlineStr"/>
+        <v>0.02</v>
+      </c>
+      <c r="K166" t="n">
+        <v>0.01</v>
+      </c>
       <c r="L166" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="167">
@@ -7241,11 +7241,11 @@
         </is>
       </c>
       <c r="B167" s="2" t="n">
-        <v>45835</v>
+        <v>45840</v>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Nanos Research</t>
+          <t>Abacus Data</t>
         </is>
       </c>
       <c r="D167" t="n">
@@ -7255,25 +7255,25 @@
         <v>0</v>
       </c>
       <c r="F167" t="n">
-        <v>0.445</v>
+        <v>0.41</v>
       </c>
       <c r="G167" t="n">
-        <v>0.314</v>
+        <v>0.4</v>
       </c>
       <c r="H167" t="n">
-        <v>0.059</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I167" t="n">
-        <v>0.128</v>
+        <v>0.09</v>
       </c>
       <c r="J167" t="n">
-        <v>0.025</v>
+        <v>0.02</v>
       </c>
       <c r="K167" t="n">
-        <v>0.017</v>
+        <v>0.02</v>
       </c>
       <c r="L167" t="n">
-        <v>0.012</v>
+        <v>0</v>
       </c>
     </row>
     <row r="168">
@@ -7283,11 +7283,11 @@
         </is>
       </c>
       <c r="B168" s="2" t="n">
-        <v>45834</v>
+        <v>45838</v>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Mainstreet Research</t>
+          <t>Innovative Research</t>
         </is>
       </c>
       <c r="D168" t="n">
@@ -7297,23 +7297,21 @@
         <v>0</v>
       </c>
       <c r="F168" t="n">
-        <v>0.47</v>
+        <v>0.43</v>
       </c>
       <c r="G168" t="n">
         <v>0.38</v>
       </c>
       <c r="H168" t="n">
-        <v>0.03</v>
+        <v>0.06</v>
       </c>
       <c r="I168" t="n">
-        <v>0.06</v>
+        <v>0.08</v>
       </c>
       <c r="J168" t="n">
         <v>0.03</v>
       </c>
-      <c r="K168" t="n">
-        <v>0.01</v>
-      </c>
+      <c r="K168" t="inlineStr"/>
       <c r="L168" t="n">
         <v>0.02</v>
       </c>
@@ -7325,11 +7323,11 @@
         </is>
       </c>
       <c r="B169" s="2" t="n">
-        <v>45828</v>
+        <v>45835</v>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Liaison Strategies</t>
+          <t>Nanos Research</t>
         </is>
       </c>
       <c r="D169" t="n">
@@ -7339,25 +7337,25 @@
         <v>0</v>
       </c>
       <c r="F169" t="n">
-        <v>0.42</v>
+        <v>0.445</v>
       </c>
       <c r="G169" t="n">
-        <v>0.38</v>
+        <v>0.314</v>
       </c>
       <c r="H169" t="n">
-        <v>0.06</v>
+        <v>0.059</v>
       </c>
       <c r="I169" t="n">
-        <v>0.11</v>
+        <v>0.128</v>
       </c>
       <c r="J169" t="n">
-        <v>0.03</v>
+        <v>0.025</v>
       </c>
       <c r="K169" t="n">
-        <v>0.01</v>
+        <v>0.017</v>
       </c>
       <c r="L169" t="n">
-        <v>0.01</v>
+        <v>0.012</v>
       </c>
     </row>
     <row r="170">
@@ -7367,11 +7365,11 @@
         </is>
       </c>
       <c r="B170" s="2" t="n">
-        <v>45828</v>
+        <v>45834</v>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Nanos Research</t>
+          <t>Mainstreet Research</t>
         </is>
       </c>
       <c r="D170" t="n">
@@ -7381,25 +7379,25 @@
         <v>0</v>
       </c>
       <c r="F170" t="n">
-        <v>0.452</v>
+        <v>0.47</v>
       </c>
       <c r="G170" t="n">
-        <v>0.308</v>
+        <v>0.38</v>
       </c>
       <c r="H170" t="n">
-        <v>0.061</v>
+        <v>0.03</v>
       </c>
       <c r="I170" t="n">
-        <v>0.122</v>
+        <v>0.06</v>
       </c>
       <c r="J170" t="n">
-        <v>0.029</v>
+        <v>0.03</v>
       </c>
       <c r="K170" t="n">
-        <v>0.015</v>
+        <v>0.01</v>
       </c>
       <c r="L170" t="n">
-        <v>0.013</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="171">
@@ -7409,11 +7407,11 @@
         </is>
       </c>
       <c r="B171" s="2" t="n">
-        <v>45827</v>
+        <v>45828</v>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Abacus Data</t>
+          <t>Liaison Strategies</t>
         </is>
       </c>
       <c r="D171" t="n">
@@ -7426,13 +7424,13 @@
         <v>0.42</v>
       </c>
       <c r="G171" t="n">
-        <v>0.39</v>
+        <v>0.38</v>
       </c>
       <c r="H171" t="n">
         <v>0.06</v>
       </c>
       <c r="I171" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.11</v>
       </c>
       <c r="J171" t="n">
         <v>0.03</v>
@@ -7451,7 +7449,7 @@
         </is>
       </c>
       <c r="B172" s="2" t="n">
-        <v>45821</v>
+        <v>45828</v>
       </c>
       <c r="C172" t="inlineStr">
         <is>
@@ -7465,25 +7463,25 @@
         <v>0</v>
       </c>
       <c r="F172" t="n">
-        <v>0.442</v>
+        <v>0.452</v>
       </c>
       <c r="G172" t="n">
-        <v>0.322</v>
+        <v>0.308</v>
       </c>
       <c r="H172" t="n">
-        <v>0.063</v>
+        <v>0.061</v>
       </c>
       <c r="I172" t="n">
-        <v>0.114</v>
+        <v>0.122</v>
       </c>
       <c r="J172" t="n">
-        <v>0.032</v>
+        <v>0.029</v>
       </c>
       <c r="K172" t="n">
-        <v>0.017</v>
+        <v>0.015</v>
       </c>
       <c r="L172" t="n">
-        <v>0.01</v>
+        <v>0.013</v>
       </c>
     </row>
     <row r="173">
@@ -7493,11 +7491,11 @@
         </is>
       </c>
       <c r="B173" s="2" t="n">
-        <v>45814</v>
+        <v>45827</v>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Liaison Strategies</t>
+          <t>Abacus Data</t>
         </is>
       </c>
       <c r="D173" t="n">
@@ -7516,10 +7514,10 @@
         <v>0.06</v>
       </c>
       <c r="I173" t="n">
-        <v>0.09</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="J173" t="n">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="K173" t="n">
         <v>0.01</v>
@@ -7535,7 +7533,7 @@
         </is>
       </c>
       <c r="B174" s="2" t="n">
-        <v>45814</v>
+        <v>45821</v>
       </c>
       <c r="C174" t="inlineStr">
         <is>
@@ -7549,25 +7547,25 @@
         <v>0</v>
       </c>
       <c r="F174" t="n">
-        <v>0.426</v>
+        <v>0.442</v>
       </c>
       <c r="G174" t="n">
-        <v>0.328</v>
+        <v>0.322</v>
       </c>
       <c r="H174" t="n">
-        <v>0.065</v>
+        <v>0.063</v>
       </c>
       <c r="I174" t="n">
-        <v>0.12</v>
+        <v>0.114</v>
       </c>
       <c r="J174" t="n">
-        <v>0.039</v>
+        <v>0.032</v>
       </c>
       <c r="K174" t="n">
-        <v>0.013</v>
+        <v>0.017</v>
       </c>
       <c r="L174" t="n">
-        <v>0.009000000000000001</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="175">
@@ -7577,11 +7575,11 @@
         </is>
       </c>
       <c r="B175" s="2" t="n">
-        <v>45813</v>
+        <v>45814</v>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Abacus Data</t>
+          <t>Liaison Strategies</t>
         </is>
       </c>
       <c r="D175" t="n">
@@ -7600,16 +7598,16 @@
         <v>0.06</v>
       </c>
       <c r="I175" t="n">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="J175" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="K175" t="n">
         <v>0.01</v>
       </c>
       <c r="L175" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="176">
@@ -7619,11 +7617,11 @@
         </is>
       </c>
       <c r="B176" s="2" t="n">
-        <v>45812</v>
+        <v>45814</v>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Ekos</t>
+          <t>Nanos Research</t>
         </is>
       </c>
       <c r="D176" t="n">
@@ -7633,25 +7631,25 @@
         <v>0</v>
       </c>
       <c r="F176" t="n">
-        <v>0.439</v>
+        <v>0.426</v>
       </c>
       <c r="G176" t="n">
-        <v>0.32</v>
+        <v>0.328</v>
       </c>
       <c r="H176" t="n">
-        <v>0.052</v>
+        <v>0.065</v>
       </c>
       <c r="I176" t="n">
-        <v>0.127</v>
+        <v>0.12</v>
       </c>
       <c r="J176" t="n">
-        <v>0.03</v>
+        <v>0.039</v>
       </c>
       <c r="K176" t="n">
-        <v>0.03</v>
+        <v>0.013</v>
       </c>
       <c r="L176" t="n">
-        <v>0.01</v>
+        <v>0.009000000000000001</v>
       </c>
     </row>
     <row r="177">
@@ -7661,11 +7659,11 @@
         </is>
       </c>
       <c r="B177" s="2" t="n">
-        <v>45807</v>
+        <v>45813</v>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Spark Insights</t>
+          <t>Abacus Data</t>
         </is>
       </c>
       <c r="D177" t="n">
@@ -7675,21 +7673,25 @@
         <v>0</v>
       </c>
       <c r="F177" t="n">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="G177" t="n">
-        <v>0.4</v>
+        <v>0.39</v>
       </c>
       <c r="H177" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="I177" t="n">
         <v>0.08</v>
       </c>
-      <c r="J177" t="inlineStr"/>
-      <c r="K177" t="inlineStr"/>
+      <c r="J177" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="K177" t="n">
+        <v>0.01</v>
+      </c>
       <c r="L177" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
     </row>
     <row r="178">
@@ -7699,11 +7701,11 @@
         </is>
       </c>
       <c r="B178" s="2" t="n">
-        <v>45807</v>
+        <v>45812</v>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Nanos Research</t>
+          <t>Ekos</t>
         </is>
       </c>
       <c r="D178" t="n">
@@ -7713,25 +7715,25 @@
         <v>0</v>
       </c>
       <c r="F178" t="n">
-        <v>0.417</v>
+        <v>0.439</v>
       </c>
       <c r="G178" t="n">
-        <v>0.364</v>
+        <v>0.32</v>
       </c>
       <c r="H178" t="n">
-        <v>0.065</v>
+        <v>0.052</v>
       </c>
       <c r="I178" t="n">
-        <v>0.105</v>
+        <v>0.127</v>
       </c>
       <c r="J178" t="n">
-        <v>0.034</v>
+        <v>0.03</v>
       </c>
       <c r="K178" t="n">
-        <v>0.011</v>
+        <v>0.03</v>
       </c>
       <c r="L178" t="n">
-        <v>0.003</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="179">
@@ -7741,11 +7743,11 @@
         </is>
       </c>
       <c r="B179" s="2" t="n">
-        <v>45800</v>
+        <v>45807</v>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Liaison Strategies</t>
+          <t>Spark Insights</t>
         </is>
       </c>
       <c r="D179" t="n">
@@ -7755,25 +7757,21 @@
         <v>0</v>
       </c>
       <c r="F179" t="n">
-        <v>0.44</v>
+        <v>0.41</v>
       </c>
       <c r="G179" t="n">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="H179" t="n">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I179" t="n">
         <v>0.08</v>
       </c>
-      <c r="J179" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="K179" t="n">
-        <v>0.01</v>
-      </c>
+      <c r="J179" t="inlineStr"/>
+      <c r="K179" t="inlineStr"/>
       <c r="L179" t="n">
-        <v>0.01</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="180">
@@ -7783,7 +7781,7 @@
         </is>
       </c>
       <c r="B180" s="2" t="n">
-        <v>45800</v>
+        <v>45807</v>
       </c>
       <c r="C180" t="inlineStr">
         <is>
@@ -7797,22 +7795,22 @@
         <v>0</v>
       </c>
       <c r="F180" t="n">
-        <v>0.404</v>
+        <v>0.417</v>
       </c>
       <c r="G180" t="n">
-        <v>0.386</v>
+        <v>0.364</v>
       </c>
       <c r="H180" t="n">
-        <v>0.059</v>
+        <v>0.065</v>
       </c>
       <c r="I180" t="n">
-        <v>0.098</v>
+        <v>0.105</v>
       </c>
       <c r="J180" t="n">
-        <v>0.03700000000000001</v>
+        <v>0.034</v>
       </c>
       <c r="K180" t="n">
-        <v>0.013</v>
+        <v>0.011</v>
       </c>
       <c r="L180" t="n">
         <v>0.003</v>
@@ -7825,11 +7823,11 @@
         </is>
       </c>
       <c r="B181" s="2" t="n">
-        <v>45799</v>
+        <v>45800</v>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Innovative Research</t>
+          <t>Liaison Strategies</t>
         </is>
       </c>
       <c r="D181" t="n">
@@ -7839,7 +7837,7 @@
         <v>0</v>
       </c>
       <c r="F181" t="n">
-        <v>0.42</v>
+        <v>0.44</v>
       </c>
       <c r="G181" t="n">
         <v>0.39</v>
@@ -7851,11 +7849,13 @@
         <v>0.08</v>
       </c>
       <c r="J181" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="K181" t="inlineStr"/>
+        <v>0.01</v>
+      </c>
+      <c r="K181" t="n">
+        <v>0.01</v>
+      </c>
       <c r="L181" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="182">
@@ -7865,11 +7865,11 @@
         </is>
       </c>
       <c r="B182" s="2" t="n">
-        <v>45798</v>
+        <v>45800</v>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Abacus Data</t>
+          <t>Nanos Research</t>
         </is>
       </c>
       <c r="D182" t="n">
@@ -7879,25 +7879,25 @@
         <v>0</v>
       </c>
       <c r="F182" t="n">
-        <v>0.41</v>
+        <v>0.404</v>
       </c>
       <c r="G182" t="n">
-        <v>0.4</v>
+        <v>0.386</v>
       </c>
       <c r="H182" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.059</v>
       </c>
       <c r="I182" t="n">
-        <v>0.08</v>
+        <v>0.098</v>
       </c>
       <c r="J182" t="n">
-        <v>0.03</v>
+        <v>0.03700000000000001</v>
       </c>
       <c r="K182" t="n">
-        <v>0.01</v>
+        <v>0.013</v>
       </c>
       <c r="L182" t="n">
-        <v>0</v>
+        <v>0.003</v>
       </c>
     </row>
     <row r="183">
@@ -7907,11 +7907,11 @@
         </is>
       </c>
       <c r="B183" s="2" t="n">
-        <v>45793</v>
+        <v>45799</v>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Nanos Research</t>
+          <t>Innovative Research</t>
         </is>
       </c>
       <c r="D183" t="n">
@@ -7921,25 +7921,23 @@
         <v>0</v>
       </c>
       <c r="F183" t="n">
-        <v>0.414</v>
+        <v>0.42</v>
       </c>
       <c r="G183" t="n">
-        <v>0.396</v>
+        <v>0.39</v>
       </c>
       <c r="H183" t="n">
-        <v>0.047</v>
+        <v>0.06</v>
       </c>
       <c r="I183" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="J183" t="n">
-        <v>0.039</v>
-      </c>
-      <c r="K183" t="n">
-        <v>0.013</v>
-      </c>
+        <v>0.03</v>
+      </c>
+      <c r="K183" t="inlineStr"/>
       <c r="L183" t="n">
-        <v>0.006</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="184">
@@ -7949,11 +7947,11 @@
         </is>
       </c>
       <c r="B184" s="2" t="n">
-        <v>45786</v>
+        <v>45798</v>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Liaison Strategies</t>
+          <t>Abacus Data</t>
         </is>
       </c>
       <c r="D184" t="n">
@@ -7963,19 +7961,19 @@
         <v>0</v>
       </c>
       <c r="F184" t="n">
-        <v>0.45</v>
+        <v>0.41</v>
       </c>
       <c r="G184" t="n">
         <v>0.4</v>
       </c>
       <c r="H184" t="n">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I184" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="J184" t="n">
-        <v>0.01</v>
+        <v>0.03</v>
       </c>
       <c r="K184" t="n">
         <v>0.01</v>
@@ -7991,7 +7989,7 @@
         </is>
       </c>
       <c r="B185" s="2" t="n">
-        <v>45786</v>
+        <v>45793</v>
       </c>
       <c r="C185" t="inlineStr">
         <is>
@@ -8005,25 +8003,25 @@
         <v>0</v>
       </c>
       <c r="F185" t="n">
-        <v>0.415</v>
+        <v>0.414</v>
       </c>
       <c r="G185" t="n">
-        <v>0.405</v>
+        <v>0.396</v>
       </c>
       <c r="H185" t="n">
-        <v>0.051</v>
+        <v>0.047</v>
       </c>
       <c r="I185" t="n">
-        <v>0.078</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="J185" t="n">
-        <v>0.033</v>
+        <v>0.039</v>
       </c>
       <c r="K185" t="n">
         <v>0.013</v>
       </c>
       <c r="L185" t="n">
-        <v>0.005</v>
+        <v>0.006</v>
       </c>
     </row>
     <row r="186">
@@ -8033,11 +8031,11 @@
         </is>
       </c>
       <c r="B186" s="2" t="n">
-        <v>45782</v>
+        <v>45786</v>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>May 5, 2025</t>
+          <t>Liaison Strategies</t>
         </is>
       </c>
       <c r="D186" t="n">
@@ -8046,13 +8044,27 @@
       <c r="E186" t="b">
         <v>0</v>
       </c>
-      <c r="F186" t="inlineStr"/>
-      <c r="G186" t="inlineStr"/>
-      <c r="H186" t="inlineStr"/>
-      <c r="I186" t="inlineStr"/>
-      <c r="J186" t="inlineStr"/>
-      <c r="K186" t="inlineStr"/>
-      <c r="L186" t="inlineStr"/>
+      <c r="F186" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="G186" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H186" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="I186" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="J186" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="K186" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L186" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -8061,7 +8073,7 @@
         </is>
       </c>
       <c r="B187" s="2" t="n">
-        <v>45779</v>
+        <v>45786</v>
       </c>
       <c r="C187" t="inlineStr">
         <is>
@@ -8075,25 +8087,25 @@
         <v>0</v>
       </c>
       <c r="F187" t="n">
-        <v>0.418</v>
+        <v>0.415</v>
       </c>
       <c r="G187" t="n">
-        <v>0.392</v>
+        <v>0.405</v>
       </c>
       <c r="H187" t="n">
-        <v>0.058</v>
+        <v>0.051</v>
       </c>
       <c r="I187" t="n">
-        <v>0.079</v>
+        <v>0.078</v>
       </c>
       <c r="J187" t="n">
-        <v>0.032</v>
+        <v>0.033</v>
       </c>
       <c r="K187" t="n">
         <v>0.013</v>
       </c>
       <c r="L187" t="n">
-        <v>0.008</v>
+        <v>0.005</v>
       </c>
     </row>
     <row r="188">
@@ -8103,11 +8115,11 @@
         </is>
       </c>
       <c r="B188" s="2" t="n">
-        <v>45777</v>
+        <v>45782</v>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>April 30, 2025</t>
+          <t>May 5, 2025</t>
         </is>
       </c>
       <c r="D188" t="n">
@@ -8131,11 +8143,11 @@
         </is>
       </c>
       <c r="B189" s="2" t="n">
-        <v>45776</v>
+        <v>45779</v>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>April 29, 2025</t>
+          <t>Nanos Research</t>
         </is>
       </c>
       <c r="D189" t="n">
@@ -8144,13 +8156,27 @@
       <c r="E189" t="b">
         <v>0</v>
       </c>
-      <c r="F189" t="inlineStr"/>
-      <c r="G189" t="inlineStr"/>
-      <c r="H189" t="inlineStr"/>
-      <c r="I189" t="inlineStr"/>
-      <c r="J189" t="inlineStr"/>
-      <c r="K189" t="inlineStr"/>
-      <c r="L189" t="inlineStr"/>
+      <c r="F189" t="n">
+        <v>0.418</v>
+      </c>
+      <c r="G189" t="n">
+        <v>0.392</v>
+      </c>
+      <c r="H189" t="n">
+        <v>0.058</v>
+      </c>
+      <c r="I189" t="n">
+        <v>0.079</v>
+      </c>
+      <c r="J189" t="n">
+        <v>0.032</v>
+      </c>
+      <c r="K189" t="n">
+        <v>0.013</v>
+      </c>
+      <c r="L189" t="n">
+        <v>0.008</v>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -8159,11 +8185,11 @@
         </is>
       </c>
       <c r="B190" s="2" t="n">
-        <v>45775</v>
+        <v>45777</v>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>2025 election</t>
+          <t>April 30, 2025</t>
         </is>
       </c>
       <c r="D190" t="n">
@@ -8172,40 +8198,26 @@
       <c r="E190" t="b">
         <v>0</v>
       </c>
-      <c r="F190" t="n">
-        <v>0.4379999999999999</v>
-      </c>
-      <c r="G190" t="n">
-        <v>0.413</v>
-      </c>
-      <c r="H190" t="n">
-        <v>0.063</v>
-      </c>
-      <c r="I190" t="n">
-        <v>0.063</v>
-      </c>
-      <c r="J190" t="n">
-        <v>0.012</v>
-      </c>
-      <c r="K190" t="n">
-        <v>0.006999999999999999</v>
-      </c>
-      <c r="L190" t="n">
-        <v>0.004</v>
-      </c>
+      <c r="F190" t="inlineStr"/>
+      <c r="G190" t="inlineStr"/>
+      <c r="H190" t="inlineStr"/>
+      <c r="I190" t="inlineStr"/>
+      <c r="J190" t="inlineStr"/>
+      <c r="K190" t="inlineStr"/>
+      <c r="L190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>Quebec</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="B191" s="2" t="n">
-        <v>46139</v>
+        <v>45776</v>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Liaison Strategies</t>
+          <t>April 29, 2025</t>
         </is>
       </c>
       <c r="D191" t="n">
@@ -8214,40 +8226,26 @@
       <c r="E191" t="b">
         <v>0</v>
       </c>
-      <c r="F191" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="G191" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="H191" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="I191" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="J191" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="K191" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="L191" t="n">
-        <v>0.01</v>
-      </c>
+      <c r="F191" t="inlineStr"/>
+      <c r="G191" t="inlineStr"/>
+      <c r="H191" t="inlineStr"/>
+      <c r="I191" t="inlineStr"/>
+      <c r="J191" t="inlineStr"/>
+      <c r="K191" t="inlineStr"/>
+      <c r="L191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>Quebec</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="B192" s="2" t="n">
-        <v>46132</v>
+        <v>45775</v>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Léger</t>
+          <t>2025 election</t>
         </is>
       </c>
       <c r="D192" t="n">
@@ -8257,23 +8255,25 @@
         <v>0</v>
       </c>
       <c r="F192" t="n">
-        <v>0.47</v>
+        <v>0.4379999999999999</v>
       </c>
       <c r="G192" t="n">
-        <v>0.17</v>
+        <v>0.413</v>
       </c>
       <c r="H192" t="n">
-        <v>0.29</v>
+        <v>0.063</v>
       </c>
       <c r="I192" t="n">
-        <v>0.05</v>
+        <v>0.063</v>
       </c>
       <c r="J192" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="K192" t="inlineStr"/>
+        <v>0.012</v>
+      </c>
+      <c r="K192" t="n">
+        <v>0.006999999999999999</v>
+      </c>
       <c r="L192" t="n">
-        <v>0.01</v>
+        <v>0.004</v>
       </c>
     </row>
     <row r="193">
@@ -8283,11 +8283,11 @@
         </is>
       </c>
       <c r="B193" s="2" t="n">
-        <v>45971</v>
+        <v>46139</v>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Léger</t>
+          <t>Liaison Strategies</t>
         </is>
       </c>
       <c r="D193" t="n">
@@ -8297,24 +8297,26 @@
         <v>0</v>
       </c>
       <c r="F193" t="n">
-        <v>0.39</v>
+        <v>0.42</v>
       </c>
       <c r="G193" t="n">
-        <v>0.25</v>
+        <v>0.21</v>
       </c>
       <c r="H193" t="n">
-        <v>0.28</v>
+        <v>0.22</v>
       </c>
       <c r="I193" t="n">
-        <v>0.05</v>
+        <v>0.09</v>
       </c>
       <c r="J193" t="n">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="K193" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="L193" t="inlineStr"/>
+        <v>0.02</v>
+      </c>
+      <c r="L193" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -8323,7 +8325,7 @@
         </is>
       </c>
       <c r="B194" s="2" t="n">
-        <v>45915</v>
+        <v>46132</v>
       </c>
       <c r="C194" t="inlineStr">
         <is>
@@ -8337,19 +8339,19 @@
         <v>0</v>
       </c>
       <c r="F194" t="n">
-        <v>0.42</v>
+        <v>0.47</v>
       </c>
       <c r="G194" t="n">
-        <v>0.21</v>
+        <v>0.17</v>
       </c>
       <c r="H194" t="n">
-        <v>0.3</v>
+        <v>0.29</v>
       </c>
       <c r="I194" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="J194" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="K194" t="inlineStr"/>
       <c r="L194" t="n">
@@ -8363,7 +8365,7 @@
         </is>
       </c>
       <c r="B195" s="2" t="n">
-        <v>45887</v>
+        <v>45971</v>
       </c>
       <c r="C195" t="inlineStr">
         <is>
@@ -8377,10 +8379,10 @@
         <v>0</v>
       </c>
       <c r="F195" t="n">
-        <v>0.43</v>
+        <v>0.39</v>
       </c>
       <c r="G195" t="n">
-        <v>0.22</v>
+        <v>0.25</v>
       </c>
       <c r="H195" t="n">
         <v>0.28</v>
@@ -8391,10 +8393,10 @@
       <c r="J195" t="n">
         <v>0.02</v>
       </c>
-      <c r="K195" t="inlineStr"/>
-      <c r="L195" t="n">
-        <v>0</v>
-      </c>
+      <c r="K195" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L195" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -8403,7 +8405,7 @@
         </is>
       </c>
       <c r="B196" s="2" t="n">
-        <v>45830</v>
+        <v>45915</v>
       </c>
       <c r="C196" t="inlineStr">
         <is>
@@ -8417,23 +8419,23 @@
         <v>0</v>
       </c>
       <c r="F196" t="n">
-        <v>0.44</v>
+        <v>0.42</v>
       </c>
       <c r="G196" t="n">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="H196" t="n">
-        <v>0.25</v>
+        <v>0.3</v>
       </c>
       <c r="I196" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="J196" t="n">
         <v>0.03</v>
       </c>
       <c r="K196" t="inlineStr"/>
       <c r="L196" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="197">
@@ -8443,11 +8445,11 @@
         </is>
       </c>
       <c r="B197" s="2" t="n">
-        <v>45775</v>
+        <v>45887</v>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>2025 election</t>
+          <t>Léger</t>
         </is>
       </c>
       <c r="D197" t="n">
@@ -8457,35 +8459,33 @@
         <v>0</v>
       </c>
       <c r="F197" t="n">
-        <v>0.426</v>
+        <v>0.43</v>
       </c>
       <c r="G197" t="n">
-        <v>0.233</v>
+        <v>0.22</v>
       </c>
       <c r="H197" t="n">
-        <v>0.277</v>
+        <v>0.28</v>
       </c>
       <c r="I197" t="n">
-        <v>0.045</v>
+        <v>0.05</v>
       </c>
       <c r="J197" t="n">
-        <v>0.009000000000000001</v>
-      </c>
-      <c r="K197" t="n">
-        <v>0.008</v>
-      </c>
+        <v>0.02</v>
+      </c>
+      <c r="K197" t="inlineStr"/>
       <c r="L197" t="n">
-        <v>0.002</v>
+        <v>0</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>Ontario</t>
+          <t>Quebec</t>
         </is>
       </c>
       <c r="B198" s="2" t="n">
-        <v>45802</v>
+        <v>45830</v>
       </c>
       <c r="C198" t="inlineStr">
         <is>
@@ -8499,12 +8499,14 @@
         <v>0</v>
       </c>
       <c r="F198" t="n">
-        <v>0.54</v>
+        <v>0.44</v>
       </c>
       <c r="G198" t="n">
-        <v>0.37</v>
-      </c>
-      <c r="H198" t="inlineStr"/>
+        <v>0.23</v>
+      </c>
+      <c r="H198" t="n">
+        <v>0.25</v>
+      </c>
       <c r="I198" t="n">
         <v>0.05</v>
       </c>
@@ -8513,13 +8515,13 @@
       </c>
       <c r="K198" t="inlineStr"/>
       <c r="L198" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>Ontario</t>
+          <t>Quebec</t>
         </is>
       </c>
       <c r="B199" s="2" t="n">
@@ -8537,20 +8539,22 @@
         <v>0</v>
       </c>
       <c r="F199" t="n">
-        <v>0.49</v>
+        <v>0.426</v>
       </c>
       <c r="G199" t="n">
-        <v>0.4379999999999999</v>
-      </c>
-      <c r="H199" t="inlineStr"/>
+        <v>0.233</v>
+      </c>
+      <c r="H199" t="n">
+        <v>0.277</v>
+      </c>
       <c r="I199" t="n">
-        <v>0.049</v>
+        <v>0.045</v>
       </c>
       <c r="J199" t="n">
-        <v>0.012</v>
+        <v>0.009000000000000001</v>
       </c>
       <c r="K199" t="n">
-        <v>0.006999999999999999</v>
+        <v>0.008</v>
       </c>
       <c r="L199" t="n">
         <v>0.002</v>
@@ -8559,15 +8563,15 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>Manitoba</t>
+          <t>Ontario</t>
         </is>
       </c>
       <c r="B200" s="2" t="n">
-        <v>46094</v>
+        <v>45802</v>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Probe Research</t>
+          <t>Léger</t>
         </is>
       </c>
       <c r="D200" t="n">
@@ -8577,33 +8581,35 @@
         <v>0</v>
       </c>
       <c r="F200" t="n">
-        <v>0.46</v>
+        <v>0.54</v>
       </c>
       <c r="G200" t="n">
-        <v>0.39</v>
+        <v>0.37</v>
       </c>
       <c r="H200" t="inlineStr"/>
       <c r="I200" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="J200" t="inlineStr"/>
+        <v>0.05</v>
+      </c>
+      <c r="J200" t="n">
+        <v>0.03</v>
+      </c>
       <c r="K200" t="inlineStr"/>
       <c r="L200" t="n">
-        <v>0.05</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>Manitoba</t>
+          <t>Ontario</t>
         </is>
       </c>
       <c r="B201" s="2" t="n">
-        <v>46001</v>
+        <v>45775</v>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Probe Research</t>
+          <t>2025 election</t>
         </is>
       </c>
       <c r="D201" t="n">
@@ -8613,19 +8619,23 @@
         <v>0</v>
       </c>
       <c r="F201" t="n">
-        <v>0.43</v>
+        <v>0.49</v>
       </c>
       <c r="G201" t="n">
-        <v>0.38</v>
+        <v>0.4379999999999999</v>
       </c>
       <c r="H201" t="inlineStr"/>
       <c r="I201" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="J201" t="inlineStr"/>
-      <c r="K201" t="inlineStr"/>
+        <v>0.049</v>
+      </c>
+      <c r="J201" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="K201" t="n">
+        <v>0.006999999999999999</v>
+      </c>
       <c r="L201" t="n">
-        <v>0.06</v>
+        <v>0.002</v>
       </c>
     </row>
     <row r="202">
@@ -8635,11 +8645,11 @@
         </is>
       </c>
       <c r="B202" s="2" t="n">
-        <v>45775</v>
+        <v>46094</v>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>2025 election</t>
+          <t>Probe Research</t>
         </is>
       </c>
       <c r="D202" t="n">
@@ -8649,37 +8659,33 @@
         <v>0</v>
       </c>
       <c r="F202" t="n">
-        <v>0.408</v>
+        <v>0.46</v>
       </c>
       <c r="G202" t="n">
-        <v>0.463</v>
+        <v>0.39</v>
       </c>
       <c r="H202" t="inlineStr"/>
       <c r="I202" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="J202" t="n">
-        <v>0.006999999999999999</v>
-      </c>
-      <c r="K202" t="n">
-        <v>0.01</v>
-      </c>
+        <v>0.08</v>
+      </c>
+      <c r="J202" t="inlineStr"/>
+      <c r="K202" t="inlineStr"/>
       <c r="L202" t="n">
-        <v>0.002</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>Alberta</t>
+          <t>Manitoba</t>
         </is>
       </c>
       <c r="B203" s="2" t="n">
-        <v>46134</v>
+        <v>46001</v>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Mainstreet Research</t>
+          <t>Probe Research</t>
         </is>
       </c>
       <c r="D203" t="n">
@@ -8689,37 +8695,33 @@
         <v>0</v>
       </c>
       <c r="F203" t="n">
-        <v>0.403</v>
+        <v>0.43</v>
       </c>
       <c r="G203" t="n">
-        <v>0.458</v>
+        <v>0.38</v>
       </c>
       <c r="H203" t="inlineStr"/>
       <c r="I203" t="n">
-        <v>0.08900000000000001</v>
-      </c>
-      <c r="J203" t="n">
-        <v>0.011</v>
-      </c>
-      <c r="K203" t="n">
-        <v>0.025</v>
-      </c>
+        <v>0.14</v>
+      </c>
+      <c r="J203" t="inlineStr"/>
+      <c r="K203" t="inlineStr"/>
       <c r="L203" t="n">
-        <v>0.014</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>Alberta</t>
+          <t>Manitoba</t>
         </is>
       </c>
       <c r="B204" s="2" t="n">
-        <v>46078</v>
+        <v>45775</v>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Abacus Data</t>
+          <t>2025 election</t>
         </is>
       </c>
       <c r="D204" t="n">
@@ -8729,23 +8731,23 @@
         <v>0</v>
       </c>
       <c r="F204" t="n">
-        <v>0.36</v>
+        <v>0.408</v>
       </c>
       <c r="G204" t="n">
-        <v>0.51</v>
+        <v>0.463</v>
       </c>
       <c r="H204" t="inlineStr"/>
       <c r="I204" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.11</v>
       </c>
       <c r="J204" t="n">
-        <v>0.01</v>
+        <v>0.006999999999999999</v>
       </c>
       <c r="K204" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="L204" t="n">
-        <v>0.02</v>
+        <v>0.002</v>
       </c>
     </row>
     <row r="205">
@@ -8755,7 +8757,7 @@
         </is>
       </c>
       <c r="B205" s="2" t="n">
-        <v>46065</v>
+        <v>46134</v>
       </c>
       <c r="C205" t="inlineStr">
         <is>
@@ -8769,23 +8771,23 @@
         <v>0</v>
       </c>
       <c r="F205" t="n">
-        <v>0.45</v>
+        <v>0.403</v>
       </c>
       <c r="G205" t="n">
-        <v>0.48</v>
+        <v>0.458</v>
       </c>
       <c r="H205" t="inlineStr"/>
       <c r="I205" t="n">
-        <v>0.05</v>
+        <v>0.08900000000000001</v>
       </c>
       <c r="J205" t="n">
-        <v>0.01</v>
+        <v>0.011</v>
       </c>
       <c r="K205" t="n">
-        <v>0.01</v>
+        <v>0.025</v>
       </c>
       <c r="L205" t="n">
-        <v>0.01</v>
+        <v>0.014</v>
       </c>
     </row>
     <row r="206">
@@ -8795,11 +8797,11 @@
         </is>
       </c>
       <c r="B206" s="2" t="n">
-        <v>45802</v>
+        <v>46078</v>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Léger</t>
+          <t>Abacus Data</t>
         </is>
       </c>
       <c r="D206" t="n">
@@ -8809,21 +8811,23 @@
         <v>0</v>
       </c>
       <c r="F206" t="n">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="G206" t="n">
-        <v>0.54</v>
+        <v>0.51</v>
       </c>
       <c r="H206" t="inlineStr"/>
       <c r="I206" t="n">
-        <v>0.05</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="J206" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="K206" t="inlineStr"/>
+        <v>0.01</v>
+      </c>
+      <c r="K206" t="n">
+        <v>0.02</v>
+      </c>
       <c r="L206" t="n">
-        <v>0.04</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="207">
@@ -8833,11 +8837,11 @@
         </is>
       </c>
       <c r="B207" s="2" t="n">
-        <v>45775</v>
+        <v>46065</v>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>2025 election</t>
+          <t>Mainstreet Research</t>
         </is>
       </c>
       <c r="D207" t="n">
@@ -8847,37 +8851,37 @@
         <v>0</v>
       </c>
       <c r="F207" t="n">
-        <v>0.279</v>
+        <v>0.45</v>
       </c>
       <c r="G207" t="n">
-        <v>0.635</v>
+        <v>0.48</v>
       </c>
       <c r="H207" t="inlineStr"/>
       <c r="I207" t="n">
-        <v>0.063</v>
+        <v>0.05</v>
       </c>
       <c r="J207" t="n">
-        <v>0.004</v>
+        <v>0.01</v>
       </c>
       <c r="K207" t="n">
-        <v>0.009000000000000001</v>
+        <v>0.01</v>
       </c>
       <c r="L207" t="n">
-        <v>0.008</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>British Columbia</t>
+          <t>Alberta</t>
         </is>
       </c>
       <c r="B208" s="2" t="n">
-        <v>46125</v>
+        <v>45802</v>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Mainstreet Research</t>
+          <t>Léger</t>
         </is>
       </c>
       <c r="D208" t="n">
@@ -8887,37 +8891,35 @@
         <v>0</v>
       </c>
       <c r="F208" t="n">
-        <v>0.512</v>
+        <v>0.35</v>
       </c>
       <c r="G208" t="n">
-        <v>0.322</v>
+        <v>0.54</v>
       </c>
       <c r="H208" t="inlineStr"/>
       <c r="I208" t="n">
-        <v>0.08800000000000001</v>
+        <v>0.05</v>
       </c>
       <c r="J208" t="n">
-        <v>0.03700000000000001</v>
-      </c>
-      <c r="K208" t="n">
-        <v>0</v>
-      </c>
+        <v>0.03</v>
+      </c>
+      <c r="K208" t="inlineStr"/>
       <c r="L208" t="n">
-        <v>0.032</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>British Columbia</t>
+          <t>Alberta</t>
         </is>
       </c>
       <c r="B209" s="2" t="n">
-        <v>46094</v>
+        <v>45775</v>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Mainstreet Research</t>
+          <t>2025 election</t>
         </is>
       </c>
       <c r="D209" t="n">
@@ -8927,23 +8929,23 @@
         <v>0</v>
       </c>
       <c r="F209" t="n">
-        <v>0.467</v>
+        <v>0.279</v>
       </c>
       <c r="G209" t="n">
-        <v>0.341</v>
+        <v>0.635</v>
       </c>
       <c r="H209" t="inlineStr"/>
       <c r="I209" t="n">
-        <v>0.096</v>
+        <v>0.063</v>
       </c>
       <c r="J209" t="n">
-        <v>0.039</v>
+        <v>0.004</v>
       </c>
       <c r="K209" t="n">
-        <v>0.014</v>
+        <v>0.009000000000000001</v>
       </c>
       <c r="L209" t="n">
-        <v>0.043</v>
+        <v>0.008</v>
       </c>
     </row>
     <row r="210">
@@ -8953,11 +8955,11 @@
         </is>
       </c>
       <c r="B210" s="2" t="n">
-        <v>45775</v>
+        <v>46125</v>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>2025 election</t>
+          <t>Mainstreet Research</t>
         </is>
       </c>
       <c r="D210" t="n">
@@ -8967,22 +8969,102 @@
         <v>0</v>
       </c>
       <c r="F210" t="n">
-        <v>0.418</v>
+        <v>0.512</v>
       </c>
       <c r="G210" t="n">
-        <v>0.41</v>
+        <v>0.322</v>
       </c>
       <c r="H210" t="inlineStr"/>
       <c r="I210" t="n">
+        <v>0.08800000000000001</v>
+      </c>
+      <c r="J210" t="n">
+        <v>0.03700000000000001</v>
+      </c>
+      <c r="K210" t="n">
+        <v>0</v>
+      </c>
+      <c r="L210" t="n">
+        <v>0.032</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="B211" s="2" t="n">
+        <v>46094</v>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>Mainstreet Research</t>
+        </is>
+      </c>
+      <c r="D211" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E211" t="b">
+        <v>0</v>
+      </c>
+      <c r="F211" t="n">
+        <v>0.467</v>
+      </c>
+      <c r="G211" t="n">
+        <v>0.341</v>
+      </c>
+      <c r="H211" t="inlineStr"/>
+      <c r="I211" t="n">
+        <v>0.096</v>
+      </c>
+      <c r="J211" t="n">
+        <v>0.039</v>
+      </c>
+      <c r="K211" t="n">
+        <v>0.014</v>
+      </c>
+      <c r="L211" t="n">
+        <v>0.043</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="B212" s="2" t="n">
+        <v>45775</v>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>2025 election</t>
+        </is>
+      </c>
+      <c r="D212" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E212" t="b">
+        <v>0</v>
+      </c>
+      <c r="F212" t="n">
+        <v>0.418</v>
+      </c>
+      <c r="G212" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="H212" t="inlineStr"/>
+      <c r="I212" t="n">
         <v>0.13</v>
       </c>
-      <c r="J210" t="n">
+      <c r="J212" t="n">
         <v>0.03</v>
       </c>
-      <c r="K210" t="n">
+      <c r="K212" t="n">
         <v>0.005</v>
       </c>
-      <c r="L210" t="n">
+      <c r="L212" t="n">
         <v>0.006</v>
       </c>
     </row>

--- a/poll_averages.xlsx
+++ b/poll_averages.xlsx
@@ -501,11 +501,11 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>46178</v>
+        <v>46179</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Nanos Research</t>
+          <t>Liaison Strategies</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -515,24 +515,26 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>0.423</v>
+        <v>0.4</v>
       </c>
       <c r="G2" t="n">
-        <v>0.294</v>
+        <v>0.32</v>
       </c>
       <c r="H2" t="n">
-        <v>0.067</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>0.131</v>
+        <v>0.15</v>
       </c>
       <c r="J2" t="n">
-        <v>0.06</v>
+        <v>0.03</v>
       </c>
       <c r="K2" t="n">
         <v>0.02</v>
       </c>
-      <c r="L2" t="inlineStr"/>
+      <c r="L2" t="n">
+        <v>0.02</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -541,11 +543,11 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>46179</v>
+        <v>46178</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Liaison Strategies</t>
+          <t>Nanos Research</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -555,26 +557,24 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>0.4</v>
+        <v>0.423</v>
       </c>
       <c r="G3" t="n">
-        <v>0.32</v>
+        <v>0.294</v>
       </c>
       <c r="H3" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.067</v>
       </c>
       <c r="I3" t="n">
-        <v>0.15</v>
+        <v>0.131</v>
       </c>
       <c r="J3" t="n">
-        <v>0.03</v>
+        <v>0.06</v>
       </c>
       <c r="K3" t="n">
         <v>0.02</v>
       </c>
-      <c r="L3" t="n">
-        <v>0.02</v>
-      </c>
+      <c r="L3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">

--- a/poll_averages.xlsx
+++ b/poll_averages.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L212"/>
+  <dimension ref="A1:L213"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -485,12 +485,12 @@
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
+          <t>oth</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
           <t>ppc</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>oth</t>
         </is>
       </c>
     </row>
@@ -501,11 +501,11 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>46179</v>
+        <v>46183</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Liaison Strategies</t>
+          <t>Angus Reid</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -515,26 +515,24 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="G2" t="n">
-        <v>0.32</v>
+        <v>0.36</v>
       </c>
       <c r="H2" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>0.15</v>
+        <v>0.12</v>
       </c>
       <c r="J2" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="K2" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="L2" t="n">
-        <v>0.02</v>
-      </c>
+        <v>0.01</v>
+      </c>
+      <c r="L2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -543,11 +541,11 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>46178</v>
+        <v>46179</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Nanos Research</t>
+          <t>Liaison Strategies</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -557,24 +555,26 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>0.423</v>
+        <v>0.4</v>
       </c>
       <c r="G3" t="n">
-        <v>0.294</v>
+        <v>0.32</v>
       </c>
       <c r="H3" t="n">
-        <v>0.067</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I3" t="n">
-        <v>0.131</v>
+        <v>0.15</v>
       </c>
       <c r="J3" t="n">
-        <v>0.06</v>
+        <v>0.03</v>
       </c>
       <c r="K3" t="n">
         <v>0.02</v>
       </c>
-      <c r="L3" t="inlineStr"/>
+      <c r="L3" t="n">
+        <v>0.02</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -583,11 +583,11 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>46175</v>
+        <v>46178</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Abacus Data</t>
+          <t>Nanos Research</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -597,25 +597,23 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>0.44</v>
+        <v>0.423</v>
       </c>
       <c r="G4" t="n">
-        <v>0.36</v>
+        <v>0.294</v>
       </c>
       <c r="H4" t="n">
+        <v>0.067</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.131</v>
+      </c>
+      <c r="J4" t="n">
         <v>0.06</v>
       </c>
-      <c r="I4" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0.01</v>
-      </c>
+      <c r="K4" t="inlineStr"/>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="5">
@@ -625,11 +623,11 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Léger</t>
+          <t>Abacus Data</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -639,21 +637,23 @@
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="G5" t="n">
-        <v>0.34</v>
+        <v>0.36</v>
       </c>
       <c r="H5" t="n">
         <v>0.06</v>
       </c>
       <c r="I5" t="n">
-        <v>0.06</v>
+        <v>0.11</v>
       </c>
       <c r="J5" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="K5" t="inlineStr"/>
+        <v>0.03</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
       <c r="L5" t="n">
         <v>0.01</v>
       </c>
@@ -665,11 +665,11 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>46173</v>
+        <v>46174</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Liaison Strategies</t>
+          <t>Léger</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -679,26 +679,24 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>0.41</v>
+        <v>0.5</v>
       </c>
       <c r="G6" t="n">
-        <v>0.32</v>
+        <v>0.34</v>
       </c>
       <c r="H6" t="n">
         <v>0.06</v>
       </c>
       <c r="I6" t="n">
-        <v>0.16</v>
+        <v>0.06</v>
       </c>
       <c r="J6" t="n">
         <v>0.02</v>
       </c>
       <c r="K6" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0.02</v>
-      </c>
+        <v>0.01</v>
+      </c>
+      <c r="L6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -707,11 +705,11 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>46171</v>
+        <v>46173</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Nanos Research</t>
+          <t>Liaison Strategies</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -721,24 +719,26 @@
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>0.403</v>
+        <v>0.41</v>
       </c>
       <c r="G7" t="n">
-        <v>0.328</v>
+        <v>0.32</v>
       </c>
       <c r="H7" t="n">
-        <v>0.066</v>
+        <v>0.06</v>
       </c>
       <c r="I7" t="n">
-        <v>0.132</v>
+        <v>0.16</v>
       </c>
       <c r="J7" t="n">
-        <v>0.051</v>
+        <v>0.02</v>
       </c>
       <c r="K7" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="L7" t="inlineStr"/>
+        <v>0.02</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.02</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -747,11 +747,11 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>46166</v>
+        <v>46171</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Pallas Data</t>
+          <t>Nanos Research</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -761,23 +761,23 @@
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>0.45</v>
+        <v>0.403</v>
       </c>
       <c r="G8" t="n">
-        <v>0.32</v>
+        <v>0.328</v>
       </c>
       <c r="H8" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.066</v>
       </c>
       <c r="I8" t="n">
-        <v>0.11</v>
+        <v>0.132</v>
       </c>
       <c r="J8" t="n">
-        <v>0.03</v>
+        <v>0.051</v>
       </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="n">
-        <v>0.02</v>
+        <v>0.015</v>
       </c>
     </row>
     <row r="9">
@@ -787,11 +787,11 @@
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>46165</v>
+        <v>46166</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Liaison Strategies</t>
+          <t>Pallas Data</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -801,26 +801,24 @@
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>0.43</v>
+        <v>0.45</v>
       </c>
       <c r="G9" t="n">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="H9" t="n">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I9" t="n">
         <v>0.11</v>
       </c>
       <c r="J9" t="n">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="K9" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0.03</v>
-      </c>
+        <v>0.02</v>
+      </c>
+      <c r="L9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -829,11 +827,11 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>46164</v>
+        <v>46165</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Nanos Research</t>
+          <t>Liaison Strategies</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -843,24 +841,26 @@
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>0.411</v>
+        <v>0.43</v>
       </c>
       <c r="G10" t="n">
-        <v>0.327</v>
+        <v>0.31</v>
       </c>
       <c r="H10" t="n">
-        <v>0.064</v>
+        <v>0.06</v>
       </c>
       <c r="I10" t="n">
-        <v>0.126</v>
+        <v>0.11</v>
       </c>
       <c r="J10" t="n">
-        <v>0.048</v>
+        <v>0.02</v>
       </c>
       <c r="K10" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="L10" t="inlineStr"/>
+        <v>0.03</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.03</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -869,11 +869,11 @@
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>46162</v>
+        <v>46164</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Abacus Data</t>
+          <t>Nanos Research</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -883,24 +883,24 @@
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>0.47</v>
+        <v>0.411</v>
       </c>
       <c r="G11" t="n">
-        <v>0.35</v>
+        <v>0.327</v>
       </c>
       <c r="H11" t="n">
-        <v>0.06</v>
+        <v>0.064</v>
       </c>
       <c r="I11" t="n">
-        <v>0.08</v>
+        <v>0.126</v>
       </c>
       <c r="J11" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="L11" t="inlineStr"/>
+        <v>0.048</v>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="n">
+        <v>0.02</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -909,11 +909,11 @@
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>46158</v>
+        <v>46162</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Liaison Strategies</t>
+          <t>Abacus Data</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -923,25 +923,23 @@
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>0.43</v>
+        <v>0.47</v>
       </c>
       <c r="G12" t="n">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="H12" t="n">
         <v>0.06</v>
       </c>
       <c r="I12" t="n">
-        <v>0.11</v>
+        <v>0.08</v>
       </c>
       <c r="J12" t="n">
         <v>0.02</v>
       </c>
-      <c r="K12" t="n">
-        <v>0.02</v>
-      </c>
+      <c r="K12" t="inlineStr"/>
       <c r="L12" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="13">
@@ -951,11 +949,11 @@
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>46157</v>
+        <v>46158</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Nanos Research</t>
+          <t>Liaison Strategies</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -965,24 +963,26 @@
         <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>0.423</v>
+        <v>0.43</v>
       </c>
       <c r="G13" t="n">
-        <v>0.327</v>
+        <v>0.34</v>
       </c>
       <c r="H13" t="n">
-        <v>0.058</v>
+        <v>0.06</v>
       </c>
       <c r="I13" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="J13" t="n">
-        <v>0.044</v>
+        <v>0.02</v>
       </c>
       <c r="K13" t="n">
-        <v>0.019</v>
-      </c>
-      <c r="L13" t="inlineStr"/>
+        <v>0.02</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0.02</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -991,11 +991,11 @@
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>46151</v>
+        <v>46157</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Liaison Strategies</t>
+          <t>Nanos Research</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -1005,25 +1005,23 @@
         <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>0.44</v>
+        <v>0.423</v>
       </c>
       <c r="G14" t="n">
-        <v>0.33</v>
+        <v>0.327</v>
       </c>
       <c r="H14" t="n">
-        <v>0.06</v>
+        <v>0.058</v>
       </c>
       <c r="I14" t="n">
-        <v>0.1</v>
+        <v>0.12</v>
       </c>
       <c r="J14" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0.02</v>
-      </c>
+        <v>0.044</v>
+      </c>
+      <c r="K14" t="inlineStr"/>
       <c r="L14" t="n">
-        <v>0.02</v>
+        <v>0.019</v>
       </c>
     </row>
     <row r="15">
@@ -1033,11 +1031,11 @@
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>46150</v>
+        <v>46151</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Nanos Research</t>
+          <t>Liaison Strategies</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -1047,24 +1045,26 @@
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>0.455</v>
+        <v>0.44</v>
       </c>
       <c r="G15" t="n">
-        <v>0.334</v>
+        <v>0.33</v>
       </c>
       <c r="H15" t="n">
-        <v>0.053</v>
+        <v>0.06</v>
       </c>
       <c r="I15" t="n">
-        <v>0.08800000000000001</v>
+        <v>0.1</v>
       </c>
       <c r="J15" t="n">
-        <v>0.035</v>
+        <v>0.02</v>
       </c>
       <c r="K15" t="n">
         <v>0.02</v>
       </c>
-      <c r="L15" t="inlineStr"/>
+      <c r="L15" t="n">
+        <v>0.02</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1077,7 +1077,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Research Co.</t>
+          <t>Nanos Research</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -1087,25 +1087,23 @@
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>0.46</v>
+        <v>0.455</v>
       </c>
       <c r="G16" t="n">
-        <v>0.31</v>
+        <v>0.334</v>
       </c>
       <c r="H16" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.053</v>
       </c>
       <c r="I16" t="n">
-        <v>0.11</v>
+        <v>0.08800000000000001</v>
       </c>
       <c r="J16" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0.01</v>
-      </c>
+        <v>0.035</v>
+      </c>
+      <c r="K16" t="inlineStr"/>
       <c r="L16" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="17">
@@ -1115,11 +1113,11 @@
         </is>
       </c>
       <c r="B17" s="2" t="n">
-        <v>46147</v>
+        <v>46150</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Abacus Data</t>
+          <t>Research Co.</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1132,13 +1130,13 @@
         <v>0.46</v>
       </c>
       <c r="G17" t="n">
-        <v>0.36</v>
+        <v>0.31</v>
       </c>
       <c r="H17" t="n">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I17" t="n">
-        <v>0.08</v>
+        <v>0.11</v>
       </c>
       <c r="J17" t="n">
         <v>0.03</v>
@@ -1147,7 +1145,7 @@
         <v>0.01</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="18">
@@ -1157,11 +1155,11 @@
         </is>
       </c>
       <c r="B18" s="2" t="n">
-        <v>46144</v>
+        <v>46147</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Liaison Strategies</t>
+          <t>Abacus Data</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1171,25 +1169,25 @@
         <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="G18" t="n">
-        <v>0.33</v>
+        <v>0.36</v>
       </c>
       <c r="H18" t="n">
         <v>0.06</v>
       </c>
       <c r="I18" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="J18" t="n">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="K18" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="19">
@@ -1199,11 +1197,11 @@
         </is>
       </c>
       <c r="B19" s="2" t="n">
-        <v>46143</v>
+        <v>46144</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Nanos Research</t>
+          <t>Liaison Strategies</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1213,24 +1211,26 @@
         <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>0.448</v>
+        <v>0.45</v>
       </c>
       <c r="G19" t="n">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="H19" t="n">
-        <v>0.05599999999999999</v>
+        <v>0.06</v>
       </c>
       <c r="I19" t="n">
-        <v>0.114</v>
+        <v>0.09</v>
       </c>
       <c r="J19" t="n">
-        <v>0.034</v>
+        <v>0.02</v>
       </c>
       <c r="K19" t="n">
-        <v>0.014</v>
-      </c>
-      <c r="L19" t="inlineStr"/>
+        <v>0.03</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0.02</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1239,11 +1239,11 @@
         </is>
       </c>
       <c r="B20" s="2" t="n">
-        <v>46138</v>
+        <v>46143</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Léger</t>
+          <t>Nanos Research</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1253,23 +1253,23 @@
         <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>0.48</v>
+        <v>0.448</v>
       </c>
       <c r="G20" t="n">
-        <v>0.37</v>
+        <v>0.32</v>
       </c>
       <c r="H20" t="n">
-        <v>0.06</v>
+        <v>0.05599999999999999</v>
       </c>
       <c r="I20" t="n">
-        <v>0.06</v>
+        <v>0.114</v>
       </c>
       <c r="J20" t="n">
-        <v>0.02</v>
+        <v>0.034</v>
       </c>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="n">
-        <v>0.01</v>
+        <v>0.014</v>
       </c>
     </row>
     <row r="21">
@@ -1279,11 +1279,11 @@
         </is>
       </c>
       <c r="B21" s="2" t="n">
-        <v>46137</v>
+        <v>46138</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Liaison Strategies</t>
+          <t>Léger</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1293,26 +1293,24 @@
         <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>0.45</v>
+        <v>0.48</v>
       </c>
       <c r="G21" t="n">
-        <v>0.34</v>
+        <v>0.37</v>
       </c>
       <c r="H21" t="n">
         <v>0.06</v>
       </c>
       <c r="I21" t="n">
-        <v>0.09</v>
+        <v>0.06</v>
       </c>
       <c r="J21" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="K21" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0.02</v>
-      </c>
+        <v>0.01</v>
+      </c>
+      <c r="L21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1321,11 +1319,11 @@
         </is>
       </c>
       <c r="B22" s="2" t="n">
-        <v>46136</v>
+        <v>46137</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Ekos</t>
+          <t>Liaison Strategies</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1335,16 +1333,16 @@
         <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>0.445</v>
+        <v>0.45</v>
       </c>
       <c r="G22" t="n">
-        <v>0.31</v>
+        <v>0.34</v>
       </c>
       <c r="H22" t="n">
-        <v>0.058</v>
+        <v>0.06</v>
       </c>
       <c r="I22" t="n">
-        <v>0.125</v>
+        <v>0.09</v>
       </c>
       <c r="J22" t="n">
         <v>0.03</v>
@@ -1353,7 +1351,7 @@
         <v>0.02</v>
       </c>
       <c r="L22" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="23">
@@ -1367,7 +1365,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Nanos Research</t>
+          <t>Ekos</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1377,24 +1375,26 @@
         <v>0</v>
       </c>
       <c r="F23" t="n">
-        <v>0.446</v>
+        <v>0.445</v>
       </c>
       <c r="G23" t="n">
-        <v>0.32</v>
+        <v>0.31</v>
       </c>
       <c r="H23" t="n">
-        <v>0.05400000000000001</v>
+        <v>0.058</v>
       </c>
       <c r="I23" t="n">
-        <v>0.115</v>
+        <v>0.125</v>
       </c>
       <c r="J23" t="n">
-        <v>0.035</v>
+        <v>0.03</v>
       </c>
       <c r="K23" t="n">
-        <v>0.011</v>
-      </c>
-      <c r="L23" t="inlineStr"/>
+        <v>0.01</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0.02</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1403,11 +1403,11 @@
         </is>
       </c>
       <c r="B24" s="2" t="n">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Abacus Data</t>
+          <t>Nanos Research</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1417,25 +1417,23 @@
         <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>0.45</v>
+        <v>0.446</v>
       </c>
       <c r="G24" t="n">
-        <v>0.36</v>
+        <v>0.32</v>
       </c>
       <c r="H24" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.05400000000000001</v>
       </c>
       <c r="I24" t="n">
-        <v>0.08</v>
+        <v>0.115</v>
       </c>
       <c r="J24" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0.01</v>
-      </c>
+        <v>0.035</v>
+      </c>
+      <c r="K24" t="inlineStr"/>
       <c r="L24" t="n">
-        <v>0.01</v>
+        <v>0.011</v>
       </c>
     </row>
     <row r="25">
@@ -1445,11 +1443,11 @@
         </is>
       </c>
       <c r="B25" s="2" t="n">
-        <v>46132</v>
+        <v>46134</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Angus Reid</t>
+          <t>Abacus Data</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1459,21 +1457,23 @@
         <v>0</v>
       </c>
       <c r="F25" t="n">
-        <v>0.42</v>
+        <v>0.45</v>
       </c>
       <c r="G25" t="n">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="H25" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="I25" t="n">
-        <v>0.12</v>
+        <v>0.08</v>
       </c>
       <c r="J25" t="n">
         <v>0.02</v>
       </c>
-      <c r="K25" t="inlineStr"/>
+      <c r="K25" t="n">
+        <v>0.01</v>
+      </c>
       <c r="L25" t="n">
         <v>0.01</v>
       </c>
@@ -1485,11 +1485,11 @@
         </is>
       </c>
       <c r="B26" s="2" t="n">
-        <v>46130</v>
+        <v>46132</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Liaison Strategies</t>
+          <t>Angus Reid</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1499,26 +1499,24 @@
         <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="G26" t="n">
-        <v>0.33</v>
+        <v>0.35</v>
       </c>
       <c r="H26" t="n">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I26" t="n">
-        <v>0.1</v>
+        <v>0.12</v>
       </c>
       <c r="J26" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="K26" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="L26" t="n">
-        <v>0.02</v>
-      </c>
+        <v>0.01</v>
+      </c>
+      <c r="L26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1527,11 +1525,11 @@
         </is>
       </c>
       <c r="B27" s="2" t="n">
-        <v>46129</v>
+        <v>46130</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Nanos Research</t>
+          <t>Liaison Strategies</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1541,24 +1539,26 @@
         <v>0</v>
       </c>
       <c r="F27" t="n">
-        <v>0.458</v>
+        <v>0.45</v>
       </c>
       <c r="G27" t="n">
-        <v>0.315</v>
+        <v>0.33</v>
       </c>
       <c r="H27" t="n">
-        <v>0.053</v>
+        <v>0.06</v>
       </c>
       <c r="I27" t="n">
-        <v>0.119</v>
+        <v>0.1</v>
       </c>
       <c r="J27" t="n">
-        <v>0.035</v>
+        <v>0.03</v>
       </c>
       <c r="K27" t="n">
-        <v>0.009000000000000001</v>
-      </c>
-      <c r="L27" t="inlineStr"/>
+        <v>0.02</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0.02</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1567,11 +1567,11 @@
         </is>
       </c>
       <c r="B28" s="2" t="n">
-        <v>46125</v>
+        <v>46129</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>April 13, 2026</t>
+          <t>Nanos Research</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1580,13 +1580,25 @@
       <c r="E28" t="b">
         <v>0</v>
       </c>
-      <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
+      <c r="F28" t="n">
+        <v>0.458</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0.315</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.053</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0.119</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0.035</v>
+      </c>
       <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
+      <c r="L28" t="n">
+        <v>0.009000000000000001</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1595,11 +1607,11 @@
         </is>
       </c>
       <c r="B29" s="2" t="n">
-        <v>46123</v>
+        <v>46125</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Liaison Strategies</t>
+          <t>April 13, 2026</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1608,27 +1620,13 @@
       <c r="E29" t="b">
         <v>0</v>
       </c>
-      <c r="F29" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="G29" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="H29" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="I29" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="J29" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="K29" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="L29" t="n">
-        <v>0.02</v>
-      </c>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1637,11 +1635,11 @@
         </is>
       </c>
       <c r="B30" s="2" t="n">
-        <v>46122</v>
+        <v>46123</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Nanos Research</t>
+          <t>Liaison Strategies</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1651,24 +1649,26 @@
         <v>0</v>
       </c>
       <c r="F30" t="n">
-        <v>0.453</v>
+        <v>0.43</v>
       </c>
       <c r="G30" t="n">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="H30" t="n">
-        <v>0.05400000000000001</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I30" t="n">
-        <v>0.122</v>
+        <v>0.1</v>
       </c>
       <c r="J30" t="n">
-        <v>0.035</v>
+        <v>0.03</v>
       </c>
       <c r="K30" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="L30" t="inlineStr"/>
+        <v>0.02</v>
+      </c>
+      <c r="L30" t="n">
+        <v>0.02</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1677,11 +1677,11 @@
         </is>
       </c>
       <c r="B31" s="2" t="n">
-        <v>46120</v>
+        <v>46122</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Spark Insights</t>
+          <t>Nanos Research</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1691,21 +1691,23 @@
         <v>0</v>
       </c>
       <c r="F31" t="n">
-        <v>0.46</v>
+        <v>0.453</v>
       </c>
       <c r="G31" t="n">
         <v>0.32</v>
       </c>
       <c r="H31" t="n">
-        <v>0.06</v>
+        <v>0.05400000000000001</v>
       </c>
       <c r="I31" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="J31" t="inlineStr"/>
+        <v>0.122</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0.035</v>
+      </c>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="n">
-        <v>0.08</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="32">
@@ -1719,7 +1721,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Abacus Data</t>
+          <t>Spark Insights</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1729,26 +1731,22 @@
         <v>0</v>
       </c>
       <c r="F32" t="n">
-        <v>0.44</v>
+        <v>0.46</v>
       </c>
       <c r="G32" t="n">
-        <v>0.38</v>
+        <v>0.32</v>
       </c>
       <c r="H32" t="n">
         <v>0.06</v>
       </c>
       <c r="I32" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="n">
         <v>0.08</v>
       </c>
-      <c r="J32" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="K32" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="L32" t="n">
-        <v>0.01</v>
-      </c>
+      <c r="L32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1757,11 +1755,11 @@
         </is>
       </c>
       <c r="B33" s="2" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Ipsos</t>
+          <t>Abacus Data</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1771,25 +1769,25 @@
         <v>0</v>
       </c>
       <c r="F33" t="n">
-        <v>0.45</v>
+        <v>0.44</v>
       </c>
       <c r="G33" t="n">
-        <v>0.33</v>
+        <v>0.38</v>
       </c>
       <c r="H33" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="I33" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="J33" t="n">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="K33" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="34">
@@ -1799,11 +1797,11 @@
         </is>
       </c>
       <c r="B34" s="2" t="n">
-        <v>46116</v>
+        <v>46119</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Liaison Strategies</t>
+          <t>Ipsos</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1813,22 +1811,22 @@
         <v>0</v>
       </c>
       <c r="F34" t="n">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="G34" t="n">
         <v>0.33</v>
       </c>
       <c r="H34" t="n">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I34" t="n">
         <v>0.09</v>
       </c>
       <c r="J34" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="K34" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="L34" t="n">
         <v>0.02</v>
@@ -1841,11 +1839,11 @@
         </is>
       </c>
       <c r="B35" s="2" t="n">
-        <v>46115</v>
+        <v>46116</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Nanos Research</t>
+          <t>Liaison Strategies</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1855,24 +1853,26 @@
         <v>0</v>
       </c>
       <c r="F35" t="n">
-        <v>0.457</v>
+        <v>0.44</v>
       </c>
       <c r="G35" t="n">
-        <v>0.305</v>
+        <v>0.33</v>
       </c>
       <c r="H35" t="n">
-        <v>0.05599999999999999</v>
+        <v>0.06</v>
       </c>
       <c r="I35" t="n">
-        <v>0.125</v>
+        <v>0.09</v>
       </c>
       <c r="J35" t="n">
-        <v>0.042</v>
+        <v>0.03</v>
       </c>
       <c r="K35" t="n">
-        <v>0.011</v>
-      </c>
-      <c r="L35" t="inlineStr"/>
+        <v>0.02</v>
+      </c>
+      <c r="L35" t="n">
+        <v>0.02</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1881,11 +1881,11 @@
         </is>
       </c>
       <c r="B36" s="2" t="n">
-        <v>46111</v>
+        <v>46115</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Léger</t>
+          <t>Nanos Research</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1895,23 +1895,23 @@
         <v>0</v>
       </c>
       <c r="F36" t="n">
-        <v>0.48</v>
+        <v>0.457</v>
       </c>
       <c r="G36" t="n">
-        <v>0.34</v>
+        <v>0.305</v>
       </c>
       <c r="H36" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.05599999999999999</v>
       </c>
       <c r="I36" t="n">
-        <v>0.06</v>
+        <v>0.125</v>
       </c>
       <c r="J36" t="n">
-        <v>0.03</v>
+        <v>0.042</v>
       </c>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="n">
-        <v>0.01</v>
+        <v>0.011</v>
       </c>
     </row>
     <row r="37">
@@ -1921,11 +1921,11 @@
         </is>
       </c>
       <c r="B37" s="2" t="n">
-        <v>46110</v>
+        <v>46111</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>March 29, 2026</t>
+          <t>Léger</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1934,12 +1934,24 @@
       <c r="E37" t="b">
         <v>0</v>
       </c>
-      <c r="F37" t="inlineStr"/>
-      <c r="G37" t="inlineStr"/>
-      <c r="H37" t="inlineStr"/>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
+      <c r="F37" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="J37" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="K37" t="n">
+        <v>0.01</v>
+      </c>
       <c r="L37" t="inlineStr"/>
     </row>
     <row r="38">
@@ -1949,11 +1961,11 @@
         </is>
       </c>
       <c r="B38" s="2" t="n">
-        <v>46109</v>
+        <v>46110</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Liaison Strategies</t>
+          <t>March 29, 2026</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1962,27 +1974,13 @@
       <c r="E38" t="b">
         <v>0</v>
       </c>
-      <c r="F38" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="G38" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="H38" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="I38" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="J38" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="K38" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="L38" t="n">
-        <v>0.02</v>
-      </c>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1991,11 +1989,11 @@
         </is>
       </c>
       <c r="B39" s="2" t="n">
-        <v>46108</v>
+        <v>46109</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Nanos Research</t>
+          <t>Liaison Strategies</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -2005,24 +2003,26 @@
         <v>0</v>
       </c>
       <c r="F39" t="n">
-        <v>0.465</v>
+        <v>0.45</v>
       </c>
       <c r="G39" t="n">
-        <v>0.322</v>
+        <v>0.33</v>
       </c>
       <c r="H39" t="n">
-        <v>0.051</v>
+        <v>0.06</v>
       </c>
       <c r="I39" t="n">
-        <v>0.113</v>
+        <v>0.09</v>
       </c>
       <c r="J39" t="n">
-        <v>0.036</v>
+        <v>0.02</v>
       </c>
       <c r="K39" t="n">
-        <v>0.011</v>
-      </c>
-      <c r="L39" t="inlineStr"/>
+        <v>0.02</v>
+      </c>
+      <c r="L39" t="n">
+        <v>0.02</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2031,11 +2031,11 @@
         </is>
       </c>
       <c r="B40" s="2" t="n">
-        <v>46107</v>
+        <v>46108</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Spark Insights</t>
+          <t>Nanos Research</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -2045,21 +2045,23 @@
         <v>0</v>
       </c>
       <c r="F40" t="n">
-        <v>0.46</v>
+        <v>0.465</v>
       </c>
       <c r="G40" t="n">
-        <v>0.3</v>
+        <v>0.322</v>
       </c>
       <c r="H40" t="n">
-        <v>0.05</v>
+        <v>0.051</v>
       </c>
       <c r="I40" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="J40" t="inlineStr"/>
+        <v>0.113</v>
+      </c>
+      <c r="J40" t="n">
+        <v>0.036</v>
+      </c>
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="n">
-        <v>0.08</v>
+        <v>0.011</v>
       </c>
     </row>
     <row r="41">
@@ -2069,11 +2071,11 @@
         </is>
       </c>
       <c r="B41" s="2" t="n">
-        <v>46105</v>
+        <v>46107</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Abacus Data</t>
+          <t>Spark Insights</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -2083,26 +2085,22 @@
         <v>0</v>
       </c>
       <c r="F41" t="n">
-        <v>0.44</v>
+        <v>0.46</v>
       </c>
       <c r="G41" t="n">
-        <v>0.37</v>
+        <v>0.3</v>
       </c>
       <c r="H41" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="I41" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="J41" t="n">
-        <v>0.03</v>
-      </c>
+        <v>0.11</v>
+      </c>
+      <c r="J41" t="inlineStr"/>
       <c r="K41" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="L41" t="n">
-        <v>0</v>
-      </c>
+        <v>0.08</v>
+      </c>
+      <c r="L41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2111,11 +2109,11 @@
         </is>
       </c>
       <c r="B42" s="2" t="n">
-        <v>46102</v>
+        <v>46105</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Liaison Strategies</t>
+          <t>Abacus Data</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -2125,13 +2123,13 @@
         <v>0</v>
       </c>
       <c r="F42" t="n">
-        <v>0.46</v>
+        <v>0.44</v>
       </c>
       <c r="G42" t="n">
-        <v>0.32</v>
+        <v>0.37</v>
       </c>
       <c r="H42" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="I42" t="n">
         <v>0.09</v>
@@ -2140,10 +2138,10 @@
         <v>0.03</v>
       </c>
       <c r="K42" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="L42" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="43">
@@ -2153,11 +2151,11 @@
         </is>
       </c>
       <c r="B43" s="2" t="n">
-        <v>46101</v>
+        <v>46102</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Nanos Research</t>
+          <t>Liaison Strategies</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -2167,24 +2165,26 @@
         <v>0</v>
       </c>
       <c r="F43" t="n">
-        <v>0.457</v>
+        <v>0.46</v>
       </c>
       <c r="G43" t="n">
-        <v>0.329</v>
+        <v>0.32</v>
       </c>
       <c r="H43" t="n">
-        <v>0.048</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I43" t="n">
-        <v>0.115</v>
+        <v>0.09</v>
       </c>
       <c r="J43" t="n">
-        <v>0.03700000000000001</v>
+        <v>0.03</v>
       </c>
       <c r="K43" t="n">
-        <v>0.008</v>
-      </c>
-      <c r="L43" t="inlineStr"/>
+        <v>0.02</v>
+      </c>
+      <c r="L43" t="n">
+        <v>0.02</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2193,11 +2193,11 @@
         </is>
       </c>
       <c r="B44" s="2" t="n">
-        <v>46098</v>
+        <v>46101</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Angus Reid</t>
+          <t>Nanos Research</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -2207,23 +2207,23 @@
         <v>0</v>
       </c>
       <c r="F44" t="n">
-        <v>0.44</v>
+        <v>0.457</v>
       </c>
       <c r="G44" t="n">
-        <v>0.36</v>
+        <v>0.329</v>
       </c>
       <c r="H44" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.048</v>
       </c>
       <c r="I44" t="n">
-        <v>0.09</v>
+        <v>0.115</v>
       </c>
       <c r="J44" t="n">
-        <v>0.02</v>
+        <v>0.03700000000000001</v>
       </c>
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="n">
-        <v>0.01</v>
+        <v>0.008</v>
       </c>
     </row>
     <row r="45">
@@ -2233,11 +2233,11 @@
         </is>
       </c>
       <c r="B45" s="2" t="n">
-        <v>46096</v>
+        <v>46098</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Ekos</t>
+          <t>Angus Reid</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2247,26 +2247,24 @@
         <v>0</v>
       </c>
       <c r="F45" t="n">
-        <v>0.475</v>
+        <v>0.44</v>
       </c>
       <c r="G45" t="n">
-        <v>0.27</v>
+        <v>0.36</v>
       </c>
       <c r="H45" t="n">
-        <v>0.04099999999999999</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I45" t="n">
-        <v>0.151</v>
+        <v>0.09</v>
       </c>
       <c r="J45" t="n">
-        <v>0.045</v>
+        <v>0.02</v>
       </c>
       <c r="K45" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="L45" t="n">
-        <v>0.004</v>
-      </c>
+        <v>0.01</v>
+      </c>
+      <c r="L45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2275,11 +2273,11 @@
         </is>
       </c>
       <c r="B46" s="2" t="n">
-        <v>46095</v>
+        <v>46096</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Liaison Strategies</t>
+          <t>Ekos</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2289,25 +2287,25 @@
         <v>0</v>
       </c>
       <c r="F46" t="n">
-        <v>0.45</v>
+        <v>0.475</v>
       </c>
       <c r="G46" t="n">
-        <v>0.31</v>
+        <v>0.27</v>
       </c>
       <c r="H46" t="n">
-        <v>0.06</v>
+        <v>0.04099999999999999</v>
       </c>
       <c r="I46" t="n">
-        <v>0.08</v>
+        <v>0.151</v>
       </c>
       <c r="J46" t="n">
-        <v>0.03</v>
+        <v>0.045</v>
       </c>
       <c r="K46" t="n">
-        <v>0.04</v>
+        <v>0.004</v>
       </c>
       <c r="L46" t="n">
-        <v>0.04</v>
+        <v>0.015</v>
       </c>
     </row>
     <row r="47">
@@ -2317,11 +2315,11 @@
         </is>
       </c>
       <c r="B47" s="2" t="n">
-        <v>46094</v>
+        <v>46095</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Nanos Research</t>
+          <t>Liaison Strategies</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2331,24 +2329,26 @@
         <v>0</v>
       </c>
       <c r="F47" t="n">
-        <v>0.478</v>
+        <v>0.45</v>
       </c>
       <c r="G47" t="n">
-        <v>0.311</v>
+        <v>0.31</v>
       </c>
       <c r="H47" t="n">
-        <v>0.045</v>
+        <v>0.06</v>
       </c>
       <c r="I47" t="n">
-        <v>0.112</v>
+        <v>0.08</v>
       </c>
       <c r="J47" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="K47" t="n">
         <v>0.04</v>
       </c>
-      <c r="K47" t="n">
-        <v>0.011</v>
-      </c>
-      <c r="L47" t="inlineStr"/>
+      <c r="L47" t="n">
+        <v>0.04</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2357,11 +2357,11 @@
         </is>
       </c>
       <c r="B48" s="2" t="n">
-        <v>46092</v>
+        <v>46094</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Abacus Data</t>
+          <t>Nanos Research</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2371,25 +2371,23 @@
         <v>0</v>
       </c>
       <c r="F48" t="n">
-        <v>0.46</v>
+        <v>0.478</v>
       </c>
       <c r="G48" t="n">
-        <v>0.35</v>
+        <v>0.311</v>
       </c>
       <c r="H48" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.045</v>
       </c>
       <c r="I48" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.112</v>
       </c>
       <c r="J48" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="K48" t="n">
-        <v>0.01</v>
-      </c>
+        <v>0.04</v>
+      </c>
+      <c r="K48" t="inlineStr"/>
       <c r="L48" t="n">
-        <v>0</v>
+        <v>0.011</v>
       </c>
     </row>
     <row r="49">
@@ -2399,11 +2397,11 @@
         </is>
       </c>
       <c r="B49" s="2" t="n">
-        <v>46088</v>
+        <v>46092</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Liaison Strategies</t>
+          <t>Abacus Data</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2413,25 +2411,25 @@
         <v>0</v>
       </c>
       <c r="F49" t="n">
-        <v>0.44</v>
+        <v>0.46</v>
       </c>
       <c r="G49" t="n">
-        <v>0.3</v>
+        <v>0.35</v>
       </c>
       <c r="H49" t="n">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I49" t="n">
-        <v>0.09</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="J49" t="n">
         <v>0.03</v>
       </c>
       <c r="K49" t="n">
-        <v>0.04</v>
+        <v>0</v>
       </c>
       <c r="L49" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="50">
@@ -2441,11 +2439,11 @@
         </is>
       </c>
       <c r="B50" s="2" t="n">
-        <v>46087</v>
+        <v>46088</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Spark Insights</t>
+          <t>Liaison Strategies</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2455,21 +2453,25 @@
         <v>0</v>
       </c>
       <c r="F50" t="n">
-        <v>0.46</v>
+        <v>0.44</v>
       </c>
       <c r="G50" t="n">
-        <v>0.31</v>
+        <v>0.3</v>
       </c>
       <c r="H50" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="I50" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="J50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
+        <v>0.09</v>
+      </c>
+      <c r="J50" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="K50" t="n">
+        <v>0.03</v>
+      </c>
       <c r="L50" t="n">
-        <v>0.08</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="51">
@@ -2483,7 +2485,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Nanos Research</t>
+          <t>Spark Insights</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2496,19 +2498,17 @@
         <v>0.46</v>
       </c>
       <c r="G51" t="n">
-        <v>0.325</v>
+        <v>0.31</v>
       </c>
       <c r="H51" t="n">
-        <v>0.052</v>
+        <v>0.05</v>
       </c>
       <c r="I51" t="n">
         <v>0.1</v>
       </c>
-      <c r="J51" t="n">
-        <v>0.047</v>
-      </c>
+      <c r="J51" t="inlineStr"/>
       <c r="K51" t="n">
-        <v>0.006999999999999999</v>
+        <v>0.08</v>
       </c>
       <c r="L51" t="inlineStr"/>
     </row>
@@ -2519,11 +2519,11 @@
         </is>
       </c>
       <c r="B52" s="2" t="n">
-        <v>46083</v>
+        <v>46087</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Mainstreet Research</t>
+          <t>Nanos Research</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2536,22 +2536,20 @@
         <v>0.46</v>
       </c>
       <c r="G52" t="n">
-        <v>0.36</v>
+        <v>0.325</v>
       </c>
       <c r="H52" t="n">
-        <v>0.04</v>
+        <v>0.052</v>
       </c>
       <c r="I52" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.1</v>
       </c>
       <c r="J52" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="K52" t="n">
-        <v>0.03</v>
-      </c>
+        <v>0.047</v>
+      </c>
+      <c r="K52" t="inlineStr"/>
       <c r="L52" t="n">
-        <v>0.02</v>
+        <v>0.006999999999999999</v>
       </c>
     </row>
     <row r="53">
@@ -2565,7 +2563,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Léger</t>
+          <t>Mainstreet Research</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2575,23 +2573,25 @@
         <v>0</v>
       </c>
       <c r="F53" t="n">
-        <v>0.49</v>
+        <v>0.46</v>
       </c>
       <c r="G53" t="n">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="H53" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="I53" t="n">
-        <v>0.05</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="J53" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="K53" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="L53" t="n">
         <v>0.03</v>
-      </c>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="n">
-        <v>0.02</v>
       </c>
     </row>
     <row r="54">
@@ -2601,11 +2601,11 @@
         </is>
       </c>
       <c r="B54" s="2" t="n">
-        <v>46081</v>
+        <v>46083</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Liaison Strategies</t>
+          <t>Léger</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2615,16 +2615,16 @@
         <v>0</v>
       </c>
       <c r="F54" t="n">
-        <v>0.43</v>
+        <v>0.49</v>
       </c>
       <c r="G54" t="n">
-        <v>0.33</v>
+        <v>0.35</v>
       </c>
       <c r="H54" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="I54" t="n">
-        <v>0.09</v>
+        <v>0.05</v>
       </c>
       <c r="J54" t="n">
         <v>0.03</v>
@@ -2632,9 +2632,7 @@
       <c r="K54" t="n">
         <v>0.02</v>
       </c>
-      <c r="L54" t="n">
-        <v>0.02</v>
-      </c>
+      <c r="L54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2643,11 +2641,11 @@
         </is>
       </c>
       <c r="B55" s="2" t="n">
-        <v>46080</v>
+        <v>46081</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Nanos Research</t>
+          <t>Liaison Strategies</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2657,24 +2655,26 @@
         <v>0</v>
       </c>
       <c r="F55" t="n">
-        <v>0.436</v>
+        <v>0.43</v>
       </c>
       <c r="G55" t="n">
-        <v>0.332</v>
+        <v>0.33</v>
       </c>
       <c r="H55" t="n">
-        <v>0.051</v>
+        <v>0.06</v>
       </c>
       <c r="I55" t="n">
-        <v>0.114</v>
+        <v>0.09</v>
       </c>
       <c r="J55" t="n">
-        <v>0.049</v>
+        <v>0.03</v>
       </c>
       <c r="K55" t="n">
-        <v>0.006999999999999999</v>
-      </c>
-      <c r="L55" t="inlineStr"/>
+        <v>0.02</v>
+      </c>
+      <c r="L55" t="n">
+        <v>0.02</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2683,11 +2683,11 @@
         </is>
       </c>
       <c r="B56" s="2" t="n">
-        <v>46079</v>
+        <v>46080</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Ipsos</t>
+          <t>Nanos Research</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2697,25 +2697,23 @@
         <v>0</v>
       </c>
       <c r="F56" t="n">
-        <v>0.44</v>
+        <v>0.436</v>
       </c>
       <c r="G56" t="n">
-        <v>0.36</v>
+        <v>0.332</v>
       </c>
       <c r="H56" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.051</v>
       </c>
       <c r="I56" t="n">
-        <v>0.08</v>
+        <v>0.114</v>
       </c>
       <c r="J56" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="K56" t="n">
-        <v>0.01</v>
-      </c>
+        <v>0.049</v>
+      </c>
+      <c r="K56" t="inlineStr"/>
       <c r="L56" t="n">
-        <v>0</v>
+        <v>0.006999999999999999</v>
       </c>
     </row>
     <row r="57">
@@ -2725,11 +2723,11 @@
         </is>
       </c>
       <c r="B57" s="2" t="n">
-        <v>46077</v>
+        <v>46079</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Pollara</t>
+          <t>Ipsos</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2739,21 +2737,25 @@
         <v>0</v>
       </c>
       <c r="F57" t="n">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="G57" t="n">
-        <v>0.34</v>
+        <v>0.36</v>
       </c>
       <c r="H57" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="I57" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="J57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
+        <v>0.08</v>
+      </c>
+      <c r="J57" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="K57" t="n">
+        <v>0</v>
+      </c>
       <c r="L57" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="58">
@@ -2763,11 +2765,11 @@
         </is>
       </c>
       <c r="B58" s="2" t="n">
-        <v>46076</v>
+        <v>46077</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Abacus Data</t>
+          <t>Pollara</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2777,26 +2779,22 @@
         <v>0</v>
       </c>
       <c r="F58" t="n">
-        <v>0.44</v>
+        <v>0.47</v>
       </c>
       <c r="G58" t="n">
-        <v>0.38</v>
+        <v>0.34</v>
       </c>
       <c r="H58" t="n">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I58" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="J58" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="n">
         <v>0.03</v>
       </c>
-      <c r="K58" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="L58" t="n">
-        <v>0</v>
-      </c>
+      <c r="L58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -2809,7 +2807,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Angus Reid</t>
+          <t>Abacus Data</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2819,23 +2817,25 @@
         <v>0</v>
       </c>
       <c r="F59" t="n">
-        <v>0.45</v>
+        <v>0.44</v>
       </c>
       <c r="G59" t="n">
-        <v>0.32</v>
+        <v>0.38</v>
       </c>
       <c r="H59" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="I59" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="I59" t="n">
-        <v>0.1</v>
-      </c>
       <c r="J59" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="K59" t="inlineStr"/>
+        <v>0.03</v>
+      </c>
+      <c r="K59" t="n">
+        <v>0</v>
+      </c>
       <c r="L59" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="60">
@@ -2845,11 +2845,11 @@
         </is>
       </c>
       <c r="B60" s="2" t="n">
-        <v>46074</v>
+        <v>46076</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Liaison Strategies</t>
+          <t>Angus Reid</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2862,23 +2862,21 @@
         <v>0.45</v>
       </c>
       <c r="G60" t="n">
-        <v>0.33</v>
+        <v>0.32</v>
       </c>
       <c r="H60" t="n">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I60" t="n">
         <v>0.1</v>
       </c>
       <c r="J60" t="n">
-        <v>0.02</v>
+        <v>0.04</v>
       </c>
       <c r="K60" t="n">
         <v>0.02</v>
       </c>
-      <c r="L60" t="n">
-        <v>0.02</v>
-      </c>
+      <c r="L60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -2887,11 +2885,11 @@
         </is>
       </c>
       <c r="B61" s="2" t="n">
-        <v>46073</v>
+        <v>46074</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Nanos Research</t>
+          <t>Liaison Strategies</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2901,24 +2899,26 @@
         <v>0</v>
       </c>
       <c r="F61" t="n">
-        <v>0.413</v>
+        <v>0.45</v>
       </c>
       <c r="G61" t="n">
-        <v>0.337</v>
+        <v>0.33</v>
       </c>
       <c r="H61" t="n">
-        <v>0.076</v>
+        <v>0.06</v>
       </c>
       <c r="I61" t="n">
-        <v>0.106</v>
+        <v>0.1</v>
       </c>
       <c r="J61" t="n">
-        <v>0.049</v>
+        <v>0.02</v>
       </c>
       <c r="K61" t="n">
-        <v>0.009000000000000001</v>
-      </c>
-      <c r="L61" t="inlineStr"/>
+        <v>0.02</v>
+      </c>
+      <c r="L61" t="n">
+        <v>0.02</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -2927,11 +2927,11 @@
         </is>
       </c>
       <c r="B62" s="2" t="n">
-        <v>46070</v>
+        <v>46073</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Innovative Research</t>
+          <t>Nanos Research</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2941,23 +2941,23 @@
         <v>0</v>
       </c>
       <c r="F62" t="n">
-        <v>0.44</v>
+        <v>0.413</v>
       </c>
       <c r="G62" t="n">
-        <v>0.37</v>
+        <v>0.337</v>
       </c>
       <c r="H62" t="n">
-        <v>0.06</v>
+        <v>0.076</v>
       </c>
       <c r="I62" t="n">
-        <v>0.08</v>
+        <v>0.106</v>
       </c>
       <c r="J62" t="n">
-        <v>0.03</v>
+        <v>0.049</v>
       </c>
       <c r="K62" t="inlineStr"/>
       <c r="L62" t="n">
-        <v>0.03</v>
+        <v>0.009000000000000001</v>
       </c>
     </row>
     <row r="63">
@@ -2967,11 +2967,11 @@
         </is>
       </c>
       <c r="B63" s="2" t="n">
-        <v>46067</v>
+        <v>46070</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Liaison Strategies</t>
+          <t>Innovative Research</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2981,26 +2981,24 @@
         <v>0</v>
       </c>
       <c r="F63" t="n">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="G63" t="n">
-        <v>0.34</v>
+        <v>0.37</v>
       </c>
       <c r="H63" t="n">
         <v>0.06</v>
       </c>
       <c r="I63" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="J63" t="n">
         <v>0.03</v>
       </c>
       <c r="K63" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="L63" t="n">
-        <v>0.02</v>
-      </c>
+        <v>0.03</v>
+      </c>
+      <c r="L63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -3009,11 +3007,11 @@
         </is>
       </c>
       <c r="B64" s="2" t="n">
-        <v>46066</v>
+        <v>46067</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Nanos Research</t>
+          <t>Liaison Strategies</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -3023,24 +3021,26 @@
         <v>0</v>
       </c>
       <c r="F64" t="n">
-        <v>0.381</v>
+        <v>0.43</v>
       </c>
       <c r="G64" t="n">
-        <v>0.365</v>
+        <v>0.34</v>
       </c>
       <c r="H64" t="n">
-        <v>0.083</v>
+        <v>0.06</v>
       </c>
       <c r="I64" t="n">
-        <v>0.111</v>
+        <v>0.09</v>
       </c>
       <c r="J64" t="n">
-        <v>0.044</v>
+        <v>0.03</v>
       </c>
       <c r="K64" t="n">
-        <v>0.006999999999999999</v>
-      </c>
-      <c r="L64" t="inlineStr"/>
+        <v>0.02</v>
+      </c>
+      <c r="L64" t="n">
+        <v>0.02</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -3049,11 +3049,11 @@
         </is>
       </c>
       <c r="B65" s="2" t="n">
-        <v>46063</v>
+        <v>46066</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Abacus Data</t>
+          <t>Nanos Research</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -3063,25 +3063,23 @@
         <v>0</v>
       </c>
       <c r="F65" t="n">
-        <v>0.44</v>
+        <v>0.381</v>
       </c>
       <c r="G65" t="n">
-        <v>0.37</v>
+        <v>0.365</v>
       </c>
       <c r="H65" t="n">
-        <v>0.06</v>
+        <v>0.083</v>
       </c>
       <c r="I65" t="n">
-        <v>0.08</v>
+        <v>0.111</v>
       </c>
       <c r="J65" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="K65" t="n">
-        <v>0.01</v>
-      </c>
+        <v>0.044</v>
+      </c>
+      <c r="K65" t="inlineStr"/>
       <c r="L65" t="n">
-        <v>0</v>
+        <v>0.006999999999999999</v>
       </c>
     </row>
     <row r="66">
@@ -3091,11 +3089,11 @@
         </is>
       </c>
       <c r="B66" s="2" t="n">
-        <v>46060</v>
+        <v>46063</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Liaison Strategies</t>
+          <t>Abacus Data</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -3105,25 +3103,25 @@
         <v>0</v>
       </c>
       <c r="F66" t="n">
-        <v>0.42</v>
+        <v>0.44</v>
       </c>
       <c r="G66" t="n">
-        <v>0.35</v>
+        <v>0.37</v>
       </c>
       <c r="H66" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="I66" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="J66" t="n">
         <v>0.03</v>
       </c>
       <c r="K66" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="L66" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="67">
@@ -3133,11 +3131,11 @@
         </is>
       </c>
       <c r="B67" s="2" t="n">
-        <v>46059</v>
+        <v>46060</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Nanos Research</t>
+          <t>Liaison Strategies</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -3147,24 +3145,26 @@
         <v>0</v>
       </c>
       <c r="F67" t="n">
-        <v>0.391</v>
+        <v>0.42</v>
       </c>
       <c r="G67" t="n">
-        <v>0.352</v>
+        <v>0.35</v>
       </c>
       <c r="H67" t="n">
-        <v>0.08800000000000001</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I67" t="n">
-        <v>0.126</v>
+        <v>0.09</v>
       </c>
       <c r="J67" t="n">
-        <v>0.029</v>
+        <v>0.03</v>
       </c>
       <c r="K67" t="n">
-        <v>0.009000000000000001</v>
-      </c>
-      <c r="L67" t="inlineStr"/>
+        <v>0.02</v>
+      </c>
+      <c r="L67" t="n">
+        <v>0.02</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -3173,11 +3173,11 @@
         </is>
       </c>
       <c r="B68" s="2" t="n">
-        <v>46058</v>
+        <v>46059</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Research Co.</t>
+          <t>Nanos Research</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -3187,25 +3187,23 @@
         <v>0</v>
       </c>
       <c r="F68" t="n">
-        <v>0.45</v>
+        <v>0.391</v>
       </c>
       <c r="G68" t="n">
-        <v>0.32</v>
+        <v>0.352</v>
       </c>
       <c r="H68" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.08800000000000001</v>
       </c>
       <c r="I68" t="n">
-        <v>0.1</v>
+        <v>0.126</v>
       </c>
       <c r="J68" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="K68" t="n">
-        <v>0.02</v>
-      </c>
+        <v>0.029</v>
+      </c>
+      <c r="K68" t="inlineStr"/>
       <c r="L68" t="n">
-        <v>0.01</v>
+        <v>0.009000000000000001</v>
       </c>
     </row>
     <row r="69">
@@ -3215,11 +3213,11 @@
         </is>
       </c>
       <c r="B69" s="2" t="n">
-        <v>46055</v>
+        <v>46058</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Innovative Research</t>
+          <t>Research Co.</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -3229,10 +3227,10 @@
         <v>0</v>
       </c>
       <c r="F69" t="n">
-        <v>0.4</v>
+        <v>0.45</v>
       </c>
       <c r="G69" t="n">
-        <v>0.38</v>
+        <v>0.32</v>
       </c>
       <c r="H69" t="n">
         <v>0.07000000000000001</v>
@@ -3243,7 +3241,9 @@
       <c r="J69" t="n">
         <v>0.03</v>
       </c>
-      <c r="K69" t="inlineStr"/>
+      <c r="K69" t="n">
+        <v>0.01</v>
+      </c>
       <c r="L69" t="n">
         <v>0.02</v>
       </c>
@@ -3259,7 +3259,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Mainstreet Research</t>
+          <t>Innovative Research</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -3269,26 +3269,24 @@
         <v>0</v>
       </c>
       <c r="F70" t="n">
-        <v>0.51</v>
+        <v>0.4</v>
       </c>
       <c r="G70" t="n">
-        <v>0.355</v>
+        <v>0.38</v>
       </c>
       <c r="H70" t="n">
-        <v>0.055</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I70" t="n">
-        <v>0.04</v>
+        <v>0.1</v>
       </c>
       <c r="J70" t="n">
-        <v>0.022</v>
+        <v>0.03</v>
       </c>
       <c r="K70" t="n">
-        <v>0.006</v>
-      </c>
-      <c r="L70" t="n">
-        <v>0.011</v>
-      </c>
+        <v>0.02</v>
+      </c>
+      <c r="L70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -3297,11 +3295,11 @@
         </is>
       </c>
       <c r="B71" s="2" t="n">
-        <v>46053</v>
+        <v>46055</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Liaison Strategies</t>
+          <t>Mainstreet Research</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -3311,25 +3309,25 @@
         <v>0</v>
       </c>
       <c r="F71" t="n">
-        <v>0.43</v>
+        <v>0.51</v>
       </c>
       <c r="G71" t="n">
-        <v>0.35</v>
+        <v>0.355</v>
       </c>
       <c r="H71" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.055</v>
       </c>
       <c r="I71" t="n">
-        <v>0.08</v>
+        <v>0.04</v>
       </c>
       <c r="J71" t="n">
-        <v>0.03</v>
+        <v>0.022</v>
       </c>
       <c r="K71" t="n">
-        <v>0.02</v>
+        <v>0.011</v>
       </c>
       <c r="L71" t="n">
-        <v>0.02</v>
+        <v>0.006</v>
       </c>
     </row>
     <row r="72">
@@ -3339,11 +3337,11 @@
         </is>
       </c>
       <c r="B72" s="2" t="n">
-        <v>46052</v>
+        <v>46053</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Ekos</t>
+          <t>Liaison Strategies</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -3353,25 +3351,25 @@
         <v>0</v>
       </c>
       <c r="F72" t="n">
-        <v>0.444</v>
+        <v>0.43</v>
       </c>
       <c r="G72" t="n">
-        <v>0.295</v>
+        <v>0.35</v>
       </c>
       <c r="H72" t="n">
-        <v>0.053</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I72" t="n">
-        <v>0.138</v>
+        <v>0.08</v>
       </c>
       <c r="J72" t="n">
-        <v>0.039</v>
+        <v>0.03</v>
       </c>
       <c r="K72" t="n">
-        <v>0.016</v>
+        <v>0.02</v>
       </c>
       <c r="L72" t="n">
-        <v>0.015</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="73">
@@ -3385,7 +3383,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Nanos Research</t>
+          <t>Ekos</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -3395,24 +3393,26 @@
         <v>0</v>
       </c>
       <c r="F73" t="n">
-        <v>0.389</v>
+        <v>0.444</v>
       </c>
       <c r="G73" t="n">
-        <v>0.352</v>
+        <v>0.295</v>
       </c>
       <c r="H73" t="n">
-        <v>0.092</v>
+        <v>0.053</v>
       </c>
       <c r="I73" t="n">
-        <v>0.125</v>
+        <v>0.138</v>
       </c>
       <c r="J73" t="n">
-        <v>0.025</v>
+        <v>0.039</v>
       </c>
       <c r="K73" t="n">
-        <v>0.013</v>
-      </c>
-      <c r="L73" t="inlineStr"/>
+        <v>0.015</v>
+      </c>
+      <c r="L73" t="n">
+        <v>0.016</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -3421,11 +3421,11 @@
         </is>
       </c>
       <c r="B74" s="2" t="n">
-        <v>46049</v>
+        <v>46052</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Abacus Data</t>
+          <t>Nanos Research</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3435,25 +3435,23 @@
         <v>0</v>
       </c>
       <c r="F74" t="n">
-        <v>0.43</v>
+        <v>0.389</v>
       </c>
       <c r="G74" t="n">
-        <v>0.39</v>
+        <v>0.352</v>
       </c>
       <c r="H74" t="n">
-        <v>0.06</v>
+        <v>0.092</v>
       </c>
       <c r="I74" t="n">
-        <v>0.08</v>
+        <v>0.125</v>
       </c>
       <c r="J74" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="K74" t="n">
-        <v>0.02</v>
-      </c>
+        <v>0.025</v>
+      </c>
+      <c r="K74" t="inlineStr"/>
       <c r="L74" t="n">
-        <v>0.01</v>
+        <v>0.013</v>
       </c>
     </row>
     <row r="75">
@@ -3463,11 +3461,11 @@
         </is>
       </c>
       <c r="B75" s="2" t="n">
-        <v>46048</v>
+        <v>46049</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Léger</t>
+          <t>Abacus Data</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3477,23 +3475,25 @@
         <v>0</v>
       </c>
       <c r="F75" t="n">
-        <v>0.47</v>
+        <v>0.43</v>
       </c>
       <c r="G75" t="n">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="H75" t="n">
         <v>0.06</v>
       </c>
       <c r="I75" t="n">
-        <v>0.05</v>
+        <v>0.08</v>
       </c>
       <c r="J75" t="n">
         <v>0.02</v>
       </c>
-      <c r="K75" t="inlineStr"/>
+      <c r="K75" t="n">
+        <v>0.01</v>
+      </c>
       <c r="L75" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="76">
@@ -3507,7 +3507,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Angus Reid</t>
+          <t>Léger</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3517,24 +3517,24 @@
         <v>0</v>
       </c>
       <c r="F76" t="n">
-        <v>0.41</v>
+        <v>0.47</v>
       </c>
       <c r="G76" t="n">
         <v>0.38</v>
       </c>
       <c r="H76" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="I76" t="n">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="J76" t="n">
         <v>0.02</v>
       </c>
-      <c r="K76" t="inlineStr"/>
-      <c r="L76" t="n">
-        <v>0.02</v>
-      </c>
+      <c r="K76" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -3543,11 +3543,11 @@
         </is>
       </c>
       <c r="B77" s="2" t="n">
-        <v>46046</v>
+        <v>46048</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Liaison Strategies</t>
+          <t>Angus Reid</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3557,26 +3557,24 @@
         <v>0</v>
       </c>
       <c r="F77" t="n">
-        <v>0.42</v>
+        <v>0.41</v>
       </c>
       <c r="G77" t="n">
-        <v>0.34</v>
+        <v>0.38</v>
       </c>
       <c r="H77" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I77" t="n">
         <v>0.1</v>
       </c>
       <c r="J77" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="K77" t="n">
         <v>0.02</v>
       </c>
-      <c r="L77" t="n">
-        <v>0.02</v>
-      </c>
+      <c r="L77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -3585,11 +3583,11 @@
         </is>
       </c>
       <c r="B78" s="2" t="n">
-        <v>46045</v>
+        <v>46046</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Nanos Research</t>
+          <t>Liaison Strategies</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3599,24 +3597,26 @@
         <v>0</v>
       </c>
       <c r="F78" t="n">
-        <v>0.392</v>
+        <v>0.42</v>
       </c>
       <c r="G78" t="n">
-        <v>0.352</v>
+        <v>0.34</v>
       </c>
       <c r="H78" t="n">
         <v>0.08</v>
       </c>
       <c r="I78" t="n">
-        <v>0.116</v>
+        <v>0.1</v>
       </c>
       <c r="J78" t="n">
-        <v>0.036</v>
+        <v>0.03</v>
       </c>
       <c r="K78" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="L78" t="inlineStr"/>
+        <v>0.02</v>
+      </c>
+      <c r="L78" t="n">
+        <v>0.02</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -3625,11 +3625,11 @@
         </is>
       </c>
       <c r="B79" s="2" t="n">
-        <v>46039</v>
+        <v>46045</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Liaison Strategies</t>
+          <t>Nanos Research</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3639,25 +3639,23 @@
         <v>0</v>
       </c>
       <c r="F79" t="n">
-        <v>0.4</v>
+        <v>0.392</v>
       </c>
       <c r="G79" t="n">
-        <v>0.35</v>
+        <v>0.352</v>
       </c>
       <c r="H79" t="n">
         <v>0.08</v>
       </c>
       <c r="I79" t="n">
-        <v>0.11</v>
+        <v>0.116</v>
       </c>
       <c r="J79" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="K79" t="n">
-        <v>0.01</v>
-      </c>
+        <v>0.036</v>
+      </c>
+      <c r="K79" t="inlineStr"/>
       <c r="L79" t="n">
-        <v>0.02</v>
+        <v>0.021</v>
       </c>
     </row>
     <row r="80">
@@ -3667,11 +3665,11 @@
         </is>
       </c>
       <c r="B80" s="2" t="n">
-        <v>46038</v>
+        <v>46039</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Abacus Data</t>
+          <t>Liaison Strategies</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3681,16 +3679,16 @@
         <v>0</v>
       </c>
       <c r="F80" t="n">
-        <v>0.41</v>
+        <v>0.4</v>
       </c>
       <c r="G80" t="n">
-        <v>0.39</v>
+        <v>0.35</v>
       </c>
       <c r="H80" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="I80" t="n">
-        <v>0.08</v>
+        <v>0.11</v>
       </c>
       <c r="J80" t="n">
         <v>0.03</v>
@@ -3713,7 +3711,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Nanos Research</t>
+          <t>Abacus Data</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3723,24 +3721,26 @@
         <v>0</v>
       </c>
       <c r="F81" t="n">
-        <v>0.388</v>
+        <v>0.41</v>
       </c>
       <c r="G81" t="n">
-        <v>0.348</v>
+        <v>0.39</v>
       </c>
       <c r="H81" t="n">
-        <v>0.077</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I81" t="n">
-        <v>0.115</v>
+        <v>0.08</v>
       </c>
       <c r="J81" t="n">
-        <v>0.046</v>
+        <v>0.03</v>
       </c>
       <c r="K81" t="n">
-        <v>0.024</v>
-      </c>
-      <c r="L81" t="inlineStr"/>
+        <v>0.01</v>
+      </c>
+      <c r="L81" t="n">
+        <v>0.02</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -3749,11 +3749,11 @@
         </is>
       </c>
       <c r="B82" s="2" t="n">
-        <v>46036</v>
+        <v>46038</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Abacus Data</t>
+          <t>Nanos Research</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3763,25 +3763,23 @@
         <v>0</v>
       </c>
       <c r="F82" t="n">
-        <v>0.4</v>
+        <v>0.388</v>
       </c>
       <c r="G82" t="n">
-        <v>0.4</v>
+        <v>0.348</v>
       </c>
       <c r="H82" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.077</v>
       </c>
       <c r="I82" t="n">
-        <v>0.08</v>
+        <v>0.115</v>
       </c>
       <c r="J82" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="K82" t="n">
-        <v>0.01</v>
-      </c>
+        <v>0.046</v>
+      </c>
+      <c r="K82" t="inlineStr"/>
       <c r="L82" t="n">
-        <v>0.01</v>
+        <v>0.024</v>
       </c>
     </row>
     <row r="83">
@@ -3791,11 +3789,11 @@
         </is>
       </c>
       <c r="B83" s="2" t="n">
-        <v>46034</v>
+        <v>46036</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Pallas Data</t>
+          <t>Abacus Data</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3808,20 +3806,22 @@
         <v>0.4</v>
       </c>
       <c r="G83" t="n">
-        <v>0.37</v>
+        <v>0.4</v>
       </c>
       <c r="H83" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="I83" t="n">
-        <v>0.11</v>
+        <v>0.08</v>
       </c>
       <c r="J83" t="n">
         <v>0.03</v>
       </c>
-      <c r="K83" t="inlineStr"/>
+      <c r="K83" t="n">
+        <v>0.01</v>
+      </c>
       <c r="L83" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="84">
@@ -3831,11 +3831,11 @@
         </is>
       </c>
       <c r="B84" s="2" t="n">
-        <v>46032</v>
+        <v>46034</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Liaison Strategies</t>
+          <t>Pallas Data</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3845,26 +3845,24 @@
         <v>0</v>
       </c>
       <c r="F84" t="n">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="G84" t="n">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="H84" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I84" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="J84" t="n">
         <v>0.03</v>
       </c>
       <c r="K84" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="L84" t="n">
-        <v>0.02</v>
-      </c>
+        <v>0.02</v>
+      </c>
+      <c r="L84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -3873,11 +3871,11 @@
         </is>
       </c>
       <c r="B85" s="2" t="n">
-        <v>46031</v>
+        <v>46032</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Nanos Research</t>
+          <t>Liaison Strategies</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3887,24 +3885,26 @@
         <v>0</v>
       </c>
       <c r="F85" t="n">
-        <v>0.388</v>
+        <v>0.39</v>
       </c>
       <c r="G85" t="n">
-        <v>0.355</v>
+        <v>0.36</v>
       </c>
       <c r="H85" t="n">
-        <v>0.076</v>
+        <v>0.08</v>
       </c>
       <c r="I85" t="n">
-        <v>0.109</v>
+        <v>0.12</v>
       </c>
       <c r="J85" t="n">
-        <v>0.039</v>
+        <v>0.03</v>
       </c>
       <c r="K85" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="L85" t="inlineStr"/>
+        <v>0.02</v>
+      </c>
+      <c r="L85" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -3913,11 +3913,11 @@
         </is>
       </c>
       <c r="B86" s="2" t="n">
-        <v>46025</v>
+        <v>46031</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Liaison Strategies</t>
+          <t>Nanos Research</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3927,25 +3927,23 @@
         <v>0</v>
       </c>
       <c r="F86" t="n">
-        <v>0.38</v>
+        <v>0.388</v>
       </c>
       <c r="G86" t="n">
-        <v>0.37</v>
+        <v>0.355</v>
       </c>
       <c r="H86" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.076</v>
       </c>
       <c r="I86" t="n">
-        <v>0.12</v>
+        <v>0.109</v>
       </c>
       <c r="J86" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="K86" t="n">
-        <v>0.01</v>
-      </c>
+        <v>0.039</v>
+      </c>
+      <c r="K86" t="inlineStr"/>
       <c r="L86" t="n">
-        <v>0.02</v>
+        <v>0.021</v>
       </c>
     </row>
     <row r="87">
@@ -3955,11 +3953,11 @@
         </is>
       </c>
       <c r="B87" s="2" t="n">
-        <v>46024</v>
+        <v>46025</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Nanos Research</t>
+          <t>Liaison Strategies</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3969,24 +3967,26 @@
         <v>0</v>
       </c>
       <c r="F87" t="n">
-        <v>0.377</v>
+        <v>0.38</v>
       </c>
       <c r="G87" t="n">
-        <v>0.355</v>
+        <v>0.37</v>
       </c>
       <c r="H87" t="n">
-        <v>0.076</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I87" t="n">
-        <v>0.117</v>
+        <v>0.12</v>
       </c>
       <c r="J87" t="n">
-        <v>0.039</v>
+        <v>0.03</v>
       </c>
       <c r="K87" t="n">
-        <v>0.019</v>
-      </c>
-      <c r="L87" t="inlineStr"/>
+        <v>0.02</v>
+      </c>
+      <c r="L87" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -3995,11 +3995,11 @@
         </is>
       </c>
       <c r="B88" s="2" t="n">
-        <v>46019</v>
+        <v>46024</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Liaison Strategies</t>
+          <t>Nanos Research</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -4009,25 +4009,23 @@
         <v>0</v>
       </c>
       <c r="F88" t="n">
-        <v>0.39</v>
+        <v>0.377</v>
       </c>
       <c r="G88" t="n">
-        <v>0.37</v>
+        <v>0.355</v>
       </c>
       <c r="H88" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.076</v>
       </c>
       <c r="I88" t="n">
-        <v>0.11</v>
+        <v>0.117</v>
       </c>
       <c r="J88" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="K88" t="n">
-        <v>0.02</v>
-      </c>
+        <v>0.039</v>
+      </c>
+      <c r="K88" t="inlineStr"/>
       <c r="L88" t="n">
-        <v>0.01</v>
+        <v>0.019</v>
       </c>
     </row>
     <row r="89">
@@ -4037,11 +4035,11 @@
         </is>
       </c>
       <c r="B89" s="2" t="n">
-        <v>46017</v>
+        <v>46019</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Nanos Research</t>
+          <t>Liaison Strategies</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -4051,24 +4049,26 @@
         <v>0</v>
       </c>
       <c r="F89" t="n">
-        <v>0.384</v>
+        <v>0.39</v>
       </c>
       <c r="G89" t="n">
-        <v>0.347</v>
+        <v>0.37</v>
       </c>
       <c r="H89" t="n">
-        <v>0.07400000000000001</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I89" t="n">
-        <v>0.113</v>
+        <v>0.11</v>
       </c>
       <c r="J89" t="n">
-        <v>0.039</v>
+        <v>0.03</v>
       </c>
       <c r="K89" t="n">
-        <v>0.017</v>
-      </c>
-      <c r="L89" t="inlineStr"/>
+        <v>0.01</v>
+      </c>
+      <c r="L89" t="n">
+        <v>0.02</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -4077,11 +4077,11 @@
         </is>
       </c>
       <c r="B90" s="2" t="n">
-        <v>46012</v>
+        <v>46017</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Liaison Strategies</t>
+          <t>Nanos Research</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -4091,25 +4091,23 @@
         <v>0</v>
       </c>
       <c r="F90" t="n">
-        <v>0.38</v>
+        <v>0.384</v>
       </c>
       <c r="G90" t="n">
-        <v>0.38</v>
+        <v>0.347</v>
       </c>
       <c r="H90" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.07400000000000001</v>
       </c>
       <c r="I90" t="n">
-        <v>0.12</v>
+        <v>0.113</v>
       </c>
       <c r="J90" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="K90" t="n">
-        <v>0.02</v>
-      </c>
+        <v>0.039</v>
+      </c>
+      <c r="K90" t="inlineStr"/>
       <c r="L90" t="n">
-        <v>0.01</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="91">
@@ -4119,11 +4117,11 @@
         </is>
       </c>
       <c r="B91" s="2" t="n">
-        <v>46010</v>
+        <v>46012</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Nanos Research</t>
+          <t>Liaison Strategies</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -4133,24 +4131,26 @@
         <v>0</v>
       </c>
       <c r="F91" t="n">
-        <v>0.363</v>
+        <v>0.38</v>
       </c>
       <c r="G91" t="n">
-        <v>0.356</v>
+        <v>0.38</v>
       </c>
       <c r="H91" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I91" t="n">
-        <v>0.114</v>
+        <v>0.12</v>
       </c>
       <c r="J91" t="n">
-        <v>0.035</v>
+        <v>0.03</v>
       </c>
       <c r="K91" t="n">
-        <v>0.018</v>
-      </c>
-      <c r="L91" t="inlineStr"/>
+        <v>0.01</v>
+      </c>
+      <c r="L91" t="n">
+        <v>0.02</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -4159,11 +4159,11 @@
         </is>
       </c>
       <c r="B92" s="2" t="n">
-        <v>46006</v>
+        <v>46010</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Pallas Data</t>
+          <t>Nanos Research</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -4173,23 +4173,23 @@
         <v>0</v>
       </c>
       <c r="F92" t="n">
-        <v>0.409</v>
+        <v>0.363</v>
       </c>
       <c r="G92" t="n">
-        <v>0.377</v>
+        <v>0.356</v>
       </c>
       <c r="H92" t="n">
-        <v>0.08199999999999999</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="I92" t="n">
-        <v>0.079</v>
+        <v>0.114</v>
       </c>
       <c r="J92" t="n">
-        <v>0.036</v>
+        <v>0.035</v>
       </c>
       <c r="K92" t="inlineStr"/>
       <c r="L92" t="n">
-        <v>0.017</v>
+        <v>0.018</v>
       </c>
     </row>
     <row r="93">
@@ -4203,7 +4203,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Ipsos</t>
+          <t>Pallas Data</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -4213,22 +4213,22 @@
         <v>0</v>
       </c>
       <c r="F93" t="n">
-        <v>0.4</v>
+        <v>0.409</v>
       </c>
       <c r="G93" t="n">
-        <v>0.37</v>
+        <v>0.377</v>
       </c>
       <c r="H93" t="n">
-        <v>0.09</v>
+        <v>0.08199999999999999</v>
       </c>
       <c r="I93" t="n">
-        <v>0.09</v>
+        <v>0.079</v>
       </c>
       <c r="J93" t="n">
-        <v>0.02</v>
+        <v>0.036</v>
       </c>
       <c r="K93" t="n">
-        <v>0.02</v>
+        <v>0.017</v>
       </c>
       <c r="L93" t="inlineStr"/>
     </row>
@@ -4239,11 +4239,11 @@
         </is>
       </c>
       <c r="B94" s="2" t="n">
-        <v>46005</v>
+        <v>46006</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Innovative Research</t>
+          <t>Ipsos</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -4253,19 +4253,19 @@
         <v>0</v>
       </c>
       <c r="F94" t="n">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="G94" t="n">
-        <v>0.39</v>
+        <v>0.37</v>
       </c>
       <c r="H94" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="I94" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="J94" t="n">
-        <v>0.04</v>
+        <v>0.02</v>
       </c>
       <c r="K94" t="inlineStr"/>
       <c r="L94" t="n">
@@ -4279,11 +4279,11 @@
         </is>
       </c>
       <c r="B95" s="2" t="n">
-        <v>46003</v>
+        <v>46005</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Mainstreet Research</t>
+          <t>Innovative Research</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -4293,26 +4293,24 @@
         <v>0</v>
       </c>
       <c r="F95" t="n">
-        <v>0.41</v>
+        <v>0.39</v>
       </c>
       <c r="G95" t="n">
-        <v>0.42</v>
+        <v>0.39</v>
       </c>
       <c r="H95" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="I95" t="n">
-        <v>0.06</v>
+        <v>0.1</v>
       </c>
       <c r="J95" t="n">
-        <v>0.01</v>
+        <v>0.04</v>
       </c>
       <c r="K95" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="L95" t="n">
-        <v>0.01</v>
-      </c>
+        <v>0.02</v>
+      </c>
+      <c r="L95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -4325,7 +4323,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Nanos Research</t>
+          <t>Mainstreet Research</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -4335,24 +4333,26 @@
         <v>0</v>
       </c>
       <c r="F96" t="n">
-        <v>0.385</v>
+        <v>0.41</v>
       </c>
       <c r="G96" t="n">
-        <v>0.36</v>
+        <v>0.42</v>
       </c>
       <c r="H96" t="n">
-        <v>0.067</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I96" t="n">
-        <v>0.108</v>
+        <v>0.06</v>
       </c>
       <c r="J96" t="n">
-        <v>0.03700000000000001</v>
+        <v>0.01</v>
       </c>
       <c r="K96" t="n">
-        <v>0.019</v>
-      </c>
-      <c r="L96" t="inlineStr"/>
+        <v>0.01</v>
+      </c>
+      <c r="L96" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -4361,11 +4361,11 @@
         </is>
       </c>
       <c r="B97" s="2" t="n">
-        <v>46000</v>
+        <v>46003</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Abacus Data</t>
+          <t>Nanos Research</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -4375,25 +4375,23 @@
         <v>0</v>
       </c>
       <c r="F97" t="n">
-        <v>0.41</v>
+        <v>0.385</v>
       </c>
       <c r="G97" t="n">
-        <v>0.41</v>
+        <v>0.36</v>
       </c>
       <c r="H97" t="n">
-        <v>0.06</v>
+        <v>0.067</v>
       </c>
       <c r="I97" t="n">
-        <v>0.09</v>
+        <v>0.108</v>
       </c>
       <c r="J97" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="K97" t="n">
-        <v>0.01</v>
-      </c>
+        <v>0.03700000000000001</v>
+      </c>
+      <c r="K97" t="inlineStr"/>
       <c r="L97" t="n">
-        <v>0</v>
+        <v>0.019</v>
       </c>
     </row>
     <row r="98">
@@ -4403,11 +4401,11 @@
         </is>
       </c>
       <c r="B98" s="2" t="n">
-        <v>45996</v>
+        <v>46000</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Nanos Research</t>
+          <t>Abacus Data</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -4417,24 +4415,26 @@
         <v>0</v>
       </c>
       <c r="F98" t="n">
-        <v>0.391</v>
+        <v>0.41</v>
       </c>
       <c r="G98" t="n">
-        <v>0.3779999999999999</v>
+        <v>0.41</v>
       </c>
       <c r="H98" t="n">
-        <v>0.063</v>
+        <v>0.06</v>
       </c>
       <c r="I98" t="n">
-        <v>0.095</v>
+        <v>0.09</v>
       </c>
       <c r="J98" t="n">
-        <v>0.033</v>
+        <v>0.02</v>
       </c>
       <c r="K98" t="n">
-        <v>0.018</v>
-      </c>
-      <c r="L98" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="L98" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -4443,11 +4443,11 @@
         </is>
       </c>
       <c r="B99" s="2" t="n">
-        <v>45992</v>
+        <v>45996</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Innovative Research</t>
+          <t>Nanos Research</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -4457,23 +4457,23 @@
         <v>0</v>
       </c>
       <c r="F99" t="n">
-        <v>0.39</v>
+        <v>0.391</v>
       </c>
       <c r="G99" t="n">
-        <v>0.38</v>
+        <v>0.3779999999999999</v>
       </c>
       <c r="H99" t="n">
-        <v>0.08</v>
+        <v>0.063</v>
       </c>
       <c r="I99" t="n">
-        <v>0.09</v>
+        <v>0.095</v>
       </c>
       <c r="J99" t="n">
-        <v>0.04</v>
+        <v>0.033</v>
       </c>
       <c r="K99" t="inlineStr"/>
       <c r="L99" t="n">
-        <v>0.02</v>
+        <v>0.018</v>
       </c>
     </row>
     <row r="100">
@@ -4487,7 +4487,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Abacus Data</t>
+          <t>Innovative Research</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -4497,26 +4497,24 @@
         <v>0</v>
       </c>
       <c r="F100" t="n">
-        <v>0.41</v>
+        <v>0.39</v>
       </c>
       <c r="G100" t="n">
-        <v>0.41</v>
+        <v>0.38</v>
       </c>
       <c r="H100" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="I100" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="J100" t="n">
-        <v>0.02</v>
+        <v>0.04</v>
       </c>
       <c r="K100" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="L100" t="n">
-        <v>0.01</v>
-      </c>
+        <v>0.02</v>
+      </c>
+      <c r="L100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -4529,7 +4527,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Angus Reid</t>
+          <t>Abacus Data</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -4539,22 +4537,26 @@
         <v>0</v>
       </c>
       <c r="F101" t="n">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="G101" t="n">
-        <v>0.37</v>
+        <v>0.41</v>
       </c>
       <c r="H101" t="n">
-        <v>0.09</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I101" t="n">
-        <v>0.1</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="J101" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="K101" t="inlineStr"/>
-      <c r="L101" t="inlineStr"/>
+        <v>0.02</v>
+      </c>
+      <c r="K101" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L101" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -4563,11 +4565,11 @@
         </is>
       </c>
       <c r="B102" s="2" t="n">
-        <v>45991</v>
+        <v>45992</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Léger</t>
+          <t>Angus Reid</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -4577,24 +4579,22 @@
         <v>0</v>
       </c>
       <c r="F102" t="n">
-        <v>0.43</v>
+        <v>0.4</v>
       </c>
       <c r="G102" t="n">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="H102" t="n">
         <v>0.09</v>
       </c>
       <c r="I102" t="n">
-        <v>0.08</v>
+        <v>0.1</v>
       </c>
       <c r="J102" t="n">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="K102" t="inlineStr"/>
-      <c r="L102" t="n">
-        <v>0.01</v>
-      </c>
+      <c r="L102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -4607,7 +4607,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Liaison Strategies</t>
+          <t>Léger</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4617,26 +4617,24 @@
         <v>0</v>
       </c>
       <c r="F103" t="n">
-        <v>0.41</v>
+        <v>0.43</v>
       </c>
       <c r="G103" t="n">
         <v>0.36</v>
       </c>
       <c r="H103" t="n">
-        <v>0.05</v>
+        <v>0.09</v>
       </c>
       <c r="I103" t="n">
-        <v>0.12</v>
+        <v>0.08</v>
       </c>
       <c r="J103" t="n">
-        <v>0.02</v>
+        <v>0.04</v>
       </c>
       <c r="K103" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="L103" t="n">
-        <v>0.01</v>
-      </c>
+        <v>0.01</v>
+      </c>
+      <c r="L103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -4645,11 +4643,11 @@
         </is>
       </c>
       <c r="B104" s="2" t="n">
-        <v>45989</v>
+        <v>45991</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Nanos Research</t>
+          <t>Liaison Strategies</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4659,25 +4657,25 @@
         <v>0</v>
       </c>
       <c r="F104" t="n">
-        <v>0.419</v>
+        <v>0.41</v>
       </c>
       <c r="G104" t="n">
-        <v>0.382</v>
+        <v>0.36</v>
       </c>
       <c r="H104" t="n">
-        <v>0.073</v>
+        <v>0.05</v>
       </c>
       <c r="I104" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.12</v>
       </c>
       <c r="J104" t="n">
-        <v>0.027</v>
+        <v>0.02</v>
       </c>
       <c r="K104" t="n">
-        <v>0.012</v>
+        <v>0.01</v>
       </c>
       <c r="L104" t="n">
-        <v>0.003</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="105">
@@ -4687,11 +4685,11 @@
         </is>
       </c>
       <c r="B105" s="2" t="n">
-        <v>45988</v>
+        <v>45989</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Abacus Data</t>
+          <t>Nanos Research</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4701,25 +4699,25 @@
         <v>0</v>
       </c>
       <c r="F105" t="n">
-        <v>0.41</v>
+        <v>0.419</v>
       </c>
       <c r="G105" t="n">
-        <v>0.4</v>
+        <v>0.382</v>
       </c>
       <c r="H105" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.073</v>
       </c>
       <c r="I105" t="n">
-        <v>0.08</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="J105" t="n">
-        <v>0.02</v>
+        <v>0.027</v>
       </c>
       <c r="K105" t="n">
-        <v>0.01</v>
+        <v>0.003</v>
       </c>
       <c r="L105" t="n">
-        <v>0.01</v>
+        <v>0.012</v>
       </c>
     </row>
     <row r="106">
@@ -4729,11 +4727,11 @@
         </is>
       </c>
       <c r="B106" s="2" t="n">
-        <v>45982</v>
+        <v>45988</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Nanos Research</t>
+          <t>Abacus Data</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4743,25 +4741,25 @@
         <v>0</v>
       </c>
       <c r="F106" t="n">
-        <v>0.419</v>
+        <v>0.41</v>
       </c>
       <c r="G106" t="n">
-        <v>0.3720000000000001</v>
+        <v>0.4</v>
       </c>
       <c r="H106" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="I106" t="n">
-        <v>0.091</v>
+        <v>0.08</v>
       </c>
       <c r="J106" t="n">
-        <v>0.027</v>
+        <v>0.02</v>
       </c>
       <c r="K106" t="n">
-        <v>0.016</v>
+        <v>0.01</v>
       </c>
       <c r="L106" t="n">
-        <v>0.005</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="107">
@@ -4771,11 +4769,11 @@
         </is>
       </c>
       <c r="B107" s="2" t="n">
-        <v>45979</v>
+        <v>45982</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Kolosowski Strategies</t>
+          <t>Nanos Research</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4785,25 +4783,25 @@
         <v>0</v>
       </c>
       <c r="F107" t="n">
-        <v>0.44</v>
+        <v>0.419</v>
       </c>
       <c r="G107" t="n">
-        <v>0.44</v>
+        <v>0.3720000000000001</v>
       </c>
       <c r="H107" t="n">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I107" t="n">
-        <v>0.03</v>
+        <v>0.091</v>
       </c>
       <c r="J107" t="n">
-        <v>0.01</v>
+        <v>0.027</v>
       </c>
       <c r="K107" t="n">
-        <v>0.01</v>
+        <v>0.005</v>
       </c>
       <c r="L107" t="n">
-        <v>0</v>
+        <v>0.016</v>
       </c>
     </row>
     <row r="108">
@@ -4813,11 +4811,11 @@
         </is>
       </c>
       <c r="B108" s="2" t="n">
-        <v>45975</v>
+        <v>45979</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Nanos Research</t>
+          <t>Kolosowski Strategies</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4827,25 +4825,25 @@
         <v>0</v>
       </c>
       <c r="F108" t="n">
-        <v>0.402</v>
+        <v>0.44</v>
       </c>
       <c r="G108" t="n">
-        <v>0.382</v>
+        <v>0.44</v>
       </c>
       <c r="H108" t="n">
-        <v>0.07400000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="I108" t="n">
-        <v>0.101</v>
+        <v>0.03</v>
       </c>
       <c r="J108" t="n">
-        <v>0.022</v>
+        <v>0.01</v>
       </c>
       <c r="K108" t="n">
-        <v>0.013</v>
+        <v>0</v>
       </c>
       <c r="L108" t="n">
-        <v>0.008</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="109">
@@ -4855,11 +4853,11 @@
         </is>
       </c>
       <c r="B109" s="2" t="n">
-        <v>45972</v>
+        <v>45975</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Ekos</t>
+          <t>Nanos Research</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4869,25 +4867,25 @@
         <v>0</v>
       </c>
       <c r="F109" t="n">
-        <v>0.441</v>
+        <v>0.402</v>
       </c>
       <c r="G109" t="n">
-        <v>0.332</v>
+        <v>0.382</v>
       </c>
       <c r="H109" t="n">
-        <v>0.05400000000000001</v>
+        <v>0.07400000000000001</v>
       </c>
       <c r="I109" t="n">
-        <v>0.107</v>
+        <v>0.101</v>
       </c>
       <c r="J109" t="n">
-        <v>0.033</v>
+        <v>0.022</v>
       </c>
       <c r="K109" t="n">
-        <v>0.018</v>
+        <v>0.008</v>
       </c>
       <c r="L109" t="n">
-        <v>0.014</v>
+        <v>0.013</v>
       </c>
     </row>
     <row r="110">
@@ -4897,11 +4895,11 @@
         </is>
       </c>
       <c r="B110" s="2" t="n">
-        <v>45969</v>
+        <v>45972</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Mainstreet Research</t>
+          <t>Ekos</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4911,25 +4909,25 @@
         <v>0</v>
       </c>
       <c r="F110" t="n">
-        <v>0.44</v>
+        <v>0.441</v>
       </c>
       <c r="G110" t="n">
-        <v>0.4</v>
+        <v>0.332</v>
       </c>
       <c r="H110" t="n">
-        <v>0.06</v>
+        <v>0.05400000000000001</v>
       </c>
       <c r="I110" t="n">
-        <v>0.05</v>
+        <v>0.107</v>
       </c>
       <c r="J110" t="n">
-        <v>0.02</v>
+        <v>0.033</v>
       </c>
       <c r="K110" t="n">
-        <v>0.02</v>
+        <v>0.014</v>
       </c>
       <c r="L110" t="n">
-        <v>0.02</v>
+        <v>0.018</v>
       </c>
     </row>
     <row r="111">
@@ -4943,7 +4941,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Liaison Strategies</t>
+          <t>Mainstreet Research</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4956,22 +4954,22 @@
         <v>0.44</v>
       </c>
       <c r="G111" t="n">
-        <v>0.36</v>
+        <v>0.4</v>
       </c>
       <c r="H111" t="n">
         <v>0.06</v>
       </c>
       <c r="I111" t="n">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="J111" t="n">
         <v>0.02</v>
       </c>
       <c r="K111" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="L111" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="112">
@@ -4981,11 +4979,11 @@
         </is>
       </c>
       <c r="B112" s="2" t="n">
-        <v>45968</v>
+        <v>45969</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Angus Reid</t>
+          <t>Liaison Strategies</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4995,22 +4993,26 @@
         <v>0</v>
       </c>
       <c r="F112" t="n">
-        <v>0.4</v>
+        <v>0.44</v>
       </c>
       <c r="G112" t="n">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="H112" t="n">
-        <v>0.08</v>
+        <v>0.06</v>
       </c>
       <c r="I112" t="n">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
       <c r="J112" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="K112" t="inlineStr"/>
-      <c r="L112" t="inlineStr"/>
+        <v>0.02</v>
+      </c>
+      <c r="K112" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L112" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -5023,7 +5025,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Nanos Research</t>
+          <t>Angus Reid</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -5036,23 +5038,19 @@
         <v>0.4</v>
       </c>
       <c r="G113" t="n">
-        <v>0.368</v>
+        <v>0.38</v>
       </c>
       <c r="H113" t="n">
-        <v>0.075</v>
+        <v>0.08</v>
       </c>
       <c r="I113" t="n">
-        <v>0.114</v>
+        <v>0.09</v>
       </c>
       <c r="J113" t="n">
-        <v>0.023</v>
-      </c>
-      <c r="K113" t="n">
-        <v>0.012</v>
-      </c>
-      <c r="L113" t="n">
-        <v>0.008</v>
-      </c>
+        <v>0.03</v>
+      </c>
+      <c r="K113" t="inlineStr"/>
+      <c r="L113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -5061,11 +5059,11 @@
         </is>
       </c>
       <c r="B114" s="2" t="n">
-        <v>45967</v>
+        <v>45968</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Abacus Data</t>
+          <t>Nanos Research</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -5078,22 +5076,22 @@
         <v>0.4</v>
       </c>
       <c r="G114" t="n">
-        <v>0.41</v>
+        <v>0.368</v>
       </c>
       <c r="H114" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.075</v>
       </c>
       <c r="I114" t="n">
-        <v>0.08</v>
+        <v>0.114</v>
       </c>
       <c r="J114" t="n">
-        <v>0.02</v>
+        <v>0.023</v>
       </c>
       <c r="K114" t="n">
-        <v>0.01</v>
+        <v>0.008</v>
       </c>
       <c r="L114" t="n">
-        <v>0</v>
+        <v>0.012</v>
       </c>
     </row>
     <row r="115">
@@ -5103,11 +5101,11 @@
         </is>
       </c>
       <c r="B115" s="2" t="n">
-        <v>45965</v>
+        <v>45967</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Ekos</t>
+          <t>Abacus Data</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -5117,25 +5115,25 @@
         <v>0</v>
       </c>
       <c r="F115" t="n">
-        <v>0.434</v>
+        <v>0.4</v>
       </c>
       <c r="G115" t="n">
-        <v>0.355</v>
+        <v>0.41</v>
       </c>
       <c r="H115" t="n">
-        <v>0.058</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I115" t="n">
         <v>0.08</v>
       </c>
       <c r="J115" t="n">
-        <v>0.035</v>
+        <v>0.02</v>
       </c>
       <c r="K115" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="L115" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="116">
@@ -5149,7 +5147,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Liaison Strategies</t>
+          <t>Ekos</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -5159,25 +5157,25 @@
         <v>0</v>
       </c>
       <c r="F116" t="n">
-        <v>0.42</v>
+        <v>0.434</v>
       </c>
       <c r="G116" t="n">
-        <v>0.38</v>
+        <v>0.355</v>
       </c>
       <c r="H116" t="n">
-        <v>0.05</v>
+        <v>0.058</v>
       </c>
       <c r="I116" t="n">
-        <v>0.11</v>
+        <v>0.08</v>
       </c>
       <c r="J116" t="n">
-        <v>0.02</v>
+        <v>0.035</v>
       </c>
       <c r="K116" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="L116" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="117">
@@ -5187,11 +5185,11 @@
         </is>
       </c>
       <c r="B117" s="2" t="n">
-        <v>45964</v>
+        <v>45965</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Léger</t>
+          <t>Liaison Strategies</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -5201,21 +5199,23 @@
         <v>0</v>
       </c>
       <c r="F117" t="n">
-        <v>0.43</v>
+        <v>0.42</v>
       </c>
       <c r="G117" t="n">
         <v>0.38</v>
       </c>
       <c r="H117" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.05</v>
       </c>
       <c r="I117" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.11</v>
       </c>
       <c r="J117" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="K117" t="inlineStr"/>
+        <v>0.02</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.01</v>
+      </c>
       <c r="L117" t="n">
         <v>0.01</v>
       </c>
@@ -5227,11 +5227,11 @@
         </is>
       </c>
       <c r="B118" s="2" t="n">
-        <v>45961</v>
+        <v>45964</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Nanos Research</t>
+          <t>Léger</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -5241,26 +5241,24 @@
         <v>0</v>
       </c>
       <c r="F118" t="n">
-        <v>0.393</v>
+        <v>0.43</v>
       </c>
       <c r="G118" t="n">
-        <v>0.371</v>
+        <v>0.38</v>
       </c>
       <c r="H118" t="n">
-        <v>0.066</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I118" t="n">
-        <v>0.125</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="J118" t="n">
-        <v>0.017</v>
+        <v>0.04</v>
       </c>
       <c r="K118" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="L118" t="n">
-        <v>0</v>
-      </c>
+        <v>0.01</v>
+      </c>
+      <c r="L118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -5269,11 +5267,11 @@
         </is>
       </c>
       <c r="B119" s="2" t="n">
-        <v>45959</v>
+        <v>45961</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Abacus Data</t>
+          <t>Nanos Research</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -5283,25 +5281,25 @@
         <v>0</v>
       </c>
       <c r="F119" t="n">
-        <v>0.4</v>
+        <v>0.393</v>
       </c>
       <c r="G119" t="n">
-        <v>0.42</v>
+        <v>0.371</v>
       </c>
       <c r="H119" t="n">
-        <v>0.06</v>
+        <v>0.066</v>
       </c>
       <c r="I119" t="n">
-        <v>0.08</v>
+        <v>0.125</v>
       </c>
       <c r="J119" t="n">
-        <v>0.03</v>
+        <v>0.017</v>
       </c>
       <c r="K119" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="L119" t="n">
-        <v>0.01</v>
+        <v>0.015</v>
       </c>
     </row>
     <row r="120">
@@ -5311,11 +5309,11 @@
         </is>
       </c>
       <c r="B120" s="2" t="n">
-        <v>45954</v>
+        <v>45959</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Nanos Research</t>
+          <t>Abacus Data</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -5325,25 +5323,25 @@
         <v>0</v>
       </c>
       <c r="F120" t="n">
-        <v>0.394</v>
+        <v>0.4</v>
       </c>
       <c r="G120" t="n">
-        <v>0.37</v>
+        <v>0.42</v>
       </c>
       <c r="H120" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="I120" t="n">
-        <v>0.127</v>
+        <v>0.08</v>
       </c>
       <c r="J120" t="n">
-        <v>0.016</v>
+        <v>0.03</v>
       </c>
       <c r="K120" t="n">
-        <v>0.012</v>
+        <v>0.01</v>
       </c>
       <c r="L120" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="121">
@@ -5357,7 +5355,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Ekos</t>
+          <t>Nanos Research</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -5367,25 +5365,25 @@
         <v>0</v>
       </c>
       <c r="F121" t="n">
-        <v>0.435</v>
+        <v>0.394</v>
       </c>
       <c r="G121" t="n">
-        <v>0.324</v>
+        <v>0.37</v>
       </c>
       <c r="H121" t="n">
-        <v>0.057</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I121" t="n">
-        <v>0.124</v>
+        <v>0.127</v>
       </c>
       <c r="J121" t="n">
-        <v>0.03</v>
+        <v>0.016</v>
       </c>
       <c r="K121" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="L121" t="n">
-        <v>0.01</v>
+        <v>0.012</v>
       </c>
     </row>
     <row r="122">
@@ -5395,11 +5393,11 @@
         </is>
       </c>
       <c r="B122" s="2" t="n">
-        <v>45947</v>
+        <v>45954</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Nanos Research</t>
+          <t>Ekos</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -5409,25 +5407,25 @@
         <v>0</v>
       </c>
       <c r="F122" t="n">
-        <v>0.393</v>
+        <v>0.435</v>
       </c>
       <c r="G122" t="n">
-        <v>0.366</v>
+        <v>0.324</v>
       </c>
       <c r="H122" t="n">
-        <v>0.068</v>
+        <v>0.057</v>
       </c>
       <c r="I122" t="n">
-        <v>0.121</v>
+        <v>0.124</v>
       </c>
       <c r="J122" t="n">
-        <v>0.028</v>
+        <v>0.03</v>
       </c>
       <c r="K122" t="n">
-        <v>0.013</v>
+        <v>0.01</v>
       </c>
       <c r="L122" t="n">
-        <v>0.011</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="123">
@@ -5437,11 +5435,11 @@
         </is>
       </c>
       <c r="B123" s="2" t="n">
-        <v>45945</v>
+        <v>45947</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Abacus Data</t>
+          <t>Nanos Research</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -5451,25 +5449,25 @@
         <v>0</v>
       </c>
       <c r="F123" t="n">
-        <v>0.4</v>
+        <v>0.393</v>
       </c>
       <c r="G123" t="n">
-        <v>0.41</v>
+        <v>0.366</v>
       </c>
       <c r="H123" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.068</v>
       </c>
       <c r="I123" t="n">
-        <v>0.08</v>
+        <v>0.121</v>
       </c>
       <c r="J123" t="n">
-        <v>0.03</v>
+        <v>0.028</v>
       </c>
       <c r="K123" t="n">
-        <v>0.01</v>
+        <v>0.011</v>
       </c>
       <c r="L123" t="n">
-        <v>0.01</v>
+        <v>0.013</v>
       </c>
     </row>
     <row r="124">
@@ -5483,7 +5481,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Pallas Data</t>
+          <t>Abacus Data</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -5493,25 +5491,25 @@
         <v>0</v>
       </c>
       <c r="F124" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G124" t="n">
         <v>0.41</v>
       </c>
-      <c r="G124" t="n">
-        <v>0.37</v>
-      </c>
       <c r="H124" t="n">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I124" t="n">
-        <v>0.11</v>
+        <v>0.08</v>
       </c>
       <c r="J124" t="n">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="K124" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="L124" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="125">
@@ -5521,11 +5519,11 @@
         </is>
       </c>
       <c r="B125" s="2" t="n">
-        <v>45940</v>
+        <v>45945</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Nanos Research</t>
+          <t>Pallas Data</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -5535,25 +5533,25 @@
         <v>0</v>
       </c>
       <c r="F125" t="n">
-        <v>0.385</v>
+        <v>0.41</v>
       </c>
       <c r="G125" t="n">
-        <v>0.368</v>
+        <v>0.37</v>
       </c>
       <c r="H125" t="n">
-        <v>0.065</v>
+        <v>0.06</v>
       </c>
       <c r="I125" t="n">
-        <v>0.122</v>
+        <v>0.11</v>
       </c>
       <c r="J125" t="n">
-        <v>0.039</v>
+        <v>0.02</v>
       </c>
       <c r="K125" t="n">
-        <v>0.014</v>
+        <v>0</v>
       </c>
       <c r="L125" t="n">
-        <v>0.006999999999999999</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="126">
@@ -5563,11 +5561,11 @@
         </is>
       </c>
       <c r="B126" s="2" t="n">
-        <v>45935</v>
+        <v>45940</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Léger</t>
+          <t>Nanos Research</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -5577,23 +5575,25 @@
         <v>0</v>
       </c>
       <c r="F126" t="n">
-        <v>0.44</v>
+        <v>0.385</v>
       </c>
       <c r="G126" t="n">
-        <v>0.38</v>
+        <v>0.368</v>
       </c>
       <c r="H126" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.065</v>
       </c>
       <c r="I126" t="n">
-        <v>0.06</v>
+        <v>0.122</v>
       </c>
       <c r="J126" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="K126" t="inlineStr"/>
+        <v>0.039</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.006999999999999999</v>
+      </c>
       <c r="L126" t="n">
-        <v>0.02</v>
+        <v>0.014</v>
       </c>
     </row>
     <row r="127">
@@ -5603,11 +5603,11 @@
         </is>
       </c>
       <c r="B127" s="2" t="n">
-        <v>45933</v>
+        <v>45935</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Nanos Research</t>
+          <t>Léger</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -5617,26 +5617,24 @@
         <v>0</v>
       </c>
       <c r="F127" t="n">
-        <v>0.391</v>
+        <v>0.44</v>
       </c>
       <c r="G127" t="n">
-        <v>0.379</v>
+        <v>0.38</v>
       </c>
       <c r="H127" t="n">
-        <v>0.062</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I127" t="n">
-        <v>0.115</v>
+        <v>0.06</v>
       </c>
       <c r="J127" t="n">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="K127" t="n">
-        <v>0.009000000000000001</v>
-      </c>
-      <c r="L127" t="n">
-        <v>0.004</v>
-      </c>
+        <v>0.02</v>
+      </c>
+      <c r="L127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -5645,11 +5643,11 @@
         </is>
       </c>
       <c r="B128" s="2" t="n">
-        <v>45931</v>
+        <v>45933</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Abacus Data</t>
+          <t>Nanos Research</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -5659,25 +5657,25 @@
         <v>0</v>
       </c>
       <c r="F128" t="n">
-        <v>0.4</v>
+        <v>0.391</v>
       </c>
       <c r="G128" t="n">
-        <v>0.41</v>
+        <v>0.379</v>
       </c>
       <c r="H128" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.062</v>
       </c>
       <c r="I128" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.115</v>
       </c>
       <c r="J128" t="n">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="K128" t="n">
-        <v>0.02</v>
+        <v>0.004</v>
       </c>
       <c r="L128" t="n">
-        <v>0.01</v>
+        <v>0.009000000000000001</v>
       </c>
     </row>
     <row r="129">
@@ -5687,11 +5685,11 @@
         </is>
       </c>
       <c r="B129" s="2" t="n">
-        <v>45926</v>
+        <v>45931</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Nanos Research</t>
+          <t>Abacus Data</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -5701,25 +5699,25 @@
         <v>0</v>
       </c>
       <c r="F129" t="n">
-        <v>0.407</v>
+        <v>0.4</v>
       </c>
       <c r="G129" t="n">
-        <v>0.366</v>
+        <v>0.41</v>
       </c>
       <c r="H129" t="n">
-        <v>0.048</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I129" t="n">
-        <v>0.119</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="J129" t="n">
-        <v>0.043</v>
+        <v>0.03</v>
       </c>
       <c r="K129" t="n">
-        <v>0.012</v>
+        <v>0.01</v>
       </c>
       <c r="L129" t="n">
-        <v>0.005</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="130">
@@ -5729,11 +5727,11 @@
         </is>
       </c>
       <c r="B130" s="2" t="n">
-        <v>45922</v>
+        <v>45926</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Angus Reid</t>
+          <t>Nanos Research</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -5743,25 +5741,25 @@
         <v>0</v>
       </c>
       <c r="F130" t="n">
-        <v>0.38</v>
+        <v>0.407</v>
       </c>
       <c r="G130" t="n">
-        <v>0.41</v>
+        <v>0.366</v>
       </c>
       <c r="H130" t="n">
-        <v>0.08</v>
+        <v>0.048</v>
       </c>
       <c r="I130" t="n">
-        <v>0.1</v>
+        <v>0.119</v>
       </c>
       <c r="J130" t="n">
-        <v>0.02</v>
+        <v>0.043</v>
       </c>
       <c r="K130" t="n">
-        <v>0.01</v>
+        <v>0.005</v>
       </c>
       <c r="L130" t="n">
-        <v>0.01</v>
+        <v>0.012</v>
       </c>
     </row>
     <row r="131">
@@ -5771,11 +5769,11 @@
         </is>
       </c>
       <c r="B131" s="2" t="n">
-        <v>45921</v>
+        <v>45922</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Liaison Strategies</t>
+          <t>Angus Reid</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5785,13 +5783,13 @@
         <v>0</v>
       </c>
       <c r="F131" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="G131" t="n">
-        <v>0.37</v>
+        <v>0.41</v>
       </c>
       <c r="H131" t="n">
-        <v>0.05</v>
+        <v>0.08</v>
       </c>
       <c r="I131" t="n">
         <v>0.1</v>
@@ -5800,7 +5798,7 @@
         <v>0.02</v>
       </c>
       <c r="K131" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="L131" t="n">
         <v>0.01</v>
@@ -5813,11 +5811,11 @@
         </is>
       </c>
       <c r="B132" s="2" t="n">
-        <v>45919</v>
+        <v>45921</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Nanos Research</t>
+          <t>Liaison Strategies</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5827,25 +5825,25 @@
         <v>0</v>
       </c>
       <c r="F132" t="n">
-        <v>0.406</v>
+        <v>0.43</v>
       </c>
       <c r="G132" t="n">
-        <v>0.357</v>
+        <v>0.37</v>
       </c>
       <c r="H132" t="n">
-        <v>0.055</v>
+        <v>0.05</v>
       </c>
       <c r="I132" t="n">
-        <v>0.116</v>
+        <v>0.1</v>
       </c>
       <c r="J132" t="n">
-        <v>0.032</v>
+        <v>0.02</v>
       </c>
       <c r="K132" t="n">
-        <v>0.022</v>
+        <v>0.01</v>
       </c>
       <c r="L132" t="n">
-        <v>0.012</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="133">
@@ -5855,11 +5853,11 @@
         </is>
       </c>
       <c r="B133" s="2" t="n">
-        <v>45917</v>
+        <v>45919</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Abacus Data</t>
+          <t>Nanos Research</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5869,25 +5867,25 @@
         <v>0</v>
       </c>
       <c r="F133" t="n">
-        <v>0.4</v>
+        <v>0.406</v>
       </c>
       <c r="G133" t="n">
-        <v>0.4</v>
+        <v>0.357</v>
       </c>
       <c r="H133" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.055</v>
       </c>
       <c r="I133" t="n">
-        <v>0.08</v>
+        <v>0.116</v>
       </c>
       <c r="J133" t="n">
-        <v>0.03</v>
+        <v>0.032</v>
       </c>
       <c r="K133" t="n">
-        <v>0.01</v>
+        <v>0.012</v>
       </c>
       <c r="L133" t="n">
-        <v>0.01</v>
+        <v>0.022</v>
       </c>
     </row>
     <row r="134">
@@ -5897,11 +5895,11 @@
         </is>
       </c>
       <c r="B134" s="2" t="n">
-        <v>45912</v>
+        <v>45917</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Research Co.</t>
+          <t>Abacus Data</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5911,19 +5909,19 @@
         <v>0</v>
       </c>
       <c r="F134" t="n">
-        <v>0.43</v>
+        <v>0.4</v>
       </c>
       <c r="G134" t="n">
-        <v>0.38</v>
+        <v>0.4</v>
       </c>
       <c r="H134" t="n">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I134" t="n">
         <v>0.08</v>
       </c>
       <c r="J134" t="n">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="K134" t="n">
         <v>0.01</v>
@@ -5943,7 +5941,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Nanos Research</t>
+          <t>Research Co.</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5953,22 +5951,22 @@
         <v>0</v>
       </c>
       <c r="F135" t="n">
-        <v>0.418</v>
+        <v>0.43</v>
       </c>
       <c r="G135" t="n">
-        <v>0.345</v>
+        <v>0.38</v>
       </c>
       <c r="H135" t="n">
-        <v>0.055</v>
+        <v>0.06</v>
       </c>
       <c r="I135" t="n">
-        <v>0.128</v>
+        <v>0.08</v>
       </c>
       <c r="J135" t="n">
-        <v>0.025</v>
+        <v>0.02</v>
       </c>
       <c r="K135" t="n">
-        <v>0.019</v>
+        <v>0.01</v>
       </c>
       <c r="L135" t="n">
         <v>0.01</v>
@@ -5985,7 +5983,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Ekos</t>
+          <t>Nanos Research</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5995,25 +5993,25 @@
         <v>0</v>
       </c>
       <c r="F136" t="n">
-        <v>0.42</v>
+        <v>0.418</v>
       </c>
       <c r="G136" t="n">
-        <v>0.34</v>
+        <v>0.345</v>
       </c>
       <c r="H136" t="n">
-        <v>0.052</v>
+        <v>0.055</v>
       </c>
       <c r="I136" t="n">
-        <v>0.126</v>
+        <v>0.128</v>
       </c>
       <c r="J136" t="n">
-        <v>0.03</v>
+        <v>0.025</v>
       </c>
       <c r="K136" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="L136" t="n">
-        <v>0.01</v>
+        <v>0.019</v>
       </c>
     </row>
     <row r="137">
@@ -6023,11 +6021,11 @@
         </is>
       </c>
       <c r="B137" s="2" t="n">
-        <v>45908</v>
+        <v>45912</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Ipsos</t>
+          <t>Ekos</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -6037,25 +6035,25 @@
         <v>0</v>
       </c>
       <c r="F137" t="n">
-        <v>0.43</v>
+        <v>0.42</v>
       </c>
       <c r="G137" t="n">
-        <v>0.39</v>
+        <v>0.34</v>
       </c>
       <c r="H137" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.052</v>
       </c>
       <c r="I137" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.126</v>
       </c>
       <c r="J137" t="n">
-        <v>0.01</v>
+        <v>0.03</v>
       </c>
       <c r="K137" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="L137" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="138">
@@ -6065,11 +6063,11 @@
         </is>
       </c>
       <c r="B138" s="2" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Léger</t>
+          <t>Ipsos</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -6079,23 +6077,25 @@
         <v>0</v>
       </c>
       <c r="F138" t="n">
-        <v>0.47</v>
+        <v>0.43</v>
       </c>
       <c r="G138" t="n">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="H138" t="n">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I138" t="n">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="J138" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="K138" t="inlineStr"/>
+        <v>0.01</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0</v>
+      </c>
       <c r="L138" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="139">
@@ -6105,11 +6105,11 @@
         </is>
       </c>
       <c r="B139" s="2" t="n">
-        <v>45905</v>
+        <v>45907</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Nanos Research</t>
+          <t>Léger</t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -6119,26 +6119,24 @@
         <v>0</v>
       </c>
       <c r="F139" t="n">
-        <v>0.427</v>
+        <v>0.47</v>
       </c>
       <c r="G139" t="n">
-        <v>0.329</v>
+        <v>0.38</v>
       </c>
       <c r="H139" t="n">
-        <v>0.052</v>
+        <v>0.06</v>
       </c>
       <c r="I139" t="n">
-        <v>0.128</v>
+        <v>0.06</v>
       </c>
       <c r="J139" t="n">
-        <v>0.035</v>
+        <v>0.02</v>
       </c>
       <c r="K139" t="n">
-        <v>0.016</v>
-      </c>
-      <c r="L139" t="n">
-        <v>0.013</v>
-      </c>
+        <v>0.01</v>
+      </c>
+      <c r="L139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -6147,11 +6145,11 @@
         </is>
       </c>
       <c r="B140" s="2" t="n">
-        <v>45904</v>
+        <v>45905</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Angus Reid</t>
+          <t>Nanos Research</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -6161,25 +6159,25 @@
         <v>0</v>
       </c>
       <c r="F140" t="n">
-        <v>0.38</v>
+        <v>0.427</v>
       </c>
       <c r="G140" t="n">
-        <v>0.4</v>
+        <v>0.329</v>
       </c>
       <c r="H140" t="n">
-        <v>0.08</v>
+        <v>0.052</v>
       </c>
       <c r="I140" t="n">
-        <v>0.1</v>
+        <v>0.128</v>
       </c>
       <c r="J140" t="n">
-        <v>0.02</v>
+        <v>0.035</v>
       </c>
       <c r="K140" t="n">
-        <v>0.01</v>
+        <v>0.013</v>
       </c>
       <c r="L140" t="n">
-        <v>0.02</v>
+        <v>0.016</v>
       </c>
     </row>
     <row r="141">
@@ -6189,11 +6187,11 @@
         </is>
       </c>
       <c r="B141" s="2" t="n">
-        <v>45902</v>
+        <v>45904</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Abacus Data</t>
+          <t>Angus Reid</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -6203,22 +6201,22 @@
         <v>0</v>
       </c>
       <c r="F141" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="G141" t="n">
         <v>0.4</v>
       </c>
       <c r="H141" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="I141" t="n">
-        <v>0.06</v>
+        <v>0.1</v>
       </c>
       <c r="J141" t="n">
         <v>0.02</v>
       </c>
       <c r="K141" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="L141" t="n">
         <v>0.01</v>
@@ -6231,11 +6229,11 @@
         </is>
       </c>
       <c r="B142" s="2" t="n">
-        <v>45901</v>
+        <v>45902</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Mainstreet Research</t>
+          <t>Abacus Data</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -6245,25 +6243,25 @@
         <v>0</v>
       </c>
       <c r="F142" t="n">
-        <v>0.423</v>
+        <v>0.43</v>
       </c>
       <c r="G142" t="n">
-        <v>0.404</v>
+        <v>0.4</v>
       </c>
       <c r="H142" t="n">
-        <v>0.05</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I142" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="J142" t="n">
-        <v>0.012</v>
+        <v>0.02</v>
       </c>
       <c r="K142" t="n">
-        <v>0.016</v>
+        <v>0.01</v>
       </c>
       <c r="L142" t="n">
-        <v>0.013</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="143">
@@ -6273,11 +6271,11 @@
         </is>
       </c>
       <c r="B143" s="2" t="n">
-        <v>45898</v>
+        <v>45901</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Nanos Research</t>
+          <t>Mainstreet Research</t>
         </is>
       </c>
       <c r="D143" t="n">
@@ -6287,25 +6285,25 @@
         <v>0</v>
       </c>
       <c r="F143" t="n">
-        <v>0.433</v>
+        <v>0.423</v>
       </c>
       <c r="G143" t="n">
-        <v>0.324</v>
+        <v>0.404</v>
       </c>
       <c r="H143" t="n">
-        <v>0.062</v>
+        <v>0.05</v>
       </c>
       <c r="I143" t="n">
-        <v>0.127</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="J143" t="n">
-        <v>0.029</v>
+        <v>0.012</v>
       </c>
       <c r="K143" t="n">
+        <v>0.013</v>
+      </c>
+      <c r="L143" t="n">
         <v>0.016</v>
-      </c>
-      <c r="L143" t="n">
-        <v>0.009000000000000001</v>
       </c>
     </row>
     <row r="144">
@@ -6315,11 +6313,11 @@
         </is>
       </c>
       <c r="B144" s="2" t="n">
-        <v>45896</v>
+        <v>45898</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Liaison Strategies</t>
+          <t>Nanos Research</t>
         </is>
       </c>
       <c r="D144" t="n">
@@ -6329,25 +6327,25 @@
         <v>0</v>
       </c>
       <c r="F144" t="n">
-        <v>0.44</v>
+        <v>0.433</v>
       </c>
       <c r="G144" t="n">
-        <v>0.35</v>
+        <v>0.324</v>
       </c>
       <c r="H144" t="n">
-        <v>0.05</v>
+        <v>0.062</v>
       </c>
       <c r="I144" t="n">
-        <v>0.1</v>
+        <v>0.127</v>
       </c>
       <c r="J144" t="n">
-        <v>0.02</v>
+        <v>0.029</v>
       </c>
       <c r="K144" t="n">
-        <v>0.02</v>
+        <v>0.009000000000000001</v>
       </c>
       <c r="L144" t="n">
-        <v>0.01</v>
+        <v>0.016</v>
       </c>
     </row>
     <row r="145">
@@ -6357,11 +6355,11 @@
         </is>
       </c>
       <c r="B145" s="2" t="n">
-        <v>45891</v>
+        <v>45896</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Nanos Research</t>
+          <t>Liaison Strategies</t>
         </is>
       </c>
       <c r="D145" t="n">
@@ -6371,25 +6369,25 @@
         <v>0</v>
       </c>
       <c r="F145" t="n">
-        <v>0.4370000000000001</v>
+        <v>0.44</v>
       </c>
       <c r="G145" t="n">
-        <v>0.342</v>
+        <v>0.35</v>
       </c>
       <c r="H145" t="n">
-        <v>0.055</v>
+        <v>0.05</v>
       </c>
       <c r="I145" t="n">
-        <v>0.107</v>
+        <v>0.1</v>
       </c>
       <c r="J145" t="n">
-        <v>0.033</v>
+        <v>0.02</v>
       </c>
       <c r="K145" t="n">
-        <v>0.016</v>
+        <v>0.01</v>
       </c>
       <c r="L145" t="n">
-        <v>0.008</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="146">
@@ -6399,11 +6397,11 @@
         </is>
       </c>
       <c r="B146" s="2" t="n">
-        <v>45888</v>
+        <v>45891</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>August 19, 2025</t>
+          <t>Nanos Research</t>
         </is>
       </c>
       <c r="D146" t="n">
@@ -6412,13 +6410,27 @@
       <c r="E146" t="b">
         <v>0</v>
       </c>
-      <c r="F146" t="inlineStr"/>
-      <c r="G146" t="inlineStr"/>
-      <c r="H146" t="inlineStr"/>
-      <c r="I146" t="inlineStr"/>
-      <c r="J146" t="inlineStr"/>
-      <c r="K146" t="inlineStr"/>
-      <c r="L146" t="inlineStr"/>
+      <c r="F146" t="n">
+        <v>0.4370000000000001</v>
+      </c>
+      <c r="G146" t="n">
+        <v>0.342</v>
+      </c>
+      <c r="H146" t="n">
+        <v>0.055</v>
+      </c>
+      <c r="I146" t="n">
+        <v>0.107</v>
+      </c>
+      <c r="J146" t="n">
+        <v>0.033</v>
+      </c>
+      <c r="K146" t="n">
+        <v>0.008</v>
+      </c>
+      <c r="L146" t="n">
+        <v>0.016</v>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -6431,7 +6443,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Abacus Data</t>
+          <t>August 19, 2025</t>
         </is>
       </c>
       <c r="D147" t="n">
@@ -6440,24 +6452,12 @@
       <c r="E147" t="b">
         <v>0</v>
       </c>
-      <c r="F147" t="n">
-        <v>0.39</v>
-      </c>
-      <c r="G147" t="n">
-        <v>0.41</v>
-      </c>
-      <c r="H147" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="I147" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="J147" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="K147" t="n">
-        <v>0.02</v>
-      </c>
+      <c r="F147" t="inlineStr"/>
+      <c r="G147" t="inlineStr"/>
+      <c r="H147" t="inlineStr"/>
+      <c r="I147" t="inlineStr"/>
+      <c r="J147" t="inlineStr"/>
+      <c r="K147" t="inlineStr"/>
       <c r="L147" t="inlineStr"/>
     </row>
     <row r="148">
@@ -6467,11 +6467,11 @@
         </is>
       </c>
       <c r="B148" s="2" t="n">
-        <v>45887</v>
+        <v>45888</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>August 18, 2025</t>
+          <t>Abacus Data</t>
         </is>
       </c>
       <c r="D148" t="n">
@@ -6480,13 +6480,25 @@
       <c r="E148" t="b">
         <v>0</v>
       </c>
-      <c r="F148" t="inlineStr"/>
-      <c r="G148" t="inlineStr"/>
-      <c r="H148" t="inlineStr"/>
-      <c r="I148" t="inlineStr"/>
-      <c r="J148" t="inlineStr"/>
+      <c r="F148" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="G148" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="H148" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="I148" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="J148" t="n">
+        <v>0.02</v>
+      </c>
       <c r="K148" t="inlineStr"/>
-      <c r="L148" t="inlineStr"/>
+      <c r="L148" t="n">
+        <v>0.02</v>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -6495,11 +6507,11 @@
         </is>
       </c>
       <c r="B149" s="2" t="n">
-        <v>45884</v>
+        <v>45887</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Nanos Research</t>
+          <t>August 18, 2025</t>
         </is>
       </c>
       <c r="D149" t="n">
@@ -6508,27 +6520,13 @@
       <c r="E149" t="b">
         <v>0</v>
       </c>
-      <c r="F149" t="n">
-        <v>0.444</v>
-      </c>
-      <c r="G149" t="n">
-        <v>0.324</v>
-      </c>
-      <c r="H149" t="n">
-        <v>0.049</v>
-      </c>
-      <c r="I149" t="n">
-        <v>0.116</v>
-      </c>
-      <c r="J149" t="n">
-        <v>0.032</v>
-      </c>
-      <c r="K149" t="n">
-        <v>0.028</v>
-      </c>
-      <c r="L149" t="n">
-        <v>0.006999999999999999</v>
-      </c>
+      <c r="F149" t="inlineStr"/>
+      <c r="G149" t="inlineStr"/>
+      <c r="H149" t="inlineStr"/>
+      <c r="I149" t="inlineStr"/>
+      <c r="J149" t="inlineStr"/>
+      <c r="K149" t="inlineStr"/>
+      <c r="L149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -6537,7 +6535,7 @@
         </is>
       </c>
       <c r="B150" s="2" t="n">
-        <v>45877</v>
+        <v>45884</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
@@ -6551,25 +6549,25 @@
         <v>0</v>
       </c>
       <c r="F150" t="n">
-        <v>0.448</v>
+        <v>0.444</v>
       </c>
       <c r="G150" t="n">
-        <v>0.319</v>
+        <v>0.324</v>
       </c>
       <c r="H150" t="n">
-        <v>0.061</v>
+        <v>0.049</v>
       </c>
       <c r="I150" t="n">
-        <v>0.115</v>
+        <v>0.116</v>
       </c>
       <c r="J150" t="n">
-        <v>0.026</v>
+        <v>0.032</v>
       </c>
       <c r="K150" t="n">
-        <v>0.025</v>
+        <v>0.006999999999999999</v>
       </c>
       <c r="L150" t="n">
-        <v>0.006</v>
+        <v>0.028</v>
       </c>
     </row>
     <row r="151">
@@ -6583,7 +6581,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Liaison Strategies</t>
+          <t>Nanos Research</t>
         </is>
       </c>
       <c r="D151" t="n">
@@ -6593,25 +6591,25 @@
         <v>0</v>
       </c>
       <c r="F151" t="n">
-        <v>0.44</v>
+        <v>0.448</v>
       </c>
       <c r="G151" t="n">
-        <v>0.35</v>
+        <v>0.319</v>
       </c>
       <c r="H151" t="n">
-        <v>0.06</v>
+        <v>0.061</v>
       </c>
       <c r="I151" t="n">
-        <v>0.11</v>
+        <v>0.115</v>
       </c>
       <c r="J151" t="n">
-        <v>0.03</v>
+        <v>0.026</v>
       </c>
       <c r="K151" t="n">
-        <v>0.01</v>
+        <v>0.006</v>
       </c>
       <c r="L151" t="n">
-        <v>0.01</v>
+        <v>0.025</v>
       </c>
     </row>
     <row r="152">
@@ -6621,11 +6619,11 @@
         </is>
       </c>
       <c r="B152" s="2" t="n">
-        <v>45876</v>
+        <v>45877</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Abacus Data</t>
+          <t>Liaison Strategies</t>
         </is>
       </c>
       <c r="D152" t="n">
@@ -6635,24 +6633,26 @@
         <v>0</v>
       </c>
       <c r="F152" t="n">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="G152" t="n">
-        <v>0.4</v>
+        <v>0.35</v>
       </c>
       <c r="H152" t="n">
         <v>0.06</v>
       </c>
       <c r="I152" t="n">
-        <v>0.08</v>
+        <v>0.11</v>
       </c>
       <c r="J152" t="n">
-        <v>0.015</v>
+        <v>0.03</v>
       </c>
       <c r="K152" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="L152" t="inlineStr"/>
+        <v>0.01</v>
+      </c>
+      <c r="L152" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -6661,11 +6661,11 @@
         </is>
       </c>
       <c r="B153" s="2" t="n">
-        <v>45873</v>
+        <v>45876</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Léger</t>
+          <t>Abacus Data</t>
         </is>
       </c>
       <c r="D153" t="n">
@@ -6675,23 +6675,23 @@
         <v>0</v>
       </c>
       <c r="F153" t="n">
-        <v>0.46</v>
+        <v>0.43</v>
       </c>
       <c r="G153" t="n">
-        <v>0.36</v>
+        <v>0.4</v>
       </c>
       <c r="H153" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="I153" t="n">
-        <v>0.06</v>
+        <v>0.08</v>
       </c>
       <c r="J153" t="n">
-        <v>0.03</v>
+        <v>0.015</v>
       </c>
       <c r="K153" t="inlineStr"/>
       <c r="L153" t="n">
-        <v>0.01</v>
+        <v>0.015</v>
       </c>
     </row>
     <row r="154">
@@ -6701,11 +6701,11 @@
         </is>
       </c>
       <c r="B154" s="2" t="n">
-        <v>45870</v>
+        <v>45873</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Pallas Data</t>
+          <t>Léger</t>
         </is>
       </c>
       <c r="D154" t="n">
@@ -6715,24 +6715,24 @@
         <v>0</v>
       </c>
       <c r="F154" t="n">
-        <v>0.4320000000000001</v>
+        <v>0.46</v>
       </c>
       <c r="G154" t="n">
-        <v>0.376</v>
+        <v>0.36</v>
       </c>
       <c r="H154" t="n">
-        <v>0.063</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I154" t="n">
-        <v>0.075</v>
+        <v>0.06</v>
       </c>
       <c r="J154" t="n">
-        <v>0.022</v>
-      </c>
-      <c r="K154" t="inlineStr"/>
-      <c r="L154" t="n">
-        <v>0.032</v>
-      </c>
+        <v>0.03</v>
+      </c>
+      <c r="K154" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -6745,7 +6745,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Nanos Research</t>
+          <t>Pallas Data</t>
         </is>
       </c>
       <c r="D155" t="n">
@@ -6755,26 +6755,24 @@
         <v>0</v>
       </c>
       <c r="F155" t="n">
-        <v>0.4370000000000001</v>
+        <v>0.4320000000000001</v>
       </c>
       <c r="G155" t="n">
-        <v>0.325</v>
+        <v>0.376</v>
       </c>
       <c r="H155" t="n">
-        <v>0.053</v>
+        <v>0.063</v>
       </c>
       <c r="I155" t="n">
-        <v>0.12</v>
+        <v>0.075</v>
       </c>
       <c r="J155" t="n">
-        <v>0.025</v>
+        <v>0.022</v>
       </c>
       <c r="K155" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="L155" t="n">
-        <v>0.01</v>
-      </c>
+        <v>0.032</v>
+      </c>
+      <c r="L155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -6783,11 +6781,11 @@
         </is>
       </c>
       <c r="B156" s="2" t="n">
-        <v>45866</v>
+        <v>45870</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Innovative Research</t>
+          <t>Nanos Research</t>
         </is>
       </c>
       <c r="D156" t="n">
@@ -6797,23 +6795,25 @@
         <v>0</v>
       </c>
       <c r="F156" t="n">
-        <v>0.41</v>
+        <v>0.4370000000000001</v>
       </c>
       <c r="G156" t="n">
-        <v>0.39</v>
+        <v>0.325</v>
       </c>
       <c r="H156" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.053</v>
       </c>
       <c r="I156" t="n">
-        <v>0.09</v>
+        <v>0.12</v>
       </c>
       <c r="J156" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="K156" t="inlineStr"/>
+        <v>0.025</v>
+      </c>
+      <c r="K156" t="n">
+        <v>0.01</v>
+      </c>
       <c r="L156" t="n">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="157">
@@ -6823,11 +6823,11 @@
         </is>
       </c>
       <c r="B157" s="2" t="n">
-        <v>45863</v>
+        <v>45866</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Liaison Strategies</t>
+          <t>Innovative Research</t>
         </is>
       </c>
       <c r="D157" t="n">
@@ -6837,26 +6837,24 @@
         <v>0</v>
       </c>
       <c r="F157" t="n">
-        <v>0.43</v>
+        <v>0.41</v>
       </c>
       <c r="G157" t="n">
-        <v>0.36</v>
+        <v>0.39</v>
       </c>
       <c r="H157" t="n">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I157" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="J157" t="n">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="K157" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="L157" t="n">
-        <v>0.01</v>
-      </c>
+        <v>0.02</v>
+      </c>
+      <c r="L157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -6869,7 +6867,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Nanos Research</t>
+          <t>Liaison Strategies</t>
         </is>
       </c>
       <c r="D158" t="n">
@@ -6879,25 +6877,25 @@
         <v>0</v>
       </c>
       <c r="F158" t="n">
-        <v>0.436</v>
+        <v>0.43</v>
       </c>
       <c r="G158" t="n">
-        <v>0.335</v>
+        <v>0.36</v>
       </c>
       <c r="H158" t="n">
-        <v>0.059</v>
+        <v>0.06</v>
       </c>
       <c r="I158" t="n">
-        <v>0.121</v>
+        <v>0.1</v>
       </c>
       <c r="J158" t="n">
-        <v>0.023</v>
+        <v>0.03</v>
       </c>
       <c r="K158" t="n">
-        <v>0.018</v>
+        <v>0.01</v>
       </c>
       <c r="L158" t="n">
-        <v>0.008</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="159">
@@ -6907,7 +6905,7 @@
         </is>
       </c>
       <c r="B159" s="2" t="n">
-        <v>45856</v>
+        <v>45863</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
@@ -6921,25 +6919,25 @@
         <v>0</v>
       </c>
       <c r="F159" t="n">
-        <v>0.4429999999999999</v>
+        <v>0.436</v>
       </c>
       <c r="G159" t="n">
-        <v>0.34</v>
+        <v>0.335</v>
       </c>
       <c r="H159" t="n">
-        <v>0.066</v>
+        <v>0.059</v>
       </c>
       <c r="I159" t="n">
-        <v>0.103</v>
+        <v>0.121</v>
       </c>
       <c r="J159" t="n">
         <v>0.023</v>
       </c>
       <c r="K159" t="n">
-        <v>0.02</v>
+        <v>0.008</v>
       </c>
       <c r="L159" t="n">
-        <v>0.005</v>
+        <v>0.018</v>
       </c>
     </row>
     <row r="160">
@@ -6949,11 +6947,11 @@
         </is>
       </c>
       <c r="B160" s="2" t="n">
-        <v>45853</v>
+        <v>45856</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Abacus Data</t>
+          <t>Nanos Research</t>
         </is>
       </c>
       <c r="D160" t="n">
@@ -6963,25 +6961,25 @@
         <v>0</v>
       </c>
       <c r="F160" t="n">
-        <v>0.43</v>
+        <v>0.4429999999999999</v>
       </c>
       <c r="G160" t="n">
-        <v>0.4</v>
+        <v>0.34</v>
       </c>
       <c r="H160" t="n">
-        <v>0.06</v>
+        <v>0.066</v>
       </c>
       <c r="I160" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.103</v>
       </c>
       <c r="J160" t="n">
-        <v>0.03</v>
+        <v>0.023</v>
       </c>
       <c r="K160" t="n">
-        <v>0.01</v>
+        <v>0.005</v>
       </c>
       <c r="L160" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="161">
@@ -6991,11 +6989,11 @@
         </is>
       </c>
       <c r="B161" s="2" t="n">
-        <v>45852</v>
+        <v>45853</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Ekos</t>
+          <t>Abacus Data</t>
         </is>
       </c>
       <c r="D161" t="n">
@@ -7005,22 +7003,22 @@
         <v>0</v>
       </c>
       <c r="F161" t="n">
-        <v>0.4320000000000001</v>
+        <v>0.43</v>
       </c>
       <c r="G161" t="n">
-        <v>0.305</v>
+        <v>0.4</v>
       </c>
       <c r="H161" t="n">
-        <v>0.055</v>
+        <v>0.06</v>
       </c>
       <c r="I161" t="n">
-        <v>0.13</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="J161" t="n">
-        <v>0.035</v>
+        <v>0.03</v>
       </c>
       <c r="K161" t="n">
-        <v>0.036</v>
+        <v>0.01</v>
       </c>
       <c r="L161" t="n">
         <v>0.01</v>
@@ -7033,11 +7031,11 @@
         </is>
       </c>
       <c r="B162" s="2" t="n">
-        <v>45849</v>
+        <v>45852</v>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Nanos Research</t>
+          <t>Ekos</t>
         </is>
       </c>
       <c r="D162" t="n">
@@ -7047,25 +7045,25 @@
         <v>0</v>
       </c>
       <c r="F162" t="n">
-        <v>0.445</v>
+        <v>0.4320000000000001</v>
       </c>
       <c r="G162" t="n">
-        <v>0.338</v>
+        <v>0.305</v>
       </c>
       <c r="H162" t="n">
-        <v>0.059</v>
+        <v>0.055</v>
       </c>
       <c r="I162" t="n">
-        <v>0.111</v>
+        <v>0.13</v>
       </c>
       <c r="J162" t="n">
-        <v>0.021</v>
+        <v>0.035</v>
       </c>
       <c r="K162" t="n">
-        <v>0.019</v>
+        <v>0.01</v>
       </c>
       <c r="L162" t="n">
-        <v>0.006999999999999999</v>
+        <v>0.036</v>
       </c>
     </row>
     <row r="163">
@@ -7075,11 +7073,11 @@
         </is>
       </c>
       <c r="B163" s="2" t="n">
-        <v>45844</v>
+        <v>45849</v>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Léger</t>
+          <t>Nanos Research</t>
         </is>
       </c>
       <c r="D163" t="n">
@@ -7089,23 +7087,25 @@
         <v>0</v>
       </c>
       <c r="F163" t="n">
-        <v>0.48</v>
+        <v>0.445</v>
       </c>
       <c r="G163" t="n">
-        <v>0.35</v>
+        <v>0.338</v>
       </c>
       <c r="H163" t="n">
-        <v>0.06</v>
+        <v>0.059</v>
       </c>
       <c r="I163" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.111</v>
       </c>
       <c r="J163" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="K163" t="inlineStr"/>
+        <v>0.021</v>
+      </c>
+      <c r="K163" t="n">
+        <v>0.006999999999999999</v>
+      </c>
       <c r="L163" t="n">
-        <v>0.01</v>
+        <v>0.019</v>
       </c>
     </row>
     <row r="164">
@@ -7115,11 +7115,11 @@
         </is>
       </c>
       <c r="B164" s="2" t="n">
-        <v>45842</v>
+        <v>45844</v>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Liaison Strategies</t>
+          <t>Léger</t>
         </is>
       </c>
       <c r="D164" t="n">
@@ -7129,7 +7129,7 @@
         <v>0</v>
       </c>
       <c r="F164" t="n">
-        <v>0.46</v>
+        <v>0.48</v>
       </c>
       <c r="G164" t="n">
         <v>0.35</v>
@@ -7138,17 +7138,15 @@
         <v>0.06</v>
       </c>
       <c r="I164" t="n">
-        <v>0.09</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="J164" t="n">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="K164" t="n">
         <v>0.01</v>
       </c>
-      <c r="L164" t="n">
-        <v>0.01</v>
-      </c>
+      <c r="L164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -7161,7 +7159,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Nanos Research</t>
+          <t>Liaison Strategies</t>
         </is>
       </c>
       <c r="D165" t="n">
@@ -7171,22 +7169,22 @@
         <v>0</v>
       </c>
       <c r="F165" t="n">
-        <v>0.451</v>
+        <v>0.46</v>
       </c>
       <c r="G165" t="n">
-        <v>0.326</v>
+        <v>0.35</v>
       </c>
       <c r="H165" t="n">
-        <v>0.062</v>
+        <v>0.06</v>
       </c>
       <c r="I165" t="n">
-        <v>0.115</v>
+        <v>0.09</v>
       </c>
       <c r="J165" t="n">
-        <v>0.018</v>
+        <v>0.02</v>
       </c>
       <c r="K165" t="n">
-        <v>0.018</v>
+        <v>0.01</v>
       </c>
       <c r="L165" t="n">
         <v>0.01</v>
@@ -7199,11 +7197,11 @@
         </is>
       </c>
       <c r="B166" s="2" t="n">
-        <v>45840</v>
+        <v>45842</v>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Research Co.</t>
+          <t>Nanos Research</t>
         </is>
       </c>
       <c r="D166" t="n">
@@ -7213,25 +7211,25 @@
         <v>0</v>
       </c>
       <c r="F166" t="n">
-        <v>0.47</v>
+        <v>0.451</v>
       </c>
       <c r="G166" t="n">
-        <v>0.37</v>
+        <v>0.326</v>
       </c>
       <c r="H166" t="n">
-        <v>0.06</v>
+        <v>0.062</v>
       </c>
       <c r="I166" t="n">
-        <v>0.06</v>
+        <v>0.115</v>
       </c>
       <c r="J166" t="n">
-        <v>0.02</v>
+        <v>0.018</v>
       </c>
       <c r="K166" t="n">
         <v>0.01</v>
       </c>
       <c r="L166" t="n">
-        <v>0.01</v>
+        <v>0.018</v>
       </c>
     </row>
     <row r="167">
@@ -7245,7 +7243,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Abacus Data</t>
+          <t>Research Co.</t>
         </is>
       </c>
       <c r="D167" t="n">
@@ -7255,25 +7253,25 @@
         <v>0</v>
       </c>
       <c r="F167" t="n">
-        <v>0.41</v>
+        <v>0.47</v>
       </c>
       <c r="G167" t="n">
-        <v>0.4</v>
+        <v>0.37</v>
       </c>
       <c r="H167" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="I167" t="n">
-        <v>0.09</v>
+        <v>0.06</v>
       </c>
       <c r="J167" t="n">
         <v>0.02</v>
       </c>
       <c r="K167" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="L167" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="168">
@@ -7283,11 +7281,11 @@
         </is>
       </c>
       <c r="B168" s="2" t="n">
-        <v>45838</v>
+        <v>45840</v>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Innovative Research</t>
+          <t>Abacus Data</t>
         </is>
       </c>
       <c r="D168" t="n">
@@ -7297,21 +7295,23 @@
         <v>0</v>
       </c>
       <c r="F168" t="n">
-        <v>0.43</v>
+        <v>0.41</v>
       </c>
       <c r="G168" t="n">
-        <v>0.38</v>
+        <v>0.4</v>
       </c>
       <c r="H168" t="n">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I168" t="n">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="J168" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="K168" t="inlineStr"/>
+        <v>0.02</v>
+      </c>
+      <c r="K168" t="n">
+        <v>0</v>
+      </c>
       <c r="L168" t="n">
         <v>0.02</v>
       </c>
@@ -7323,11 +7323,11 @@
         </is>
       </c>
       <c r="B169" s="2" t="n">
-        <v>45835</v>
+        <v>45838</v>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Nanos Research</t>
+          <t>Innovative Research</t>
         </is>
       </c>
       <c r="D169" t="n">
@@ -7337,26 +7337,24 @@
         <v>0</v>
       </c>
       <c r="F169" t="n">
-        <v>0.445</v>
+        <v>0.43</v>
       </c>
       <c r="G169" t="n">
-        <v>0.314</v>
+        <v>0.38</v>
       </c>
       <c r="H169" t="n">
-        <v>0.059</v>
+        <v>0.06</v>
       </c>
       <c r="I169" t="n">
-        <v>0.128</v>
+        <v>0.08</v>
       </c>
       <c r="J169" t="n">
-        <v>0.025</v>
+        <v>0.03</v>
       </c>
       <c r="K169" t="n">
-        <v>0.017</v>
-      </c>
-      <c r="L169" t="n">
-        <v>0.012</v>
-      </c>
+        <v>0.02</v>
+      </c>
+      <c r="L169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -7365,11 +7363,11 @@
         </is>
       </c>
       <c r="B170" s="2" t="n">
-        <v>45834</v>
+        <v>45835</v>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Mainstreet Research</t>
+          <t>Nanos Research</t>
         </is>
       </c>
       <c r="D170" t="n">
@@ -7379,25 +7377,25 @@
         <v>0</v>
       </c>
       <c r="F170" t="n">
-        <v>0.47</v>
+        <v>0.445</v>
       </c>
       <c r="G170" t="n">
-        <v>0.38</v>
+        <v>0.314</v>
       </c>
       <c r="H170" t="n">
-        <v>0.03</v>
+        <v>0.059</v>
       </c>
       <c r="I170" t="n">
-        <v>0.06</v>
+        <v>0.128</v>
       </c>
       <c r="J170" t="n">
-        <v>0.03</v>
+        <v>0.025</v>
       </c>
       <c r="K170" t="n">
-        <v>0.01</v>
+        <v>0.012</v>
       </c>
       <c r="L170" t="n">
-        <v>0.02</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="171">
@@ -7407,11 +7405,11 @@
         </is>
       </c>
       <c r="B171" s="2" t="n">
-        <v>45828</v>
+        <v>45834</v>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Liaison Strategies</t>
+          <t>Mainstreet Research</t>
         </is>
       </c>
       <c r="D171" t="n">
@@ -7421,22 +7419,22 @@
         <v>0</v>
       </c>
       <c r="F171" t="n">
-        <v>0.42</v>
+        <v>0.47</v>
       </c>
       <c r="G171" t="n">
         <v>0.38</v>
       </c>
       <c r="H171" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="I171" t="n">
         <v>0.06</v>
-      </c>
-      <c r="I171" t="n">
-        <v>0.11</v>
       </c>
       <c r="J171" t="n">
         <v>0.03</v>
       </c>
       <c r="K171" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="L171" t="n">
         <v>0.01</v>
@@ -7453,7 +7451,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Nanos Research</t>
+          <t>Liaison Strategies</t>
         </is>
       </c>
       <c r="D172" t="n">
@@ -7463,25 +7461,25 @@
         <v>0</v>
       </c>
       <c r="F172" t="n">
-        <v>0.452</v>
+        <v>0.42</v>
       </c>
       <c r="G172" t="n">
-        <v>0.308</v>
+        <v>0.38</v>
       </c>
       <c r="H172" t="n">
-        <v>0.061</v>
+        <v>0.06</v>
       </c>
       <c r="I172" t="n">
-        <v>0.122</v>
+        <v>0.11</v>
       </c>
       <c r="J172" t="n">
-        <v>0.029</v>
+        <v>0.03</v>
       </c>
       <c r="K172" t="n">
-        <v>0.015</v>
+        <v>0.01</v>
       </c>
       <c r="L172" t="n">
-        <v>0.013</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="173">
@@ -7491,11 +7489,11 @@
         </is>
       </c>
       <c r="B173" s="2" t="n">
-        <v>45827</v>
+        <v>45828</v>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Abacus Data</t>
+          <t>Nanos Research</t>
         </is>
       </c>
       <c r="D173" t="n">
@@ -7505,25 +7503,25 @@
         <v>0</v>
       </c>
       <c r="F173" t="n">
-        <v>0.42</v>
+        <v>0.452</v>
       </c>
       <c r="G173" t="n">
-        <v>0.39</v>
+        <v>0.308</v>
       </c>
       <c r="H173" t="n">
-        <v>0.06</v>
+        <v>0.061</v>
       </c>
       <c r="I173" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.122</v>
       </c>
       <c r="J173" t="n">
-        <v>0.03</v>
+        <v>0.029</v>
       </c>
       <c r="K173" t="n">
-        <v>0.01</v>
+        <v>0.013</v>
       </c>
       <c r="L173" t="n">
-        <v>0.01</v>
+        <v>0.015</v>
       </c>
     </row>
     <row r="174">
@@ -7533,11 +7531,11 @@
         </is>
       </c>
       <c r="B174" s="2" t="n">
-        <v>45821</v>
+        <v>45827</v>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Nanos Research</t>
+          <t>Abacus Data</t>
         </is>
       </c>
       <c r="D174" t="n">
@@ -7547,22 +7545,22 @@
         <v>0</v>
       </c>
       <c r="F174" t="n">
-        <v>0.442</v>
+        <v>0.42</v>
       </c>
       <c r="G174" t="n">
-        <v>0.322</v>
+        <v>0.39</v>
       </c>
       <c r="H174" t="n">
-        <v>0.063</v>
+        <v>0.06</v>
       </c>
       <c r="I174" t="n">
-        <v>0.114</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="J174" t="n">
-        <v>0.032</v>
+        <v>0.03</v>
       </c>
       <c r="K174" t="n">
-        <v>0.017</v>
+        <v>0.01</v>
       </c>
       <c r="L174" t="n">
         <v>0.01</v>
@@ -7575,11 +7573,11 @@
         </is>
       </c>
       <c r="B175" s="2" t="n">
-        <v>45814</v>
+        <v>45821</v>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Liaison Strategies</t>
+          <t>Nanos Research</t>
         </is>
       </c>
       <c r="D175" t="n">
@@ -7589,25 +7587,25 @@
         <v>0</v>
       </c>
       <c r="F175" t="n">
-        <v>0.42</v>
+        <v>0.442</v>
       </c>
       <c r="G175" t="n">
-        <v>0.39</v>
+        <v>0.322</v>
       </c>
       <c r="H175" t="n">
-        <v>0.06</v>
+        <v>0.063</v>
       </c>
       <c r="I175" t="n">
-        <v>0.09</v>
+        <v>0.114</v>
       </c>
       <c r="J175" t="n">
-        <v>0.02</v>
+        <v>0.032</v>
       </c>
       <c r="K175" t="n">
         <v>0.01</v>
       </c>
       <c r="L175" t="n">
-        <v>0.01</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="176">
@@ -7621,7 +7619,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Nanos Research</t>
+          <t>Liaison Strategies</t>
         </is>
       </c>
       <c r="D176" t="n">
@@ -7631,25 +7629,25 @@
         <v>0</v>
       </c>
       <c r="F176" t="n">
-        <v>0.426</v>
+        <v>0.42</v>
       </c>
       <c r="G176" t="n">
-        <v>0.328</v>
+        <v>0.39</v>
       </c>
       <c r="H176" t="n">
-        <v>0.065</v>
+        <v>0.06</v>
       </c>
       <c r="I176" t="n">
-        <v>0.12</v>
+        <v>0.09</v>
       </c>
       <c r="J176" t="n">
-        <v>0.039</v>
+        <v>0.02</v>
       </c>
       <c r="K176" t="n">
-        <v>0.013</v>
+        <v>0.01</v>
       </c>
       <c r="L176" t="n">
-        <v>0.009000000000000001</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="177">
@@ -7659,11 +7657,11 @@
         </is>
       </c>
       <c r="B177" s="2" t="n">
-        <v>45813</v>
+        <v>45814</v>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Abacus Data</t>
+          <t>Nanos Research</t>
         </is>
       </c>
       <c r="D177" t="n">
@@ -7673,25 +7671,25 @@
         <v>0</v>
       </c>
       <c r="F177" t="n">
-        <v>0.42</v>
+        <v>0.426</v>
       </c>
       <c r="G177" t="n">
-        <v>0.39</v>
+        <v>0.328</v>
       </c>
       <c r="H177" t="n">
-        <v>0.06</v>
+        <v>0.065</v>
       </c>
       <c r="I177" t="n">
-        <v>0.08</v>
+        <v>0.12</v>
       </c>
       <c r="J177" t="n">
-        <v>0.03</v>
+        <v>0.039</v>
       </c>
       <c r="K177" t="n">
-        <v>0.01</v>
+        <v>0.009000000000000001</v>
       </c>
       <c r="L177" t="n">
-        <v>0</v>
+        <v>0.013</v>
       </c>
     </row>
     <row r="178">
@@ -7701,11 +7699,11 @@
         </is>
       </c>
       <c r="B178" s="2" t="n">
-        <v>45812</v>
+        <v>45813</v>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Ekos</t>
+          <t>Abacus Data</t>
         </is>
       </c>
       <c r="D178" t="n">
@@ -7715,22 +7713,22 @@
         <v>0</v>
       </c>
       <c r="F178" t="n">
-        <v>0.439</v>
+        <v>0.42</v>
       </c>
       <c r="G178" t="n">
-        <v>0.32</v>
+        <v>0.39</v>
       </c>
       <c r="H178" t="n">
-        <v>0.052</v>
+        <v>0.06</v>
       </c>
       <c r="I178" t="n">
-        <v>0.127</v>
+        <v>0.08</v>
       </c>
       <c r="J178" t="n">
         <v>0.03</v>
       </c>
       <c r="K178" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="L178" t="n">
         <v>0.01</v>
@@ -7743,11 +7741,11 @@
         </is>
       </c>
       <c r="B179" s="2" t="n">
-        <v>45807</v>
+        <v>45812</v>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Spark Insights</t>
+          <t>Ekos</t>
         </is>
       </c>
       <c r="D179" t="n">
@@ -7757,21 +7755,25 @@
         <v>0</v>
       </c>
       <c r="F179" t="n">
-        <v>0.41</v>
+        <v>0.439</v>
       </c>
       <c r="G179" t="n">
-        <v>0.4</v>
+        <v>0.32</v>
       </c>
       <c r="H179" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.052</v>
       </c>
       <c r="I179" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="J179" t="inlineStr"/>
-      <c r="K179" t="inlineStr"/>
+        <v>0.127</v>
+      </c>
+      <c r="J179" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="K179" t="n">
+        <v>0.01</v>
+      </c>
       <c r="L179" t="n">
-        <v>0.05</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="180">
@@ -7785,7 +7787,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Nanos Research</t>
+          <t>Spark Insights</t>
         </is>
       </c>
       <c r="D180" t="n">
@@ -7795,26 +7797,22 @@
         <v>0</v>
       </c>
       <c r="F180" t="n">
-        <v>0.417</v>
+        <v>0.41</v>
       </c>
       <c r="G180" t="n">
-        <v>0.364</v>
+        <v>0.4</v>
       </c>
       <c r="H180" t="n">
-        <v>0.065</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I180" t="n">
-        <v>0.105</v>
-      </c>
-      <c r="J180" t="n">
-        <v>0.034</v>
-      </c>
+        <v>0.08</v>
+      </c>
+      <c r="J180" t="inlineStr"/>
       <c r="K180" t="n">
-        <v>0.011</v>
-      </c>
-      <c r="L180" t="n">
-        <v>0.003</v>
-      </c>
+        <v>0.05</v>
+      </c>
+      <c r="L180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -7823,11 +7821,11 @@
         </is>
       </c>
       <c r="B181" s="2" t="n">
-        <v>45800</v>
+        <v>45807</v>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Liaison Strategies</t>
+          <t>Nanos Research</t>
         </is>
       </c>
       <c r="D181" t="n">
@@ -7837,25 +7835,25 @@
         <v>0</v>
       </c>
       <c r="F181" t="n">
-        <v>0.44</v>
+        <v>0.417</v>
       </c>
       <c r="G181" t="n">
-        <v>0.39</v>
+        <v>0.364</v>
       </c>
       <c r="H181" t="n">
-        <v>0.06</v>
+        <v>0.065</v>
       </c>
       <c r="I181" t="n">
-        <v>0.08</v>
+        <v>0.105</v>
       </c>
       <c r="J181" t="n">
-        <v>0.01</v>
+        <v>0.034</v>
       </c>
       <c r="K181" t="n">
-        <v>0.01</v>
+        <v>0.003</v>
       </c>
       <c r="L181" t="n">
-        <v>0.01</v>
+        <v>0.011</v>
       </c>
     </row>
     <row r="182">
@@ -7869,7 +7867,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Nanos Research</t>
+          <t>Liaison Strategies</t>
         </is>
       </c>
       <c r="D182" t="n">
@@ -7879,25 +7877,25 @@
         <v>0</v>
       </c>
       <c r="F182" t="n">
-        <v>0.404</v>
+        <v>0.44</v>
       </c>
       <c r="G182" t="n">
-        <v>0.386</v>
+        <v>0.39</v>
       </c>
       <c r="H182" t="n">
-        <v>0.059</v>
+        <v>0.06</v>
       </c>
       <c r="I182" t="n">
-        <v>0.098</v>
+        <v>0.08</v>
       </c>
       <c r="J182" t="n">
-        <v>0.03700000000000001</v>
+        <v>0.01</v>
       </c>
       <c r="K182" t="n">
-        <v>0.013</v>
+        <v>0.01</v>
       </c>
       <c r="L182" t="n">
-        <v>0.003</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="183">
@@ -7907,11 +7905,11 @@
         </is>
       </c>
       <c r="B183" s="2" t="n">
-        <v>45799</v>
+        <v>45800</v>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Innovative Research</t>
+          <t>Nanos Research</t>
         </is>
       </c>
       <c r="D183" t="n">
@@ -7921,23 +7919,25 @@
         <v>0</v>
       </c>
       <c r="F183" t="n">
-        <v>0.42</v>
+        <v>0.404</v>
       </c>
       <c r="G183" t="n">
-        <v>0.39</v>
+        <v>0.386</v>
       </c>
       <c r="H183" t="n">
-        <v>0.06</v>
+        <v>0.059</v>
       </c>
       <c r="I183" t="n">
-        <v>0.08</v>
+        <v>0.098</v>
       </c>
       <c r="J183" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="K183" t="inlineStr"/>
+        <v>0.03700000000000001</v>
+      </c>
+      <c r="K183" t="n">
+        <v>0.003</v>
+      </c>
       <c r="L183" t="n">
-        <v>0.02</v>
+        <v>0.013</v>
       </c>
     </row>
     <row r="184">
@@ -7947,11 +7947,11 @@
         </is>
       </c>
       <c r="B184" s="2" t="n">
-        <v>45798</v>
+        <v>45799</v>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Abacus Data</t>
+          <t>Innovative Research</t>
         </is>
       </c>
       <c r="D184" t="n">
@@ -7961,13 +7961,13 @@
         <v>0</v>
       </c>
       <c r="F184" t="n">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="G184" t="n">
-        <v>0.4</v>
+        <v>0.39</v>
       </c>
       <c r="H184" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="I184" t="n">
         <v>0.08</v>
@@ -7976,11 +7976,9 @@
         <v>0.03</v>
       </c>
       <c r="K184" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="L184" t="n">
-        <v>0</v>
-      </c>
+        <v>0.02</v>
+      </c>
+      <c r="L184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -7989,11 +7987,11 @@
         </is>
       </c>
       <c r="B185" s="2" t="n">
-        <v>45793</v>
+        <v>45798</v>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Nanos Research</t>
+          <t>Abacus Data</t>
         </is>
       </c>
       <c r="D185" t="n">
@@ -8003,25 +8001,25 @@
         <v>0</v>
       </c>
       <c r="F185" t="n">
-        <v>0.414</v>
+        <v>0.41</v>
       </c>
       <c r="G185" t="n">
-        <v>0.396</v>
+        <v>0.4</v>
       </c>
       <c r="H185" t="n">
-        <v>0.047</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I185" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="J185" t="n">
-        <v>0.039</v>
+        <v>0.03</v>
       </c>
       <c r="K185" t="n">
-        <v>0.013</v>
+        <v>0</v>
       </c>
       <c r="L185" t="n">
-        <v>0.006</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="186">
@@ -8031,11 +8029,11 @@
         </is>
       </c>
       <c r="B186" s="2" t="n">
-        <v>45786</v>
+        <v>45793</v>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Liaison Strategies</t>
+          <t>Nanos Research</t>
         </is>
       </c>
       <c r="D186" t="n">
@@ -8045,25 +8043,25 @@
         <v>0</v>
       </c>
       <c r="F186" t="n">
-        <v>0.45</v>
+        <v>0.414</v>
       </c>
       <c r="G186" t="n">
-        <v>0.4</v>
+        <v>0.396</v>
       </c>
       <c r="H186" t="n">
-        <v>0.06</v>
+        <v>0.047</v>
       </c>
       <c r="I186" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="J186" t="n">
-        <v>0.01</v>
+        <v>0.039</v>
       </c>
       <c r="K186" t="n">
-        <v>0.01</v>
+        <v>0.006</v>
       </c>
       <c r="L186" t="n">
-        <v>0</v>
+        <v>0.013</v>
       </c>
     </row>
     <row r="187">
@@ -8077,7 +8075,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Nanos Research</t>
+          <t>Liaison Strategies</t>
         </is>
       </c>
       <c r="D187" t="n">
@@ -8087,25 +8085,25 @@
         <v>0</v>
       </c>
       <c r="F187" t="n">
-        <v>0.415</v>
+        <v>0.45</v>
       </c>
       <c r="G187" t="n">
-        <v>0.405</v>
+        <v>0.4</v>
       </c>
       <c r="H187" t="n">
-        <v>0.051</v>
+        <v>0.06</v>
       </c>
       <c r="I187" t="n">
-        <v>0.078</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="J187" t="n">
-        <v>0.033</v>
+        <v>0.01</v>
       </c>
       <c r="K187" t="n">
-        <v>0.013</v>
+        <v>0</v>
       </c>
       <c r="L187" t="n">
-        <v>0.005</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="188">
@@ -8115,11 +8113,11 @@
         </is>
       </c>
       <c r="B188" s="2" t="n">
-        <v>45782</v>
+        <v>45786</v>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>May 5, 2025</t>
+          <t>Nanos Research</t>
         </is>
       </c>
       <c r="D188" t="n">
@@ -8128,13 +8126,27 @@
       <c r="E188" t="b">
         <v>0</v>
       </c>
-      <c r="F188" t="inlineStr"/>
-      <c r="G188" t="inlineStr"/>
-      <c r="H188" t="inlineStr"/>
-      <c r="I188" t="inlineStr"/>
-      <c r="J188" t="inlineStr"/>
-      <c r="K188" t="inlineStr"/>
-      <c r="L188" t="inlineStr"/>
+      <c r="F188" t="n">
+        <v>0.415</v>
+      </c>
+      <c r="G188" t="n">
+        <v>0.405</v>
+      </c>
+      <c r="H188" t="n">
+        <v>0.051</v>
+      </c>
+      <c r="I188" t="n">
+        <v>0.078</v>
+      </c>
+      <c r="J188" t="n">
+        <v>0.033</v>
+      </c>
+      <c r="K188" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="L188" t="n">
+        <v>0.013</v>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -8143,11 +8155,11 @@
         </is>
       </c>
       <c r="B189" s="2" t="n">
-        <v>45779</v>
+        <v>45782</v>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Nanos Research</t>
+          <t>May 5, 2025</t>
         </is>
       </c>
       <c r="D189" t="n">
@@ -8156,27 +8168,13 @@
       <c r="E189" t="b">
         <v>0</v>
       </c>
-      <c r="F189" t="n">
-        <v>0.418</v>
-      </c>
-      <c r="G189" t="n">
-        <v>0.392</v>
-      </c>
-      <c r="H189" t="n">
-        <v>0.058</v>
-      </c>
-      <c r="I189" t="n">
-        <v>0.079</v>
-      </c>
-      <c r="J189" t="n">
-        <v>0.032</v>
-      </c>
-      <c r="K189" t="n">
-        <v>0.013</v>
-      </c>
-      <c r="L189" t="n">
-        <v>0.008</v>
-      </c>
+      <c r="F189" t="inlineStr"/>
+      <c r="G189" t="inlineStr"/>
+      <c r="H189" t="inlineStr"/>
+      <c r="I189" t="inlineStr"/>
+      <c r="J189" t="inlineStr"/>
+      <c r="K189" t="inlineStr"/>
+      <c r="L189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -8185,11 +8183,11 @@
         </is>
       </c>
       <c r="B190" s="2" t="n">
-        <v>45777</v>
+        <v>45779</v>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>April 30, 2025</t>
+          <t>Nanos Research</t>
         </is>
       </c>
       <c r="D190" t="n">
@@ -8198,13 +8196,27 @@
       <c r="E190" t="b">
         <v>0</v>
       </c>
-      <c r="F190" t="inlineStr"/>
-      <c r="G190" t="inlineStr"/>
-      <c r="H190" t="inlineStr"/>
-      <c r="I190" t="inlineStr"/>
-      <c r="J190" t="inlineStr"/>
-      <c r="K190" t="inlineStr"/>
-      <c r="L190" t="inlineStr"/>
+      <c r="F190" t="n">
+        <v>0.418</v>
+      </c>
+      <c r="G190" t="n">
+        <v>0.392</v>
+      </c>
+      <c r="H190" t="n">
+        <v>0.058</v>
+      </c>
+      <c r="I190" t="n">
+        <v>0.079</v>
+      </c>
+      <c r="J190" t="n">
+        <v>0.032</v>
+      </c>
+      <c r="K190" t="n">
+        <v>0.008</v>
+      </c>
+      <c r="L190" t="n">
+        <v>0.013</v>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -8213,11 +8225,11 @@
         </is>
       </c>
       <c r="B191" s="2" t="n">
-        <v>45776</v>
+        <v>45777</v>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>April 29, 2025</t>
+          <t>April 30, 2025</t>
         </is>
       </c>
       <c r="D191" t="n">
@@ -8241,11 +8253,11 @@
         </is>
       </c>
       <c r="B192" s="2" t="n">
-        <v>45775</v>
+        <v>45776</v>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>2025 election</t>
+          <t>April 29, 2025</t>
         </is>
       </c>
       <c r="D192" t="n">
@@ -8254,40 +8266,26 @@
       <c r="E192" t="b">
         <v>0</v>
       </c>
-      <c r="F192" t="n">
-        <v>0.4379999999999999</v>
-      </c>
-      <c r="G192" t="n">
-        <v>0.413</v>
-      </c>
-      <c r="H192" t="n">
-        <v>0.063</v>
-      </c>
-      <c r="I192" t="n">
-        <v>0.063</v>
-      </c>
-      <c r="J192" t="n">
-        <v>0.012</v>
-      </c>
-      <c r="K192" t="n">
-        <v>0.006999999999999999</v>
-      </c>
-      <c r="L192" t="n">
-        <v>0.004</v>
-      </c>
+      <c r="F192" t="inlineStr"/>
+      <c r="G192" t="inlineStr"/>
+      <c r="H192" t="inlineStr"/>
+      <c r="I192" t="inlineStr"/>
+      <c r="J192" t="inlineStr"/>
+      <c r="K192" t="inlineStr"/>
+      <c r="L192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>Quebec</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="B193" s="2" t="n">
-        <v>46139</v>
+        <v>45775</v>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Liaison Strategies</t>
+          <t>2025 election</t>
         </is>
       </c>
       <c r="D193" t="n">
@@ -8297,25 +8295,25 @@
         <v>0</v>
       </c>
       <c r="F193" t="n">
-        <v>0.42</v>
+        <v>0.4379999999999999</v>
       </c>
       <c r="G193" t="n">
-        <v>0.21</v>
+        <v>0.413</v>
       </c>
       <c r="H193" t="n">
-        <v>0.22</v>
+        <v>0.063</v>
       </c>
       <c r="I193" t="n">
-        <v>0.09</v>
+        <v>0.063</v>
       </c>
       <c r="J193" t="n">
-        <v>0.03</v>
+        <v>0.012</v>
       </c>
       <c r="K193" t="n">
-        <v>0.02</v>
+        <v>0.004</v>
       </c>
       <c r="L193" t="n">
-        <v>0.01</v>
+        <v>0.006999999999999999</v>
       </c>
     </row>
     <row r="194">
@@ -8325,11 +8323,11 @@
         </is>
       </c>
       <c r="B194" s="2" t="n">
-        <v>46132</v>
+        <v>46139</v>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Léger</t>
+          <t>Liaison Strategies</t>
         </is>
       </c>
       <c r="D194" t="n">
@@ -8339,23 +8337,25 @@
         <v>0</v>
       </c>
       <c r="F194" t="n">
-        <v>0.47</v>
+        <v>0.42</v>
       </c>
       <c r="G194" t="n">
-        <v>0.17</v>
+        <v>0.21</v>
       </c>
       <c r="H194" t="n">
-        <v>0.29</v>
+        <v>0.22</v>
       </c>
       <c r="I194" t="n">
-        <v>0.05</v>
+        <v>0.09</v>
       </c>
       <c r="J194" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="K194" t="inlineStr"/>
+        <v>0.03</v>
+      </c>
+      <c r="K194" t="n">
+        <v>0.01</v>
+      </c>
       <c r="L194" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="195">
@@ -8365,7 +8365,7 @@
         </is>
       </c>
       <c r="B195" s="2" t="n">
-        <v>45971</v>
+        <v>46132</v>
       </c>
       <c r="C195" t="inlineStr">
         <is>
@@ -8379,13 +8379,13 @@
         <v>0</v>
       </c>
       <c r="F195" t="n">
-        <v>0.39</v>
+        <v>0.47</v>
       </c>
       <c r="G195" t="n">
-        <v>0.25</v>
+        <v>0.17</v>
       </c>
       <c r="H195" t="n">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="I195" t="n">
         <v>0.05</v>
@@ -8405,7 +8405,7 @@
         </is>
       </c>
       <c r="B196" s="2" t="n">
-        <v>45915</v>
+        <v>45971</v>
       </c>
       <c r="C196" t="inlineStr">
         <is>
@@ -8419,19 +8419,19 @@
         <v>0</v>
       </c>
       <c r="F196" t="n">
-        <v>0.42</v>
+        <v>0.39</v>
       </c>
       <c r="G196" t="n">
-        <v>0.21</v>
+        <v>0.25</v>
       </c>
       <c r="H196" t="n">
-        <v>0.3</v>
+        <v>0.28</v>
       </c>
       <c r="I196" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="J196" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="K196" t="inlineStr"/>
       <c r="L196" t="n">
@@ -8445,7 +8445,7 @@
         </is>
       </c>
       <c r="B197" s="2" t="n">
-        <v>45887</v>
+        <v>45915</v>
       </c>
       <c r="C197" t="inlineStr">
         <is>
@@ -8459,24 +8459,24 @@
         <v>0</v>
       </c>
       <c r="F197" t="n">
-        <v>0.43</v>
+        <v>0.42</v>
       </c>
       <c r="G197" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="H197" t="n">
-        <v>0.28</v>
+        <v>0.3</v>
       </c>
       <c r="I197" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="J197" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="K197" t="inlineStr"/>
-      <c r="L197" t="n">
-        <v>0</v>
-      </c>
+        <v>0.03</v>
+      </c>
+      <c r="K197" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L197" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -8485,7 +8485,7 @@
         </is>
       </c>
       <c r="B198" s="2" t="n">
-        <v>45830</v>
+        <v>45887</v>
       </c>
       <c r="C198" t="inlineStr">
         <is>
@@ -8499,24 +8499,24 @@
         <v>0</v>
       </c>
       <c r="F198" t="n">
-        <v>0.44</v>
+        <v>0.43</v>
       </c>
       <c r="G198" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="H198" t="n">
-        <v>0.25</v>
+        <v>0.28</v>
       </c>
       <c r="I198" t="n">
         <v>0.05</v>
       </c>
       <c r="J198" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="K198" t="inlineStr"/>
-      <c r="L198" t="n">
-        <v>0</v>
-      </c>
+        <v>0.02</v>
+      </c>
+      <c r="K198" t="n">
+        <v>0</v>
+      </c>
+      <c r="L198" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -8525,11 +8525,11 @@
         </is>
       </c>
       <c r="B199" s="2" t="n">
-        <v>45775</v>
+        <v>45830</v>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>2025 election</t>
+          <t>Léger</t>
         </is>
       </c>
       <c r="D199" t="n">
@@ -8539,39 +8539,37 @@
         <v>0</v>
       </c>
       <c r="F199" t="n">
-        <v>0.426</v>
+        <v>0.44</v>
       </c>
       <c r="G199" t="n">
-        <v>0.233</v>
+        <v>0.23</v>
       </c>
       <c r="H199" t="n">
-        <v>0.277</v>
+        <v>0.25</v>
       </c>
       <c r="I199" t="n">
-        <v>0.045</v>
+        <v>0.05</v>
       </c>
       <c r="J199" t="n">
-        <v>0.009000000000000001</v>
+        <v>0.03</v>
       </c>
       <c r="K199" t="n">
-        <v>0.008</v>
-      </c>
-      <c r="L199" t="n">
-        <v>0.002</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="L199" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>Ontario</t>
+          <t>Quebec</t>
         </is>
       </c>
       <c r="B200" s="2" t="n">
-        <v>45802</v>
+        <v>45775</v>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Léger</t>
+          <t>2025 election</t>
         </is>
       </c>
       <c r="D200" t="n">
@@ -8581,21 +8579,25 @@
         <v>0</v>
       </c>
       <c r="F200" t="n">
-        <v>0.54</v>
+        <v>0.426</v>
       </c>
       <c r="G200" t="n">
-        <v>0.37</v>
-      </c>
-      <c r="H200" t="inlineStr"/>
+        <v>0.233</v>
+      </c>
+      <c r="H200" t="n">
+        <v>0.277</v>
+      </c>
       <c r="I200" t="n">
-        <v>0.05</v>
+        <v>0.045</v>
       </c>
       <c r="J200" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="K200" t="inlineStr"/>
+        <v>0.009000000000000001</v>
+      </c>
+      <c r="K200" t="n">
+        <v>0.002</v>
+      </c>
       <c r="L200" t="n">
-        <v>0.01</v>
+        <v>0.008</v>
       </c>
     </row>
     <row r="201">
@@ -8605,11 +8607,11 @@
         </is>
       </c>
       <c r="B201" s="2" t="n">
-        <v>45775</v>
+        <v>45802</v>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>2025 election</t>
+          <t>Léger</t>
         </is>
       </c>
       <c r="D201" t="n">
@@ -8619,37 +8621,35 @@
         <v>0</v>
       </c>
       <c r="F201" t="n">
-        <v>0.49</v>
+        <v>0.54</v>
       </c>
       <c r="G201" t="n">
-        <v>0.4379999999999999</v>
+        <v>0.37</v>
       </c>
       <c r="H201" t="inlineStr"/>
       <c r="I201" t="n">
-        <v>0.049</v>
+        <v>0.05</v>
       </c>
       <c r="J201" t="n">
-        <v>0.012</v>
+        <v>0.03</v>
       </c>
       <c r="K201" t="n">
-        <v>0.006999999999999999</v>
-      </c>
-      <c r="L201" t="n">
-        <v>0.002</v>
-      </c>
+        <v>0.01</v>
+      </c>
+      <c r="L201" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>Manitoba</t>
+          <t>Ontario</t>
         </is>
       </c>
       <c r="B202" s="2" t="n">
-        <v>46094</v>
+        <v>45775</v>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Probe Research</t>
+          <t>2025 election</t>
         </is>
       </c>
       <c r="D202" t="n">
@@ -8659,19 +8659,23 @@
         <v>0</v>
       </c>
       <c r="F202" t="n">
-        <v>0.46</v>
+        <v>0.49</v>
       </c>
       <c r="G202" t="n">
-        <v>0.39</v>
+        <v>0.4379999999999999</v>
       </c>
       <c r="H202" t="inlineStr"/>
       <c r="I202" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="J202" t="inlineStr"/>
-      <c r="K202" t="inlineStr"/>
+        <v>0.049</v>
+      </c>
+      <c r="J202" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="K202" t="n">
+        <v>0.002</v>
+      </c>
       <c r="L202" t="n">
-        <v>0.05</v>
+        <v>0.006999999999999999</v>
       </c>
     </row>
     <row r="203">
@@ -8681,7 +8685,7 @@
         </is>
       </c>
       <c r="B203" s="2" t="n">
-        <v>46001</v>
+        <v>46094</v>
       </c>
       <c r="C203" t="inlineStr">
         <is>
@@ -8695,20 +8699,20 @@
         <v>0</v>
       </c>
       <c r="F203" t="n">
-        <v>0.43</v>
+        <v>0.46</v>
       </c>
       <c r="G203" t="n">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="H203" t="inlineStr"/>
       <c r="I203" t="n">
-        <v>0.14</v>
+        <v>0.08</v>
       </c>
       <c r="J203" t="inlineStr"/>
-      <c r="K203" t="inlineStr"/>
-      <c r="L203" t="n">
-        <v>0.06</v>
-      </c>
+      <c r="K203" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="L203" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -8717,11 +8721,11 @@
         </is>
       </c>
       <c r="B204" s="2" t="n">
-        <v>45775</v>
+        <v>46001</v>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>2025 election</t>
+          <t>Probe Research</t>
         </is>
       </c>
       <c r="D204" t="n">
@@ -8731,37 +8735,33 @@
         <v>0</v>
       </c>
       <c r="F204" t="n">
-        <v>0.408</v>
+        <v>0.43</v>
       </c>
       <c r="G204" t="n">
-        <v>0.463</v>
+        <v>0.38</v>
       </c>
       <c r="H204" t="inlineStr"/>
       <c r="I204" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="J204" t="n">
-        <v>0.006999999999999999</v>
-      </c>
+        <v>0.14</v>
+      </c>
+      <c r="J204" t="inlineStr"/>
       <c r="K204" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="L204" t="n">
-        <v>0.002</v>
-      </c>
+        <v>0.06</v>
+      </c>
+      <c r="L204" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>Alberta</t>
+          <t>Manitoba</t>
         </is>
       </c>
       <c r="B205" s="2" t="n">
-        <v>46134</v>
+        <v>45775</v>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Mainstreet Research</t>
+          <t>2025 election</t>
         </is>
       </c>
       <c r="D205" t="n">
@@ -8771,23 +8771,23 @@
         <v>0</v>
       </c>
       <c r="F205" t="n">
-        <v>0.403</v>
+        <v>0.408</v>
       </c>
       <c r="G205" t="n">
-        <v>0.458</v>
+        <v>0.463</v>
       </c>
       <c r="H205" t="inlineStr"/>
       <c r="I205" t="n">
-        <v>0.08900000000000001</v>
+        <v>0.11</v>
       </c>
       <c r="J205" t="n">
-        <v>0.011</v>
+        <v>0.006999999999999999</v>
       </c>
       <c r="K205" t="n">
-        <v>0.025</v>
+        <v>0.002</v>
       </c>
       <c r="L205" t="n">
-        <v>0.014</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="206">
@@ -8797,11 +8797,11 @@
         </is>
       </c>
       <c r="B206" s="2" t="n">
-        <v>46078</v>
+        <v>46134</v>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Abacus Data</t>
+          <t>Mainstreet Research</t>
         </is>
       </c>
       <c r="D206" t="n">
@@ -8811,23 +8811,23 @@
         <v>0</v>
       </c>
       <c r="F206" t="n">
-        <v>0.36</v>
+        <v>0.403</v>
       </c>
       <c r="G206" t="n">
-        <v>0.51</v>
+        <v>0.458</v>
       </c>
       <c r="H206" t="inlineStr"/>
       <c r="I206" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.08900000000000001</v>
       </c>
       <c r="J206" t="n">
-        <v>0.01</v>
+        <v>0.011</v>
       </c>
       <c r="K206" t="n">
-        <v>0.02</v>
+        <v>0.014</v>
       </c>
       <c r="L206" t="n">
-        <v>0.02</v>
+        <v>0.025</v>
       </c>
     </row>
     <row r="207">
@@ -8837,11 +8837,11 @@
         </is>
       </c>
       <c r="B207" s="2" t="n">
-        <v>46065</v>
+        <v>46078</v>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Mainstreet Research</t>
+          <t>Abacus Data</t>
         </is>
       </c>
       <c r="D207" t="n">
@@ -8851,23 +8851,23 @@
         <v>0</v>
       </c>
       <c r="F207" t="n">
-        <v>0.45</v>
+        <v>0.36</v>
       </c>
       <c r="G207" t="n">
-        <v>0.48</v>
+        <v>0.51</v>
       </c>
       <c r="H207" t="inlineStr"/>
       <c r="I207" t="n">
-        <v>0.05</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="J207" t="n">
         <v>0.01</v>
       </c>
       <c r="K207" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="L207" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="208">
@@ -8877,11 +8877,11 @@
         </is>
       </c>
       <c r="B208" s="2" t="n">
-        <v>45802</v>
+        <v>46065</v>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Léger</t>
+          <t>Mainstreet Research</t>
         </is>
       </c>
       <c r="D208" t="n">
@@ -8891,21 +8891,23 @@
         <v>0</v>
       </c>
       <c r="F208" t="n">
-        <v>0.35</v>
+        <v>0.45</v>
       </c>
       <c r="G208" t="n">
-        <v>0.54</v>
+        <v>0.48</v>
       </c>
       <c r="H208" t="inlineStr"/>
       <c r="I208" t="n">
         <v>0.05</v>
       </c>
       <c r="J208" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="K208" t="inlineStr"/>
+        <v>0.01</v>
+      </c>
+      <c r="K208" t="n">
+        <v>0.01</v>
+      </c>
       <c r="L208" t="n">
-        <v>0.04</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="209">
@@ -8915,11 +8917,11 @@
         </is>
       </c>
       <c r="B209" s="2" t="n">
-        <v>45775</v>
+        <v>45802</v>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>2025 election</t>
+          <t>Léger</t>
         </is>
       </c>
       <c r="D209" t="n">
@@ -8929,37 +8931,35 @@
         <v>0</v>
       </c>
       <c r="F209" t="n">
-        <v>0.279</v>
+        <v>0.35</v>
       </c>
       <c r="G209" t="n">
-        <v>0.635</v>
+        <v>0.54</v>
       </c>
       <c r="H209" t="inlineStr"/>
       <c r="I209" t="n">
-        <v>0.063</v>
+        <v>0.05</v>
       </c>
       <c r="J209" t="n">
-        <v>0.004</v>
+        <v>0.03</v>
       </c>
       <c r="K209" t="n">
-        <v>0.009000000000000001</v>
-      </c>
-      <c r="L209" t="n">
-        <v>0.008</v>
-      </c>
+        <v>0.04</v>
+      </c>
+      <c r="L209" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>British Columbia</t>
+          <t>Alberta</t>
         </is>
       </c>
       <c r="B210" s="2" t="n">
-        <v>46125</v>
+        <v>45775</v>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Mainstreet Research</t>
+          <t>2025 election</t>
         </is>
       </c>
       <c r="D210" t="n">
@@ -8969,23 +8969,23 @@
         <v>0</v>
       </c>
       <c r="F210" t="n">
-        <v>0.512</v>
+        <v>0.279</v>
       </c>
       <c r="G210" t="n">
-        <v>0.322</v>
+        <v>0.635</v>
       </c>
       <c r="H210" t="inlineStr"/>
       <c r="I210" t="n">
-        <v>0.08800000000000001</v>
+        <v>0.063</v>
       </c>
       <c r="J210" t="n">
-        <v>0.03700000000000001</v>
+        <v>0.004</v>
       </c>
       <c r="K210" t="n">
-        <v>0</v>
+        <v>0.008</v>
       </c>
       <c r="L210" t="n">
-        <v>0.032</v>
+        <v>0.009000000000000001</v>
       </c>
     </row>
     <row r="211">
@@ -8995,7 +8995,7 @@
         </is>
       </c>
       <c r="B211" s="2" t="n">
-        <v>46094</v>
+        <v>46125</v>
       </c>
       <c r="C211" t="inlineStr">
         <is>
@@ -9009,23 +9009,23 @@
         <v>0</v>
       </c>
       <c r="F211" t="n">
-        <v>0.467</v>
+        <v>0.512</v>
       </c>
       <c r="G211" t="n">
-        <v>0.341</v>
+        <v>0.322</v>
       </c>
       <c r="H211" t="inlineStr"/>
       <c r="I211" t="n">
-        <v>0.096</v>
+        <v>0.08800000000000001</v>
       </c>
       <c r="J211" t="n">
-        <v>0.039</v>
+        <v>0.03700000000000001</v>
       </c>
       <c r="K211" t="n">
-        <v>0.014</v>
+        <v>0.032</v>
       </c>
       <c r="L211" t="n">
-        <v>0.043</v>
+        <v>0</v>
       </c>
     </row>
     <row r="212">
@@ -9035,11 +9035,11 @@
         </is>
       </c>
       <c r="B212" s="2" t="n">
-        <v>45775</v>
+        <v>46094</v>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>2025 election</t>
+          <t>Mainstreet Research</t>
         </is>
       </c>
       <c r="D212" t="n">
@@ -9049,23 +9049,63 @@
         <v>0</v>
       </c>
       <c r="F212" t="n">
-        <v>0.418</v>
+        <v>0.467</v>
       </c>
       <c r="G212" t="n">
-        <v>0.41</v>
+        <v>0.341</v>
       </c>
       <c r="H212" t="inlineStr"/>
       <c r="I212" t="n">
+        <v>0.096</v>
+      </c>
+      <c r="J212" t="n">
+        <v>0.039</v>
+      </c>
+      <c r="K212" t="n">
+        <v>0.043</v>
+      </c>
+      <c r="L212" t="n">
+        <v>0.014</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>British Columbia</t>
+        </is>
+      </c>
+      <c r="B213" s="2" t="n">
+        <v>45775</v>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>2025 election</t>
+        </is>
+      </c>
+      <c r="D213" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E213" t="b">
+        <v>0</v>
+      </c>
+      <c r="F213" t="n">
+        <v>0.418</v>
+      </c>
+      <c r="G213" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="H213" t="inlineStr"/>
+      <c r="I213" t="n">
         <v>0.13</v>
       </c>
-      <c r="J212" t="n">
+      <c r="J213" t="n">
         <v>0.03</v>
       </c>
-      <c r="K212" t="n">
+      <c r="K213" t="n">
+        <v>0.006</v>
+      </c>
+      <c r="L213" t="n">
         <v>0.005</v>
-      </c>
-      <c r="L212" t="n">
-        <v>0.006</v>
       </c>
     </row>
   </sheetData>
